--- a/Mapping Template BrotZeit.xlsx
+++ b/Mapping Template BrotZeit.xlsx
@@ -8,19 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alfa\Documents\Data Engineer\Projekt\BackZeit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB5A3C6-6C3F-4D96-9E61-C041E4840822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A71AA7AD-5EEC-4ED1-87C6-95248D544953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{1083ED64-F082-44F9-9F2A-19C2CA2699CD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{1083ED64-F082-44F9-9F2A-19C2CA2699CD}"/>
   </bookViews>
   <sheets>
-    <sheet name="Dim 1  (6)" sheetId="9" r:id="rId1"/>
-    <sheet name="Dim 1  (5)" sheetId="8" r:id="rId2"/>
-    <sheet name="Dim 1  (4)" sheetId="7" r:id="rId3"/>
-    <sheet name="Dim 1  (3)" sheetId="6" r:id="rId4"/>
-    <sheet name="Dim 1  (2)" sheetId="5" r:id="rId5"/>
-    <sheet name="Dim 1 " sheetId="1" r:id="rId6"/>
-    <sheet name="Fact (2)" sheetId="10" r:id="rId7"/>
-    <sheet name="Fact" sheetId="4" r:id="rId8"/>
+    <sheet name="D_Filiale" sheetId="9" r:id="rId1"/>
+    <sheet name="D_Verkaufsvorgang" sheetId="8" r:id="rId2"/>
+    <sheet name="D_Verkäufer" sheetId="7" r:id="rId3"/>
+    <sheet name="D_Tag" sheetId="6" r:id="rId4"/>
+    <sheet name="D_Stunde" sheetId="5" r:id="rId5"/>
+    <sheet name="D_Produkt" sheetId="1" r:id="rId6"/>
+    <sheet name="F_Verkäufe" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -34,8 +33,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -43,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="88">
   <si>
     <t>Notes</t>
   </si>
@@ -124,6 +121,189 @@
   </si>
   <si>
     <t>CleanUp-Process (3-6 Monaten gelöscht)</t>
+  </si>
+  <si>
+    <t>Filiale</t>
+  </si>
+  <si>
+    <t>FilialID</t>
+  </si>
+  <si>
+    <t>Filialname</t>
+  </si>
+  <si>
+    <t>AdresseID</t>
+  </si>
+  <si>
+    <t>Adresse</t>
+  </si>
+  <si>
+    <t>Ort</t>
+  </si>
+  <si>
+    <t>FilialOrt</t>
+  </si>
+  <si>
+    <t>FilialName</t>
+  </si>
+  <si>
+    <t>VerkaufsID</t>
+  </si>
+  <si>
+    <t>Verkäufe</t>
+  </si>
+  <si>
+    <t>Zeitpunkt</t>
+  </si>
+  <si>
+    <t>Zahlart</t>
+  </si>
+  <si>
+    <t>Verkäufer</t>
+  </si>
+  <si>
+    <t>VerkäuferID</t>
+  </si>
+  <si>
+    <t>MitarbeiterID</t>
+  </si>
+  <si>
+    <t>durchschnittlicher Umsatz</t>
+  </si>
+  <si>
+    <t>Tag</t>
+  </si>
+  <si>
+    <t>Monat</t>
+  </si>
+  <si>
+    <t>Quartal</t>
+  </si>
+  <si>
+    <t>Jahr</t>
+  </si>
+  <si>
+    <t>Stunde</t>
+  </si>
+  <si>
+    <t>Tageszeit</t>
+  </si>
+  <si>
+    <t>Produkt</t>
+  </si>
+  <si>
+    <t>ProduktID</t>
+  </si>
+  <si>
+    <t>Bruttopreis</t>
+  </si>
+  <si>
+    <t>Nettopreis</t>
+  </si>
+  <si>
+    <t>ProduktName</t>
+  </si>
+  <si>
+    <t>KategorieID</t>
+  </si>
+  <si>
+    <t>Rezept</t>
+  </si>
+  <si>
+    <t>ZutatID</t>
+  </si>
+  <si>
+    <t>LagerkostenProg</t>
+  </si>
+  <si>
+    <t>Allergen</t>
+  </si>
+  <si>
+    <t>PreisProKg</t>
+  </si>
+  <si>
+    <t>Bezeichnung</t>
+  </si>
+  <si>
+    <t>beinhaltet</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>Menge</t>
+  </si>
+  <si>
+    <t>Zubereitungsdauer</t>
+  </si>
+  <si>
+    <t>gültig_bis</t>
+  </si>
+  <si>
+    <t>gültig_ab</t>
+  </si>
+  <si>
+    <t>Backzeit</t>
+  </si>
+  <si>
+    <t>Autor</t>
+  </si>
+  <si>
+    <t>Stückzahl</t>
+  </si>
+  <si>
+    <t>Zutaten</t>
+  </si>
+  <si>
+    <t>Lagerkosten</t>
+  </si>
+  <si>
+    <t>Lohnkosten</t>
+  </si>
+  <si>
+    <t>Zutatenkosten</t>
+  </si>
+  <si>
+    <t>Backkosten</t>
+  </si>
+  <si>
+    <t>Gewinnmarge</t>
+  </si>
+  <si>
+    <t>VerkäuferName</t>
+  </si>
+  <si>
+    <t>Mitarbeiter</t>
+  </si>
+  <si>
+    <t>MItarbeiterID</t>
+  </si>
+  <si>
+    <t>MitarbeiterName</t>
+  </si>
+  <si>
+    <t>D_Produkt</t>
+  </si>
+  <si>
+    <t>D_Tageszeit</t>
+  </si>
+  <si>
+    <t>D_Zeit</t>
+  </si>
+  <si>
+    <t>D_Verkäufer</t>
+  </si>
+  <si>
+    <t>D_Verkaufsvorgang</t>
+  </si>
+  <si>
+    <t>D_Filiale</t>
+  </si>
+  <si>
+    <t>AnzahlVerkäufe</t>
+  </si>
+  <si>
+    <t>Gesamtumsatz</t>
   </si>
 </sst>
 </file>
@@ -406,7 +586,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -437,15 +617,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -478,13 +666,8 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -835,30 +1018,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="22" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="32"/>
       <c r="I1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="16" t="s">
         <v>0</v>
       </c>
     </row>
@@ -869,10 +1052,10 @@
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -880,51 +1063,63 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="12"/>
+      <c r="J2" s="16"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="29" t="s">
+      <c r="A3" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="18"/>
+      <c r="D3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
+      <c r="G3" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>28</v>
+      </c>
       <c r="I3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="14"/>
+      <c r="J3" s="13"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
       <c r="I4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="14"/>
+      <c r="J4" s="13"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
+      <c r="B5" s="12" t="s">
+        <v>29</v>
+      </c>
       <c r="C5" s="11"/>
-      <c r="D5" s="30"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
+      <c r="H5" s="10" t="s">
+        <v>34</v>
+      </c>
       <c r="I5" s="10" t="s">
         <v>20</v>
       </c>
@@ -932,13 +1127,17 @@
     </row>
     <row r="6" spans="1:10" ht="15">
       <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
+      <c r="B6" s="10" t="s">
+        <v>30</v>
+      </c>
       <c r="C6" s="11"/>
-      <c r="D6" s="30"/>
+      <c r="D6" s="21"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
+      <c r="H6" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
     </row>
@@ -946,7 +1145,7 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="30"/>
+      <c r="D7" s="21"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
@@ -955,10 +1154,14 @@
       <c r="J7" s="10"/>
     </row>
     <row r="8" spans="1:10" ht="15">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
+      <c r="A8" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="30"/>
+      <c r="D8" s="21"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
@@ -972,7 +1175,7 @@
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="30"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -986,7 +1189,7 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="30"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -1000,7 +1203,7 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="30"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -1014,7 +1217,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="30"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -1026,7 +1229,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="30"/>
+      <c r="D13" s="21"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -1040,7 +1243,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="30"/>
+      <c r="D14" s="21"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -1052,7 +1255,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="30"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
@@ -1066,7 +1269,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="30"/>
+      <c r="D16" s="21"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -1075,94 +1278,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="31"/>
-      <c r="B17" s="31"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="14"/>
+      <c r="J17" s="13"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="31"/>
-      <c r="B18" s="31"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="14"/>
+      <c r="J18" s="13"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="31"/>
-      <c r="B19" s="31"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="14"/>
+      <c r="J19" s="13"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="31"/>
-      <c r="B20" s="31"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="14"/>
+      <c r="J20" s="13"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="31"/>
-      <c r="B21" s="31"/>
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="14"/>
+      <c r="J21" s="13"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="31"/>
-      <c r="B22" s="31"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="14"/>
+      <c r="J22" s="13"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="31"/>
-      <c r="B23" s="31"/>
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="14"/>
+      <c r="J23" s="13"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="30"/>
+      <c r="D24" s="21"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -1174,7 +1377,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="30"/>
+      <c r="D25" s="21"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -1186,7 +1389,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="30"/>
+      <c r="D26" s="21"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -1198,7 +1401,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="30"/>
+      <c r="D27" s="21"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -1210,7 +1413,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="30"/>
+      <c r="D28" s="21"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -1222,7 +1425,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="30"/>
+      <c r="D29" s="21"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -1234,7 +1437,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="30"/>
+      <c r="D30" s="21"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -1246,7 +1449,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="30"/>
+      <c r="D31" s="21"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -1258,7 +1461,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="30"/>
+      <c r="D32" s="21"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -1270,7 +1473,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="30"/>
+      <c r="D33" s="21"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -1282,7 +1485,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="30"/>
+      <c r="D34" s="21"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -1294,7 +1497,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="30"/>
+      <c r="D35" s="21"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -1306,7 +1509,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="30"/>
+      <c r="D36" s="21"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -1318,7 +1521,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="30"/>
+      <c r="D37" s="21"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -1330,7 +1533,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="30"/>
+      <c r="D38" s="21"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -1342,7 +1545,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="30"/>
+      <c r="D39" s="21"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -1354,7 +1557,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="30"/>
+      <c r="D40" s="21"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -1366,7 +1569,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="30"/>
+      <c r="D41" s="21"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -1378,7 +1581,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="30"/>
+      <c r="D42" s="21"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -1390,7 +1593,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="30"/>
+      <c r="D43" s="21"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -1402,7 +1605,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="30"/>
+      <c r="D44" s="21"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -1414,7 +1617,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="30"/>
+      <c r="D45" s="21"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -1426,7 +1629,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="30"/>
+      <c r="D46" s="21"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -1438,7 +1641,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="30"/>
+      <c r="D47" s="21"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -1450,7 +1653,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="30"/>
+      <c r="D48" s="21"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -1462,7 +1665,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="30"/>
+      <c r="D49" s="21"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -1474,7 +1677,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="30"/>
+      <c r="D50" s="21"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -1486,7 +1689,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="30"/>
+      <c r="D51" s="21"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -1498,7 +1701,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="30"/>
+      <c r="D52" s="21"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -1510,7 +1713,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="30"/>
+      <c r="D53" s="21"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -1522,7 +1725,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="30"/>
+      <c r="D54" s="21"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -1534,7 +1737,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="30"/>
+      <c r="D55" s="21"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -1546,7 +1749,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="30"/>
+      <c r="D56" s="21"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -1558,7 +1761,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="30"/>
+      <c r="D57" s="21"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -2480,13 +2683,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -2503,6 +2699,13 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2526,30 +2729,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="22" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="32"/>
       <c r="I1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="16" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2560,10 +2763,10 @@
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2571,51 +2774,63 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="12"/>
+      <c r="J2" s="16"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="29" t="s">
+      <c r="A3" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="18"/>
+      <c r="D3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
+      <c r="G3" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>35</v>
+      </c>
       <c r="I3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="14"/>
+      <c r="J3" s="13"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
       <c r="I4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="14"/>
+      <c r="J4" s="13"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
+      <c r="B5" s="10" t="s">
+        <v>28</v>
+      </c>
       <c r="C5" s="11"/>
-      <c r="D5" s="30"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
+      <c r="H5" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="I5" s="10" t="s">
         <v>20</v>
       </c>
@@ -2623,9 +2838,11 @@
     </row>
     <row r="6" spans="1:10" ht="15">
       <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
+      <c r="B6" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="C6" s="11"/>
-      <c r="D6" s="30"/>
+      <c r="D6" s="21"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
@@ -2637,7 +2854,7 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="30"/>
+      <c r="D7" s="21"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
@@ -2649,7 +2866,7 @@
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="30"/>
+      <c r="D8" s="21"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
@@ -2663,7 +2880,7 @@
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="30"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -2677,7 +2894,7 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="30"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -2691,7 +2908,7 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="30"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -2705,7 +2922,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="30"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -2717,7 +2934,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="30"/>
+      <c r="D13" s="21"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -2731,7 +2948,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="30"/>
+      <c r="D14" s="21"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -2743,7 +2960,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="30"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
@@ -2757,7 +2974,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="30"/>
+      <c r="D16" s="21"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -2766,94 +2983,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="31"/>
-      <c r="B17" s="31"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="34"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="14"/>
+      <c r="J17" s="13"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="31"/>
-      <c r="B18" s="31"/>
+      <c r="A18" s="34"/>
+      <c r="B18" s="34"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="14"/>
+      <c r="J18" s="13"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="31"/>
-      <c r="B19" s="31"/>
+      <c r="A19" s="34"/>
+      <c r="B19" s="34"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="14"/>
+      <c r="J19" s="13"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="31"/>
-      <c r="B20" s="31"/>
+      <c r="A20" s="34"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="14"/>
+      <c r="J20" s="13"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="31"/>
-      <c r="B21" s="31"/>
+      <c r="A21" s="34"/>
+      <c r="B21" s="34"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="14"/>
+      <c r="J21" s="13"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="31"/>
-      <c r="B22" s="31"/>
+      <c r="A22" s="34"/>
+      <c r="B22" s="34"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="14"/>
+      <c r="J22" s="13"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="31"/>
-      <c r="B23" s="31"/>
+      <c r="A23" s="34"/>
+      <c r="B23" s="34"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="14"/>
+      <c r="J23" s="13"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="30"/>
+      <c r="D24" s="21"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -2865,7 +3082,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="30"/>
+      <c r="D25" s="21"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -2877,7 +3094,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="30"/>
+      <c r="D26" s="21"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -2889,7 +3106,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="30"/>
+      <c r="D27" s="21"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -2901,7 +3118,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="30"/>
+      <c r="D28" s="21"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -2913,7 +3130,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="30"/>
+      <c r="D29" s="21"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -2925,7 +3142,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="30"/>
+      <c r="D30" s="21"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -2937,7 +3154,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="30"/>
+      <c r="D31" s="21"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -2949,7 +3166,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="30"/>
+      <c r="D32" s="21"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -2961,7 +3178,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="30"/>
+      <c r="D33" s="21"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -2973,7 +3190,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="30"/>
+      <c r="D34" s="21"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -2985,7 +3202,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="30"/>
+      <c r="D35" s="21"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -2997,7 +3214,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="30"/>
+      <c r="D36" s="21"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -3009,7 +3226,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="30"/>
+      <c r="D37" s="21"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -3021,7 +3238,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="30"/>
+      <c r="D38" s="21"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -3033,7 +3250,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="30"/>
+      <c r="D39" s="21"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -3045,7 +3262,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="30"/>
+      <c r="D40" s="21"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -3057,7 +3274,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="30"/>
+      <c r="D41" s="21"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -3069,7 +3286,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="30"/>
+      <c r="D42" s="21"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -3081,7 +3298,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="30"/>
+      <c r="D43" s="21"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -3093,7 +3310,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="30"/>
+      <c r="D44" s="21"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -3105,7 +3322,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="30"/>
+      <c r="D45" s="21"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -3117,7 +3334,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="30"/>
+      <c r="D46" s="21"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -3129,7 +3346,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="30"/>
+      <c r="D47" s="21"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -3141,7 +3358,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="30"/>
+      <c r="D48" s="21"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -3153,7 +3370,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="30"/>
+      <c r="D49" s="21"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -3165,7 +3382,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="30"/>
+      <c r="D50" s="21"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -3177,7 +3394,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="30"/>
+      <c r="D51" s="21"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -3189,7 +3406,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="30"/>
+      <c r="D52" s="21"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -3201,7 +3418,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="30"/>
+      <c r="D53" s="21"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -3213,7 +3430,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="30"/>
+      <c r="D54" s="21"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -3225,7 +3442,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="30"/>
+      <c r="D55" s="21"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -3237,7 +3454,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="30"/>
+      <c r="D56" s="21"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -3249,7 +3466,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="30"/>
+      <c r="D57" s="21"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -4170,14 +4387,7 @@
       <c r="J133" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
+  <mergeCells count="21">
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -4194,6 +4404,11 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4212,35 +4427,35 @@
     <col min="6" max="6" width="22.375" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="20.75" customWidth="1"/>
     <col min="8" max="8" width="17.25" customWidth="1"/>
-    <col min="9" max="9" width="29.5" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="7.875" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="22" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="32"/>
       <c r="I1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="16" t="s">
         <v>0</v>
       </c>
     </row>
@@ -4251,10 +4466,10 @@
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -4262,51 +4477,63 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="12"/>
+      <c r="J2" s="16"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="29" t="s">
+      <c r="A3" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="18"/>
+      <c r="D3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
+      <c r="G3" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>40</v>
+      </c>
       <c r="I3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="14"/>
+      <c r="J3" s="13"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
       <c r="I4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="14"/>
+      <c r="J4" s="13"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
+      <c r="B5" s="10" t="s">
+        <v>41</v>
+      </c>
       <c r="C5" s="11"/>
-      <c r="D5" s="30"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
+      <c r="H5" s="12" t="s">
+        <v>76</v>
+      </c>
       <c r="I5" s="10" t="s">
         <v>20</v>
       </c>
@@ -4314,13 +4541,17 @@
     </row>
     <row r="6" spans="1:10" ht="15">
       <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
+      <c r="B6" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="C6" s="11"/>
-      <c r="D6" s="30"/>
+      <c r="D6" s="21"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
+      <c r="H6" s="12" t="s">
+        <v>42</v>
+      </c>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
     </row>
@@ -4328,23 +4559,31 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="30"/>
+      <c r="D7" s="21"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
+      <c r="H7" s="10" t="s">
+        <v>86</v>
+      </c>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
     </row>
     <row r="8" spans="1:10" ht="15">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
+      <c r="A8" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>78</v>
+      </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="30"/>
+      <c r="D8" s="21"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
+      <c r="H8" s="10" t="s">
+        <v>87</v>
+      </c>
       <c r="I8" s="10" t="s">
         <v>21</v>
       </c>
@@ -4352,9 +4591,11 @@
     </row>
     <row r="9" spans="1:10" ht="15">
       <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
+      <c r="B9" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="C9" s="10"/>
-      <c r="D9" s="30"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -4368,7 +4609,7 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="30"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -4382,7 +4623,7 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="30"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -4396,7 +4637,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="30"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -4408,7 +4649,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="30"/>
+      <c r="D13" s="21"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -4422,7 +4663,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="30"/>
+      <c r="D14" s="21"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -4434,7 +4675,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="30"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
@@ -4448,7 +4689,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="30"/>
+      <c r="D16" s="21"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -4457,94 +4698,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="31"/>
-      <c r="B17" s="31"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="14"/>
+      <c r="J17" s="13"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="31"/>
-      <c r="B18" s="31"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="14"/>
+      <c r="J18" s="13"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="31"/>
-      <c r="B19" s="31"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="14"/>
+      <c r="J19" s="13"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="31"/>
-      <c r="B20" s="31"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="14"/>
+      <c r="J20" s="13"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="31"/>
-      <c r="B21" s="31"/>
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="14"/>
+      <c r="J21" s="13"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="31"/>
-      <c r="B22" s="31"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="14"/>
+      <c r="J22" s="13"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="31"/>
-      <c r="B23" s="31"/>
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="14"/>
+      <c r="J23" s="13"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="30"/>
+      <c r="D24" s="21"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -4556,7 +4797,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="30"/>
+      <c r="D25" s="21"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -4568,7 +4809,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="30"/>
+      <c r="D26" s="21"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -4580,7 +4821,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="30"/>
+      <c r="D27" s="21"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -4592,7 +4833,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="30"/>
+      <c r="D28" s="21"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -4604,7 +4845,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="30"/>
+      <c r="D29" s="21"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -4616,7 +4857,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="30"/>
+      <c r="D30" s="21"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -4628,7 +4869,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="30"/>
+      <c r="D31" s="21"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -4640,7 +4881,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="30"/>
+      <c r="D32" s="21"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -4652,7 +4893,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="30"/>
+      <c r="D33" s="21"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -4664,7 +4905,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="30"/>
+      <c r="D34" s="21"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -4676,7 +4917,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="30"/>
+      <c r="D35" s="21"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -4688,7 +4929,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="30"/>
+      <c r="D36" s="21"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -4700,7 +4941,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="30"/>
+      <c r="D37" s="21"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -4712,7 +4953,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="30"/>
+      <c r="D38" s="21"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -4724,7 +4965,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="30"/>
+      <c r="D39" s="21"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -4736,7 +4977,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="30"/>
+      <c r="D40" s="21"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -4748,7 +4989,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="30"/>
+      <c r="D41" s="21"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -4760,7 +5001,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="30"/>
+      <c r="D42" s="21"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -4772,7 +5013,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="30"/>
+      <c r="D43" s="21"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -4784,7 +5025,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="30"/>
+      <c r="D44" s="21"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -4796,7 +5037,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="30"/>
+      <c r="D45" s="21"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -4808,7 +5049,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="30"/>
+      <c r="D46" s="21"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -4820,7 +5061,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="30"/>
+      <c r="D47" s="21"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -4832,7 +5073,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="30"/>
+      <c r="D48" s="21"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -4844,7 +5085,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="30"/>
+      <c r="D49" s="21"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -4856,7 +5097,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="30"/>
+      <c r="D50" s="21"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -4868,7 +5109,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="30"/>
+      <c r="D51" s="21"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -4880,7 +5121,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="30"/>
+      <c r="D52" s="21"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -4892,7 +5133,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="30"/>
+      <c r="D53" s="21"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -4904,7 +5145,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="30"/>
+      <c r="D54" s="21"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -4916,7 +5157,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="30"/>
+      <c r="D55" s="21"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -4928,7 +5169,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="30"/>
+      <c r="D56" s="21"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -4940,7 +5181,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="30"/>
+      <c r="D57" s="21"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -5862,13 +6103,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -5885,6 +6119,13 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5908,30 +6149,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="22" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="32"/>
       <c r="I1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="16" t="s">
         <v>0</v>
       </c>
     </row>
@@ -5942,10 +6183,10 @@
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -5953,51 +6194,57 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="12"/>
+      <c r="J2" s="16"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="29" t="s">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
+      <c r="G3" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>43</v>
+      </c>
       <c r="I3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="14"/>
+      <c r="J3" s="13"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
       <c r="I4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="14"/>
+      <c r="J4" s="13"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="10"/>
       <c r="C5" s="11"/>
-      <c r="D5" s="30"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
+      <c r="H5" s="10" t="s">
+        <v>44</v>
+      </c>
       <c r="I5" s="10" t="s">
         <v>20</v>
       </c>
@@ -6007,11 +6254,13 @@
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
       <c r="C6" s="11"/>
-      <c r="D6" s="30"/>
+      <c r="D6" s="21"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
+      <c r="H6" s="10" t="s">
+        <v>45</v>
+      </c>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
     </row>
@@ -6019,11 +6268,13 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="30"/>
+      <c r="D7" s="21"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
+      <c r="H7" s="10" t="s">
+        <v>46</v>
+      </c>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
     </row>
@@ -6031,7 +6282,7 @@
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="30"/>
+      <c r="D8" s="21"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
@@ -6045,7 +6296,7 @@
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="30"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -6059,7 +6310,7 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="30"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -6073,7 +6324,7 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="30"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -6087,7 +6338,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="30"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -6099,7 +6350,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="30"/>
+      <c r="D13" s="21"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -6113,7 +6364,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="30"/>
+      <c r="D14" s="21"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -6125,7 +6376,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="30"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
@@ -6139,7 +6390,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="30"/>
+      <c r="D16" s="21"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -6148,94 +6399,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="31"/>
-      <c r="B17" s="31"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="14"/>
+      <c r="J17" s="13"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="31"/>
-      <c r="B18" s="31"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="14"/>
+      <c r="J18" s="13"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="31"/>
-      <c r="B19" s="31"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="14"/>
+      <c r="J19" s="13"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="31"/>
-      <c r="B20" s="31"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="14"/>
+      <c r="J20" s="13"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="31"/>
-      <c r="B21" s="31"/>
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="14"/>
+      <c r="J21" s="13"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="31"/>
-      <c r="B22" s="31"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="14"/>
+      <c r="J22" s="13"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="31"/>
-      <c r="B23" s="31"/>
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="14"/>
+      <c r="J23" s="13"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="30"/>
+      <c r="D24" s="21"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -6247,7 +6498,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="30"/>
+      <c r="D25" s="21"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -6259,7 +6510,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="30"/>
+      <c r="D26" s="21"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -6271,7 +6522,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="30"/>
+      <c r="D27" s="21"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -6283,7 +6534,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="30"/>
+      <c r="D28" s="21"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -6295,7 +6546,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="30"/>
+      <c r="D29" s="21"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -6307,7 +6558,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="30"/>
+      <c r="D30" s="21"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -6319,7 +6570,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="30"/>
+      <c r="D31" s="21"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -6331,7 +6582,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="30"/>
+      <c r="D32" s="21"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -6343,7 +6594,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="30"/>
+      <c r="D33" s="21"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -6355,7 +6606,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="30"/>
+      <c r="D34" s="21"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -6367,7 +6618,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="30"/>
+      <c r="D35" s="21"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -6379,7 +6630,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="30"/>
+      <c r="D36" s="21"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -6391,7 +6642,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="30"/>
+      <c r="D37" s="21"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -6403,7 +6654,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="30"/>
+      <c r="D38" s="21"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -6415,7 +6666,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="30"/>
+      <c r="D39" s="21"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -6427,7 +6678,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="30"/>
+      <c r="D40" s="21"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -6439,7 +6690,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="30"/>
+      <c r="D41" s="21"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -6451,7 +6702,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="30"/>
+      <c r="D42" s="21"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -6463,7 +6714,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="30"/>
+      <c r="D43" s="21"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -6475,7 +6726,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="30"/>
+      <c r="D44" s="21"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -6487,7 +6738,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="30"/>
+      <c r="D45" s="21"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -6499,7 +6750,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="30"/>
+      <c r="D46" s="21"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -6511,7 +6762,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="30"/>
+      <c r="D47" s="21"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -6523,7 +6774,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="30"/>
+      <c r="D48" s="21"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -6535,7 +6786,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="30"/>
+      <c r="D49" s="21"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -6547,7 +6798,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="30"/>
+      <c r="D50" s="21"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -6559,7 +6810,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="30"/>
+      <c r="D51" s="21"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -6571,7 +6822,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="30"/>
+      <c r="D52" s="21"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -6583,7 +6834,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="30"/>
+      <c r="D53" s="21"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -6595,7 +6846,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="30"/>
+      <c r="D54" s="21"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -6607,7 +6858,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="30"/>
+      <c r="D55" s="21"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -6619,7 +6870,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="30"/>
+      <c r="D56" s="21"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -6631,7 +6882,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="30"/>
+      <c r="D57" s="21"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -7553,13 +7804,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -7576,6 +7820,13 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7599,30 +7850,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="22" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="32"/>
       <c r="I1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="16" t="s">
         <v>0</v>
       </c>
     </row>
@@ -7633,10 +7884,10 @@
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -7644,51 +7895,57 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="12"/>
+      <c r="J2" s="16"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="29" t="s">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
+      <c r="G3" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>47</v>
+      </c>
       <c r="I3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="14"/>
+      <c r="J3" s="13"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
       <c r="I4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="14"/>
+      <c r="J4" s="13"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="10"/>
       <c r="C5" s="11"/>
-      <c r="D5" s="30"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
+      <c r="H5" s="10" t="s">
+        <v>48</v>
+      </c>
       <c r="I5" s="10" t="s">
         <v>20</v>
       </c>
@@ -7698,7 +7955,7 @@
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
       <c r="C6" s="11"/>
-      <c r="D6" s="30"/>
+      <c r="D6" s="21"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
@@ -7710,7 +7967,7 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="30"/>
+      <c r="D7" s="21"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
@@ -7722,7 +7979,7 @@
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="30"/>
+      <c r="D8" s="21"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
@@ -7736,7 +7993,7 @@
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="30"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -7750,7 +8007,7 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="30"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -7764,7 +8021,7 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="30"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -7778,7 +8035,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="30"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -7790,7 +8047,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="30"/>
+      <c r="D13" s="21"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -7804,7 +8061,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="30"/>
+      <c r="D14" s="21"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -7816,7 +8073,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="30"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
@@ -7830,7 +8087,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="30"/>
+      <c r="D16" s="21"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -7839,94 +8096,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="31"/>
-      <c r="B17" s="31"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="14"/>
+      <c r="J17" s="13"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="31"/>
-      <c r="B18" s="31"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="14"/>
+      <c r="J18" s="13"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="31"/>
-      <c r="B19" s="31"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="14"/>
+      <c r="J19" s="13"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="31"/>
-      <c r="B20" s="31"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="14"/>
+      <c r="J20" s="13"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="31"/>
-      <c r="B21" s="31"/>
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="14"/>
+      <c r="J21" s="13"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="31"/>
-      <c r="B22" s="31"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="14"/>
+      <c r="J22" s="13"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="31"/>
-      <c r="B23" s="31"/>
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="14"/>
+      <c r="J23" s="13"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="30"/>
+      <c r="D24" s="21"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -7938,7 +8195,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="30"/>
+      <c r="D25" s="21"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -7950,7 +8207,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="30"/>
+      <c r="D26" s="21"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -7962,7 +8219,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="30"/>
+      <c r="D27" s="21"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -7974,7 +8231,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="30"/>
+      <c r="D28" s="21"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -7986,7 +8243,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="30"/>
+      <c r="D29" s="21"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -7998,7 +8255,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="30"/>
+      <c r="D30" s="21"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -8010,7 +8267,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="30"/>
+      <c r="D31" s="21"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -8022,7 +8279,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="30"/>
+      <c r="D32" s="21"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -8034,7 +8291,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="30"/>
+      <c r="D33" s="21"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -8046,7 +8303,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="30"/>
+      <c r="D34" s="21"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -8058,7 +8315,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="30"/>
+      <c r="D35" s="21"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -8070,7 +8327,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="30"/>
+      <c r="D36" s="21"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -8082,7 +8339,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="30"/>
+      <c r="D37" s="21"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -8094,7 +8351,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="30"/>
+      <c r="D38" s="21"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -8106,7 +8363,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="30"/>
+      <c r="D39" s="21"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -8118,7 +8375,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="30"/>
+      <c r="D40" s="21"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -8130,7 +8387,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="30"/>
+      <c r="D41" s="21"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -8142,7 +8399,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="30"/>
+      <c r="D42" s="21"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -8154,7 +8411,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="30"/>
+      <c r="D43" s="21"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -8166,7 +8423,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="30"/>
+      <c r="D44" s="21"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -8178,7 +8435,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="30"/>
+      <c r="D45" s="21"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -8190,7 +8447,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="30"/>
+      <c r="D46" s="21"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -8202,7 +8459,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="30"/>
+      <c r="D47" s="21"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -8214,7 +8471,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="30"/>
+      <c r="D48" s="21"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -8226,7 +8483,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="30"/>
+      <c r="D49" s="21"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -8238,7 +8495,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="30"/>
+      <c r="D50" s="21"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -8250,7 +8507,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="30"/>
+      <c r="D51" s="21"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -8262,7 +8519,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="30"/>
+      <c r="D52" s="21"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -8274,7 +8531,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="30"/>
+      <c r="D53" s="21"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -8286,7 +8543,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="30"/>
+      <c r="D54" s="21"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -8298,7 +8555,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="30"/>
+      <c r="D55" s="21"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -8310,7 +8567,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="30"/>
+      <c r="D56" s="21"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -8322,7 +8579,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="30"/>
+      <c r="D57" s="21"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -9244,13 +9501,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -9267,6 +9517,13 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9290,30 +9547,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="22" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="32"/>
       <c r="I1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="16" t="s">
         <v>0</v>
       </c>
     </row>
@@ -9324,10 +9581,10 @@
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -9335,167 +9592,201 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="12"/>
+      <c r="J2" s="16"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="29" t="s">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="18"/>
+      <c r="D3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
+      <c r="G3" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>50</v>
+      </c>
       <c r="I3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="14"/>
+      <c r="J3" s="13"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
       <c r="I4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="14"/>
+      <c r="J4" s="13"/>
     </row>
     <row r="5" spans="1:10" ht="15">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
       <c r="C5" s="7"/>
-      <c r="D5" s="30"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+      <c r="H5" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="I5" s="4" t="s">
         <v>20</v>
       </c>
       <c r="J5" s="4"/>
     </row>
     <row r="6" spans="1:10" ht="15">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
       <c r="C6" s="7"/>
-      <c r="D6" s="30"/>
+      <c r="D6" s="21"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
+      <c r="H6" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:10" ht="15">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
+      <c r="B7" t="s">
+        <v>54</v>
+      </c>
       <c r="C7" s="7"/>
-      <c r="D7" s="30"/>
+      <c r="D7" s="21"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="H7" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
     </row>
     <row r="8" spans="1:10" ht="15">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="30"/>
+      <c r="D8" s="21"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="H8" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="I8" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J8" s="4"/>
     </row>
     <row r="9" spans="1:10" ht="15">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
+      <c r="A9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s">
+        <v>56</v>
+      </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="30"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="H9" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="I9" s="4" t="s">
         <v>22</v>
       </c>
       <c r="J9" s="4"/>
     </row>
     <row r="10" spans="1:10" ht="15">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
       <c r="C10" s="7"/>
-      <c r="D10" s="30"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="H10" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="I10" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J10" s="4"/>
     </row>
     <row r="11" spans="1:10" ht="15">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="30"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="H11" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="I11" s="4" t="s">
         <v>23</v>
       </c>
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:10" ht="15">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
+      <c r="B12" t="s">
+        <v>59</v>
+      </c>
       <c r="C12" s="7"/>
-      <c r="D12" s="30"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="H12" s="4" t="s">
+        <v>73</v>
+      </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
     </row>
     <row r="13" spans="1:10" ht="15">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
+      <c r="B13" t="s">
+        <v>60</v>
+      </c>
       <c r="C13" s="7"/>
-      <c r="D13" s="30"/>
+      <c r="D13" s="21"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="H13" s="4" t="s">
+        <v>75</v>
+      </c>
       <c r="I13" s="4" t="s">
         <v>25</v>
       </c>
       <c r="J13" s="4"/>
     </row>
     <row r="14" spans="1:10" ht="15">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="30"/>
+      <c r="D14" s="21"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="4"/>
@@ -9504,10 +9795,14 @@
       <c r="J14" s="4"/>
     </row>
     <row r="15" spans="1:10" ht="15">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
+      <c r="A15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
       <c r="C15" s="7"/>
-      <c r="D15" s="30"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="4"/>
@@ -9518,10 +9813,11 @@
       <c r="J15" s="4"/>
     </row>
     <row r="16" spans="1:10" ht="15">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
+      <c r="B16" t="s">
+        <v>62</v>
+      </c>
       <c r="C16" s="7"/>
-      <c r="D16" s="30"/>
+      <c r="D16" s="21"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -9530,94 +9826,102 @@
       <c r="J16" s="4"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="31"/>
-      <c r="B17" s="31"/>
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
       <c r="C17" s="8"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="14"/>
+      <c r="J17" s="13"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="31"/>
-      <c r="B18" s="31"/>
+      <c r="B18" t="s">
+        <v>63</v>
+      </c>
       <c r="C18" s="8"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
       <c r="I18" s="4"/>
-      <c r="J18" s="14"/>
+      <c r="J18" s="13"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="31"/>
-      <c r="B19" s="31"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
       <c r="I19" s="4"/>
-      <c r="J19" s="14"/>
+      <c r="J19" s="13"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="31"/>
-      <c r="B20" s="31"/>
+      <c r="A20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" t="s">
+        <v>50</v>
+      </c>
       <c r="C20" s="8"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="14"/>
+      <c r="J20" s="13"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="31"/>
-      <c r="B21" s="31"/>
+      <c r="B21" t="s">
+        <v>62</v>
+      </c>
       <c r="C21" s="8"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="14"/>
+      <c r="J21" s="13"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="31"/>
-      <c r="B22" s="31"/>
+      <c r="B22" t="s">
+        <v>64</v>
+      </c>
       <c r="C22" s="8"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
       <c r="I22" s="4"/>
-      <c r="J22" s="14"/>
+      <c r="J22" s="13"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="31"/>
-      <c r="B23" s="31"/>
+      <c r="B23" t="s">
+        <v>65</v>
+      </c>
       <c r="C23" s="8"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
       <c r="I23" s="4"/>
-      <c r="J23" s="14"/>
+      <c r="J23" s="13"/>
     </row>
     <row r="24" spans="1:10" ht="15">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
+      <c r="B24" t="s">
+        <v>66</v>
+      </c>
       <c r="C24" s="7"/>
-      <c r="D24" s="30"/>
+      <c r="D24" s="21"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
       <c r="G24" s="4"/>
@@ -9626,10 +9930,11 @@
       <c r="J24" s="4"/>
     </row>
     <row r="25" spans="1:10" ht="15">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
+      <c r="B25" t="s">
+        <v>67</v>
+      </c>
       <c r="C25" s="7"/>
-      <c r="D25" s="30"/>
+      <c r="D25" s="21"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="4"/>
@@ -9638,10 +9943,11 @@
       <c r="J25" s="4"/>
     </row>
     <row r="26" spans="1:10" ht="15">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
+      <c r="B26" t="s">
+        <v>68</v>
+      </c>
       <c r="C26" s="7"/>
-      <c r="D26" s="30"/>
+      <c r="D26" s="21"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -9650,10 +9956,11 @@
       <c r="J26" s="4"/>
     </row>
     <row r="27" spans="1:10" ht="15">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
+      <c r="B27" t="s">
+        <v>69</v>
+      </c>
       <c r="C27" s="7"/>
-      <c r="D27" s="30"/>
+      <c r="D27" s="21"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
@@ -9665,7 +9972,7 @@
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="30"/>
+      <c r="D28" s="21"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -9677,7 +9984,7 @@
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="30"/>
+      <c r="D29" s="21"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -9689,7 +9996,7 @@
       <c r="A30" s="4"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="30"/>
+      <c r="D30" s="21"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="4"/>
@@ -9701,7 +10008,7 @@
       <c r="A31" s="4"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="30"/>
+      <c r="D31" s="21"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="4"/>
@@ -9713,7 +10020,7 @@
       <c r="A32" s="4"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
-      <c r="D32" s="30"/>
+      <c r="D32" s="21"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="4"/>
@@ -9725,7 +10032,7 @@
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="30"/>
+      <c r="D33" s="21"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
@@ -9737,7 +10044,7 @@
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="30"/>
+      <c r="D34" s="21"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
       <c r="G34" s="4"/>
@@ -9749,7 +10056,7 @@
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="30"/>
+      <c r="D35" s="21"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
       <c r="G35" s="4"/>
@@ -9761,7 +10068,7 @@
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="7"/>
-      <c r="D36" s="30"/>
+      <c r="D36" s="21"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="4"/>
@@ -9773,7 +10080,7 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="30"/>
+      <c r="D37" s="21"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="4"/>
@@ -9785,7 +10092,7 @@
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="7"/>
-      <c r="D38" s="30"/>
+      <c r="D38" s="21"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="4"/>
@@ -9797,7 +10104,7 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="7"/>
-      <c r="D39" s="30"/>
+      <c r="D39" s="21"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="4"/>
@@ -9809,7 +10116,7 @@
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="7"/>
-      <c r="D40" s="30"/>
+      <c r="D40" s="21"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="4"/>
@@ -9821,7 +10128,7 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="30"/>
+      <c r="D41" s="21"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="4"/>
@@ -9833,7 +10140,7 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="30"/>
+      <c r="D42" s="21"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="4"/>
@@ -9845,7 +10152,7 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="30"/>
+      <c r="D43" s="21"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="4"/>
@@ -9857,7 +10164,7 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="7"/>
-      <c r="D44" s="30"/>
+      <c r="D44" s="21"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="4"/>
@@ -9869,7 +10176,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="30"/>
+      <c r="D45" s="21"/>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
       <c r="G45" s="4"/>
@@ -9881,7 +10188,7 @@
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="7"/>
-      <c r="D46" s="30"/>
+      <c r="D46" s="21"/>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
       <c r="G46" s="4"/>
@@ -9893,7 +10200,7 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="7"/>
-      <c r="D47" s="30"/>
+      <c r="D47" s="21"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
       <c r="G47" s="4"/>
@@ -9905,7 +10212,7 @@
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="7"/>
-      <c r="D48" s="30"/>
+      <c r="D48" s="21"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
       <c r="G48" s="4"/>
@@ -9917,7 +10224,7 @@
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="7"/>
-      <c r="D49" s="30"/>
+      <c r="D49" s="21"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
       <c r="G49" s="4"/>
@@ -9929,7 +10236,7 @@
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="30"/>
+      <c r="D50" s="21"/>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
       <c r="G50" s="4"/>
@@ -9941,7 +10248,7 @@
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="7"/>
-      <c r="D51" s="30"/>
+      <c r="D51" s="21"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
       <c r="G51" s="4"/>
@@ -9953,7 +10260,7 @@
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="7"/>
-      <c r="D52" s="30"/>
+      <c r="D52" s="21"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
       <c r="G52" s="4"/>
@@ -9965,7 +10272,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="30"/>
+      <c r="D53" s="21"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="4"/>
@@ -9977,7 +10284,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="30"/>
+      <c r="D54" s="21"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
       <c r="G54" s="4"/>
@@ -9989,7 +10296,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="7"/>
-      <c r="D55" s="30"/>
+      <c r="D55" s="21"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
       <c r="G55" s="4"/>
@@ -10001,7 +10308,7 @@
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="7"/>
-      <c r="D56" s="30"/>
+      <c r="D56" s="21"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
       <c r="G56" s="4"/>
@@ -10013,7 +10320,7 @@
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="7"/>
-      <c r="D57" s="30"/>
+      <c r="D57" s="21"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
       <c r="G57" s="4"/>
@@ -10934,17 +11241,8 @@
       <c r="J133" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
+  <mergeCells count="19">
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
@@ -10958,13 +11256,19 @@
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="D3:D57"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9982EFDA-A878-45F6-B070-788A492CB147}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94A74049-1771-468B-813D-A487483CB510}">
   <dimension ref="A1:I133"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
@@ -10979,27 +11283,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="22" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="28"/>
-      <c r="I1" s="12" t="s">
+      <c r="H1" s="32"/>
+      <c r="I1" s="16" t="s">
         <v>0</v>
       </c>
     </row>
@@ -11010,1470 +11314,1463 @@
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="12"/>
+      <c r="I2" s="16"/>
     </row>
     <row r="3" spans="1:9" ht="159.4" customHeight="1">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="29" t="s">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="17"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="14"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="13"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
     </row>
     <row r="5" spans="1:9" ht="15">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
     </row>
     <row r="6" spans="1:9" ht="15">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:9" ht="15">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" ht="15">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:9" ht="15">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" ht="15">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" ht="15">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
     </row>
     <row r="12" spans="1:9" ht="15">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:9" ht="15">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:9" ht="15">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="15">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:9" ht="15">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" ht="15">
-      <c r="A17" s="31"/>
-      <c r="B17" s="31"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
     </row>
     <row r="18" spans="1:9" ht="15">
-      <c r="A18" s="31"/>
-      <c r="B18" s="31"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
     </row>
     <row r="19" spans="1:9" ht="15">
-      <c r="A19" s="31"/>
-      <c r="B19" s="31"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
     </row>
     <row r="20" spans="1:9" ht="15">
-      <c r="A20" s="31"/>
-      <c r="B20" s="31"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
     </row>
     <row r="21" spans="1:9" ht="15">
-      <c r="A21" s="31"/>
-      <c r="B21" s="31"/>
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
     </row>
     <row r="22" spans="1:9" ht="15">
-      <c r="A22" s="31"/>
-      <c r="B22" s="31"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
     </row>
     <row r="23" spans="1:9" ht="15">
-      <c r="A23" s="31"/>
-      <c r="B23" s="31"/>
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
     </row>
     <row r="24" spans="1:9" ht="15">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9" ht="15">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" ht="15">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
     </row>
     <row r="27" spans="1:9" ht="15">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
     </row>
     <row r="28" spans="1:9" ht="15">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
     </row>
     <row r="29" spans="1:9" ht="15">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
     </row>
     <row r="30" spans="1:9" ht="15">
-      <c r="A30" s="10"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
+      <c r="A30" s="4"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
     </row>
     <row r="31" spans="1:9" ht="15">
-      <c r="A31" s="10"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="10"/>
+      <c r="A31" s="4"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="4"/>
     </row>
     <row r="32" spans="1:9" ht="15">
-      <c r="A32" s="10"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
+      <c r="A32" s="4"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
     </row>
     <row r="33" spans="1:9" ht="15">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
     </row>
     <row r="34" spans="1:9" ht="15">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
     </row>
     <row r="35" spans="1:9" ht="15">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
     </row>
     <row r="36" spans="1:9" ht="15">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
     </row>
     <row r="37" spans="1:9" ht="15">
-      <c r="A37" s="10"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
     </row>
     <row r="38" spans="1:9" ht="15">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
     </row>
     <row r="39" spans="1:9" ht="15">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
+      <c r="A39" s="4"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
     </row>
     <row r="40" spans="1:9" ht="15">
-      <c r="A40" s="10"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
     </row>
     <row r="41" spans="1:9" ht="15">
-      <c r="A41" s="10"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
     </row>
     <row r="42" spans="1:9" ht="15">
-      <c r="A42" s="10"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
     </row>
     <row r="43" spans="1:9" ht="15">
-      <c r="A43" s="10"/>
-      <c r="B43" s="10"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
     </row>
     <row r="44" spans="1:9" ht="15">
-      <c r="A44" s="10"/>
-      <c r="B44" s="10"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
+      <c r="A44" s="4"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
     </row>
     <row r="45" spans="1:9" ht="15">
-      <c r="A45" s="10"/>
-      <c r="B45" s="10"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
     </row>
     <row r="46" spans="1:9" ht="15">
-      <c r="A46" s="10"/>
-      <c r="B46" s="10"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
+      <c r="A46" s="4"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
     </row>
     <row r="47" spans="1:9" ht="15">
-      <c r="A47" s="10"/>
-      <c r="B47" s="10"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="30"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
+      <c r="A47" s="4"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
     </row>
     <row r="48" spans="1:9" ht="15">
-      <c r="A48" s="10"/>
-      <c r="B48" s="10"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
+      <c r="A48" s="4"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
     </row>
     <row r="49" spans="1:9" ht="15">
-      <c r="A49" s="10"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
+      <c r="A49" s="4"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
     </row>
     <row r="50" spans="1:9" ht="15">
-      <c r="A50" s="10"/>
-      <c r="B50" s="10"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="30"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
+      <c r="A50" s="4"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="21"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
     </row>
     <row r="51" spans="1:9" ht="15">
-      <c r="A51" s="10"/>
-      <c r="B51" s="10"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="30"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
+      <c r="A51" s="4"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
     </row>
     <row r="52" spans="1:9" ht="15">
-      <c r="A52" s="10"/>
-      <c r="B52" s="10"/>
-      <c r="C52" s="11"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="11"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
-      <c r="I52" s="10"/>
+      <c r="A52" s="4"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
     </row>
     <row r="53" spans="1:9" ht="15">
-      <c r="A53" s="10"/>
-      <c r="B53" s="10"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="30"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
+      <c r="A53" s="4"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
     </row>
     <row r="54" spans="1:9" ht="15">
-      <c r="A54" s="10"/>
-      <c r="B54" s="10"/>
-      <c r="C54" s="11"/>
-      <c r="D54" s="30"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
+      <c r="A54" s="4"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="21"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
     </row>
     <row r="55" spans="1:9" ht="15">
-      <c r="A55" s="10"/>
-      <c r="B55" s="10"/>
-      <c r="C55" s="11"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="11"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="10"/>
-      <c r="H55" s="10"/>
-      <c r="I55" s="10"/>
+      <c r="A55" s="4"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
     </row>
     <row r="56" spans="1:9" ht="15">
-      <c r="A56" s="10"/>
-      <c r="B56" s="10"/>
-      <c r="C56" s="11"/>
-      <c r="D56" s="30"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="10"/>
-      <c r="H56" s="10"/>
-      <c r="I56" s="10"/>
+      <c r="A56" s="4"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
     </row>
     <row r="57" spans="1:9" ht="15">
-      <c r="A57" s="10"/>
-      <c r="B57" s="10"/>
-      <c r="C57" s="11"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="10"/>
-      <c r="H57" s="10"/>
-      <c r="I57" s="10"/>
+      <c r="A57" s="4"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="21"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
     </row>
     <row r="58" spans="1:9" ht="15">
-      <c r="A58" s="10"/>
-      <c r="B58" s="10"/>
-      <c r="C58" s="11"/>
+      <c r="A58" s="4"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="7"/>
       <c r="D58" s="6"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="10"/>
-      <c r="H58" s="10"/>
-      <c r="I58" s="10"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
     </row>
     <row r="59" spans="1:9" ht="15">
-      <c r="A59" s="10"/>
-      <c r="B59" s="10"/>
-      <c r="C59" s="11"/>
+      <c r="A59" s="4"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="7"/>
       <c r="D59" s="6"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="10"/>
-      <c r="H59" s="10"/>
-      <c r="I59" s="10"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
     </row>
     <row r="60" spans="1:9" ht="15">
-      <c r="A60" s="10"/>
-      <c r="B60" s="10"/>
-      <c r="C60" s="11"/>
+      <c r="A60" s="4"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="7"/>
       <c r="D60" s="6"/>
-      <c r="E60" s="11"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="10"/>
-      <c r="H60" s="10"/>
-      <c r="I60" s="10"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
     </row>
     <row r="61" spans="1:9" ht="15">
-      <c r="A61" s="10"/>
-      <c r="B61" s="10"/>
-      <c r="C61" s="11"/>
+      <c r="A61" s="4"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="7"/>
       <c r="D61" s="6"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="10"/>
-      <c r="H61" s="10"/>
-      <c r="I61" s="10"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
     </row>
     <row r="62" spans="1:9" ht="15">
-      <c r="A62" s="10"/>
-      <c r="B62" s="10"/>
-      <c r="C62" s="11"/>
+      <c r="A62" s="4"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="7"/>
       <c r="D62" s="6"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="10"/>
-      <c r="H62" s="10"/>
-      <c r="I62" s="10"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
     </row>
     <row r="63" spans="1:9" ht="15">
-      <c r="A63" s="10"/>
-      <c r="B63" s="10"/>
-      <c r="C63" s="11"/>
+      <c r="A63" s="4"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="7"/>
       <c r="D63" s="6"/>
-      <c r="E63" s="11"/>
-      <c r="F63" s="11"/>
-      <c r="G63" s="10"/>
-      <c r="H63" s="10"/>
-      <c r="I63" s="10"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
     </row>
     <row r="64" spans="1:9" ht="15">
-      <c r="A64" s="10"/>
-      <c r="B64" s="10"/>
-      <c r="C64" s="11"/>
+      <c r="A64" s="4"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="7"/>
       <c r="D64" s="6"/>
-      <c r="E64" s="11"/>
-      <c r="F64" s="11"/>
-      <c r="G64" s="10"/>
-      <c r="H64" s="10"/>
-      <c r="I64" s="10"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
     </row>
     <row r="65" spans="1:9" ht="15">
-      <c r="A65" s="10"/>
-      <c r="B65" s="10"/>
-      <c r="C65" s="11"/>
+      <c r="A65" s="4"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="7"/>
       <c r="D65" s="6"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="11"/>
-      <c r="G65" s="10"/>
-      <c r="H65" s="10"/>
-      <c r="I65" s="10"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="7"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
     </row>
     <row r="66" spans="1:9" ht="15">
-      <c r="A66" s="10"/>
-      <c r="B66" s="10"/>
-      <c r="C66" s="11"/>
+      <c r="A66" s="4"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="7"/>
       <c r="D66" s="6"/>
-      <c r="E66" s="11"/>
-      <c r="F66" s="11"/>
-      <c r="G66" s="10"/>
-      <c r="H66" s="10"/>
-      <c r="I66" s="10"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="7"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
     </row>
     <row r="67" spans="1:9" ht="15">
-      <c r="A67" s="10"/>
-      <c r="B67" s="10"/>
-      <c r="C67" s="11"/>
+      <c r="A67" s="4"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="7"/>
       <c r="D67" s="5"/>
-      <c r="E67" s="11"/>
-      <c r="F67" s="11"/>
-      <c r="G67" s="10"/>
-      <c r="H67" s="10"/>
-      <c r="I67" s="10"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
     </row>
     <row r="68" spans="1:9" ht="15">
-      <c r="A68" s="10"/>
-      <c r="B68" s="10"/>
-      <c r="C68" s="11"/>
+      <c r="A68" s="4"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="7"/>
       <c r="D68" s="6"/>
-      <c r="E68" s="11"/>
-      <c r="F68" s="11"/>
-      <c r="G68" s="10"/>
-      <c r="H68" s="10"/>
-      <c r="I68" s="10"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
     </row>
     <row r="69" spans="1:9" ht="15">
-      <c r="A69" s="10"/>
-      <c r="B69" s="10"/>
-      <c r="C69" s="11"/>
+      <c r="A69" s="4"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="7"/>
       <c r="D69" s="6"/>
-      <c r="E69" s="11"/>
-      <c r="F69" s="11"/>
-      <c r="G69" s="10"/>
-      <c r="H69" s="10"/>
-      <c r="I69" s="10"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="15">
-      <c r="A70" s="10"/>
-      <c r="B70" s="10"/>
-      <c r="C70" s="11"/>
+      <c r="A70" s="4"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="7"/>
       <c r="D70" s="6"/>
-      <c r="E70" s="11"/>
-      <c r="F70" s="11"/>
-      <c r="G70" s="10"/>
-      <c r="H70" s="10"/>
-      <c r="I70" s="10"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
     </row>
     <row r="71" spans="1:9" ht="15">
-      <c r="A71" s="10"/>
-      <c r="B71" s="10"/>
-      <c r="C71" s="11"/>
+      <c r="A71" s="4"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="7"/>
       <c r="D71" s="6"/>
-      <c r="E71" s="11"/>
-      <c r="F71" s="11"/>
-      <c r="G71" s="10"/>
-      <c r="H71" s="10"/>
-      <c r="I71" s="10"/>
+      <c r="E71" s="7"/>
+      <c r="F71" s="7"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
     </row>
     <row r="72" spans="1:9" ht="15">
-      <c r="A72" s="10"/>
-      <c r="B72" s="10"/>
-      <c r="C72" s="11"/>
+      <c r="A72" s="4"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="7"/>
       <c r="D72" s="6"/>
-      <c r="E72" s="11"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="10"/>
-      <c r="H72" s="10"/>
-      <c r="I72" s="10"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="7"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
     </row>
     <row r="73" spans="1:9" ht="15">
-      <c r="A73" s="10"/>
-      <c r="B73" s="10"/>
-      <c r="C73" s="11"/>
+      <c r="A73" s="4"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="7"/>
       <c r="D73" s="5"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="11"/>
-      <c r="G73" s="10"/>
-      <c r="H73" s="10"/>
-      <c r="I73" s="10"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="7"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+      <c r="I73" s="4"/>
     </row>
     <row r="74" spans="1:9" ht="15">
-      <c r="A74" s="10"/>
-      <c r="B74" s="10"/>
-      <c r="C74" s="11"/>
+      <c r="A74" s="4"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="7"/>
       <c r="D74" s="6"/>
-      <c r="E74" s="11"/>
-      <c r="F74" s="11"/>
-      <c r="G74" s="10"/>
-      <c r="H74" s="10"/>
-      <c r="I74" s="10"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
     </row>
     <row r="75" spans="1:9" ht="15">
-      <c r="A75" s="10"/>
-      <c r="B75" s="10"/>
-      <c r="C75" s="11"/>
+      <c r="A75" s="4"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="7"/>
       <c r="D75" s="6"/>
-      <c r="E75" s="11"/>
-      <c r="F75" s="11"/>
-      <c r="G75" s="10"/>
-      <c r="H75" s="10"/>
-      <c r="I75" s="10"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="7"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
     </row>
     <row r="76" spans="1:9" ht="15">
-      <c r="A76" s="10"/>
-      <c r="B76" s="10"/>
-      <c r="C76" s="11"/>
+      <c r="A76" s="4"/>
+      <c r="B76" s="4"/>
+      <c r="C76" s="7"/>
       <c r="D76" s="6"/>
-      <c r="E76" s="11"/>
-      <c r="F76" s="11"/>
-      <c r="G76" s="10"/>
-      <c r="H76" s="10"/>
-      <c r="I76" s="10"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="7"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
     </row>
     <row r="77" spans="1:9" ht="15">
-      <c r="A77" s="10"/>
-      <c r="B77" s="10"/>
-      <c r="C77" s="11"/>
+      <c r="A77" s="4"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="7"/>
       <c r="D77" s="6"/>
-      <c r="E77" s="11"/>
-      <c r="F77" s="11"/>
-      <c r="G77" s="10"/>
-      <c r="H77" s="10"/>
-      <c r="I77" s="10"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="7"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
     </row>
     <row r="78" spans="1:9" ht="15">
-      <c r="A78" s="10"/>
-      <c r="B78" s="10"/>
-      <c r="C78" s="11"/>
+      <c r="A78" s="4"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="7"/>
       <c r="D78" s="6"/>
-      <c r="E78" s="11"/>
-      <c r="F78" s="11"/>
-      <c r="G78" s="10"/>
-      <c r="H78" s="10"/>
-      <c r="I78" s="10"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="7"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
     </row>
     <row r="79" spans="1:9" ht="15">
-      <c r="A79" s="10"/>
-      <c r="B79" s="10"/>
-      <c r="C79" s="11"/>
+      <c r="A79" s="4"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="7"/>
       <c r="D79" s="6"/>
-      <c r="E79" s="11"/>
-      <c r="F79" s="11"/>
-      <c r="G79" s="10"/>
-      <c r="H79" s="10"/>
-      <c r="I79" s="10"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="7"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
     </row>
     <row r="80" spans="1:9" ht="15">
-      <c r="A80" s="10"/>
-      <c r="B80" s="10"/>
-      <c r="C80" s="11"/>
+      <c r="A80" s="4"/>
+      <c r="B80" s="4"/>
+      <c r="C80" s="7"/>
       <c r="D80" s="6"/>
-      <c r="E80" s="11"/>
-      <c r="F80" s="11"/>
-      <c r="G80" s="10"/>
-      <c r="H80" s="10"/>
-      <c r="I80" s="10"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="7"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+      <c r="I80" s="4"/>
     </row>
     <row r="81" spans="1:9" ht="15">
-      <c r="A81" s="10"/>
-      <c r="B81" s="10"/>
-      <c r="C81" s="11"/>
+      <c r="A81" s="4"/>
+      <c r="B81" s="4"/>
+      <c r="C81" s="7"/>
       <c r="D81" s="6"/>
-      <c r="E81" s="11"/>
-      <c r="F81" s="11"/>
-      <c r="G81" s="10"/>
-      <c r="H81" s="10"/>
-      <c r="I81" s="10"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
     </row>
     <row r="82" spans="1:9" ht="15">
-      <c r="A82" s="10"/>
-      <c r="B82" s="10"/>
-      <c r="C82" s="11"/>
+      <c r="A82" s="4"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="7"/>
       <c r="D82" s="6"/>
-      <c r="E82" s="11"/>
-      <c r="F82" s="11"/>
-      <c r="G82" s="10"/>
-      <c r="H82" s="10"/>
-      <c r="I82" s="10"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="7"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4"/>
     </row>
     <row r="83" spans="1:9" ht="15">
-      <c r="A83" s="10"/>
-      <c r="B83" s="10"/>
-      <c r="C83" s="11"/>
+      <c r="A83" s="4"/>
+      <c r="B83" s="4"/>
+      <c r="C83" s="7"/>
       <c r="D83" s="6"/>
-      <c r="E83" s="11"/>
-      <c r="F83" s="11"/>
-      <c r="G83" s="10"/>
-      <c r="H83" s="10"/>
-      <c r="I83" s="10"/>
+      <c r="E83" s="7"/>
+      <c r="F83" s="7"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+      <c r="I83" s="4"/>
     </row>
     <row r="84" spans="1:9" ht="15">
-      <c r="A84" s="10"/>
-      <c r="B84" s="10"/>
-      <c r="C84" s="11"/>
+      <c r="A84" s="4"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="7"/>
       <c r="D84" s="5"/>
-      <c r="E84" s="11"/>
-      <c r="F84" s="11"/>
-      <c r="G84" s="10"/>
-      <c r="H84" s="10"/>
-      <c r="I84" s="10"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="7"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+      <c r="I84" s="4"/>
     </row>
     <row r="85" spans="1:9" ht="15">
-      <c r="A85" s="10"/>
-      <c r="B85" s="10"/>
-      <c r="C85" s="11"/>
+      <c r="A85" s="4"/>
+      <c r="B85" s="4"/>
+      <c r="C85" s="7"/>
       <c r="D85" s="6"/>
-      <c r="E85" s="11"/>
-      <c r="F85" s="11"/>
-      <c r="G85" s="10"/>
-      <c r="H85" s="10"/>
-      <c r="I85" s="10"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="7"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
+      <c r="I85" s="4"/>
     </row>
     <row r="86" spans="1:9" ht="15">
-      <c r="A86" s="10"/>
-      <c r="B86" s="10"/>
-      <c r="C86" s="11"/>
+      <c r="A86" s="4"/>
+      <c r="B86" s="4"/>
+      <c r="C86" s="7"/>
       <c r="D86" s="6"/>
-      <c r="E86" s="11"/>
-      <c r="F86" s="11"/>
-      <c r="G86" s="10"/>
-      <c r="H86" s="10"/>
-      <c r="I86" s="10"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="7"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+      <c r="I86" s="4"/>
     </row>
     <row r="87" spans="1:9" ht="15">
-      <c r="A87" s="10"/>
-      <c r="B87" s="10"/>
-      <c r="C87" s="11"/>
+      <c r="A87" s="4"/>
+      <c r="B87" s="4"/>
+      <c r="C87" s="7"/>
       <c r="D87" s="6"/>
-      <c r="E87" s="11"/>
-      <c r="F87" s="11"/>
-      <c r="G87" s="10"/>
-      <c r="H87" s="10"/>
-      <c r="I87" s="10"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="7"/>
+      <c r="G87" s="4"/>
+      <c r="H87" s="4"/>
+      <c r="I87" s="4"/>
     </row>
     <row r="88" spans="1:9" ht="15">
-      <c r="A88" s="10"/>
-      <c r="B88" s="10"/>
-      <c r="C88" s="11"/>
+      <c r="A88" s="4"/>
+      <c r="B88" s="4"/>
+      <c r="C88" s="7"/>
       <c r="D88" s="6"/>
-      <c r="E88" s="11"/>
-      <c r="F88" s="11"/>
-      <c r="G88" s="10"/>
-      <c r="H88" s="10"/>
-      <c r="I88" s="10"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="7"/>
+      <c r="G88" s="4"/>
+      <c r="H88" s="4"/>
+      <c r="I88" s="4"/>
     </row>
     <row r="89" spans="1:9" ht="15">
-      <c r="A89" s="10"/>
-      <c r="B89" s="10"/>
-      <c r="C89" s="11"/>
+      <c r="A89" s="4"/>
+      <c r="B89" s="4"/>
+      <c r="C89" s="7"/>
       <c r="D89" s="6"/>
-      <c r="E89" s="11"/>
-      <c r="F89" s="11"/>
-      <c r="G89" s="10"/>
-      <c r="H89" s="10"/>
-      <c r="I89" s="10"/>
+      <c r="E89" s="7"/>
+      <c r="F89" s="7"/>
+      <c r="G89" s="4"/>
+      <c r="H89" s="4"/>
+      <c r="I89" s="4"/>
     </row>
     <row r="90" spans="1:9" ht="15">
-      <c r="A90" s="10"/>
-      <c r="B90" s="10"/>
-      <c r="C90" s="11"/>
+      <c r="A90" s="4"/>
+      <c r="B90" s="4"/>
+      <c r="C90" s="7"/>
       <c r="D90" s="6"/>
-      <c r="E90" s="11"/>
-      <c r="F90" s="11"/>
-      <c r="G90" s="10"/>
-      <c r="H90" s="10"/>
-      <c r="I90" s="10"/>
+      <c r="E90" s="7"/>
+      <c r="F90" s="7"/>
+      <c r="G90" s="4"/>
+      <c r="H90" s="4"/>
+      <c r="I90" s="4"/>
     </row>
     <row r="91" spans="1:9" ht="15">
-      <c r="A91" s="10"/>
-      <c r="B91" s="10"/>
-      <c r="C91" s="11"/>
+      <c r="A91" s="4"/>
+      <c r="B91" s="4"/>
+      <c r="C91" s="7"/>
       <c r="D91" s="6"/>
-      <c r="E91" s="11"/>
-      <c r="F91" s="11"/>
-      <c r="G91" s="10"/>
-      <c r="H91" s="10"/>
-      <c r="I91" s="10"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="7"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4"/>
+      <c r="I91" s="4"/>
     </row>
     <row r="92" spans="1:9" ht="15">
-      <c r="A92" s="10"/>
-      <c r="B92" s="10"/>
-      <c r="C92" s="11"/>
+      <c r="A92" s="4"/>
+      <c r="B92" s="4"/>
+      <c r="C92" s="7"/>
       <c r="D92" s="6"/>
-      <c r="E92" s="11"/>
-      <c r="F92" s="11"/>
-      <c r="G92" s="10"/>
-      <c r="H92" s="10"/>
-      <c r="I92" s="10"/>
+      <c r="E92" s="7"/>
+      <c r="F92" s="7"/>
+      <c r="G92" s="4"/>
+      <c r="H92" s="4"/>
+      <c r="I92" s="4"/>
     </row>
     <row r="93" spans="1:9" ht="15">
-      <c r="A93" s="10"/>
-      <c r="B93" s="10"/>
-      <c r="C93" s="11"/>
+      <c r="A93" s="4"/>
+      <c r="B93" s="4"/>
+      <c r="C93" s="7"/>
       <c r="D93" s="6"/>
-      <c r="E93" s="11"/>
-      <c r="F93" s="11"/>
-      <c r="G93" s="10"/>
-      <c r="H93" s="10"/>
-      <c r="I93" s="10"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="7"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
+      <c r="I93" s="4"/>
     </row>
     <row r="94" spans="1:9" ht="15">
-      <c r="A94" s="10"/>
-      <c r="B94" s="10"/>
-      <c r="C94" s="11"/>
+      <c r="A94" s="4"/>
+      <c r="B94" s="4"/>
+      <c r="C94" s="7"/>
       <c r="D94" s="6"/>
-      <c r="E94" s="11"/>
-      <c r="F94" s="11"/>
-      <c r="G94" s="10"/>
-      <c r="H94" s="10"/>
-      <c r="I94" s="10"/>
+      <c r="E94" s="7"/>
+      <c r="F94" s="7"/>
+      <c r="G94" s="4"/>
+      <c r="H94" s="4"/>
+      <c r="I94" s="4"/>
     </row>
     <row r="95" spans="1:9" ht="15">
-      <c r="A95" s="10"/>
-      <c r="B95" s="10"/>
-      <c r="C95" s="11"/>
+      <c r="A95" s="4"/>
+      <c r="B95" s="4"/>
+      <c r="C95" s="7"/>
       <c r="D95" s="5"/>
-      <c r="E95" s="11"/>
-      <c r="F95" s="11"/>
-      <c r="G95" s="10"/>
-      <c r="H95" s="10"/>
-      <c r="I95" s="10"/>
+      <c r="E95" s="7"/>
+      <c r="F95" s="7"/>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4"/>
+      <c r="I95" s="4"/>
     </row>
     <row r="96" spans="1:9" ht="15">
-      <c r="A96" s="10"/>
-      <c r="B96" s="10"/>
-      <c r="C96" s="11"/>
+      <c r="A96" s="4"/>
+      <c r="B96" s="4"/>
+      <c r="C96" s="7"/>
       <c r="D96" s="6"/>
-      <c r="E96" s="11"/>
-      <c r="F96" s="11"/>
-      <c r="G96" s="10"/>
-      <c r="H96" s="10"/>
-      <c r="I96" s="10"/>
+      <c r="E96" s="7"/>
+      <c r="F96" s="7"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4"/>
     </row>
     <row r="97" spans="1:9" ht="15">
-      <c r="A97" s="10"/>
-      <c r="B97" s="10"/>
-      <c r="C97" s="11"/>
+      <c r="A97" s="4"/>
+      <c r="B97" s="4"/>
+      <c r="C97" s="7"/>
       <c r="D97" s="6"/>
-      <c r="E97" s="11"/>
-      <c r="F97" s="11"/>
-      <c r="G97" s="10"/>
-      <c r="H97" s="10"/>
-      <c r="I97" s="10"/>
+      <c r="E97" s="7"/>
+      <c r="F97" s="7"/>
+      <c r="G97" s="4"/>
+      <c r="H97" s="4"/>
+      <c r="I97" s="4"/>
     </row>
     <row r="98" spans="1:9" ht="15">
-      <c r="A98" s="10"/>
-      <c r="B98" s="10"/>
-      <c r="C98" s="11"/>
+      <c r="A98" s="4"/>
+      <c r="B98" s="4"/>
+      <c r="C98" s="7"/>
       <c r="D98" s="6"/>
-      <c r="E98" s="11"/>
-      <c r="F98" s="11"/>
-      <c r="G98" s="10"/>
-      <c r="H98" s="10"/>
-      <c r="I98" s="10"/>
+      <c r="E98" s="7"/>
+      <c r="F98" s="7"/>
+      <c r="G98" s="4"/>
+      <c r="H98" s="4"/>
+      <c r="I98" s="4"/>
     </row>
     <row r="99" spans="1:9" ht="15">
-      <c r="A99" s="10"/>
-      <c r="B99" s="10"/>
-      <c r="C99" s="11"/>
+      <c r="A99" s="4"/>
+      <c r="B99" s="4"/>
+      <c r="C99" s="7"/>
       <c r="D99" s="6"/>
-      <c r="E99" s="11"/>
-      <c r="F99" s="11"/>
-      <c r="G99" s="10"/>
-      <c r="H99" s="10"/>
-      <c r="I99" s="10"/>
+      <c r="E99" s="7"/>
+      <c r="F99" s="7"/>
+      <c r="G99" s="4"/>
+      <c r="H99" s="4"/>
+      <c r="I99" s="4"/>
     </row>
     <row r="100" spans="1:9" ht="15">
-      <c r="A100" s="10"/>
-      <c r="B100" s="10"/>
-      <c r="C100" s="11"/>
+      <c r="A100" s="4"/>
+      <c r="B100" s="4"/>
+      <c r="C100" s="7"/>
       <c r="D100" s="6"/>
-      <c r="E100" s="11"/>
-      <c r="F100" s="11"/>
-      <c r="G100" s="10"/>
-      <c r="H100" s="10"/>
-      <c r="I100" s="10"/>
+      <c r="E100" s="7"/>
+      <c r="F100" s="7"/>
+      <c r="G100" s="4"/>
+      <c r="H100" s="4"/>
+      <c r="I100" s="4"/>
     </row>
     <row r="101" spans="1:9" ht="15">
-      <c r="A101" s="10"/>
-      <c r="B101" s="10"/>
-      <c r="C101" s="11"/>
+      <c r="A101" s="4"/>
+      <c r="B101" s="4"/>
+      <c r="C101" s="7"/>
       <c r="D101" s="6"/>
-      <c r="E101" s="11"/>
-      <c r="F101" s="11"/>
-      <c r="G101" s="10"/>
-      <c r="H101" s="10"/>
-      <c r="I101" s="10"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="7"/>
+      <c r="G101" s="4"/>
+      <c r="H101" s="4"/>
+      <c r="I101" s="4"/>
     </row>
     <row r="102" spans="1:9" ht="15">
-      <c r="A102" s="10"/>
-      <c r="B102" s="10"/>
-      <c r="C102" s="11"/>
+      <c r="A102" s="4"/>
+      <c r="B102" s="4"/>
+      <c r="C102" s="7"/>
       <c r="D102" s="6"/>
-      <c r="E102" s="11"/>
-      <c r="F102" s="11"/>
-      <c r="G102" s="10"/>
-      <c r="H102" s="10"/>
-      <c r="I102" s="10"/>
+      <c r="E102" s="7"/>
+      <c r="F102" s="7"/>
+      <c r="G102" s="4"/>
+      <c r="H102" s="4"/>
+      <c r="I102" s="4"/>
     </row>
     <row r="103" spans="1:9" ht="15">
-      <c r="A103" s="10"/>
-      <c r="B103" s="10"/>
-      <c r="C103" s="11"/>
+      <c r="A103" s="4"/>
+      <c r="B103" s="4"/>
+      <c r="C103" s="7"/>
       <c r="D103" s="6"/>
-      <c r="E103" s="11"/>
-      <c r="F103" s="11"/>
-      <c r="G103" s="10"/>
-      <c r="H103" s="10"/>
-      <c r="I103" s="10"/>
+      <c r="E103" s="7"/>
+      <c r="F103" s="7"/>
+      <c r="G103" s="4"/>
+      <c r="H103" s="4"/>
+      <c r="I103" s="4"/>
     </row>
     <row r="104" spans="1:9" ht="15">
-      <c r="A104" s="10"/>
-      <c r="B104" s="10"/>
-      <c r="C104" s="11"/>
+      <c r="A104" s="4"/>
+      <c r="B104" s="4"/>
+      <c r="C104" s="7"/>
       <c r="D104" s="6"/>
-      <c r="E104" s="11"/>
-      <c r="F104" s="11"/>
-      <c r="G104" s="10"/>
-      <c r="H104" s="10"/>
-      <c r="I104" s="10"/>
+      <c r="E104" s="7"/>
+      <c r="F104" s="7"/>
+      <c r="G104" s="4"/>
+      <c r="H104" s="4"/>
+      <c r="I104" s="4"/>
     </row>
     <row r="105" spans="1:9" ht="15">
-      <c r="A105" s="10"/>
-      <c r="B105" s="10"/>
-      <c r="C105" s="11"/>
+      <c r="A105" s="4"/>
+      <c r="B105" s="4"/>
+      <c r="C105" s="7"/>
       <c r="D105" s="6"/>
-      <c r="E105" s="11"/>
-      <c r="F105" s="11"/>
-      <c r="G105" s="10"/>
-      <c r="H105" s="10"/>
-      <c r="I105" s="10"/>
+      <c r="E105" s="7"/>
+      <c r="F105" s="7"/>
+      <c r="G105" s="4"/>
+      <c r="H105" s="4"/>
+      <c r="I105" s="4"/>
     </row>
     <row r="106" spans="1:9" ht="15">
-      <c r="A106" s="10"/>
-      <c r="B106" s="10"/>
-      <c r="C106" s="11"/>
+      <c r="A106" s="4"/>
+      <c r="B106" s="4"/>
+      <c r="C106" s="7"/>
       <c r="D106" s="5"/>
-      <c r="E106" s="11"/>
-      <c r="F106" s="11"/>
-      <c r="G106" s="10"/>
-      <c r="H106" s="10"/>
-      <c r="I106" s="10"/>
+      <c r="E106" s="7"/>
+      <c r="F106" s="7"/>
+      <c r="G106" s="4"/>
+      <c r="H106" s="4"/>
+      <c r="I106" s="4"/>
     </row>
     <row r="107" spans="1:9" ht="15">
-      <c r="A107" s="10"/>
-      <c r="B107" s="10"/>
-      <c r="C107" s="11"/>
+      <c r="A107" s="4"/>
+      <c r="B107" s="4"/>
+      <c r="C107" s="7"/>
       <c r="D107" s="6"/>
-      <c r="E107" s="11"/>
-      <c r="F107" s="11"/>
-      <c r="G107" s="10"/>
-      <c r="H107" s="10"/>
-      <c r="I107" s="10"/>
+      <c r="E107" s="7"/>
+      <c r="F107" s="7"/>
+      <c r="G107" s="4"/>
+      <c r="H107" s="4"/>
+      <c r="I107" s="4"/>
     </row>
     <row r="108" spans="1:9" ht="15">
-      <c r="A108" s="10"/>
-      <c r="B108" s="10"/>
-      <c r="C108" s="11"/>
+      <c r="A108" s="4"/>
+      <c r="B108" s="4"/>
+      <c r="C108" s="7"/>
       <c r="D108" s="6"/>
-      <c r="E108" s="11"/>
-      <c r="F108" s="11"/>
-      <c r="G108" s="10"/>
-      <c r="H108" s="10"/>
-      <c r="I108" s="10"/>
+      <c r="E108" s="7"/>
+      <c r="F108" s="7"/>
+      <c r="G108" s="4"/>
+      <c r="H108" s="4"/>
+      <c r="I108" s="4"/>
     </row>
     <row r="109" spans="1:9" ht="15">
-      <c r="A109" s="10"/>
-      <c r="B109" s="10"/>
-      <c r="C109" s="11"/>
+      <c r="A109" s="4"/>
+      <c r="B109" s="4"/>
+      <c r="C109" s="7"/>
       <c r="D109" s="6"/>
-      <c r="E109" s="11"/>
-      <c r="F109" s="11"/>
-      <c r="G109" s="10"/>
-      <c r="H109" s="10"/>
-      <c r="I109" s="10"/>
+      <c r="E109" s="7"/>
+      <c r="F109" s="7"/>
+      <c r="G109" s="4"/>
+      <c r="H109" s="4"/>
+      <c r="I109" s="4"/>
     </row>
     <row r="110" spans="1:9" ht="15">
-      <c r="A110" s="10"/>
-      <c r="B110" s="10"/>
-      <c r="C110" s="11"/>
+      <c r="A110" s="4"/>
+      <c r="B110" s="4"/>
+      <c r="C110" s="7"/>
       <c r="D110" s="6"/>
-      <c r="E110" s="11"/>
-      <c r="F110" s="11"/>
-      <c r="G110" s="10"/>
-      <c r="H110" s="10"/>
-      <c r="I110" s="10"/>
+      <c r="E110" s="7"/>
+      <c r="F110" s="7"/>
+      <c r="G110" s="4"/>
+      <c r="H110" s="4"/>
+      <c r="I110" s="4"/>
     </row>
     <row r="111" spans="1:9" ht="15">
-      <c r="A111" s="10"/>
-      <c r="B111" s="10"/>
-      <c r="C111" s="11"/>
+      <c r="A111" s="4"/>
+      <c r="B111" s="4"/>
+      <c r="C111" s="7"/>
       <c r="D111" s="6"/>
-      <c r="E111" s="11"/>
-      <c r="F111" s="11"/>
-      <c r="G111" s="10"/>
-      <c r="H111" s="10"/>
-      <c r="I111" s="10"/>
+      <c r="E111" s="7"/>
+      <c r="F111" s="7"/>
+      <c r="G111" s="4"/>
+      <c r="H111" s="4"/>
+      <c r="I111" s="4"/>
     </row>
     <row r="112" spans="1:9" ht="15">
-      <c r="A112" s="10"/>
-      <c r="B112" s="10"/>
-      <c r="C112" s="11"/>
+      <c r="A112" s="4"/>
+      <c r="B112" s="4"/>
+      <c r="C112" s="7"/>
       <c r="D112" s="6"/>
-      <c r="E112" s="11"/>
-      <c r="F112" s="11"/>
-      <c r="G112" s="10"/>
-      <c r="H112" s="10"/>
-      <c r="I112" s="10"/>
+      <c r="E112" s="7"/>
+      <c r="F112" s="7"/>
+      <c r="G112" s="4"/>
+      <c r="H112" s="4"/>
+      <c r="I112" s="4"/>
     </row>
     <row r="113" spans="1:9" ht="15">
-      <c r="A113" s="10"/>
-      <c r="B113" s="10"/>
-      <c r="C113" s="11"/>
+      <c r="A113" s="4"/>
+      <c r="B113" s="4"/>
+      <c r="C113" s="7"/>
       <c r="D113" s="6"/>
-      <c r="E113" s="11"/>
-      <c r="F113" s="11"/>
-      <c r="G113" s="10"/>
-      <c r="H113" s="10"/>
-      <c r="I113" s="10"/>
+      <c r="E113" s="7"/>
+      <c r="F113" s="7"/>
+      <c r="G113" s="4"/>
+      <c r="H113" s="4"/>
+      <c r="I113" s="4"/>
     </row>
     <row r="114" spans="1:9" ht="15">
-      <c r="A114" s="10"/>
-      <c r="B114" s="10"/>
-      <c r="C114" s="11"/>
+      <c r="A114" s="4"/>
+      <c r="B114" s="4"/>
+      <c r="C114" s="7"/>
       <c r="D114" s="6"/>
-      <c r="E114" s="11"/>
-      <c r="F114" s="11"/>
-      <c r="G114" s="10"/>
-      <c r="H114" s="10"/>
-      <c r="I114" s="10"/>
+      <c r="E114" s="7"/>
+      <c r="F114" s="7"/>
+      <c r="G114" s="4"/>
+      <c r="H114" s="4"/>
+      <c r="I114" s="4"/>
     </row>
     <row r="115" spans="1:9" ht="15">
-      <c r="A115" s="10"/>
-      <c r="B115" s="10"/>
-      <c r="C115" s="11"/>
+      <c r="A115" s="4"/>
+      <c r="B115" s="4"/>
+      <c r="C115" s="7"/>
       <c r="D115" s="6"/>
-      <c r="E115" s="11"/>
-      <c r="F115" s="11"/>
-      <c r="G115" s="10"/>
-      <c r="H115" s="10"/>
-      <c r="I115" s="10"/>
+      <c r="E115" s="7"/>
+      <c r="F115" s="7"/>
+      <c r="G115" s="4"/>
+      <c r="H115" s="4"/>
+      <c r="I115" s="4"/>
     </row>
     <row r="116" spans="1:9" ht="15">
-      <c r="A116" s="10"/>
-      <c r="B116" s="10"/>
-      <c r="C116" s="11"/>
+      <c r="A116" s="4"/>
+      <c r="B116" s="4"/>
+      <c r="C116" s="7"/>
       <c r="D116" s="6"/>
-      <c r="E116" s="11"/>
-      <c r="F116" s="11"/>
-      <c r="G116" s="10"/>
-      <c r="H116" s="10"/>
-      <c r="I116" s="10"/>
+      <c r="E116" s="7"/>
+      <c r="F116" s="7"/>
+      <c r="G116" s="4"/>
+      <c r="H116" s="4"/>
+      <c r="I116" s="4"/>
     </row>
     <row r="117" spans="1:9" ht="15">
-      <c r="A117" s="10"/>
-      <c r="B117" s="10"/>
-      <c r="C117" s="11"/>
+      <c r="A117" s="4"/>
+      <c r="B117" s="4"/>
+      <c r="C117" s="7"/>
       <c r="D117" s="5"/>
-      <c r="E117" s="11"/>
-      <c r="F117" s="11"/>
-      <c r="G117" s="10"/>
-      <c r="H117" s="10"/>
-      <c r="I117" s="10"/>
+      <c r="E117" s="7"/>
+      <c r="F117" s="7"/>
+      <c r="G117" s="4"/>
+      <c r="H117" s="4"/>
+      <c r="I117" s="4"/>
     </row>
     <row r="118" spans="1:9" ht="15">
-      <c r="A118" s="10"/>
-      <c r="B118" s="10"/>
-      <c r="C118" s="11"/>
+      <c r="A118" s="4"/>
+      <c r="B118" s="4"/>
+      <c r="C118" s="7"/>
       <c r="D118" s="6"/>
-      <c r="E118" s="11"/>
-      <c r="F118" s="11"/>
-      <c r="G118" s="10"/>
-      <c r="H118" s="10"/>
-      <c r="I118" s="10"/>
+      <c r="E118" s="7"/>
+      <c r="F118" s="7"/>
+      <c r="G118" s="4"/>
+      <c r="H118" s="4"/>
+      <c r="I118" s="4"/>
     </row>
     <row r="119" spans="1:9" ht="15">
-      <c r="A119" s="10"/>
-      <c r="B119" s="10"/>
-      <c r="C119" s="11"/>
+      <c r="A119" s="4"/>
+      <c r="B119" s="4"/>
+      <c r="C119" s="7"/>
       <c r="D119" s="6"/>
-      <c r="E119" s="11"/>
-      <c r="F119" s="11"/>
-      <c r="G119" s="10"/>
-      <c r="H119" s="10"/>
-      <c r="I119" s="10"/>
+      <c r="E119" s="7"/>
+      <c r="F119" s="7"/>
+      <c r="G119" s="4"/>
+      <c r="H119" s="4"/>
+      <c r="I119" s="4"/>
     </row>
     <row r="120" spans="1:9" ht="15">
-      <c r="A120" s="10"/>
-      <c r="B120" s="10"/>
-      <c r="C120" s="11"/>
+      <c r="A120" s="4"/>
+      <c r="B120" s="4"/>
+      <c r="C120" s="7"/>
       <c r="D120" s="6"/>
-      <c r="E120" s="11"/>
-      <c r="F120" s="11"/>
-      <c r="G120" s="10"/>
-      <c r="H120" s="10"/>
-      <c r="I120" s="10"/>
+      <c r="E120" s="7"/>
+      <c r="F120" s="7"/>
+      <c r="G120" s="4"/>
+      <c r="H120" s="4"/>
+      <c r="I120" s="4"/>
     </row>
     <row r="121" spans="1:9" ht="15">
-      <c r="A121" s="10"/>
-      <c r="B121" s="10"/>
-      <c r="C121" s="11"/>
+      <c r="A121" s="4"/>
+      <c r="B121" s="4"/>
+      <c r="C121" s="7"/>
       <c r="D121" s="6"/>
-      <c r="E121" s="11"/>
-      <c r="F121" s="11"/>
-      <c r="G121" s="10"/>
-      <c r="H121" s="10"/>
-      <c r="I121" s="10"/>
+      <c r="E121" s="7"/>
+      <c r="F121" s="7"/>
+      <c r="G121" s="4"/>
+      <c r="H121" s="4"/>
+      <c r="I121" s="4"/>
     </row>
     <row r="122" spans="1:9" ht="15">
-      <c r="A122" s="10"/>
-      <c r="B122" s="10"/>
-      <c r="C122" s="11"/>
+      <c r="A122" s="4"/>
+      <c r="B122" s="4"/>
+      <c r="C122" s="7"/>
       <c r="D122" s="6"/>
-      <c r="E122" s="11"/>
-      <c r="F122" s="11"/>
-      <c r="G122" s="10"/>
-      <c r="H122" s="10"/>
-      <c r="I122" s="10"/>
+      <c r="E122" s="7"/>
+      <c r="F122" s="7"/>
+      <c r="G122" s="4"/>
+      <c r="H122" s="4"/>
+      <c r="I122" s="4"/>
     </row>
     <row r="123" spans="1:9" ht="15">
-      <c r="A123" s="10"/>
-      <c r="B123" s="10"/>
-      <c r="C123" s="11"/>
+      <c r="A123" s="4"/>
+      <c r="B123" s="4"/>
+      <c r="C123" s="7"/>
       <c r="D123" s="6"/>
-      <c r="E123" s="11"/>
-      <c r="F123" s="11"/>
-      <c r="G123" s="10"/>
-      <c r="H123" s="10"/>
-      <c r="I123" s="10"/>
+      <c r="E123" s="7"/>
+      <c r="F123" s="7"/>
+      <c r="G123" s="4"/>
+      <c r="H123" s="4"/>
+      <c r="I123" s="4"/>
     </row>
     <row r="124" spans="1:9" ht="15">
-      <c r="A124" s="10"/>
-      <c r="B124" s="10"/>
-      <c r="C124" s="11"/>
+      <c r="A124" s="4"/>
+      <c r="B124" s="4"/>
+      <c r="C124" s="7"/>
       <c r="D124" s="6"/>
-      <c r="E124" s="11"/>
-      <c r="F124" s="11"/>
-      <c r="G124" s="10"/>
-      <c r="H124" s="10"/>
-      <c r="I124" s="10"/>
+      <c r="E124" s="7"/>
+      <c r="F124" s="7"/>
+      <c r="G124" s="4"/>
+      <c r="H124" s="4"/>
+      <c r="I124" s="4"/>
     </row>
     <row r="125" spans="1:9" ht="15">
-      <c r="A125" s="10"/>
-      <c r="B125" s="10"/>
-      <c r="C125" s="11"/>
+      <c r="A125" s="4"/>
+      <c r="B125" s="4"/>
+      <c r="C125" s="7"/>
       <c r="D125" s="6"/>
-      <c r="E125" s="11"/>
-      <c r="F125" s="11"/>
-      <c r="G125" s="10"/>
-      <c r="H125" s="10"/>
-      <c r="I125" s="10"/>
+      <c r="E125" s="7"/>
+      <c r="F125" s="7"/>
+      <c r="G125" s="4"/>
+      <c r="H125" s="4"/>
+      <c r="I125" s="4"/>
     </row>
     <row r="126" spans="1:9" ht="15">
-      <c r="A126" s="10"/>
-      <c r="B126" s="10"/>
-      <c r="C126" s="11"/>
+      <c r="A126" s="4"/>
+      <c r="B126" s="4"/>
+      <c r="C126" s="7"/>
       <c r="D126" s="6"/>
-      <c r="E126" s="11"/>
-      <c r="F126" s="11"/>
-      <c r="G126" s="10"/>
-      <c r="H126" s="10"/>
-      <c r="I126" s="10"/>
+      <c r="E126" s="7"/>
+      <c r="F126" s="7"/>
+      <c r="G126" s="4"/>
+      <c r="H126" s="4"/>
+      <c r="I126" s="4"/>
     </row>
     <row r="127" spans="1:9" ht="15">
-      <c r="A127" s="10"/>
-      <c r="B127" s="10"/>
-      <c r="C127" s="11"/>
+      <c r="A127" s="4"/>
+      <c r="B127" s="4"/>
+      <c r="C127" s="7"/>
       <c r="D127" s="6"/>
-      <c r="E127" s="11"/>
-      <c r="F127" s="11"/>
-      <c r="G127" s="10"/>
-      <c r="H127" s="10"/>
-      <c r="I127" s="10"/>
+      <c r="E127" s="7"/>
+      <c r="F127" s="7"/>
+      <c r="G127" s="4"/>
+      <c r="H127" s="4"/>
+      <c r="I127" s="4"/>
     </row>
     <row r="128" spans="1:9" ht="15">
-      <c r="A128" s="10"/>
-      <c r="B128" s="10"/>
-      <c r="C128" s="11"/>
+      <c r="A128" s="4"/>
+      <c r="B128" s="4"/>
+      <c r="C128" s="7"/>
       <c r="D128" s="6"/>
-      <c r="E128" s="11"/>
-      <c r="F128" s="11"/>
-      <c r="G128" s="10"/>
-      <c r="H128" s="10"/>
-      <c r="I128" s="10"/>
+      <c r="E128" s="7"/>
+      <c r="F128" s="7"/>
+      <c r="G128" s="4"/>
+      <c r="H128" s="4"/>
+      <c r="I128" s="4"/>
     </row>
     <row r="129" spans="1:9" ht="15">
-      <c r="A129" s="10"/>
-      <c r="B129" s="10"/>
-      <c r="C129" s="11"/>
+      <c r="A129" s="4"/>
+      <c r="B129" s="4"/>
+      <c r="C129" s="7"/>
       <c r="D129" s="6"/>
-      <c r="E129" s="11"/>
-      <c r="F129" s="11"/>
-      <c r="G129" s="10"/>
-      <c r="H129" s="10"/>
-      <c r="I129" s="10"/>
+      <c r="E129" s="7"/>
+      <c r="F129" s="7"/>
+      <c r="G129" s="4"/>
+      <c r="H129" s="4"/>
+      <c r="I129" s="4"/>
     </row>
     <row r="130" spans="1:9" ht="15">
-      <c r="A130" s="10"/>
-      <c r="B130" s="10"/>
-      <c r="C130" s="11"/>
+      <c r="A130" s="4"/>
+      <c r="B130" s="4"/>
+      <c r="C130" s="7"/>
       <c r="D130" s="6"/>
-      <c r="E130" s="11"/>
-      <c r="F130" s="11"/>
-      <c r="G130" s="10"/>
-      <c r="H130" s="10"/>
-      <c r="I130" s="10"/>
+      <c r="E130" s="7"/>
+      <c r="F130" s="7"/>
+      <c r="G130" s="4"/>
+      <c r="H130" s="4"/>
+      <c r="I130" s="4"/>
     </row>
     <row r="131" spans="1:9" ht="15">
-      <c r="A131" s="10"/>
-      <c r="B131" s="10"/>
-      <c r="C131" s="11"/>
+      <c r="A131" s="4"/>
+      <c r="B131" s="4"/>
+      <c r="C131" s="7"/>
       <c r="D131" s="6"/>
-      <c r="E131" s="11"/>
-      <c r="F131" s="11"/>
-      <c r="G131" s="10"/>
-      <c r="H131" s="10"/>
-      <c r="I131" s="10"/>
+      <c r="E131" s="7"/>
+      <c r="F131" s="7"/>
+      <c r="G131" s="4"/>
+      <c r="H131" s="4"/>
+      <c r="I131" s="4"/>
     </row>
     <row r="132" spans="1:9" ht="15">
-      <c r="A132" s="10"/>
-      <c r="B132" s="10"/>
-      <c r="C132" s="11"/>
+      <c r="A132" s="4"/>
+      <c r="B132" s="4"/>
+      <c r="C132" s="7"/>
       <c r="D132" s="6"/>
-      <c r="E132" s="11"/>
-      <c r="F132" s="11"/>
-      <c r="G132" s="10"/>
-      <c r="H132" s="10"/>
-      <c r="I132" s="10"/>
+      <c r="E132" s="7"/>
+      <c r="F132" s="7"/>
+      <c r="G132" s="4"/>
+      <c r="H132" s="4"/>
+      <c r="I132" s="4"/>
     </row>
     <row r="133" spans="1:9" ht="15">
-      <c r="A133" s="10"/>
-      <c r="B133" s="10"/>
-      <c r="C133" s="11"/>
+      <c r="A133" s="4"/>
+      <c r="B133" s="4"/>
+      <c r="C133" s="7"/>
       <c r="D133" s="6"/>
-      <c r="E133" s="11"/>
-      <c r="F133" s="11"/>
-      <c r="G133" s="10"/>
-      <c r="H133" s="10"/>
-      <c r="I133" s="10"/>
+      <c r="E133" s="7"/>
+      <c r="F133" s="7"/>
+      <c r="G133" s="4"/>
+      <c r="H133" s="4"/>
+      <c r="I133" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="I17:I23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -12490,1515 +12787,6 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94A74049-1771-468B-813D-A487483CB510}">
-  <dimension ref="A1:I133"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="29.75" customWidth="1"/>
-    <col min="2" max="2" width="45.25" customWidth="1"/>
-    <col min="3" max="3" width="32.625" customWidth="1"/>
-    <col min="4" max="4" width="59.125" customWidth="1"/>
-    <col min="5" max="5" width="20" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="17.25" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="28.625" customWidth="1"/>
-    <col min="8" max="8" width="33.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="28"/>
-      <c r="I1" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="15" thickBot="1">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="12"/>
-    </row>
-    <row r="3" spans="1:9" ht="159.4" customHeight="1">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="17"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="14"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-    </row>
-    <row r="5" spans="1:9" ht="15">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-    </row>
-    <row r="6" spans="1:9" ht="15">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-    </row>
-    <row r="7" spans="1:9" ht="15">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-    </row>
-    <row r="8" spans="1:9" ht="15">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-    </row>
-    <row r="9" spans="1:9" ht="15">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-    </row>
-    <row r="10" spans="1:9" ht="15">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-    </row>
-    <row r="11" spans="1:9" ht="15">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-    </row>
-    <row r="12" spans="1:9" ht="15">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-    </row>
-    <row r="13" spans="1:9" ht="15">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-    </row>
-    <row r="14" spans="1:9" ht="15">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-    </row>
-    <row r="15" spans="1:9" ht="15">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-    </row>
-    <row r="16" spans="1:9" ht="15">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-    </row>
-    <row r="17" spans="1:9" ht="15">
-      <c r="A17" s="31"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-    </row>
-    <row r="18" spans="1:9" ht="15">
-      <c r="A18" s="31"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-    </row>
-    <row r="19" spans="1:9" ht="15">
-      <c r="A19" s="31"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-    </row>
-    <row r="20" spans="1:9" ht="15">
-      <c r="A20" s="31"/>
-      <c r="B20" s="31"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-    </row>
-    <row r="21" spans="1:9" ht="15">
-      <c r="A21" s="31"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-    </row>
-    <row r="22" spans="1:9" ht="15">
-      <c r="A22" s="31"/>
-      <c r="B22" s="31"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-    </row>
-    <row r="23" spans="1:9" ht="15">
-      <c r="A23" s="31"/>
-      <c r="B23" s="31"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-    </row>
-    <row r="24" spans="1:9" ht="15">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-    </row>
-    <row r="25" spans="1:9" ht="15">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-    </row>
-    <row r="26" spans="1:9" ht="15">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-    </row>
-    <row r="27" spans="1:9" ht="15">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-    </row>
-    <row r="28" spans="1:9" ht="15">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-    </row>
-    <row r="29" spans="1:9" ht="15">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-    </row>
-    <row r="30" spans="1:9" ht="15">
-      <c r="A30" s="4"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-    </row>
-    <row r="31" spans="1:9" ht="15">
-      <c r="A31" s="4"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="4"/>
-    </row>
-    <row r="32" spans="1:9" ht="15">
-      <c r="A32" s="4"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-    </row>
-    <row r="33" spans="1:9" ht="15">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-    </row>
-    <row r="34" spans="1:9" ht="15">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-    </row>
-    <row r="35" spans="1:9" ht="15">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-    </row>
-    <row r="36" spans="1:9" ht="15">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-    </row>
-    <row r="37" spans="1:9" ht="15">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-    </row>
-    <row r="38" spans="1:9" ht="15">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-    </row>
-    <row r="39" spans="1:9" ht="15">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-    </row>
-    <row r="40" spans="1:9" ht="15">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-    </row>
-    <row r="41" spans="1:9" ht="15">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-    </row>
-    <row r="42" spans="1:9" ht="15">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-    </row>
-    <row r="43" spans="1:9" ht="15">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-    </row>
-    <row r="44" spans="1:9" ht="15">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-    </row>
-    <row r="45" spans="1:9" ht="15">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-    </row>
-    <row r="46" spans="1:9" ht="15">
-      <c r="A46" s="4"/>
-      <c r="B46" s="4"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-    </row>
-    <row r="47" spans="1:9" ht="15">
-      <c r="A47" s="4"/>
-      <c r="B47" s="4"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="30"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-    </row>
-    <row r="48" spans="1:9" ht="15">
-      <c r="A48" s="4"/>
-      <c r="B48" s="4"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-    </row>
-    <row r="49" spans="1:9" ht="15">
-      <c r="A49" s="4"/>
-      <c r="B49" s="4"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-    </row>
-    <row r="50" spans="1:9" ht="15">
-      <c r="A50" s="4"/>
-      <c r="B50" s="4"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="30"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-    </row>
-    <row r="51" spans="1:9" ht="15">
-      <c r="A51" s="4"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="30"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-    </row>
-    <row r="52" spans="1:9" ht="15">
-      <c r="A52" s="4"/>
-      <c r="B52" s="4"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-    </row>
-    <row r="53" spans="1:9" ht="15">
-      <c r="A53" s="4"/>
-      <c r="B53" s="4"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="30"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-    </row>
-    <row r="54" spans="1:9" ht="15">
-      <c r="A54" s="4"/>
-      <c r="B54" s="4"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="30"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-    </row>
-    <row r="55" spans="1:9" ht="15">
-      <c r="A55" s="4"/>
-      <c r="B55" s="4"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
-    </row>
-    <row r="56" spans="1:9" ht="15">
-      <c r="A56" s="4"/>
-      <c r="B56" s="4"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="30"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-    </row>
-    <row r="57" spans="1:9" ht="15">
-      <c r="A57" s="4"/>
-      <c r="B57" s="4"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-    </row>
-    <row r="58" spans="1:9" ht="15">
-      <c r="A58" s="4"/>
-      <c r="B58" s="4"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
-    </row>
-    <row r="59" spans="1:9" ht="15">
-      <c r="A59" s="4"/>
-      <c r="B59" s="4"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="4"/>
-    </row>
-    <row r="60" spans="1:9" ht="15">
-      <c r="A60" s="4"/>
-      <c r="B60" s="4"/>
-      <c r="C60" s="7"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
-    </row>
-    <row r="61" spans="1:9" ht="15">
-      <c r="A61" s="4"/>
-      <c r="B61" s="4"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
-      <c r="I61" s="4"/>
-    </row>
-    <row r="62" spans="1:9" ht="15">
-      <c r="A62" s="4"/>
-      <c r="B62" s="4"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="6"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
-    </row>
-    <row r="63" spans="1:9" ht="15">
-      <c r="A63" s="4"/>
-      <c r="B63" s="4"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
-    </row>
-    <row r="64" spans="1:9" ht="15">
-      <c r="A64" s="4"/>
-      <c r="B64" s="4"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
-      <c r="I64" s="4"/>
-    </row>
-    <row r="65" spans="1:9" ht="15">
-      <c r="A65" s="4"/>
-      <c r="B65" s="4"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
-      <c r="G65" s="4"/>
-      <c r="H65" s="4"/>
-      <c r="I65" s="4"/>
-    </row>
-    <row r="66" spans="1:9" ht="15">
-      <c r="A66" s="4"/>
-      <c r="B66" s="4"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="4"/>
-      <c r="I66" s="4"/>
-    </row>
-    <row r="67" spans="1:9" ht="15">
-      <c r="A67" s="4"/>
-      <c r="B67" s="4"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4"/>
-      <c r="I67" s="4"/>
-    </row>
-    <row r="68" spans="1:9" ht="15">
-      <c r="A68" s="4"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="6"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
-    </row>
-    <row r="69" spans="1:9" ht="15">
-      <c r="A69" s="4"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="7"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="7"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
-    </row>
-    <row r="70" spans="1:9" ht="15">
-      <c r="A70" s="4"/>
-      <c r="B70" s="4"/>
-      <c r="C70" s="7"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="7"/>
-      <c r="G70" s="4"/>
-      <c r="H70" s="4"/>
-      <c r="I70" s="4"/>
-    </row>
-    <row r="71" spans="1:9" ht="15">
-      <c r="A71" s="4"/>
-      <c r="B71" s="4"/>
-      <c r="C71" s="7"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="7"/>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
-      <c r="I71" s="4"/>
-    </row>
-    <row r="72" spans="1:9" ht="15">
-      <c r="A72" s="4"/>
-      <c r="B72" s="4"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="6"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
-    </row>
-    <row r="73" spans="1:9" ht="15">
-      <c r="A73" s="4"/>
-      <c r="B73" s="4"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="5"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="7"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
-      <c r="I73" s="4"/>
-    </row>
-    <row r="74" spans="1:9" ht="15">
-      <c r="A74" s="4"/>
-      <c r="B74" s="4"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
-    </row>
-    <row r="75" spans="1:9" ht="15">
-      <c r="A75" s="4"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="6"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="7"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
-      <c r="I75" s="4"/>
-    </row>
-    <row r="76" spans="1:9" ht="15">
-      <c r="A76" s="4"/>
-      <c r="B76" s="4"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="6"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
-      <c r="I76" s="4"/>
-    </row>
-    <row r="77" spans="1:9" ht="15">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="6"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="7"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="4"/>
-    </row>
-    <row r="78" spans="1:9" ht="15">
-      <c r="A78" s="4"/>
-      <c r="B78" s="4"/>
-      <c r="C78" s="7"/>
-      <c r="D78" s="6"/>
-      <c r="E78" s="7"/>
-      <c r="F78" s="7"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
-      <c r="I78" s="4"/>
-    </row>
-    <row r="79" spans="1:9" ht="15">
-      <c r="A79" s="4"/>
-      <c r="B79" s="4"/>
-      <c r="C79" s="7"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="7"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-      <c r="I79" s="4"/>
-    </row>
-    <row r="80" spans="1:9" ht="15">
-      <c r="A80" s="4"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="7"/>
-      <c r="D80" s="6"/>
-      <c r="E80" s="7"/>
-      <c r="F80" s="7"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-      <c r="I80" s="4"/>
-    </row>
-    <row r="81" spans="1:9" ht="15">
-      <c r="A81" s="4"/>
-      <c r="B81" s="4"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="7"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4"/>
-      <c r="I81" s="4"/>
-    </row>
-    <row r="82" spans="1:9" ht="15">
-      <c r="A82" s="4"/>
-      <c r="B82" s="4"/>
-      <c r="C82" s="7"/>
-      <c r="D82" s="6"/>
-      <c r="E82" s="7"/>
-      <c r="F82" s="7"/>
-      <c r="G82" s="4"/>
-      <c r="H82" s="4"/>
-      <c r="I82" s="4"/>
-    </row>
-    <row r="83" spans="1:9" ht="15">
-      <c r="A83" s="4"/>
-      <c r="B83" s="4"/>
-      <c r="C83" s="7"/>
-      <c r="D83" s="6"/>
-      <c r="E83" s="7"/>
-      <c r="F83" s="7"/>
-      <c r="G83" s="4"/>
-      <c r="H83" s="4"/>
-      <c r="I83" s="4"/>
-    </row>
-    <row r="84" spans="1:9" ht="15">
-      <c r="A84" s="4"/>
-      <c r="B84" s="4"/>
-      <c r="C84" s="7"/>
-      <c r="D84" s="5"/>
-      <c r="E84" s="7"/>
-      <c r="F84" s="7"/>
-      <c r="G84" s="4"/>
-      <c r="H84" s="4"/>
-      <c r="I84" s="4"/>
-    </row>
-    <row r="85" spans="1:9" ht="15">
-      <c r="A85" s="4"/>
-      <c r="B85" s="4"/>
-      <c r="C85" s="7"/>
-      <c r="D85" s="6"/>
-      <c r="E85" s="7"/>
-      <c r="F85" s="7"/>
-      <c r="G85" s="4"/>
-      <c r="H85" s="4"/>
-      <c r="I85" s="4"/>
-    </row>
-    <row r="86" spans="1:9" ht="15">
-      <c r="A86" s="4"/>
-      <c r="B86" s="4"/>
-      <c r="C86" s="7"/>
-      <c r="D86" s="6"/>
-      <c r="E86" s="7"/>
-      <c r="F86" s="7"/>
-      <c r="G86" s="4"/>
-      <c r="H86" s="4"/>
-      <c r="I86" s="4"/>
-    </row>
-    <row r="87" spans="1:9" ht="15">
-      <c r="A87" s="4"/>
-      <c r="B87" s="4"/>
-      <c r="C87" s="7"/>
-      <c r="D87" s="6"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="7"/>
-      <c r="G87" s="4"/>
-      <c r="H87" s="4"/>
-      <c r="I87" s="4"/>
-    </row>
-    <row r="88" spans="1:9" ht="15">
-      <c r="A88" s="4"/>
-      <c r="B88" s="4"/>
-      <c r="C88" s="7"/>
-      <c r="D88" s="6"/>
-      <c r="E88" s="7"/>
-      <c r="F88" s="7"/>
-      <c r="G88" s="4"/>
-      <c r="H88" s="4"/>
-      <c r="I88" s="4"/>
-    </row>
-    <row r="89" spans="1:9" ht="15">
-      <c r="A89" s="4"/>
-      <c r="B89" s="4"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="7"/>
-      <c r="F89" s="7"/>
-      <c r="G89" s="4"/>
-      <c r="H89" s="4"/>
-      <c r="I89" s="4"/>
-    </row>
-    <row r="90" spans="1:9" ht="15">
-      <c r="A90" s="4"/>
-      <c r="B90" s="4"/>
-      <c r="C90" s="7"/>
-      <c r="D90" s="6"/>
-      <c r="E90" s="7"/>
-      <c r="F90" s="7"/>
-      <c r="G90" s="4"/>
-      <c r="H90" s="4"/>
-      <c r="I90" s="4"/>
-    </row>
-    <row r="91" spans="1:9" ht="15">
-      <c r="A91" s="4"/>
-      <c r="B91" s="4"/>
-      <c r="C91" s="7"/>
-      <c r="D91" s="6"/>
-      <c r="E91" s="7"/>
-      <c r="F91" s="7"/>
-      <c r="G91" s="4"/>
-      <c r="H91" s="4"/>
-      <c r="I91" s="4"/>
-    </row>
-    <row r="92" spans="1:9" ht="15">
-      <c r="A92" s="4"/>
-      <c r="B92" s="4"/>
-      <c r="C92" s="7"/>
-      <c r="D92" s="6"/>
-      <c r="E92" s="7"/>
-      <c r="F92" s="7"/>
-      <c r="G92" s="4"/>
-      <c r="H92" s="4"/>
-      <c r="I92" s="4"/>
-    </row>
-    <row r="93" spans="1:9" ht="15">
-      <c r="A93" s="4"/>
-      <c r="B93" s="4"/>
-      <c r="C93" s="7"/>
-      <c r="D93" s="6"/>
-      <c r="E93" s="7"/>
-      <c r="F93" s="7"/>
-      <c r="G93" s="4"/>
-      <c r="H93" s="4"/>
-      <c r="I93" s="4"/>
-    </row>
-    <row r="94" spans="1:9" ht="15">
-      <c r="A94" s="4"/>
-      <c r="B94" s="4"/>
-      <c r="C94" s="7"/>
-      <c r="D94" s="6"/>
-      <c r="E94" s="7"/>
-      <c r="F94" s="7"/>
-      <c r="G94" s="4"/>
-      <c r="H94" s="4"/>
-      <c r="I94" s="4"/>
-    </row>
-    <row r="95" spans="1:9" ht="15">
-      <c r="A95" s="4"/>
-      <c r="B95" s="4"/>
-      <c r="C95" s="7"/>
-      <c r="D95" s="5"/>
-      <c r="E95" s="7"/>
-      <c r="F95" s="7"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
-      <c r="I95" s="4"/>
-    </row>
-    <row r="96" spans="1:9" ht="15">
-      <c r="A96" s="4"/>
-      <c r="B96" s="4"/>
-      <c r="C96" s="7"/>
-      <c r="D96" s="6"/>
-      <c r="E96" s="7"/>
-      <c r="F96" s="7"/>
-      <c r="G96" s="4"/>
-      <c r="H96" s="4"/>
-      <c r="I96" s="4"/>
-    </row>
-    <row r="97" spans="1:9" ht="15">
-      <c r="A97" s="4"/>
-      <c r="B97" s="4"/>
-      <c r="C97" s="7"/>
-      <c r="D97" s="6"/>
-      <c r="E97" s="7"/>
-      <c r="F97" s="7"/>
-      <c r="G97" s="4"/>
-      <c r="H97" s="4"/>
-      <c r="I97" s="4"/>
-    </row>
-    <row r="98" spans="1:9" ht="15">
-      <c r="A98" s="4"/>
-      <c r="B98" s="4"/>
-      <c r="C98" s="7"/>
-      <c r="D98" s="6"/>
-      <c r="E98" s="7"/>
-      <c r="F98" s="7"/>
-      <c r="G98" s="4"/>
-      <c r="H98" s="4"/>
-      <c r="I98" s="4"/>
-    </row>
-    <row r="99" spans="1:9" ht="15">
-      <c r="A99" s="4"/>
-      <c r="B99" s="4"/>
-      <c r="C99" s="7"/>
-      <c r="D99" s="6"/>
-      <c r="E99" s="7"/>
-      <c r="F99" s="7"/>
-      <c r="G99" s="4"/>
-      <c r="H99" s="4"/>
-      <c r="I99" s="4"/>
-    </row>
-    <row r="100" spans="1:9" ht="15">
-      <c r="A100" s="4"/>
-      <c r="B100" s="4"/>
-      <c r="C100" s="7"/>
-      <c r="D100" s="6"/>
-      <c r="E100" s="7"/>
-      <c r="F100" s="7"/>
-      <c r="G100" s="4"/>
-      <c r="H100" s="4"/>
-      <c r="I100" s="4"/>
-    </row>
-    <row r="101" spans="1:9" ht="15">
-      <c r="A101" s="4"/>
-      <c r="B101" s="4"/>
-      <c r="C101" s="7"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="7"/>
-      <c r="F101" s="7"/>
-      <c r="G101" s="4"/>
-      <c r="H101" s="4"/>
-      <c r="I101" s="4"/>
-    </row>
-    <row r="102" spans="1:9" ht="15">
-      <c r="A102" s="4"/>
-      <c r="B102" s="4"/>
-      <c r="C102" s="7"/>
-      <c r="D102" s="6"/>
-      <c r="E102" s="7"/>
-      <c r="F102" s="7"/>
-      <c r="G102" s="4"/>
-      <c r="H102" s="4"/>
-      <c r="I102" s="4"/>
-    </row>
-    <row r="103" spans="1:9" ht="15">
-      <c r="A103" s="4"/>
-      <c r="B103" s="4"/>
-      <c r="C103" s="7"/>
-      <c r="D103" s="6"/>
-      <c r="E103" s="7"/>
-      <c r="F103" s="7"/>
-      <c r="G103" s="4"/>
-      <c r="H103" s="4"/>
-      <c r="I103" s="4"/>
-    </row>
-    <row r="104" spans="1:9" ht="15">
-      <c r="A104" s="4"/>
-      <c r="B104" s="4"/>
-      <c r="C104" s="7"/>
-      <c r="D104" s="6"/>
-      <c r="E104" s="7"/>
-      <c r="F104" s="7"/>
-      <c r="G104" s="4"/>
-      <c r="H104" s="4"/>
-      <c r="I104" s="4"/>
-    </row>
-    <row r="105" spans="1:9" ht="15">
-      <c r="A105" s="4"/>
-      <c r="B105" s="4"/>
-      <c r="C105" s="7"/>
-      <c r="D105" s="6"/>
-      <c r="E105" s="7"/>
-      <c r="F105" s="7"/>
-      <c r="G105" s="4"/>
-      <c r="H105" s="4"/>
-      <c r="I105" s="4"/>
-    </row>
-    <row r="106" spans="1:9" ht="15">
-      <c r="A106" s="4"/>
-      <c r="B106" s="4"/>
-      <c r="C106" s="7"/>
-      <c r="D106" s="5"/>
-      <c r="E106" s="7"/>
-      <c r="F106" s="7"/>
-      <c r="G106" s="4"/>
-      <c r="H106" s="4"/>
-      <c r="I106" s="4"/>
-    </row>
-    <row r="107" spans="1:9" ht="15">
-      <c r="A107" s="4"/>
-      <c r="B107" s="4"/>
-      <c r="C107" s="7"/>
-      <c r="D107" s="6"/>
-      <c r="E107" s="7"/>
-      <c r="F107" s="7"/>
-      <c r="G107" s="4"/>
-      <c r="H107" s="4"/>
-      <c r="I107" s="4"/>
-    </row>
-    <row r="108" spans="1:9" ht="15">
-      <c r="A108" s="4"/>
-      <c r="B108" s="4"/>
-      <c r="C108" s="7"/>
-      <c r="D108" s="6"/>
-      <c r="E108" s="7"/>
-      <c r="F108" s="7"/>
-      <c r="G108" s="4"/>
-      <c r="H108" s="4"/>
-      <c r="I108" s="4"/>
-    </row>
-    <row r="109" spans="1:9" ht="15">
-      <c r="A109" s="4"/>
-      <c r="B109" s="4"/>
-      <c r="C109" s="7"/>
-      <c r="D109" s="6"/>
-      <c r="E109" s="7"/>
-      <c r="F109" s="7"/>
-      <c r="G109" s="4"/>
-      <c r="H109" s="4"/>
-      <c r="I109" s="4"/>
-    </row>
-    <row r="110" spans="1:9" ht="15">
-      <c r="A110" s="4"/>
-      <c r="B110" s="4"/>
-      <c r="C110" s="7"/>
-      <c r="D110" s="6"/>
-      <c r="E110" s="7"/>
-      <c r="F110" s="7"/>
-      <c r="G110" s="4"/>
-      <c r="H110" s="4"/>
-      <c r="I110" s="4"/>
-    </row>
-    <row r="111" spans="1:9" ht="15">
-      <c r="A111" s="4"/>
-      <c r="B111" s="4"/>
-      <c r="C111" s="7"/>
-      <c r="D111" s="6"/>
-      <c r="E111" s="7"/>
-      <c r="F111" s="7"/>
-      <c r="G111" s="4"/>
-      <c r="H111" s="4"/>
-      <c r="I111" s="4"/>
-    </row>
-    <row r="112" spans="1:9" ht="15">
-      <c r="A112" s="4"/>
-      <c r="B112" s="4"/>
-      <c r="C112" s="7"/>
-      <c r="D112" s="6"/>
-      <c r="E112" s="7"/>
-      <c r="F112" s="7"/>
-      <c r="G112" s="4"/>
-      <c r="H112" s="4"/>
-      <c r="I112" s="4"/>
-    </row>
-    <row r="113" spans="1:9" ht="15">
-      <c r="A113" s="4"/>
-      <c r="B113" s="4"/>
-      <c r="C113" s="7"/>
-      <c r="D113" s="6"/>
-      <c r="E113" s="7"/>
-      <c r="F113" s="7"/>
-      <c r="G113" s="4"/>
-      <c r="H113" s="4"/>
-      <c r="I113" s="4"/>
-    </row>
-    <row r="114" spans="1:9" ht="15">
-      <c r="A114" s="4"/>
-      <c r="B114" s="4"/>
-      <c r="C114" s="7"/>
-      <c r="D114" s="6"/>
-      <c r="E114" s="7"/>
-      <c r="F114" s="7"/>
-      <c r="G114" s="4"/>
-      <c r="H114" s="4"/>
-      <c r="I114" s="4"/>
-    </row>
-    <row r="115" spans="1:9" ht="15">
-      <c r="A115" s="4"/>
-      <c r="B115" s="4"/>
-      <c r="C115" s="7"/>
-      <c r="D115" s="6"/>
-      <c r="E115" s="7"/>
-      <c r="F115" s="7"/>
-      <c r="G115" s="4"/>
-      <c r="H115" s="4"/>
-      <c r="I115" s="4"/>
-    </row>
-    <row r="116" spans="1:9" ht="15">
-      <c r="A116" s="4"/>
-      <c r="B116" s="4"/>
-      <c r="C116" s="7"/>
-      <c r="D116" s="6"/>
-      <c r="E116" s="7"/>
-      <c r="F116" s="7"/>
-      <c r="G116" s="4"/>
-      <c r="H116" s="4"/>
-      <c r="I116" s="4"/>
-    </row>
-    <row r="117" spans="1:9" ht="15">
-      <c r="A117" s="4"/>
-      <c r="B117" s="4"/>
-      <c r="C117" s="7"/>
-      <c r="D117" s="5"/>
-      <c r="E117" s="7"/>
-      <c r="F117" s="7"/>
-      <c r="G117" s="4"/>
-      <c r="H117" s="4"/>
-      <c r="I117" s="4"/>
-    </row>
-    <row r="118" spans="1:9" ht="15">
-      <c r="A118" s="4"/>
-      <c r="B118" s="4"/>
-      <c r="C118" s="7"/>
-      <c r="D118" s="6"/>
-      <c r="E118" s="7"/>
-      <c r="F118" s="7"/>
-      <c r="G118" s="4"/>
-      <c r="H118" s="4"/>
-      <c r="I118" s="4"/>
-    </row>
-    <row r="119" spans="1:9" ht="15">
-      <c r="A119" s="4"/>
-      <c r="B119" s="4"/>
-      <c r="C119" s="7"/>
-      <c r="D119" s="6"/>
-      <c r="E119" s="7"/>
-      <c r="F119" s="7"/>
-      <c r="G119" s="4"/>
-      <c r="H119" s="4"/>
-      <c r="I119" s="4"/>
-    </row>
-    <row r="120" spans="1:9" ht="15">
-      <c r="A120" s="4"/>
-      <c r="B120" s="4"/>
-      <c r="C120" s="7"/>
-      <c r="D120" s="6"/>
-      <c r="E120" s="7"/>
-      <c r="F120" s="7"/>
-      <c r="G120" s="4"/>
-      <c r="H120" s="4"/>
-      <c r="I120" s="4"/>
-    </row>
-    <row r="121" spans="1:9" ht="15">
-      <c r="A121" s="4"/>
-      <c r="B121" s="4"/>
-      <c r="C121" s="7"/>
-      <c r="D121" s="6"/>
-      <c r="E121" s="7"/>
-      <c r="F121" s="7"/>
-      <c r="G121" s="4"/>
-      <c r="H121" s="4"/>
-      <c r="I121" s="4"/>
-    </row>
-    <row r="122" spans="1:9" ht="15">
-      <c r="A122" s="4"/>
-      <c r="B122" s="4"/>
-      <c r="C122" s="7"/>
-      <c r="D122" s="6"/>
-      <c r="E122" s="7"/>
-      <c r="F122" s="7"/>
-      <c r="G122" s="4"/>
-      <c r="H122" s="4"/>
-      <c r="I122" s="4"/>
-    </row>
-    <row r="123" spans="1:9" ht="15">
-      <c r="A123" s="4"/>
-      <c r="B123" s="4"/>
-      <c r="C123" s="7"/>
-      <c r="D123" s="6"/>
-      <c r="E123" s="7"/>
-      <c r="F123" s="7"/>
-      <c r="G123" s="4"/>
-      <c r="H123" s="4"/>
-      <c r="I123" s="4"/>
-    </row>
-    <row r="124" spans="1:9" ht="15">
-      <c r="A124" s="4"/>
-      <c r="B124" s="4"/>
-      <c r="C124" s="7"/>
-      <c r="D124" s="6"/>
-      <c r="E124" s="7"/>
-      <c r="F124" s="7"/>
-      <c r="G124" s="4"/>
-      <c r="H124" s="4"/>
-      <c r="I124" s="4"/>
-    </row>
-    <row r="125" spans="1:9" ht="15">
-      <c r="A125" s="4"/>
-      <c r="B125" s="4"/>
-      <c r="C125" s="7"/>
-      <c r="D125" s="6"/>
-      <c r="E125" s="7"/>
-      <c r="F125" s="7"/>
-      <c r="G125" s="4"/>
-      <c r="H125" s="4"/>
-      <c r="I125" s="4"/>
-    </row>
-    <row r="126" spans="1:9" ht="15">
-      <c r="A126" s="4"/>
-      <c r="B126" s="4"/>
-      <c r="C126" s="7"/>
-      <c r="D126" s="6"/>
-      <c r="E126" s="7"/>
-      <c r="F126" s="7"/>
-      <c r="G126" s="4"/>
-      <c r="H126" s="4"/>
-      <c r="I126" s="4"/>
-    </row>
-    <row r="127" spans="1:9" ht="15">
-      <c r="A127" s="4"/>
-      <c r="B127" s="4"/>
-      <c r="C127" s="7"/>
-      <c r="D127" s="6"/>
-      <c r="E127" s="7"/>
-      <c r="F127" s="7"/>
-      <c r="G127" s="4"/>
-      <c r="H127" s="4"/>
-      <c r="I127" s="4"/>
-    </row>
-    <row r="128" spans="1:9" ht="15">
-      <c r="A128" s="4"/>
-      <c r="B128" s="4"/>
-      <c r="C128" s="7"/>
-      <c r="D128" s="6"/>
-      <c r="E128" s="7"/>
-      <c r="F128" s="7"/>
-      <c r="G128" s="4"/>
-      <c r="H128" s="4"/>
-      <c r="I128" s="4"/>
-    </row>
-    <row r="129" spans="1:9" ht="15">
-      <c r="A129" s="4"/>
-      <c r="B129" s="4"/>
-      <c r="C129" s="7"/>
-      <c r="D129" s="6"/>
-      <c r="E129" s="7"/>
-      <c r="F129" s="7"/>
-      <c r="G129" s="4"/>
-      <c r="H129" s="4"/>
-      <c r="I129" s="4"/>
-    </row>
-    <row r="130" spans="1:9" ht="15">
-      <c r="A130" s="4"/>
-      <c r="B130" s="4"/>
-      <c r="C130" s="7"/>
-      <c r="D130" s="6"/>
-      <c r="E130" s="7"/>
-      <c r="F130" s="7"/>
-      <c r="G130" s="4"/>
-      <c r="H130" s="4"/>
-      <c r="I130" s="4"/>
-    </row>
-    <row r="131" spans="1:9" ht="15">
-      <c r="A131" s="4"/>
-      <c r="B131" s="4"/>
-      <c r="C131" s="7"/>
-      <c r="D131" s="6"/>
-      <c r="E131" s="7"/>
-      <c r="F131" s="7"/>
-      <c r="G131" s="4"/>
-      <c r="H131" s="4"/>
-      <c r="I131" s="4"/>
-    </row>
-    <row r="132" spans="1:9" ht="15">
-      <c r="A132" s="4"/>
-      <c r="B132" s="4"/>
-      <c r="C132" s="7"/>
-      <c r="D132" s="6"/>
-      <c r="E132" s="7"/>
-      <c r="F132" s="7"/>
-      <c r="G132" s="4"/>
-      <c r="H132" s="4"/>
-      <c r="I132" s="4"/>
-    </row>
-    <row r="133" spans="1:9" ht="15">
-      <c r="A133" s="4"/>
-      <c r="B133" s="4"/>
-      <c r="C133" s="7"/>
-      <c r="D133" s="6"/>
-      <c r="E133" s="7"/>
-      <c r="F133" s="7"/>
-      <c r="G133" s="4"/>
-      <c r="H133" s="4"/>
-      <c r="I133" s="4"/>
-    </row>
-  </sheetData>
-  <mergeCells count="23">
     <mergeCell ref="I17:I23"/>
     <mergeCell ref="A17:A23"/>
     <mergeCell ref="B17:B23"/>
@@ -14006,22 +12794,6 @@
     <mergeCell ref="F17:F23"/>
     <mergeCell ref="G17:G23"/>
     <mergeCell ref="H17:H23"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D57"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Mapping Template BrotZeit.xlsx
+++ b/Mapping Template BrotZeit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alfa\Documents\Data Engineer\Projekt\BackZeit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A71AA7AD-5EEC-4ED1-87C6-95248D544953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A38082A2-E033-4730-9B0B-4D94FF9C439A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{1083ED64-F082-44F9-9F2A-19C2CA2699CD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{1083ED64-F082-44F9-9F2A-19C2CA2699CD}"/>
   </bookViews>
   <sheets>
     <sheet name="D_Filiale" sheetId="9" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="106">
   <si>
     <t>Notes</t>
   </si>
@@ -61,9 +61,6 @@
   </si>
   <si>
     <t>complete Query for selecting Data</t>
-  </si>
-  <si>
-    <t>maaping - transformation</t>
   </si>
   <si>
     <t>Source DB / csv / ….</t>
@@ -129,25 +126,7 @@
     <t>FilialID</t>
   </si>
   <si>
-    <t>Filialname</t>
-  </si>
-  <si>
-    <t>AdresseID</t>
-  </si>
-  <si>
     <t>Adresse</t>
-  </si>
-  <si>
-    <t>Ort</t>
-  </si>
-  <si>
-    <t>FilialOrt</t>
-  </si>
-  <si>
-    <t>FilialName</t>
-  </si>
-  <si>
-    <t>VerkaufsID</t>
   </si>
   <si>
     <t>Verkäufe</t>
@@ -165,130 +144,31 @@
     <t>VerkäuferID</t>
   </si>
   <si>
-    <t>MitarbeiterID</t>
-  </si>
-  <si>
-    <t>durchschnittlicher Umsatz</t>
-  </si>
-  <si>
-    <t>Tag</t>
-  </si>
-  <si>
-    <t>Monat</t>
-  </si>
-  <si>
-    <t>Quartal</t>
-  </si>
-  <si>
-    <t>Jahr</t>
-  </si>
-  <si>
-    <t>Stunde</t>
-  </si>
-  <si>
-    <t>Tageszeit</t>
-  </si>
-  <si>
     <t>Produkt</t>
   </si>
   <si>
     <t>ProduktID</t>
   </si>
   <si>
-    <t>Bruttopreis</t>
-  </si>
-  <si>
-    <t>Nettopreis</t>
-  </si>
-  <si>
-    <t>ProduktName</t>
-  </si>
-  <si>
-    <t>KategorieID</t>
-  </si>
-  <si>
     <t>Rezept</t>
-  </si>
-  <si>
-    <t>ZutatID</t>
-  </si>
-  <si>
-    <t>LagerkostenProg</t>
-  </si>
-  <si>
-    <t>Allergen</t>
-  </si>
-  <si>
-    <t>PreisProKg</t>
-  </si>
-  <si>
-    <t>Bezeichnung</t>
   </si>
   <si>
     <t>beinhaltet</t>
   </si>
   <si>
-    <t>Version</t>
-  </si>
-  <si>
     <t>Menge</t>
-  </si>
-  <si>
-    <t>Zubereitungsdauer</t>
-  </si>
-  <si>
-    <t>gültig_bis</t>
-  </si>
-  <si>
-    <t>gültig_ab</t>
-  </si>
-  <si>
-    <t>Backzeit</t>
-  </si>
-  <si>
-    <t>Autor</t>
-  </si>
-  <si>
-    <t>Stückzahl</t>
   </si>
   <si>
     <t>Zutaten</t>
   </si>
   <si>
-    <t>Lagerkosten</t>
-  </si>
-  <si>
-    <t>Lohnkosten</t>
-  </si>
-  <si>
-    <t>Zutatenkosten</t>
-  </si>
-  <si>
-    <t>Backkosten</t>
-  </si>
-  <si>
-    <t>Gewinnmarge</t>
-  </si>
-  <si>
-    <t>VerkäuferName</t>
-  </si>
-  <si>
     <t>Mitarbeiter</t>
-  </si>
-  <si>
-    <t>MItarbeiterID</t>
-  </si>
-  <si>
-    <t>MitarbeiterName</t>
   </si>
   <si>
     <t>D_Produkt</t>
   </si>
   <si>
     <t>D_Tageszeit</t>
-  </si>
-  <si>
-    <t>D_Zeit</t>
   </si>
   <si>
     <t>D_Verkäufer</t>
@@ -300,10 +180,184 @@
     <t>D_Filiale</t>
   </si>
   <si>
-    <t>AnzahlVerkäufe</t>
+    <t>D_Stunden</t>
   </si>
   <si>
-    <t>Gesamtumsatz</t>
+    <t>StundeID</t>
+  </si>
+  <si>
+    <t>[FilialID]</t>
+  </si>
+  <si>
+    <t>[FilialName]</t>
+  </si>
+  <si>
+    <t>[FilialOrt]</t>
+  </si>
+  <si>
+    <t>[Filialname]</t>
+  </si>
+  <si>
+    <t>[AdresseID]</t>
+  </si>
+  <si>
+    <t>[Ort]</t>
+  </si>
+  <si>
+    <t>[VerkaufsvorgangID]</t>
+  </si>
+  <si>
+    <t>[Zahlart]</t>
+  </si>
+  <si>
+    <t>[Zeitpunkt]</t>
+  </si>
+  <si>
+    <t>[VerkäuferID]</t>
+  </si>
+  <si>
+    <t>[MitarbeiterID]</t>
+  </si>
+  <si>
+    <t>[MItarbeiterID]</t>
+  </si>
+  <si>
+    <t>[MitarbeiterName]</t>
+  </si>
+  <si>
+    <t>[VerkäuferName]</t>
+  </si>
+  <si>
+    <t>[durchschnittlicherUmsatz]</t>
+  </si>
+  <si>
+    <t>[AnzahlVerkäufe]</t>
+  </si>
+  <si>
+    <t>[Gesamtumsatz]</t>
+  </si>
+  <si>
+    <t>[Tag]</t>
+  </si>
+  <si>
+    <t>[Monat]</t>
+  </si>
+  <si>
+    <t>[Quartal]</t>
+  </si>
+  <si>
+    <t>[Jahr]</t>
+  </si>
+  <si>
+    <t>[TagID]</t>
+  </si>
+  <si>
+    <t>[Stunde]</t>
+  </si>
+  <si>
+    <t>[Tageszeit]</t>
+  </si>
+  <si>
+    <t>[ProduktID]</t>
+  </si>
+  <si>
+    <t>[ProduktName]</t>
+  </si>
+  <si>
+    <t>[KategorieID]</t>
+  </si>
+  <si>
+    <t>[Bruttopreis]</t>
+  </si>
+  <si>
+    <t>[Nettopreis]</t>
+  </si>
+  <si>
+    <t>[Lagerkosten]</t>
+  </si>
+  <si>
+    <t>[Backkosten]</t>
+  </si>
+  <si>
+    <t>[Lohnkosten]</t>
+  </si>
+  <si>
+    <t>[Zutatenkosten]</t>
+  </si>
+  <si>
+    <t>[Gewinnmarge]</t>
+  </si>
+  <si>
+    <t>[ZutatID]</t>
+  </si>
+  <si>
+    <t>[LagerkostenProg]</t>
+  </si>
+  <si>
+    <t>[Allergen]</t>
+  </si>
+  <si>
+    <t>[PreisProKg]</t>
+  </si>
+  <si>
+    <t>[Bezeichnung]</t>
+  </si>
+  <si>
+    <t>[Version]</t>
+  </si>
+  <si>
+    <t>[Menge]</t>
+  </si>
+  <si>
+    <t>[Zubereitungsdauer]</t>
+  </si>
+  <si>
+    <t>[gültig_bis]</t>
+  </si>
+  <si>
+    <t>[gültig_ab]</t>
+  </si>
+  <si>
+    <t>[Backzeit]</t>
+  </si>
+  <si>
+    <t>[Autor]</t>
+  </si>
+  <si>
+    <t>[Stückzahl]</t>
+  </si>
+  <si>
+    <t>F_Verkäufe</t>
+  </si>
+  <si>
+    <t>[VerkäuferID] FK</t>
+  </si>
+  <si>
+    <t>[FilialID] FK</t>
+  </si>
+  <si>
+    <t>[TagID] FK</t>
+  </si>
+  <si>
+    <t>[StundenID] FK</t>
+  </si>
+  <si>
+    <t>[VerkaufsvorgangID] FK</t>
+  </si>
+  <si>
+    <t>[Gewinn]</t>
+  </si>
+  <si>
+    <t>[Umsatz]</t>
+  </si>
+  <si>
+    <t>[AnzahlProdukte]</t>
+  </si>
+  <si>
+    <t>Verkauf</t>
+  </si>
+  <si>
+    <t>wird verkauft</t>
   </si>
 </sst>
 </file>
@@ -586,7 +640,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -619,14 +673,14 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -634,6 +688,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -666,8 +723,8 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1018,28 +1075,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="26" t="s">
+      <c r="A1" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="32"/>
+      <c r="H1" s="35"/>
       <c r="I1" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J1" s="16" t="s">
         <v>0</v>
@@ -1047,15 +1104,15 @@
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1">
       <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1067,76 +1124,76 @@
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A3" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="H3" s="23" t="s">
-        <v>28</v>
+      <c r="G3" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>48</v>
       </c>
       <c r="I3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="18"/>
+    </row>
+    <row r="4" spans="1:10" ht="15">
+      <c r="A4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="13"/>
-    </row>
-    <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="13"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="13"/>
+      <c r="J4" s="18"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="12" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C5" s="11"/>
-      <c r="D5" s="21"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
       <c r="H5" s="10" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J5" s="10"/>
     </row>
     <row r="6" spans="1:10" ht="15">
       <c r="A6" s="10"/>
       <c r="B6" s="10" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="C6" s="11"/>
-      <c r="D6" s="21"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
@@ -1145,7 +1202,7 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="21"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
@@ -1155,19 +1212,19 @@
     </row>
     <row r="8" spans="1:10" ht="15">
       <c r="A8" s="10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="21"/>
+      <c r="D8" s="23"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
       <c r="I8" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J8" s="10"/>
     </row>
@@ -1175,13 +1232,13 @@
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="21"/>
+      <c r="D9" s="23"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
       <c r="I9" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J9" s="10"/>
     </row>
@@ -1189,13 +1246,13 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="21"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J10" s="10"/>
     </row>
@@ -1203,13 +1260,13 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="21"/>
+      <c r="D11" s="23"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
       <c r="I11" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J11" s="10"/>
     </row>
@@ -1217,7 +1274,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="21"/>
+      <c r="D12" s="23"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -1229,13 +1286,13 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="21"/>
+      <c r="D13" s="23"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
       <c r="I13" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J13" s="10"/>
     </row>
@@ -1243,7 +1300,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="21"/>
+      <c r="D14" s="23"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -1255,13 +1312,13 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="21"/>
+      <c r="D15" s="23"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
       <c r="I15" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J15" s="10"/>
     </row>
@@ -1269,7 +1326,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="21"/>
+      <c r="D16" s="23"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -1278,94 +1335,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
+      <c r="A17" s="36"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="13"/>
+      <c r="J17" s="18"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
+      <c r="A18" s="36"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="13"/>
+      <c r="J18" s="18"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
+      <c r="A19" s="36"/>
+      <c r="B19" s="36"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="13"/>
+      <c r="J19" s="18"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
+      <c r="A20" s="36"/>
+      <c r="B20" s="36"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="13"/>
+      <c r="J20" s="18"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
+      <c r="A21" s="36"/>
+      <c r="B21" s="36"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="13"/>
+      <c r="J21" s="18"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
+      <c r="A22" s="36"/>
+      <c r="B22" s="36"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="13"/>
+      <c r="J22" s="18"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
+      <c r="A23" s="36"/>
+      <c r="B23" s="36"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="13"/>
+      <c r="J23" s="18"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="21"/>
+      <c r="D24" s="23"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -1377,7 +1434,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="21"/>
+      <c r="D25" s="23"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -1389,7 +1446,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="21"/>
+      <c r="D26" s="23"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -1401,7 +1458,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="21"/>
+      <c r="D27" s="23"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -1413,7 +1470,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="21"/>
+      <c r="D28" s="23"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -1425,7 +1482,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="21"/>
+      <c r="D29" s="23"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -1437,7 +1494,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="21"/>
+      <c r="D30" s="23"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -1449,7 +1506,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="21"/>
+      <c r="D31" s="23"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -1461,7 +1518,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="21"/>
+      <c r="D32" s="23"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -1473,7 +1530,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="21"/>
+      <c r="D33" s="23"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -1485,7 +1542,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="21"/>
+      <c r="D34" s="23"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -1497,7 +1554,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="21"/>
+      <c r="D35" s="23"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -1509,7 +1566,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="21"/>
+      <c r="D36" s="23"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -1521,7 +1578,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="21"/>
+      <c r="D37" s="23"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -1533,7 +1590,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="21"/>
+      <c r="D38" s="23"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -1545,7 +1602,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="21"/>
+      <c r="D39" s="23"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -1557,7 +1614,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="21"/>
+      <c r="D40" s="23"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -1569,7 +1626,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="21"/>
+      <c r="D41" s="23"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -1581,7 +1638,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="21"/>
+      <c r="D42" s="23"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -1593,7 +1650,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="21"/>
+      <c r="D43" s="23"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -1605,7 +1662,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="21"/>
+      <c r="D44" s="23"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -1617,7 +1674,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="21"/>
+      <c r="D45" s="23"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -1629,7 +1686,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="21"/>
+      <c r="D46" s="23"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -1641,7 +1698,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="21"/>
+      <c r="D47" s="23"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -1653,7 +1710,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="21"/>
+      <c r="D48" s="23"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -1665,7 +1722,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="21"/>
+      <c r="D49" s="23"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -1677,7 +1734,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="21"/>
+      <c r="D50" s="23"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -1689,7 +1746,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="21"/>
+      <c r="D51" s="23"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -1701,7 +1758,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="21"/>
+      <c r="D52" s="23"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -1713,7 +1770,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="21"/>
+      <c r="D53" s="23"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -1725,7 +1782,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="21"/>
+      <c r="D54" s="23"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -1737,7 +1794,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="21"/>
+      <c r="D55" s="23"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -1749,7 +1806,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="21"/>
+      <c r="D56" s="23"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -1761,7 +1818,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="21"/>
+      <c r="D57" s="23"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -2683,6 +2740,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -2699,13 +2763,6 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2729,28 +2786,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="26" t="s">
+      <c r="A1" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="32"/>
+      <c r="H1" s="35"/>
       <c r="I1" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J1" s="16" t="s">
         <v>0</v>
@@ -2758,15 +2815,15 @@
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1">
       <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2778,71 +2835,71 @@
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A3" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="H3" s="23" t="s">
-        <v>35</v>
+      <c r="G3" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>54</v>
       </c>
       <c r="I3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="18"/>
+    </row>
+    <row r="4" spans="1:10" ht="15">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="13"/>
-    </row>
-    <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="13"/>
+      <c r="J4" s="18"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="10" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="C5" s="11"/>
-      <c r="D5" s="21"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
       <c r="H5" s="10" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J5" s="10"/>
     </row>
     <row r="6" spans="1:10" ht="15">
       <c r="A6" s="10"/>
       <c r="B6" s="10" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C6" s="11"/>
-      <c r="D6" s="21"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
@@ -2854,7 +2911,7 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="21"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
@@ -2866,13 +2923,13 @@
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="21"/>
+      <c r="D8" s="23"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
       <c r="I8" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J8" s="10"/>
     </row>
@@ -2880,13 +2937,13 @@
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="21"/>
+      <c r="D9" s="23"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
       <c r="I9" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J9" s="10"/>
     </row>
@@ -2894,13 +2951,13 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="21"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J10" s="10"/>
     </row>
@@ -2908,13 +2965,13 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="21"/>
+      <c r="D11" s="23"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
       <c r="I11" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J11" s="10"/>
     </row>
@@ -2922,7 +2979,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="21"/>
+      <c r="D12" s="23"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -2934,13 +2991,13 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="21"/>
+      <c r="D13" s="23"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
       <c r="I13" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J13" s="10"/>
     </row>
@@ -2948,7 +3005,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="21"/>
+      <c r="D14" s="23"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -2960,13 +3017,13 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="21"/>
+      <c r="D15" s="23"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
       <c r="I15" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J15" s="10"/>
     </row>
@@ -2974,7 +3031,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="21"/>
+      <c r="D16" s="23"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -2983,94 +3040,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="34"/>
-      <c r="B17" s="34"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="13"/>
+      <c r="J17" s="18"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="34"/>
-      <c r="B18" s="34"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="13"/>
+      <c r="J18" s="18"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="34"/>
-      <c r="B19" s="34"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="13"/>
+      <c r="J19" s="18"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="34"/>
-      <c r="B20" s="34"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="15"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="13"/>
+      <c r="J20" s="18"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="34"/>
-      <c r="B21" s="34"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="15"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="13"/>
+      <c r="J21" s="18"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="34"/>
-      <c r="B22" s="34"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="13"/>
+      <c r="J22" s="18"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="34"/>
-      <c r="B23" s="34"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="15"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="13"/>
+      <c r="J23" s="18"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="21"/>
+      <c r="D24" s="23"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -3082,7 +3139,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="21"/>
+      <c r="D25" s="23"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -3094,7 +3151,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="21"/>
+      <c r="D26" s="23"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -3106,7 +3163,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="21"/>
+      <c r="D27" s="23"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -3118,7 +3175,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="21"/>
+      <c r="D28" s="23"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -3130,7 +3187,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="21"/>
+      <c r="D29" s="23"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -3142,7 +3199,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="21"/>
+      <c r="D30" s="23"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -3154,7 +3211,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="21"/>
+      <c r="D31" s="23"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -3166,7 +3223,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="21"/>
+      <c r="D32" s="23"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -3178,7 +3235,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="21"/>
+      <c r="D33" s="23"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -3190,7 +3247,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="21"/>
+      <c r="D34" s="23"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -3202,7 +3259,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="21"/>
+      <c r="D35" s="23"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -3214,7 +3271,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="21"/>
+      <c r="D36" s="23"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -3226,7 +3283,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="21"/>
+      <c r="D37" s="23"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -3238,7 +3295,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="21"/>
+      <c r="D38" s="23"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -3250,7 +3307,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="21"/>
+      <c r="D39" s="23"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -3262,7 +3319,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="21"/>
+      <c r="D40" s="23"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -3274,7 +3331,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="21"/>
+      <c r="D41" s="23"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -3286,7 +3343,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="21"/>
+      <c r="D42" s="23"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -3298,7 +3355,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="21"/>
+      <c r="D43" s="23"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -3310,7 +3367,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="21"/>
+      <c r="D44" s="23"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -3322,7 +3379,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="21"/>
+      <c r="D45" s="23"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -3334,7 +3391,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="21"/>
+      <c r="D46" s="23"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -3346,7 +3403,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="21"/>
+      <c r="D47" s="23"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -3358,7 +3415,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="21"/>
+      <c r="D48" s="23"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -3370,7 +3427,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="21"/>
+      <c r="D49" s="23"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -3382,7 +3439,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="21"/>
+      <c r="D50" s="23"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -3394,7 +3451,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="21"/>
+      <c r="D51" s="23"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -3406,7 +3463,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="21"/>
+      <c r="D52" s="23"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -3418,7 +3475,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="21"/>
+      <c r="D53" s="23"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -3430,7 +3487,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="21"/>
+      <c r="D54" s="23"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -3442,7 +3499,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="21"/>
+      <c r="D55" s="23"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -3454,7 +3511,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="21"/>
+      <c r="D56" s="23"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -3466,7 +3523,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="21"/>
+      <c r="D57" s="23"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -4388,6 +4445,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -4404,11 +4466,6 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4432,28 +4489,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="26" t="s">
+      <c r="A1" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="32"/>
+      <c r="H1" s="35"/>
       <c r="I1" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J1" s="16" t="s">
         <v>0</v>
@@ -4461,15 +4518,15 @@
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1">
       <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -4481,76 +4538,74 @@
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A3" s="17" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="23" t="s">
-        <v>83</v>
+      <c r="G3" s="26" t="s">
+        <v>43</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="I3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="18"/>
+    </row>
+    <row r="4" spans="1:10" ht="15">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="13"/>
-    </row>
-    <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="13"/>
+      <c r="J4" s="18"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="10" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="C5" s="11"/>
-      <c r="D5" s="21"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
       <c r="H5" s="12" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J5" s="10"/>
     </row>
     <row r="6" spans="1:10" ht="15">
       <c r="A6" s="10"/>
-      <c r="B6" s="10" t="s">
-        <v>42</v>
-      </c>
+      <c r="B6" s="10"/>
       <c r="C6" s="11"/>
-      <c r="D6" s="21"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
       <c r="H6" s="12" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
@@ -4559,49 +4614,49 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="21"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
       <c r="H7" s="10" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
     </row>
     <row r="8" spans="1:10" ht="15">
       <c r="A8" s="10" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="21"/>
+      <c r="D8" s="23"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
       <c r="H8" s="10" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J8" s="10"/>
     </row>
     <row r="9" spans="1:10" ht="15">
       <c r="A9" s="10"/>
       <c r="B9" s="10" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="C9" s="10"/>
-      <c r="D9" s="21"/>
+      <c r="D9" s="23"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
       <c r="I9" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J9" s="10"/>
     </row>
@@ -4609,13 +4664,13 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="21"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J10" s="10"/>
     </row>
@@ -4623,13 +4678,13 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="21"/>
+      <c r="D11" s="23"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
       <c r="I11" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J11" s="10"/>
     </row>
@@ -4637,7 +4692,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="21"/>
+      <c r="D12" s="23"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -4649,13 +4704,13 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="21"/>
+      <c r="D13" s="23"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
       <c r="I13" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J13" s="10"/>
     </row>
@@ -4663,7 +4718,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="21"/>
+      <c r="D14" s="23"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -4675,13 +4730,13 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="21"/>
+      <c r="D15" s="23"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
       <c r="I15" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J15" s="10"/>
     </row>
@@ -4689,7 +4744,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="21"/>
+      <c r="D16" s="23"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -4698,94 +4753,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
+      <c r="A17" s="36"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="13"/>
+      <c r="J17" s="18"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
+      <c r="A18" s="36"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="13"/>
+      <c r="J18" s="18"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
+      <c r="A19" s="36"/>
+      <c r="B19" s="36"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="13"/>
+      <c r="J19" s="18"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
+      <c r="A20" s="36"/>
+      <c r="B20" s="36"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="13"/>
+      <c r="J20" s="18"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
+      <c r="A21" s="36"/>
+      <c r="B21" s="36"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="13"/>
+      <c r="J21" s="18"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
+      <c r="A22" s="36"/>
+      <c r="B22" s="36"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="13"/>
+      <c r="J22" s="18"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
+      <c r="A23" s="36"/>
+      <c r="B23" s="36"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="13"/>
+      <c r="J23" s="18"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="21"/>
+      <c r="D24" s="23"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -4797,7 +4852,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="21"/>
+      <c r="D25" s="23"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -4809,7 +4864,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="21"/>
+      <c r="D26" s="23"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -4821,7 +4876,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="21"/>
+      <c r="D27" s="23"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -4833,7 +4888,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="21"/>
+      <c r="D28" s="23"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -4845,7 +4900,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="21"/>
+      <c r="D29" s="23"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -4857,7 +4912,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="21"/>
+      <c r="D30" s="23"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -4869,7 +4924,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="21"/>
+      <c r="D31" s="23"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -4881,7 +4936,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="21"/>
+      <c r="D32" s="23"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -4893,7 +4948,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="21"/>
+      <c r="D33" s="23"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -4905,7 +4960,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="21"/>
+      <c r="D34" s="23"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -4917,7 +4972,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="21"/>
+      <c r="D35" s="23"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -4929,7 +4984,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="21"/>
+      <c r="D36" s="23"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -4941,7 +4996,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="21"/>
+      <c r="D37" s="23"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -4953,7 +5008,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="21"/>
+      <c r="D38" s="23"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -4965,7 +5020,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="21"/>
+      <c r="D39" s="23"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -4977,7 +5032,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="21"/>
+      <c r="D40" s="23"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -4989,7 +5044,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="21"/>
+      <c r="D41" s="23"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -5001,7 +5056,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="21"/>
+      <c r="D42" s="23"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -5013,7 +5068,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="21"/>
+      <c r="D43" s="23"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -5025,7 +5080,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="21"/>
+      <c r="D44" s="23"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -5037,7 +5092,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="21"/>
+      <c r="D45" s="23"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -5049,7 +5104,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="21"/>
+      <c r="D46" s="23"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -5061,7 +5116,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="21"/>
+      <c r="D47" s="23"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -5073,7 +5128,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="21"/>
+      <c r="D48" s="23"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -5085,7 +5140,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="21"/>
+      <c r="D49" s="23"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -5097,7 +5152,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="21"/>
+      <c r="D50" s="23"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -5109,7 +5164,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="21"/>
+      <c r="D51" s="23"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -5121,7 +5176,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="21"/>
+      <c r="D52" s="23"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -5133,7 +5188,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="21"/>
+      <c r="D53" s="23"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -5145,7 +5200,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="21"/>
+      <c r="D54" s="23"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -5157,7 +5212,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="21"/>
+      <c r="D55" s="23"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -5169,7 +5224,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="21"/>
+      <c r="D56" s="23"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -5181,7 +5236,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="21"/>
+      <c r="D57" s="23"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -6103,6 +6158,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -6119,13 +6181,6 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6149,28 +6204,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="26" t="s">
+      <c r="A1" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="32"/>
+      <c r="H1" s="35"/>
       <c r="I1" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J1" s="16" t="s">
         <v>0</v>
@@ -6178,15 +6233,15 @@
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1">
       <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -6199,54 +6254,54 @@
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="20"/>
+      <c r="D3" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="H3" s="23" t="s">
-        <v>43</v>
+      <c r="G3" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>65</v>
       </c>
       <c r="I3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="18"/>
+    </row>
+    <row r="4" spans="1:10" ht="15">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="13"/>
-    </row>
-    <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="13"/>
+      <c r="J4" s="18"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="10"/>
       <c r="C5" s="11"/>
-      <c r="D5" s="21"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
       <c r="H5" s="10" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J5" s="10"/>
     </row>
@@ -6254,12 +6309,12 @@
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
       <c r="C6" s="11"/>
-      <c r="D6" s="21"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
@@ -6268,12 +6323,12 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="21"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
       <c r="H7" s="10" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
@@ -6282,13 +6337,15 @@
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="21"/>
+      <c r="D8" s="23"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
+      <c r="H8" s="10" t="s">
+        <v>69</v>
+      </c>
       <c r="I8" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J8" s="10"/>
     </row>
@@ -6296,13 +6353,13 @@
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="21"/>
+      <c r="D9" s="23"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
       <c r="I9" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J9" s="10"/>
     </row>
@@ -6310,13 +6367,13 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="21"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J10" s="10"/>
     </row>
@@ -6324,13 +6381,13 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="21"/>
+      <c r="D11" s="23"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
       <c r="I11" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J11" s="10"/>
     </row>
@@ -6338,7 +6395,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="21"/>
+      <c r="D12" s="23"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -6350,13 +6407,13 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="21"/>
+      <c r="D13" s="23"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
       <c r="I13" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J13" s="10"/>
     </row>
@@ -6364,7 +6421,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="21"/>
+      <c r="D14" s="23"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -6376,13 +6433,13 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="21"/>
+      <c r="D15" s="23"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
       <c r="I15" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J15" s="10"/>
     </row>
@@ -6390,7 +6447,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="21"/>
+      <c r="D16" s="23"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -6399,94 +6456,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
+      <c r="A17" s="36"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="13"/>
+      <c r="J17" s="18"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
+      <c r="A18" s="36"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="13"/>
+      <c r="J18" s="18"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
+      <c r="A19" s="36"/>
+      <c r="B19" s="36"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="13"/>
+      <c r="J19" s="18"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
+      <c r="A20" s="36"/>
+      <c r="B20" s="36"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="13"/>
+      <c r="J20" s="18"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
+      <c r="A21" s="36"/>
+      <c r="B21" s="36"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="13"/>
+      <c r="J21" s="18"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
+      <c r="A22" s="36"/>
+      <c r="B22" s="36"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="13"/>
+      <c r="J22" s="18"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
+      <c r="A23" s="36"/>
+      <c r="B23" s="36"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="13"/>
+      <c r="J23" s="18"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="21"/>
+      <c r="D24" s="23"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -6498,7 +6555,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="21"/>
+      <c r="D25" s="23"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -6510,7 +6567,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="21"/>
+      <c r="D26" s="23"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -6522,7 +6579,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="21"/>
+      <c r="D27" s="23"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -6534,7 +6591,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="21"/>
+      <c r="D28" s="23"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -6546,7 +6603,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="21"/>
+      <c r="D29" s="23"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -6558,7 +6615,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="21"/>
+      <c r="D30" s="23"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -6570,7 +6627,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="21"/>
+      <c r="D31" s="23"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -6582,7 +6639,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="21"/>
+      <c r="D32" s="23"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -6594,7 +6651,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="21"/>
+      <c r="D33" s="23"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -6606,7 +6663,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="21"/>
+      <c r="D34" s="23"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -6618,7 +6675,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="21"/>
+      <c r="D35" s="23"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -6630,7 +6687,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="21"/>
+      <c r="D36" s="23"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -6642,7 +6699,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="21"/>
+      <c r="D37" s="23"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -6654,7 +6711,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="21"/>
+      <c r="D38" s="23"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -6666,7 +6723,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="21"/>
+      <c r="D39" s="23"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -6678,7 +6735,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="21"/>
+      <c r="D40" s="23"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -6690,7 +6747,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="21"/>
+      <c r="D41" s="23"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -6702,7 +6759,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="21"/>
+      <c r="D42" s="23"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -6714,7 +6771,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="21"/>
+      <c r="D43" s="23"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -6726,7 +6783,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="21"/>
+      <c r="D44" s="23"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -6738,7 +6795,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="21"/>
+      <c r="D45" s="23"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -6750,7 +6807,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="21"/>
+      <c r="D46" s="23"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -6762,7 +6819,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="21"/>
+      <c r="D47" s="23"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -6774,7 +6831,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="21"/>
+      <c r="D48" s="23"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -6786,7 +6843,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="21"/>
+      <c r="D49" s="23"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -6798,7 +6855,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="21"/>
+      <c r="D50" s="23"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -6810,7 +6867,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="21"/>
+      <c r="D51" s="23"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -6822,7 +6879,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="21"/>
+      <c r="D52" s="23"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -6834,7 +6891,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="21"/>
+      <c r="D53" s="23"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -6846,7 +6903,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="21"/>
+      <c r="D54" s="23"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -6858,7 +6915,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="21"/>
+      <c r="D55" s="23"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -6870,7 +6927,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="21"/>
+      <c r="D56" s="23"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -6882,7 +6939,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="21"/>
+      <c r="D57" s="23"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -7804,6 +7861,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -7820,13 +7884,6 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7850,28 +7907,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="26" t="s">
+      <c r="A1" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="32"/>
+      <c r="H1" s="35"/>
       <c r="I1" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J1" s="16" t="s">
         <v>0</v>
@@ -7879,15 +7936,15 @@
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1">
       <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -7900,54 +7957,54 @@
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="20"/>
+      <c r="D3" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="H3" s="23" t="s">
-        <v>47</v>
+      <c r="G3" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>70</v>
       </c>
       <c r="I3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="18"/>
+    </row>
+    <row r="4" spans="1:10" ht="15">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="13"/>
-    </row>
-    <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="13"/>
+      <c r="J4" s="18"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="10"/>
       <c r="C5" s="11"/>
-      <c r="D5" s="21"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
       <c r="H5" s="10" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J5" s="10"/>
     </row>
@@ -7955,11 +8012,13 @@
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
       <c r="C6" s="11"/>
-      <c r="D6" s="21"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
+      <c r="H6" s="10" t="s">
+        <v>47</v>
+      </c>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
     </row>
@@ -7967,7 +8026,7 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="21"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
@@ -7979,13 +8038,13 @@
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="21"/>
+      <c r="D8" s="23"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
       <c r="I8" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J8" s="10"/>
     </row>
@@ -7993,13 +8052,13 @@
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="21"/>
+      <c r="D9" s="23"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
       <c r="I9" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J9" s="10"/>
     </row>
@@ -8007,13 +8066,13 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="21"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J10" s="10"/>
     </row>
@@ -8021,13 +8080,13 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="21"/>
+      <c r="D11" s="23"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
       <c r="I11" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J11" s="10"/>
     </row>
@@ -8035,7 +8094,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="21"/>
+      <c r="D12" s="23"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -8047,13 +8106,13 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="21"/>
+      <c r="D13" s="23"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
       <c r="I13" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J13" s="10"/>
     </row>
@@ -8061,7 +8120,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="21"/>
+      <c r="D14" s="23"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -8073,13 +8132,13 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="21"/>
+      <c r="D15" s="23"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
       <c r="I15" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J15" s="10"/>
     </row>
@@ -8087,7 +8146,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="21"/>
+      <c r="D16" s="23"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -8096,94 +8155,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
+      <c r="A17" s="36"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="13"/>
+      <c r="J17" s="18"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
+      <c r="A18" s="36"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="13"/>
+      <c r="J18" s="18"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
+      <c r="A19" s="36"/>
+      <c r="B19" s="36"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="13"/>
+      <c r="J19" s="18"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
+      <c r="A20" s="36"/>
+      <c r="B20" s="36"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="13"/>
+      <c r="J20" s="18"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
+      <c r="A21" s="36"/>
+      <c r="B21" s="36"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="13"/>
+      <c r="J21" s="18"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
+      <c r="A22" s="36"/>
+      <c r="B22" s="36"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="13"/>
+      <c r="J22" s="18"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
+      <c r="A23" s="36"/>
+      <c r="B23" s="36"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="13"/>
+      <c r="J23" s="18"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="21"/>
+      <c r="D24" s="23"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -8195,7 +8254,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="21"/>
+      <c r="D25" s="23"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -8207,7 +8266,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="21"/>
+      <c r="D26" s="23"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -8219,7 +8278,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="21"/>
+      <c r="D27" s="23"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -8231,7 +8290,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="21"/>
+      <c r="D28" s="23"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -8243,7 +8302,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="21"/>
+      <c r="D29" s="23"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -8255,7 +8314,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="21"/>
+      <c r="D30" s="23"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -8267,7 +8326,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="21"/>
+      <c r="D31" s="23"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -8279,7 +8338,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="21"/>
+      <c r="D32" s="23"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -8291,7 +8350,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="21"/>
+      <c r="D33" s="23"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -8303,7 +8362,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="21"/>
+      <c r="D34" s="23"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -8315,7 +8374,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="21"/>
+      <c r="D35" s="23"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -8327,7 +8386,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="21"/>
+      <c r="D36" s="23"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -8339,7 +8398,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="21"/>
+      <c r="D37" s="23"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -8351,7 +8410,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="21"/>
+      <c r="D38" s="23"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -8363,7 +8422,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="21"/>
+      <c r="D39" s="23"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -8375,7 +8434,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="21"/>
+      <c r="D40" s="23"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -8387,7 +8446,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="21"/>
+      <c r="D41" s="23"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -8399,7 +8458,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="21"/>
+      <c r="D42" s="23"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -8411,7 +8470,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="21"/>
+      <c r="D43" s="23"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -8423,7 +8482,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="21"/>
+      <c r="D44" s="23"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -8435,7 +8494,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="21"/>
+      <c r="D45" s="23"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -8447,7 +8506,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="21"/>
+      <c r="D46" s="23"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -8459,7 +8518,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="21"/>
+      <c r="D47" s="23"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -8471,7 +8530,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="21"/>
+      <c r="D48" s="23"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -8483,7 +8542,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="21"/>
+      <c r="D49" s="23"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -8495,7 +8554,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="21"/>
+      <c r="D50" s="23"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -8507,7 +8566,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="21"/>
+      <c r="D51" s="23"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -8519,7 +8578,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="21"/>
+      <c r="D52" s="23"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -8531,7 +8590,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="21"/>
+      <c r="D53" s="23"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -8543,7 +8602,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="21"/>
+      <c r="D54" s="23"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -8555,7 +8614,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="21"/>
+      <c r="D55" s="23"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -8567,7 +8626,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="21"/>
+      <c r="D56" s="23"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -8579,7 +8638,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="21"/>
+      <c r="D57" s="23"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -9501,6 +9560,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -9517,13 +9583,6 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9547,28 +9606,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="26" t="s">
+      <c r="A1" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="32"/>
+      <c r="H1" s="35"/>
       <c r="I1" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J1" s="16" t="s">
         <v>0</v>
@@ -9576,15 +9635,15 @@
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1">
       <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -9596,197 +9655,197 @@
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="H3" s="23" t="s">
-        <v>50</v>
+      <c r="G3" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>72</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="13"/>
+        <v>17</v>
+      </c>
+      <c r="J3" s="18"/>
     </row>
     <row r="4" spans="1:10" ht="15">
       <c r="B4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="19"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
+        <v>75</v>
+      </c>
+      <c r="C4" s="21"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
       <c r="I4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="13"/>
+        <v>18</v>
+      </c>
+      <c r="J4" s="18"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="B5" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="C5" s="7"/>
-      <c r="D5" s="21"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J5" s="4"/>
     </row>
     <row r="6" spans="1:10" ht="15">
       <c r="B6" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C6" s="7"/>
-      <c r="D6" s="21"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:10" ht="15">
       <c r="B7" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="C7" s="7"/>
-      <c r="D7" s="21"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
     </row>
     <row r="8" spans="1:10" ht="15">
       <c r="C8" s="7"/>
-      <c r="D8" s="21"/>
+      <c r="D8" s="23"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J8" s="4"/>
     </row>
     <row r="9" spans="1:10" ht="15">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="21"/>
+      <c r="D9" s="23"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J9" s="4"/>
     </row>
     <row r="10" spans="1:10" ht="15">
       <c r="B10" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="C10" s="7"/>
-      <c r="D10" s="21"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J10" s="4"/>
     </row>
     <row r="11" spans="1:10" ht="15">
       <c r="B11" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="21"/>
+      <c r="D11" s="23"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:10" ht="15">
       <c r="B12" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="C12" s="7"/>
-      <c r="D12" s="21"/>
+      <c r="D12" s="23"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
     </row>
     <row r="13" spans="1:10" ht="15">
       <c r="B13" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="C13" s="7"/>
-      <c r="D13" s="21"/>
+      <c r="D13" s="23"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J13" s="4"/>
     </row>
     <row r="14" spans="1:10" ht="15">
       <c r="C14" s="7"/>
-      <c r="D14" s="21"/>
+      <c r="D14" s="23"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="4"/>
@@ -9796,28 +9855,28 @@
     </row>
     <row r="15" spans="1:10" ht="15">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="C15" s="7"/>
-      <c r="D15" s="21"/>
+      <c r="D15" s="23"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J15" s="4"/>
     </row>
     <row r="16" spans="1:10" ht="15">
       <c r="B16" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="C16" s="7"/>
-      <c r="D16" s="21"/>
+      <c r="D16" s="23"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -9827,101 +9886,101 @@
     </row>
     <row r="17" spans="1:10" ht="15">
       <c r="B17" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C17" s="8"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="13"/>
+      <c r="J17" s="18"/>
     </row>
     <row r="18" spans="1:10" ht="15">
       <c r="B18" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="C18" s="8"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
       <c r="I18" s="4"/>
-      <c r="J18" s="13"/>
+      <c r="J18" s="18"/>
     </row>
     <row r="19" spans="1:10" ht="15">
       <c r="C19" s="8"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
       <c r="I19" s="4"/>
-      <c r="J19" s="13"/>
+      <c r="J19" s="18"/>
     </row>
     <row r="20" spans="1:10" ht="15">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C20" s="8"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="13"/>
+      <c r="J20" s="18"/>
     </row>
     <row r="21" spans="1:10" ht="15">
       <c r="B21" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="C21" s="8"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="13"/>
+      <c r="J21" s="18"/>
     </row>
     <row r="22" spans="1:10" ht="15">
       <c r="B22" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="C22" s="8"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
       <c r="I22" s="4"/>
-      <c r="J22" s="13"/>
+      <c r="J22" s="18"/>
     </row>
     <row r="23" spans="1:10" ht="15">
       <c r="B23" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="C23" s="8"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
       <c r="I23" s="4"/>
-      <c r="J23" s="13"/>
+      <c r="J23" s="18"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="B24" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="C24" s="7"/>
-      <c r="D24" s="21"/>
+      <c r="D24" s="23"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
       <c r="G24" s="4"/>
@@ -9931,10 +9990,10 @@
     </row>
     <row r="25" spans="1:10" ht="15">
       <c r="B25" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="C25" s="7"/>
-      <c r="D25" s="21"/>
+      <c r="D25" s="23"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="4"/>
@@ -9944,10 +10003,10 @@
     </row>
     <row r="26" spans="1:10" ht="15">
       <c r="B26" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="C26" s="7"/>
-      <c r="D26" s="21"/>
+      <c r="D26" s="23"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -9957,10 +10016,10 @@
     </row>
     <row r="27" spans="1:10" ht="15">
       <c r="B27" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="C27" s="7"/>
-      <c r="D27" s="21"/>
+      <c r="D27" s="23"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
@@ -9972,7 +10031,7 @@
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="21"/>
+      <c r="D28" s="23"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -9984,7 +10043,7 @@
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="21"/>
+      <c r="D29" s="23"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -9996,7 +10055,7 @@
       <c r="A30" s="4"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="21"/>
+      <c r="D30" s="23"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="4"/>
@@ -10008,7 +10067,7 @@
       <c r="A31" s="4"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="21"/>
+      <c r="D31" s="23"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="4"/>
@@ -10020,7 +10079,7 @@
       <c r="A32" s="4"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
-      <c r="D32" s="21"/>
+      <c r="D32" s="23"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="4"/>
@@ -10032,7 +10091,7 @@
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="21"/>
+      <c r="D33" s="23"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
@@ -10044,7 +10103,7 @@
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="21"/>
+      <c r="D34" s="23"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
       <c r="G34" s="4"/>
@@ -10056,7 +10115,7 @@
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="21"/>
+      <c r="D35" s="23"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
       <c r="G35" s="4"/>
@@ -10068,7 +10127,7 @@
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="7"/>
-      <c r="D36" s="21"/>
+      <c r="D36" s="23"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="4"/>
@@ -10080,7 +10139,7 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="21"/>
+      <c r="D37" s="23"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="4"/>
@@ -10092,7 +10151,7 @@
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="7"/>
-      <c r="D38" s="21"/>
+      <c r="D38" s="23"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="4"/>
@@ -10104,7 +10163,7 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="7"/>
-      <c r="D39" s="21"/>
+      <c r="D39" s="23"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="4"/>
@@ -10116,7 +10175,7 @@
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="7"/>
-      <c r="D40" s="21"/>
+      <c r="D40" s="23"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="4"/>
@@ -10128,7 +10187,7 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="21"/>
+      <c r="D41" s="23"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="4"/>
@@ -10140,7 +10199,7 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="21"/>
+      <c r="D42" s="23"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="4"/>
@@ -10152,7 +10211,7 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="21"/>
+      <c r="D43" s="23"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="4"/>
@@ -10164,7 +10223,7 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="7"/>
-      <c r="D44" s="21"/>
+      <c r="D44" s="23"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="4"/>
@@ -10176,7 +10235,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="21"/>
+      <c r="D45" s="23"/>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
       <c r="G45" s="4"/>
@@ -10188,7 +10247,7 @@
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="7"/>
-      <c r="D46" s="21"/>
+      <c r="D46" s="23"/>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
       <c r="G46" s="4"/>
@@ -10200,7 +10259,7 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="7"/>
-      <c r="D47" s="21"/>
+      <c r="D47" s="23"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
       <c r="G47" s="4"/>
@@ -10212,7 +10271,7 @@
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="7"/>
-      <c r="D48" s="21"/>
+      <c r="D48" s="23"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
       <c r="G48" s="4"/>
@@ -10224,7 +10283,7 @@
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="7"/>
-      <c r="D49" s="21"/>
+      <c r="D49" s="23"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
       <c r="G49" s="4"/>
@@ -10236,7 +10295,7 @@
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="21"/>
+      <c r="D50" s="23"/>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
       <c r="G50" s="4"/>
@@ -10248,7 +10307,7 @@
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="7"/>
-      <c r="D51" s="21"/>
+      <c r="D51" s="23"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
       <c r="G51" s="4"/>
@@ -10260,7 +10319,7 @@
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="7"/>
-      <c r="D52" s="21"/>
+      <c r="D52" s="23"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
       <c r="G52" s="4"/>
@@ -10272,7 +10331,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="21"/>
+      <c r="D53" s="23"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="4"/>
@@ -10284,7 +10343,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="21"/>
+      <c r="D54" s="23"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
       <c r="G54" s="4"/>
@@ -10296,7 +10355,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="7"/>
-      <c r="D55" s="21"/>
+      <c r="D55" s="23"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
       <c r="G55" s="4"/>
@@ -10308,7 +10367,7 @@
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="7"/>
-      <c r="D56" s="21"/>
+      <c r="D56" s="23"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
       <c r="G56" s="4"/>
@@ -10320,7 +10379,7 @@
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="7"/>
-      <c r="D57" s="21"/>
+      <c r="D57" s="23"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
       <c r="G57" s="4"/>
@@ -11242,6 +11301,11 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="E3:E4"/>
@@ -11249,11 +11313,6 @@
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="J3:J4"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="D3:D57"/>
     <mergeCell ref="J17:J23"/>
@@ -11283,41 +11342,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="32"/>
+      <c r="H1" s="35"/>
       <c r="I1" s="16" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" thickBot="1">
       <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -11326,101 +11385,139 @@
       </c>
       <c r="I2" s="16"/>
     </row>
-    <row r="3" spans="1:9" ht="159.4" customHeight="1">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="15"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="13"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="22"/>
+    <row r="3" spans="1:9" ht="15">
+      <c r="A3" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="37"/>
+      <c r="D3" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="24"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="I3" s="18"/>
+    </row>
+    <row r="4" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="37"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="25"/>
       <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
+      <c r="H4" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="I4" s="18"/>
     </row>
     <row r="5" spans="1:9" ht="15">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="14" t="s">
+        <v>31</v>
+      </c>
       <c r="C5" s="7"/>
-      <c r="D5" s="21"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+      <c r="H5" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="I5" s="4"/>
     </row>
     <row r="6" spans="1:9" ht="15">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="14" t="s">
+        <v>33</v>
+      </c>
       <c r="C6" s="7"/>
-      <c r="D6" s="21"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
+      <c r="H6" s="4" t="s">
+        <v>99</v>
+      </c>
       <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:9" ht="15">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="21"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="H7" s="4" t="s">
+        <v>100</v>
+      </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" ht="15">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
+      <c r="A8" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>27</v>
+      </c>
       <c r="C8" s="7"/>
-      <c r="D8" s="21"/>
+      <c r="D8" s="23"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="H8" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:9" ht="15">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="14" t="s">
+        <v>30</v>
+      </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="21"/>
+      <c r="D9" s="23"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="H9" s="4" t="s">
+        <v>102</v>
+      </c>
       <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" ht="15">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14" t="s">
+        <v>35</v>
+      </c>
       <c r="C10" s="7"/>
-      <c r="D10" s="21"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="H10" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" ht="15">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14" t="s">
+        <v>38</v>
+      </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="21"/>
+      <c r="D11" s="23"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="4"/>
@@ -11431,7 +11528,7 @@
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="21"/>
+      <c r="D12" s="23"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="4"/>
@@ -11442,7 +11539,7 @@
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="21"/>
+      <c r="D13" s="23"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="4"/>
@@ -11453,7 +11550,7 @@
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="21"/>
+      <c r="D14" s="23"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="4"/>
@@ -11464,7 +11561,7 @@
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="21"/>
+      <c r="D15" s="23"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="4"/>
@@ -11475,7 +11572,7 @@
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="21"/>
+      <c r="D16" s="23"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -11483,87 +11580,87 @@
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" ht="15">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
     </row>
     <row r="18" spans="1:9" ht="15">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
     </row>
     <row r="19" spans="1:9" ht="15">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
     </row>
     <row r="20" spans="1:9" ht="15">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="15"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
     </row>
     <row r="21" spans="1:9" ht="15">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="15"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
     </row>
     <row r="22" spans="1:9" ht="15">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
     </row>
     <row r="23" spans="1:9" ht="15">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="15"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
     </row>
     <row r="24" spans="1:9" ht="15">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="7"/>
-      <c r="D24" s="21"/>
+      <c r="D24" s="23"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
       <c r="G24" s="4"/>
@@ -11574,7 +11671,7 @@
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="21"/>
+      <c r="D25" s="23"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="4"/>
@@ -11585,7 +11682,7 @@
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="21"/>
+      <c r="D26" s="23"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -11596,7 +11693,7 @@
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="7"/>
-      <c r="D27" s="21"/>
+      <c r="D27" s="23"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
@@ -11607,7 +11704,7 @@
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="21"/>
+      <c r="D28" s="23"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -11618,7 +11715,7 @@
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="21"/>
+      <c r="D29" s="23"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -11629,7 +11726,7 @@
       <c r="A30" s="4"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="21"/>
+      <c r="D30" s="23"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="4"/>
@@ -11640,7 +11737,7 @@
       <c r="A31" s="4"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="21"/>
+      <c r="D31" s="23"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="4"/>
@@ -11651,7 +11748,7 @@
       <c r="A32" s="4"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
-      <c r="D32" s="21"/>
+      <c r="D32" s="23"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="4"/>
@@ -11662,7 +11759,7 @@
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="21"/>
+      <c r="D33" s="23"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
@@ -11673,7 +11770,7 @@
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="21"/>
+      <c r="D34" s="23"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
       <c r="G34" s="4"/>
@@ -11684,7 +11781,7 @@
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="21"/>
+      <c r="D35" s="23"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
       <c r="G35" s="4"/>
@@ -11695,7 +11792,7 @@
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="7"/>
-      <c r="D36" s="21"/>
+      <c r="D36" s="23"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="4"/>
@@ -11706,7 +11803,7 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="21"/>
+      <c r="D37" s="23"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="4"/>
@@ -11717,7 +11814,7 @@
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="7"/>
-      <c r="D38" s="21"/>
+      <c r="D38" s="23"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="4"/>
@@ -11728,7 +11825,7 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="7"/>
-      <c r="D39" s="21"/>
+      <c r="D39" s="23"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="4"/>
@@ -11739,7 +11836,7 @@
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="7"/>
-      <c r="D40" s="21"/>
+      <c r="D40" s="23"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="4"/>
@@ -11750,7 +11847,7 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="21"/>
+      <c r="D41" s="23"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="4"/>
@@ -11761,7 +11858,7 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="21"/>
+      <c r="D42" s="23"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="4"/>
@@ -11772,7 +11869,7 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="21"/>
+      <c r="D43" s="23"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="4"/>
@@ -11783,7 +11880,7 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="7"/>
-      <c r="D44" s="21"/>
+      <c r="D44" s="23"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="4"/>
@@ -11794,7 +11891,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="21"/>
+      <c r="D45" s="23"/>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
       <c r="G45" s="4"/>
@@ -11805,7 +11902,7 @@
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="7"/>
-      <c r="D46" s="21"/>
+      <c r="D46" s="23"/>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
       <c r="G46" s="4"/>
@@ -11816,7 +11913,7 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="7"/>
-      <c r="D47" s="21"/>
+      <c r="D47" s="23"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
       <c r="G47" s="4"/>
@@ -11827,7 +11924,7 @@
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="7"/>
-      <c r="D48" s="21"/>
+      <c r="D48" s="23"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
       <c r="G48" s="4"/>
@@ -11838,7 +11935,7 @@
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="7"/>
-      <c r="D49" s="21"/>
+      <c r="D49" s="23"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
       <c r="G49" s="4"/>
@@ -11849,7 +11946,7 @@
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="21"/>
+      <c r="D50" s="23"/>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
       <c r="G50" s="4"/>
@@ -11860,7 +11957,7 @@
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="7"/>
-      <c r="D51" s="21"/>
+      <c r="D51" s="23"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
       <c r="G51" s="4"/>
@@ -11871,7 +11968,7 @@
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="7"/>
-      <c r="D52" s="21"/>
+      <c r="D52" s="23"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
       <c r="G52" s="4"/>
@@ -11882,7 +11979,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="21"/>
+      <c r="D53" s="23"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="4"/>
@@ -11893,7 +11990,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="21"/>
+      <c r="D54" s="23"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
       <c r="G54" s="4"/>
@@ -11904,7 +12001,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="7"/>
-      <c r="D55" s="21"/>
+      <c r="D55" s="23"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
       <c r="G55" s="4"/>
@@ -11915,7 +12012,7 @@
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="7"/>
-      <c r="D56" s="21"/>
+      <c r="D56" s="23"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
       <c r="G56" s="4"/>
@@ -11926,7 +12023,7 @@
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="7"/>
-      <c r="D57" s="21"/>
+      <c r="D57" s="23"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
       <c r="G57" s="4"/>
@@ -12770,16 +12867,16 @@
       <c r="I133" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="16">
+    <mergeCell ref="I17:I23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D57"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:C2"/>
@@ -12787,13 +12884,6 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I17:I23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Mapping Template BrotZeit.xlsx
+++ b/Mapping Template BrotZeit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alfa\Documents\Data Engineer\Projekt\BackZeit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A38082A2-E033-4730-9B0B-4D94FF9C439A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D411F67-5ACF-4B13-97D8-BCE881ACABA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{1083ED64-F082-44F9-9F2A-19C2CA2699CD}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" xr2:uid="{1083ED64-F082-44F9-9F2A-19C2CA2699CD}"/>
   </bookViews>
   <sheets>
     <sheet name="D_Filiale" sheetId="9" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="D_Stunde" sheetId="5" r:id="rId5"/>
     <sheet name="D_Produkt" sheetId="1" r:id="rId6"/>
     <sheet name="F_Verkäufe" sheetId="4" r:id="rId7"/>
+    <sheet name="F_Verkäuferumsatz" sheetId="10" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="107">
   <si>
     <t>Notes</t>
   </si>
@@ -183,9 +184,6 @@
     <t>D_Stunden</t>
   </si>
   <si>
-    <t>StundeID</t>
-  </si>
-  <si>
     <t>[FilialID]</t>
   </si>
   <si>
@@ -247,9 +245,6 @@
   </si>
   <si>
     <t>[Jahr]</t>
-  </si>
-  <si>
-    <t>[TagID]</t>
   </si>
   <si>
     <t>[Stunde]</t>
@@ -358,6 +353,15 @@
   </si>
   <si>
     <t>wird verkauft</t>
+  </si>
+  <si>
+    <t>F_Verkäuferumsatz</t>
+  </si>
+  <si>
+    <t>[DatumID]</t>
+  </si>
+  <si>
+    <t>[ZeitID]</t>
   </si>
 </sst>
 </file>
@@ -640,7 +644,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -675,11 +679,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -688,9 +703,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -723,8 +735,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1075,30 +1086,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="35"/>
+      <c r="H1" s="41"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="24" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1109,10 +1120,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1120,62 +1131,62 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="16"/>
+      <c r="J2" s="24"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="22" t="s">
+      <c r="B3" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="27"/>
+      <c r="D3" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="H3" s="26" t="s">
-        <v>48</v>
+      <c r="H3" s="32" t="s">
+        <v>47</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="18"/>
+      <c r="J3" s="21"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="18"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
       <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="18"/>
+      <c r="J4" s="21"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5" s="11"/>
-      <c r="D5" s="23"/>
+      <c r="D5" s="30"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
       <c r="H5" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I5" s="10" t="s">
         <v>19</v>
@@ -1185,15 +1196,15 @@
     <row r="6" spans="1:10" ht="15">
       <c r="A6" s="10"/>
       <c r="B6" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6" s="11"/>
-      <c r="D6" s="23"/>
+      <c r="D6" s="30"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
@@ -1202,7 +1213,7 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="23"/>
+      <c r="D7" s="30"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
@@ -1215,10 +1226,10 @@
         <v>28</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="23"/>
+      <c r="D8" s="30"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
@@ -1232,7 +1243,7 @@
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="23"/>
+      <c r="D9" s="30"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -1246,7 +1257,7 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="23"/>
+      <c r="D10" s="30"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -1260,7 +1271,7 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="23"/>
+      <c r="D11" s="30"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -1274,7 +1285,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="23"/>
+      <c r="D12" s="30"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -1286,7 +1297,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="23"/>
+      <c r="D13" s="30"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -1300,7 +1311,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="23"/>
+      <c r="D14" s="30"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -1312,7 +1323,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="23"/>
+      <c r="D15" s="30"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
@@ -1326,7 +1337,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="23"/>
+      <c r="D16" s="30"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -1335,94 +1346,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="36"/>
-      <c r="B17" s="36"/>
+      <c r="A17" s="22"/>
+      <c r="B17" s="22"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="18"/>
+      <c r="J17" s="21"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="36"/>
-      <c r="B18" s="36"/>
+      <c r="A18" s="22"/>
+      <c r="B18" s="22"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="18"/>
+      <c r="J18" s="21"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="36"/>
-      <c r="B19" s="36"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="22"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="18"/>
+      <c r="J19" s="21"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="36"/>
-      <c r="B20" s="36"/>
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="18"/>
+      <c r="J20" s="21"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="18"/>
+      <c r="J21" s="21"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="36"/>
-      <c r="B22" s="36"/>
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="18"/>
+      <c r="J22" s="21"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="36"/>
-      <c r="B23" s="36"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="18"/>
+      <c r="J23" s="21"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="23"/>
+      <c r="D24" s="30"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -1434,7 +1445,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="23"/>
+      <c r="D25" s="30"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -1446,7 +1457,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="23"/>
+      <c r="D26" s="30"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -1458,7 +1469,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="23"/>
+      <c r="D27" s="30"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -1470,7 +1481,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="23"/>
+      <c r="D28" s="30"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -1482,7 +1493,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="23"/>
+      <c r="D29" s="30"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -1494,7 +1505,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="23"/>
+      <c r="D30" s="30"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -1506,7 +1517,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="23"/>
+      <c r="D31" s="30"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -1518,7 +1529,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="23"/>
+      <c r="D32" s="30"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -1530,7 +1541,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="23"/>
+      <c r="D33" s="30"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -1542,7 +1553,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="23"/>
+      <c r="D34" s="30"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -1554,7 +1565,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="23"/>
+      <c r="D35" s="30"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -1566,7 +1577,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="23"/>
+      <c r="D36" s="30"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -1578,7 +1589,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="23"/>
+      <c r="D37" s="30"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -1590,7 +1601,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="23"/>
+      <c r="D38" s="30"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -1602,7 +1613,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="23"/>
+      <c r="D39" s="30"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -1614,7 +1625,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="23"/>
+      <c r="D40" s="30"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -1626,7 +1637,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="23"/>
+      <c r="D41" s="30"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -1638,7 +1649,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="23"/>
+      <c r="D42" s="30"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -1650,7 +1661,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="23"/>
+      <c r="D43" s="30"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -1662,7 +1673,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="23"/>
+      <c r="D44" s="30"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -1674,7 +1685,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="23"/>
+      <c r="D45" s="30"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -1686,7 +1697,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="23"/>
+      <c r="D46" s="30"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -1698,7 +1709,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="23"/>
+      <c r="D47" s="30"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -1710,7 +1721,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="23"/>
+      <c r="D48" s="30"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -1722,7 +1733,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="23"/>
+      <c r="D49" s="30"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -1734,7 +1745,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="23"/>
+      <c r="D50" s="30"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -1746,7 +1757,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="23"/>
+      <c r="D51" s="30"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -1758,7 +1769,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="23"/>
+      <c r="D52" s="30"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -1770,7 +1781,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="23"/>
+      <c r="D53" s="30"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -1782,7 +1793,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="23"/>
+      <c r="D54" s="30"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -1794,7 +1805,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="23"/>
+      <c r="D55" s="30"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -1806,7 +1817,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="23"/>
+      <c r="D56" s="30"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -1818,7 +1829,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="23"/>
+      <c r="D57" s="30"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -2740,13 +2751,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -2763,6 +2767,13 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2786,30 +2797,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="35"/>
+      <c r="H1" s="41"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="24" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2820,10 +2831,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2831,62 +2842,62 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="16"/>
+      <c r="J2" s="24"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="22" t="s">
+      <c r="B3" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="27"/>
+      <c r="D3" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="26" t="s">
-        <v>54</v>
+      <c r="H3" s="32" t="s">
+        <v>53</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="18"/>
+      <c r="J3" s="21"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
       <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="18"/>
+      <c r="J4" s="21"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" s="11"/>
-      <c r="D5" s="23"/>
+      <c r="D5" s="30"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
       <c r="H5" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I5" s="10" t="s">
         <v>19</v>
@@ -2896,10 +2907,10 @@
     <row r="6" spans="1:10" ht="15">
       <c r="A6" s="10"/>
       <c r="B6" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C6" s="11"/>
-      <c r="D6" s="23"/>
+      <c r="D6" s="30"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
@@ -2911,7 +2922,7 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="23"/>
+      <c r="D7" s="30"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
@@ -2923,7 +2934,7 @@
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="23"/>
+      <c r="D8" s="30"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
@@ -2937,7 +2948,7 @@
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="23"/>
+      <c r="D9" s="30"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -2951,7 +2962,7 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="23"/>
+      <c r="D10" s="30"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -2965,7 +2976,7 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="23"/>
+      <c r="D11" s="30"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -2979,7 +2990,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="23"/>
+      <c r="D12" s="30"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -2991,7 +3002,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="23"/>
+      <c r="D13" s="30"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -3005,7 +3016,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="23"/>
+      <c r="D14" s="30"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -3017,7 +3028,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="23"/>
+      <c r="D15" s="30"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
@@ -3031,7 +3042,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="23"/>
+      <c r="D16" s="30"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -3043,91 +3054,91 @@
       <c r="A17" s="15"/>
       <c r="B17" s="15"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="18"/>
+      <c r="J17" s="21"/>
     </row>
     <row r="18" spans="1:10" ht="15">
       <c r="A18" s="15"/>
       <c r="B18" s="15"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="18"/>
+      <c r="J18" s="21"/>
     </row>
     <row r="19" spans="1:10" ht="15">
       <c r="A19" s="15"/>
       <c r="B19" s="15"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="18"/>
+      <c r="J19" s="21"/>
     </row>
     <row r="20" spans="1:10" ht="15">
       <c r="A20" s="15"/>
       <c r="B20" s="15"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="18"/>
+      <c r="J20" s="21"/>
     </row>
     <row r="21" spans="1:10" ht="15">
       <c r="A21" s="15"/>
       <c r="B21" s="15"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="18"/>
+      <c r="J21" s="21"/>
     </row>
     <row r="22" spans="1:10" ht="15">
       <c r="A22" s="15"/>
       <c r="B22" s="15"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="18"/>
+      <c r="J22" s="21"/>
     </row>
     <row r="23" spans="1:10" ht="15">
       <c r="A23" s="15"/>
       <c r="B23" s="15"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="18"/>
+      <c r="J23" s="21"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="23"/>
+      <c r="D24" s="30"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -3139,7 +3150,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="23"/>
+      <c r="D25" s="30"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -3151,7 +3162,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="23"/>
+      <c r="D26" s="30"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -3163,7 +3174,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="23"/>
+      <c r="D27" s="30"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -3175,7 +3186,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="23"/>
+      <c r="D28" s="30"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -3187,7 +3198,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="23"/>
+      <c r="D29" s="30"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -3199,7 +3210,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="23"/>
+      <c r="D30" s="30"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -3211,7 +3222,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="23"/>
+      <c r="D31" s="30"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -3223,7 +3234,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="23"/>
+      <c r="D32" s="30"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -3235,7 +3246,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="23"/>
+      <c r="D33" s="30"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -3247,7 +3258,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="23"/>
+      <c r="D34" s="30"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -3259,7 +3270,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="23"/>
+      <c r="D35" s="30"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -3271,7 +3282,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="23"/>
+      <c r="D36" s="30"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -3283,7 +3294,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="23"/>
+      <c r="D37" s="30"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -3295,7 +3306,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="23"/>
+      <c r="D38" s="30"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -3307,7 +3318,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="23"/>
+      <c r="D39" s="30"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -3319,7 +3330,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="23"/>
+      <c r="D40" s="30"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -3331,7 +3342,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="23"/>
+      <c r="D41" s="30"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -3343,7 +3354,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="23"/>
+      <c r="D42" s="30"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -3355,7 +3366,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="23"/>
+      <c r="D43" s="30"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -3367,7 +3378,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="23"/>
+      <c r="D44" s="30"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -3379,7 +3390,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="23"/>
+      <c r="D45" s="30"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -3391,7 +3402,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="23"/>
+      <c r="D46" s="30"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -3403,7 +3414,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="23"/>
+      <c r="D47" s="30"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -3415,7 +3426,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="23"/>
+      <c r="D48" s="30"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -3427,7 +3438,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="23"/>
+      <c r="D49" s="30"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -3439,7 +3450,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="23"/>
+      <c r="D50" s="30"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -3451,7 +3462,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="23"/>
+      <c r="D51" s="30"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -3463,7 +3474,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="23"/>
+      <c r="D52" s="30"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -3475,7 +3486,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="23"/>
+      <c r="D53" s="30"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -3487,7 +3498,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="23"/>
+      <c r="D54" s="30"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -3499,7 +3510,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="23"/>
+      <c r="D55" s="30"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -3511,7 +3522,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="23"/>
+      <c r="D56" s="30"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -3523,7 +3534,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="23"/>
+      <c r="D57" s="30"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -4445,11 +4456,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -4466,6 +4472,11 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4489,30 +4500,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="35"/>
+      <c r="H1" s="41"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="24" t="s">
         <v>0</v>
       </c>
     </row>
@@ -4523,10 +4534,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -4534,62 +4545,62 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="16"/>
+      <c r="J2" s="24"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="22" t="s">
+      <c r="B3" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="27"/>
+      <c r="D3" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="17" t="s">
-        <v>57</v>
+      <c r="H3" s="25" t="s">
+        <v>56</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="18"/>
+      <c r="J3" s="21"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
       <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="18"/>
+      <c r="J4" s="21"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5" s="11"/>
-      <c r="D5" s="23"/>
+      <c r="D5" s="30"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
       <c r="H5" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I5" s="10" t="s">
         <v>19</v>
@@ -4600,13 +4611,11 @@
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
       <c r="C6" s="11"/>
-      <c r="D6" s="23"/>
+      <c r="D6" s="30"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="12" t="s">
-        <v>62</v>
-      </c>
+      <c r="H6" s="12"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
     </row>
@@ -4614,13 +4623,11 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="23"/>
+      <c r="D7" s="30"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
-      <c r="H7" s="10" t="s">
-        <v>63</v>
-      </c>
+      <c r="H7" s="10"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
     </row>
@@ -4629,16 +4636,14 @@
         <v>40</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="23"/>
+      <c r="D8" s="30"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
-      <c r="H8" s="10" t="s">
-        <v>64</v>
-      </c>
+      <c r="H8" s="10"/>
       <c r="I8" s="10" t="s">
         <v>20</v>
       </c>
@@ -4647,10 +4652,10 @@
     <row r="9" spans="1:10" ht="15">
       <c r="A9" s="10"/>
       <c r="B9" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C9" s="10"/>
-      <c r="D9" s="23"/>
+      <c r="D9" s="30"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -4664,7 +4669,7 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="23"/>
+      <c r="D10" s="30"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -4678,7 +4683,7 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="23"/>
+      <c r="D11" s="30"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -4692,7 +4697,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="23"/>
+      <c r="D12" s="30"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -4704,7 +4709,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="23"/>
+      <c r="D13" s="30"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -4718,7 +4723,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="23"/>
+      <c r="D14" s="30"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -4730,7 +4735,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="23"/>
+      <c r="D15" s="30"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
@@ -4744,7 +4749,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="23"/>
+      <c r="D16" s="30"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -4753,94 +4758,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="36"/>
-      <c r="B17" s="36"/>
+      <c r="A17" s="22"/>
+      <c r="B17" s="22"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="18"/>
+      <c r="J17" s="21"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="36"/>
-      <c r="B18" s="36"/>
+      <c r="A18" s="22"/>
+      <c r="B18" s="22"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="18"/>
+      <c r="J18" s="21"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="36"/>
-      <c r="B19" s="36"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="22"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="18"/>
+      <c r="J19" s="21"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="36"/>
-      <c r="B20" s="36"/>
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="18"/>
+      <c r="J20" s="21"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="18"/>
+      <c r="J21" s="21"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="36"/>
-      <c r="B22" s="36"/>
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="18"/>
+      <c r="J22" s="21"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="36"/>
-      <c r="B23" s="36"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="18"/>
+      <c r="J23" s="21"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="23"/>
+      <c r="D24" s="30"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -4852,7 +4857,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="23"/>
+      <c r="D25" s="30"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -4864,7 +4869,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="23"/>
+      <c r="D26" s="30"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -4876,7 +4881,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="23"/>
+      <c r="D27" s="30"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -4888,7 +4893,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="23"/>
+      <c r="D28" s="30"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -4900,7 +4905,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="23"/>
+      <c r="D29" s="30"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -4912,7 +4917,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="23"/>
+      <c r="D30" s="30"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -4924,7 +4929,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="23"/>
+      <c r="D31" s="30"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -4936,7 +4941,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="23"/>
+      <c r="D32" s="30"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -4948,7 +4953,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="23"/>
+      <c r="D33" s="30"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -4960,7 +4965,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="23"/>
+      <c r="D34" s="30"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -4972,7 +4977,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="23"/>
+      <c r="D35" s="30"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -4984,7 +4989,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="23"/>
+      <c r="D36" s="30"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -4996,7 +5001,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="23"/>
+      <c r="D37" s="30"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -5008,7 +5013,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="23"/>
+      <c r="D38" s="30"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -5020,7 +5025,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="23"/>
+      <c r="D39" s="30"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -5032,7 +5037,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="23"/>
+      <c r="D40" s="30"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -5044,7 +5049,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="23"/>
+      <c r="D41" s="30"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -5056,7 +5061,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="23"/>
+      <c r="D42" s="30"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -5068,7 +5073,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="23"/>
+      <c r="D43" s="30"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -5080,7 +5085,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="23"/>
+      <c r="D44" s="30"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -5092,7 +5097,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="23"/>
+      <c r="D45" s="30"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -5104,7 +5109,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="23"/>
+      <c r="D46" s="30"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -5116,7 +5121,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="23"/>
+      <c r="D47" s="30"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -5128,7 +5133,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="23"/>
+      <c r="D48" s="30"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -5140,7 +5145,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="23"/>
+      <c r="D49" s="30"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -5152,7 +5157,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="23"/>
+      <c r="D50" s="30"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -5164,7 +5169,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="23"/>
+      <c r="D51" s="30"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -5176,7 +5181,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="23"/>
+      <c r="D52" s="30"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -5188,7 +5193,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="23"/>
+      <c r="D53" s="30"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -5200,7 +5205,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="23"/>
+      <c r="D54" s="30"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -5212,7 +5217,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="23"/>
+      <c r="D55" s="30"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -5224,7 +5229,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="23"/>
+      <c r="D56" s="30"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -5236,7 +5241,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="23"/>
+      <c r="D57" s="30"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -6158,13 +6163,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -6181,6 +6179,13 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6204,30 +6209,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="35"/>
+      <c r="H1" s="41"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="24" t="s">
         <v>0</v>
       </c>
     </row>
@@ -6238,10 +6243,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -6249,56 +6254,56 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="16"/>
+      <c r="J2" s="24"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="22" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="H3" s="26" t="s">
-        <v>65</v>
+      <c r="H3" s="32" t="s">
+        <v>64</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="18"/>
+      <c r="J3" s="21"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
       <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="18"/>
+      <c r="J4" s="21"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="10"/>
       <c r="C5" s="11"/>
-      <c r="D5" s="23"/>
+      <c r="D5" s="30"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
       <c r="H5" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I5" s="10" t="s">
         <v>19</v>
@@ -6309,12 +6314,12 @@
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
       <c r="C6" s="11"/>
-      <c r="D6" s="23"/>
+      <c r="D6" s="30"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
@@ -6323,12 +6328,12 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="23"/>
+      <c r="D7" s="30"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
       <c r="H7" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
@@ -6337,12 +6342,12 @@
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="23"/>
+      <c r="D8" s="30"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
       <c r="H8" s="10" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>20</v>
@@ -6353,7 +6358,7 @@
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="23"/>
+      <c r="D9" s="30"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -6367,7 +6372,7 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="23"/>
+      <c r="D10" s="30"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -6381,7 +6386,7 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="23"/>
+      <c r="D11" s="30"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -6395,7 +6400,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="23"/>
+      <c r="D12" s="30"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -6407,7 +6412,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="23"/>
+      <c r="D13" s="30"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -6421,7 +6426,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="23"/>
+      <c r="D14" s="30"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -6433,7 +6438,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="23"/>
+      <c r="D15" s="30"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
@@ -6447,7 +6452,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="23"/>
+      <c r="D16" s="30"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -6456,94 +6461,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="36"/>
-      <c r="B17" s="36"/>
+      <c r="A17" s="22"/>
+      <c r="B17" s="22"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="18"/>
+      <c r="J17" s="21"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="36"/>
-      <c r="B18" s="36"/>
+      <c r="A18" s="22"/>
+      <c r="B18" s="22"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="18"/>
+      <c r="J18" s="21"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="36"/>
-      <c r="B19" s="36"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="22"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="18"/>
+      <c r="J19" s="21"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="36"/>
-      <c r="B20" s="36"/>
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="18"/>
+      <c r="J20" s="21"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="18"/>
+      <c r="J21" s="21"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="36"/>
-      <c r="B22" s="36"/>
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="18"/>
+      <c r="J22" s="21"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="36"/>
-      <c r="B23" s="36"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="18"/>
+      <c r="J23" s="21"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="23"/>
+      <c r="D24" s="30"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -6555,7 +6560,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="23"/>
+      <c r="D25" s="30"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -6567,7 +6572,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="23"/>
+      <c r="D26" s="30"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -6579,7 +6584,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="23"/>
+      <c r="D27" s="30"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -6591,7 +6596,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="23"/>
+      <c r="D28" s="30"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -6603,7 +6608,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="23"/>
+      <c r="D29" s="30"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -6615,7 +6620,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="23"/>
+      <c r="D30" s="30"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -6627,7 +6632,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="23"/>
+      <c r="D31" s="30"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -6639,7 +6644,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="23"/>
+      <c r="D32" s="30"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -6651,7 +6656,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="23"/>
+      <c r="D33" s="30"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -6663,7 +6668,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="23"/>
+      <c r="D34" s="30"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -6675,7 +6680,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="23"/>
+      <c r="D35" s="30"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -6687,7 +6692,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="23"/>
+      <c r="D36" s="30"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -6699,7 +6704,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="23"/>
+      <c r="D37" s="30"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -6711,7 +6716,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="23"/>
+      <c r="D38" s="30"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -6723,7 +6728,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="23"/>
+      <c r="D39" s="30"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -6735,7 +6740,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="23"/>
+      <c r="D40" s="30"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -6747,7 +6752,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="23"/>
+      <c r="D41" s="30"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -6759,7 +6764,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="23"/>
+      <c r="D42" s="30"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -6771,7 +6776,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="23"/>
+      <c r="D43" s="30"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -6783,7 +6788,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="23"/>
+      <c r="D44" s="30"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -6795,7 +6800,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="23"/>
+      <c r="D45" s="30"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -6807,7 +6812,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="23"/>
+      <c r="D46" s="30"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -6819,7 +6824,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="23"/>
+      <c r="D47" s="30"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -6831,7 +6836,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="23"/>
+      <c r="D48" s="30"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -6843,7 +6848,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="23"/>
+      <c r="D49" s="30"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -6855,7 +6860,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="23"/>
+      <c r="D50" s="30"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -6867,7 +6872,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="23"/>
+      <c r="D51" s="30"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -6879,7 +6884,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="23"/>
+      <c r="D52" s="30"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -6891,7 +6896,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="23"/>
+      <c r="D53" s="30"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -6903,7 +6908,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="23"/>
+      <c r="D54" s="30"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -6915,7 +6920,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="23"/>
+      <c r="D55" s="30"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -6927,7 +6932,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="23"/>
+      <c r="D56" s="30"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -6939,7 +6944,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="23"/>
+      <c r="D57" s="30"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -7861,13 +7866,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -7884,6 +7882,13 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7907,30 +7912,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="35"/>
+      <c r="H1" s="41"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="24" t="s">
         <v>0</v>
       </c>
     </row>
@@ -7941,10 +7946,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -7952,56 +7957,56 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="16"/>
+      <c r="J2" s="24"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="22" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="26" t="s">
-        <v>70</v>
+      <c r="H3" s="32" t="s">
+        <v>68</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="18"/>
+      <c r="J3" s="21"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
       <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="18"/>
+      <c r="J4" s="21"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="10"/>
       <c r="C5" s="11"/>
-      <c r="D5" s="23"/>
+      <c r="D5" s="30"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
       <c r="H5" s="10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I5" s="10" t="s">
         <v>19</v>
@@ -8012,12 +8017,12 @@
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
       <c r="C6" s="11"/>
-      <c r="D6" s="23"/>
+      <c r="D6" s="30"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10" t="s">
-        <v>47</v>
+        <v>106</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
@@ -8026,7 +8031,7 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="23"/>
+      <c r="D7" s="30"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
@@ -8038,7 +8043,7 @@
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="23"/>
+      <c r="D8" s="30"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
@@ -8052,7 +8057,7 @@
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="23"/>
+      <c r="D9" s="30"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -8066,7 +8071,7 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="23"/>
+      <c r="D10" s="30"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -8080,7 +8085,7 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="23"/>
+      <c r="D11" s="30"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -8094,7 +8099,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="23"/>
+      <c r="D12" s="30"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -8106,7 +8111,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="23"/>
+      <c r="D13" s="30"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -8120,7 +8125,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="23"/>
+      <c r="D14" s="30"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -8132,7 +8137,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="23"/>
+      <c r="D15" s="30"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
@@ -8146,7 +8151,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="23"/>
+      <c r="D16" s="30"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -8155,94 +8160,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="36"/>
-      <c r="B17" s="36"/>
+      <c r="A17" s="22"/>
+      <c r="B17" s="22"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="18"/>
+      <c r="J17" s="21"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="36"/>
-      <c r="B18" s="36"/>
+      <c r="A18" s="22"/>
+      <c r="B18" s="22"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="18"/>
+      <c r="J18" s="21"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="36"/>
-      <c r="B19" s="36"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="22"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="18"/>
+      <c r="J19" s="21"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="36"/>
-      <c r="B20" s="36"/>
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="18"/>
+      <c r="J20" s="21"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="18"/>
+      <c r="J21" s="21"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="36"/>
-      <c r="B22" s="36"/>
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="18"/>
+      <c r="J22" s="21"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="36"/>
-      <c r="B23" s="36"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="18"/>
+      <c r="J23" s="21"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="23"/>
+      <c r="D24" s="30"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -8254,7 +8259,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="23"/>
+      <c r="D25" s="30"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -8266,7 +8271,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="23"/>
+      <c r="D26" s="30"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -8278,7 +8283,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="23"/>
+      <c r="D27" s="30"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -8290,7 +8295,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="23"/>
+      <c r="D28" s="30"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -8302,7 +8307,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="23"/>
+      <c r="D29" s="30"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -8314,7 +8319,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="23"/>
+      <c r="D30" s="30"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -8326,7 +8331,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="23"/>
+      <c r="D31" s="30"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -8338,7 +8343,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="23"/>
+      <c r="D32" s="30"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -8350,7 +8355,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="23"/>
+      <c r="D33" s="30"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -8362,7 +8367,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="23"/>
+      <c r="D34" s="30"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -8374,7 +8379,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="23"/>
+      <c r="D35" s="30"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -8386,7 +8391,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="23"/>
+      <c r="D36" s="30"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -8398,7 +8403,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="23"/>
+      <c r="D37" s="30"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -8410,7 +8415,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="23"/>
+      <c r="D38" s="30"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -8422,7 +8427,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="23"/>
+      <c r="D39" s="30"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -8434,7 +8439,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="23"/>
+      <c r="D40" s="30"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -8446,7 +8451,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="23"/>
+      <c r="D41" s="30"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -8458,7 +8463,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="23"/>
+      <c r="D42" s="30"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -8470,7 +8475,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="23"/>
+      <c r="D43" s="30"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -8482,7 +8487,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="23"/>
+      <c r="D44" s="30"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -8494,7 +8499,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="23"/>
+      <c r="D45" s="30"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -8506,7 +8511,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="23"/>
+      <c r="D46" s="30"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -8518,7 +8523,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="23"/>
+      <c r="D47" s="30"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -8530,7 +8535,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="23"/>
+      <c r="D48" s="30"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -8542,7 +8547,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="23"/>
+      <c r="D49" s="30"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -8554,7 +8559,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="23"/>
+      <c r="D50" s="30"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -8566,7 +8571,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="23"/>
+      <c r="D51" s="30"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -8578,7 +8583,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="23"/>
+      <c r="D52" s="30"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -8590,7 +8595,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="23"/>
+      <c r="D53" s="30"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -8602,7 +8607,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="23"/>
+      <c r="D54" s="30"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -8614,7 +8619,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="23"/>
+      <c r="D55" s="30"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -8626,7 +8631,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="23"/>
+      <c r="D56" s="30"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -8638,7 +8643,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="23"/>
+      <c r="D57" s="30"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -9560,13 +9565,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -9583,6 +9581,13 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9606,30 +9611,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="35"/>
+      <c r="H1" s="41"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="24" t="s">
         <v>0</v>
       </c>
     </row>
@@ -9640,10 +9645,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -9651,62 +9656,62 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="16"/>
+      <c r="J2" s="24"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A3" t="s">
         <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="27"/>
+      <c r="D3" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="26" t="s">
-        <v>72</v>
+      <c r="H3" s="32" t="s">
+        <v>70</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="18"/>
+      <c r="J3" s="21"/>
     </row>
     <row r="4" spans="1:10" ht="15">
       <c r="B4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
+        <v>73</v>
+      </c>
+      <c r="C4" s="28"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
       <c r="I4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="18"/>
+      <c r="J4" s="21"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="B5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C5" s="7"/>
-      <c r="D5" s="23"/>
+      <c r="D5" s="30"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>19</v>
@@ -9715,42 +9720,42 @@
     </row>
     <row r="6" spans="1:10" ht="15">
       <c r="B6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C6" s="7"/>
-      <c r="D6" s="23"/>
+      <c r="D6" s="30"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:10" ht="15">
       <c r="B7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C7" s="7"/>
-      <c r="D7" s="23"/>
+      <c r="D7" s="30"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
     </row>
     <row r="8" spans="1:10" ht="15">
       <c r="C8" s="7"/>
-      <c r="D8" s="23"/>
+      <c r="D8" s="30"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>20</v>
@@ -9762,15 +9767,15 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="23"/>
+      <c r="D9" s="30"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>21</v>
@@ -9779,15 +9784,15 @@
     </row>
     <row r="10" spans="1:10" ht="15">
       <c r="B10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C10" s="7"/>
-      <c r="D10" s="23"/>
+      <c r="D10" s="30"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>23</v>
@@ -9796,15 +9801,15 @@
     </row>
     <row r="11" spans="1:10" ht="15">
       <c r="B11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="23"/>
+      <c r="D11" s="30"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>22</v>
@@ -9813,30 +9818,30 @@
     </row>
     <row r="12" spans="1:10" ht="15">
       <c r="B12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C12" s="7"/>
-      <c r="D12" s="23"/>
+      <c r="D12" s="30"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
     </row>
     <row r="13" spans="1:10" ht="15">
       <c r="B13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C13" s="7"/>
-      <c r="D13" s="23"/>
+      <c r="D13" s="30"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>24</v>
@@ -9845,7 +9850,7 @@
     </row>
     <row r="14" spans="1:10" ht="15">
       <c r="C14" s="7"/>
-      <c r="D14" s="23"/>
+      <c r="D14" s="30"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="4"/>
@@ -9858,10 +9863,10 @@
         <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C15" s="7"/>
-      <c r="D15" s="23"/>
+      <c r="D15" s="30"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="4"/>
@@ -9873,10 +9878,10 @@
     </row>
     <row r="16" spans="1:10" ht="15">
       <c r="B16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C16" s="7"/>
-      <c r="D16" s="23"/>
+      <c r="D16" s="30"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -9886,101 +9891,101 @@
     </row>
     <row r="17" spans="1:10" ht="15">
       <c r="B17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C17" s="8"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="18"/>
+      <c r="J17" s="21"/>
     </row>
     <row r="18" spans="1:10" ht="15">
       <c r="B18" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C18" s="8"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
       <c r="I18" s="4"/>
-      <c r="J18" s="18"/>
+      <c r="J18" s="21"/>
     </row>
     <row r="19" spans="1:10" ht="15">
       <c r="C19" s="8"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
       <c r="I19" s="4"/>
-      <c r="J19" s="18"/>
+      <c r="J19" s="21"/>
     </row>
     <row r="20" spans="1:10" ht="15">
       <c r="A20" t="s">
         <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C20" s="8"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="18"/>
+      <c r="J20" s="21"/>
     </row>
     <row r="21" spans="1:10" ht="15">
       <c r="B21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C21" s="8"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="18"/>
+      <c r="J21" s="21"/>
     </row>
     <row r="22" spans="1:10" ht="15">
       <c r="B22" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C22" s="8"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
       <c r="I22" s="4"/>
-      <c r="J22" s="18"/>
+      <c r="J22" s="21"/>
     </row>
     <row r="23" spans="1:10" ht="15">
       <c r="B23" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C23" s="8"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
       <c r="I23" s="4"/>
-      <c r="J23" s="18"/>
+      <c r="J23" s="21"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="B24" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C24" s="7"/>
-      <c r="D24" s="23"/>
+      <c r="D24" s="30"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
       <c r="G24" s="4"/>
@@ -9990,10 +9995,10 @@
     </row>
     <row r="25" spans="1:10" ht="15">
       <c r="B25" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C25" s="7"/>
-      <c r="D25" s="23"/>
+      <c r="D25" s="30"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="4"/>
@@ -10003,10 +10008,10 @@
     </row>
     <row r="26" spans="1:10" ht="15">
       <c r="B26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C26" s="7"/>
-      <c r="D26" s="23"/>
+      <c r="D26" s="30"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -10016,10 +10021,10 @@
     </row>
     <row r="27" spans="1:10" ht="15">
       <c r="B27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C27" s="7"/>
-      <c r="D27" s="23"/>
+      <c r="D27" s="30"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
@@ -10031,7 +10036,7 @@
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="23"/>
+      <c r="D28" s="30"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -10043,7 +10048,7 @@
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="23"/>
+      <c r="D29" s="30"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -10055,7 +10060,7 @@
       <c r="A30" s="4"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="23"/>
+      <c r="D30" s="30"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="4"/>
@@ -10067,7 +10072,7 @@
       <c r="A31" s="4"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="23"/>
+      <c r="D31" s="30"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="4"/>
@@ -10079,7 +10084,7 @@
       <c r="A32" s="4"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
-      <c r="D32" s="23"/>
+      <c r="D32" s="30"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="4"/>
@@ -10091,7 +10096,7 @@
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="23"/>
+      <c r="D33" s="30"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
@@ -10103,7 +10108,7 @@
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="23"/>
+      <c r="D34" s="30"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
       <c r="G34" s="4"/>
@@ -10115,7 +10120,7 @@
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="23"/>
+      <c r="D35" s="30"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
       <c r="G35" s="4"/>
@@ -10127,7 +10132,7 @@
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="7"/>
-      <c r="D36" s="23"/>
+      <c r="D36" s="30"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="4"/>
@@ -10139,7 +10144,7 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="23"/>
+      <c r="D37" s="30"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="4"/>
@@ -10151,7 +10156,7 @@
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="7"/>
-      <c r="D38" s="23"/>
+      <c r="D38" s="30"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="4"/>
@@ -10163,7 +10168,7 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="7"/>
-      <c r="D39" s="23"/>
+      <c r="D39" s="30"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="4"/>
@@ -10175,7 +10180,7 @@
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="7"/>
-      <c r="D40" s="23"/>
+      <c r="D40" s="30"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="4"/>
@@ -10187,7 +10192,7 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="23"/>
+      <c r="D41" s="30"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="4"/>
@@ -10199,7 +10204,7 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="23"/>
+      <c r="D42" s="30"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="4"/>
@@ -10211,7 +10216,7 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="23"/>
+      <c r="D43" s="30"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="4"/>
@@ -10223,7 +10228,7 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="7"/>
-      <c r="D44" s="23"/>
+      <c r="D44" s="30"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="4"/>
@@ -10235,7 +10240,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="23"/>
+      <c r="D45" s="30"/>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
       <c r="G45" s="4"/>
@@ -10247,7 +10252,7 @@
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="7"/>
-      <c r="D46" s="23"/>
+      <c r="D46" s="30"/>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
       <c r="G46" s="4"/>
@@ -10259,7 +10264,7 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="7"/>
-      <c r="D47" s="23"/>
+      <c r="D47" s="30"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
       <c r="G47" s="4"/>
@@ -10271,7 +10276,7 @@
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="7"/>
-      <c r="D48" s="23"/>
+      <c r="D48" s="30"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
       <c r="G48" s="4"/>
@@ -10283,7 +10288,7 @@
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="7"/>
-      <c r="D49" s="23"/>
+      <c r="D49" s="30"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
       <c r="G49" s="4"/>
@@ -10295,7 +10300,7 @@
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="23"/>
+      <c r="D50" s="30"/>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
       <c r="G50" s="4"/>
@@ -10307,7 +10312,7 @@
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="7"/>
-      <c r="D51" s="23"/>
+      <c r="D51" s="30"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
       <c r="G51" s="4"/>
@@ -10319,7 +10324,7 @@
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="7"/>
-      <c r="D52" s="23"/>
+      <c r="D52" s="30"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
       <c r="G52" s="4"/>
@@ -10331,7 +10336,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="23"/>
+      <c r="D53" s="30"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="4"/>
@@ -10343,7 +10348,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="23"/>
+      <c r="D54" s="30"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
       <c r="G54" s="4"/>
@@ -10355,7 +10360,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="7"/>
-      <c r="D55" s="23"/>
+      <c r="D55" s="30"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
       <c r="G55" s="4"/>
@@ -10367,7 +10372,7 @@
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="7"/>
-      <c r="D56" s="23"/>
+      <c r="D56" s="30"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
       <c r="G56" s="4"/>
@@ -10379,7 +10384,7 @@
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="7"/>
-      <c r="D57" s="23"/>
+      <c r="D57" s="30"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
       <c r="G57" s="4"/>
@@ -11301,11 +11306,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="E3:E4"/>
@@ -11320,6 +11320,11 @@
     <mergeCell ref="F17:F23"/>
     <mergeCell ref="G17:G23"/>
     <mergeCell ref="H17:H23"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11342,27 +11347,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="35"/>
-      <c r="I1" s="16" t="s">
+      <c r="H1" s="41"/>
+      <c r="I1" s="24" t="s">
         <v>0</v>
       </c>
     </row>
@@ -11373,53 +11378,53 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="16"/>
+      <c r="I2" s="24"/>
     </row>
     <row r="3" spans="1:9" ht="15">
       <c r="A3" s="14" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="22" t="s">
+      <c r="C3" s="20"/>
+      <c r="D3" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="25"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="31"/>
       <c r="G3" s="14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="I3" s="18"/>
+        <v>94</v>
+      </c>
+      <c r="I3" s="21"/>
     </row>
     <row r="4" spans="1:9" ht="14.25" customHeight="1">
       <c r="A4" s="14"/>
       <c r="B4" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="37"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="25"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="31"/>
       <c r="G4" s="13"/>
       <c r="H4" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="I4" s="18"/>
+        <v>95</v>
+      </c>
+      <c r="I4" s="21"/>
     </row>
     <row r="5" spans="1:9" ht="15">
       <c r="A5" s="14"/>
@@ -11427,12 +11432,12 @@
         <v>31</v>
       </c>
       <c r="C5" s="7"/>
-      <c r="D5" s="23"/>
+      <c r="D5" s="30"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I5" s="4"/>
     </row>
@@ -11442,12 +11447,12 @@
         <v>33</v>
       </c>
       <c r="C6" s="7"/>
-      <c r="D6" s="23"/>
+      <c r="D6" s="30"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I6" s="4"/>
     </row>
@@ -11455,29 +11460,29 @@
       <c r="A7" s="14"/>
       <c r="B7" s="14"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="23"/>
+      <c r="D7" s="30"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="A8" s="14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="7"/>
-      <c r="D8" s="23"/>
+      <c r="D8" s="30"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I8" s="4"/>
     </row>
@@ -11487,12 +11492,12 @@
         <v>30</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="23"/>
+      <c r="D9" s="30"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I9" s="4"/>
     </row>
@@ -11502,13 +11507,11 @@
         <v>35</v>
       </c>
       <c r="C10" s="7"/>
-      <c r="D10" s="23"/>
+      <c r="D10" s="30"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="4"/>
-      <c r="H10" s="4" t="s">
-        <v>103</v>
-      </c>
+      <c r="H10" s="4"/>
       <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" ht="15">
@@ -11517,7 +11520,7 @@
         <v>38</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="23"/>
+      <c r="D11" s="30"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="4"/>
@@ -11528,7 +11531,7 @@
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="23"/>
+      <c r="D12" s="30"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="4"/>
@@ -11539,7 +11542,7 @@
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="23"/>
+      <c r="D13" s="30"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="4"/>
@@ -11550,7 +11553,7 @@
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="23"/>
+      <c r="D14" s="30"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="4"/>
@@ -11561,7 +11564,7 @@
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="23"/>
+      <c r="D15" s="30"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="4"/>
@@ -11572,95 +11575,95 @@
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="23"/>
+      <c r="D16" s="30"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
+      <c r="H16" s="21"/>
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" ht="15">
       <c r="A17" s="15"/>
       <c r="B17" s="15"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
     </row>
     <row r="18" spans="1:9" ht="15">
       <c r="A18" s="15"/>
       <c r="B18" s="15"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
     </row>
     <row r="19" spans="1:9" ht="15">
       <c r="A19" s="15"/>
       <c r="B19" s="15"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
     </row>
     <row r="20" spans="1:9" ht="15">
       <c r="A20" s="15"/>
       <c r="B20" s="15"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
     </row>
     <row r="21" spans="1:9" ht="15">
       <c r="A21" s="15"/>
       <c r="B21" s="15"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
     </row>
     <row r="22" spans="1:9" ht="15">
       <c r="A22" s="15"/>
       <c r="B22" s="15"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
     </row>
     <row r="23" spans="1:9" ht="15">
       <c r="A23" s="15"/>
       <c r="B23" s="15"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="21"/>
     </row>
     <row r="24" spans="1:9" ht="15">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="7"/>
-      <c r="D24" s="23"/>
+      <c r="D24" s="30"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
       <c r="G24" s="4"/>
@@ -11671,7 +11674,7 @@
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="23"/>
+      <c r="D25" s="30"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="4"/>
@@ -11682,7 +11685,7 @@
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="23"/>
+      <c r="D26" s="30"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -11693,7 +11696,7 @@
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="7"/>
-      <c r="D27" s="23"/>
+      <c r="D27" s="30"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
@@ -11704,7 +11707,7 @@
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="23"/>
+      <c r="D28" s="30"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -11715,7 +11718,7 @@
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="23"/>
+      <c r="D29" s="30"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -11726,29 +11729,29 @@
       <c r="A30" s="4"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="23"/>
+      <c r="D30" s="30"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
+      <c r="H30" s="7"/>
       <c r="I30" s="4"/>
     </row>
     <row r="31" spans="1:9" ht="15">
       <c r="A31" s="4"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="23"/>
+      <c r="D31" s="30"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="4"/>
-      <c r="H31" s="7"/>
+      <c r="H31" s="4"/>
       <c r="I31" s="4"/>
     </row>
     <row r="32" spans="1:9" ht="15">
       <c r="A32" s="4"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
-      <c r="D32" s="23"/>
+      <c r="D32" s="30"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="4"/>
@@ -11759,7 +11762,7 @@
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="23"/>
+      <c r="D33" s="30"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
@@ -11770,7 +11773,7 @@
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="23"/>
+      <c r="D34" s="30"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
       <c r="G34" s="4"/>
@@ -11781,7 +11784,7 @@
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="23"/>
+      <c r="D35" s="30"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
       <c r="G35" s="4"/>
@@ -11792,7 +11795,7 @@
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="7"/>
-      <c r="D36" s="23"/>
+      <c r="D36" s="30"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="4"/>
@@ -11803,7 +11806,7 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="23"/>
+      <c r="D37" s="30"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="4"/>
@@ -11814,7 +11817,7 @@
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="7"/>
-      <c r="D38" s="23"/>
+      <c r="D38" s="30"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="4"/>
@@ -11825,7 +11828,7 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="7"/>
-      <c r="D39" s="23"/>
+      <c r="D39" s="30"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="4"/>
@@ -11836,7 +11839,7 @@
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="7"/>
-      <c r="D40" s="23"/>
+      <c r="D40" s="30"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="4"/>
@@ -11847,7 +11850,7 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="23"/>
+      <c r="D41" s="30"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="4"/>
@@ -11858,7 +11861,7 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="23"/>
+      <c r="D42" s="30"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="4"/>
@@ -11869,7 +11872,7 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="23"/>
+      <c r="D43" s="30"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="4"/>
@@ -11880,7 +11883,7 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="7"/>
-      <c r="D44" s="23"/>
+      <c r="D44" s="30"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="4"/>
@@ -11891,7 +11894,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="23"/>
+      <c r="D45" s="30"/>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
       <c r="G45" s="4"/>
@@ -11902,7 +11905,7 @@
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="7"/>
-      <c r="D46" s="23"/>
+      <c r="D46" s="30"/>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
       <c r="G46" s="4"/>
@@ -11913,7 +11916,7 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="7"/>
-      <c r="D47" s="23"/>
+      <c r="D47" s="30"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
       <c r="G47" s="4"/>
@@ -11924,7 +11927,7 @@
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="7"/>
-      <c r="D48" s="23"/>
+      <c r="D48" s="30"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
       <c r="G48" s="4"/>
@@ -11935,7 +11938,7 @@
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="7"/>
-      <c r="D49" s="23"/>
+      <c r="D49" s="30"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
       <c r="G49" s="4"/>
@@ -11946,7 +11949,7 @@
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="23"/>
+      <c r="D50" s="30"/>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
       <c r="G50" s="4"/>
@@ -11957,7 +11960,7 @@
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="7"/>
-      <c r="D51" s="23"/>
+      <c r="D51" s="30"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
       <c r="G51" s="4"/>
@@ -11968,7 +11971,7 @@
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="7"/>
-      <c r="D52" s="23"/>
+      <c r="D52" s="30"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
       <c r="G52" s="4"/>
@@ -11979,7 +11982,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="23"/>
+      <c r="D53" s="30"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="4"/>
@@ -11990,7 +11993,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="23"/>
+      <c r="D54" s="30"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
       <c r="G54" s="4"/>
@@ -12001,7 +12004,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="7"/>
-      <c r="D55" s="23"/>
+      <c r="D55" s="30"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
       <c r="G55" s="4"/>
@@ -12012,7 +12015,7 @@
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="7"/>
-      <c r="D56" s="23"/>
+      <c r="D56" s="30"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
       <c r="G56" s="4"/>
@@ -12023,7 +12026,7 @@
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="7"/>
-      <c r="D57" s="23"/>
+      <c r="D57" s="30"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
       <c r="G57" s="4"/>
@@ -12863,21 +12866,1588 @@
       <c r="E133" s="7"/>
       <c r="F133" s="7"/>
       <c r="G133" s="4"/>
-      <c r="H133" s="4"/>
       <c r="I133" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="I17:I23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="D3:D57"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="I3:I4"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I17:I23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H16:H22"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D516808C-CAAA-4C26-8FF7-1049B7072999}">
+  <dimension ref="A1:I133"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="29.75" customWidth="1"/>
+    <col min="2" max="2" width="45.25" customWidth="1"/>
+    <col min="3" max="3" width="32.625" customWidth="1"/>
+    <col min="4" max="4" width="59.125" customWidth="1"/>
+    <col min="5" max="5" width="20" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="17.25" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="33.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="32.65" customHeight="1" thickBot="1">
+      <c r="A1" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="41"/>
+      <c r="I1" s="24" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15" thickBot="1">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="36"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="24"/>
+    </row>
+    <row r="3" spans="1:9" ht="15">
+      <c r="A3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="23"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I3" s="21"/>
+    </row>
+    <row r="4" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A4" s="19"/>
+      <c r="B4" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="20"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="21"/>
+    </row>
+    <row r="5" spans="1:9" ht="15">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="18"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="I5" s="16"/>
+    </row>
+    <row r="6" spans="1:9" ht="15">
+      <c r="A6" s="19"/>
+      <c r="B6" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="18"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="I6" s="16"/>
+    </row>
+    <row r="7" spans="1:9" ht="15">
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="I7" s="16"/>
+    </row>
+    <row r="8" spans="1:9" ht="15">
+      <c r="A8" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="18"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="16"/>
+    </row>
+    <row r="9" spans="1:9" ht="15">
+      <c r="A9" s="19"/>
+      <c r="B9" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="I9" s="16"/>
+    </row>
+    <row r="10" spans="1:9" ht="15">
+      <c r="A10" s="19"/>
+      <c r="B10" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="18"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+    </row>
+    <row r="11" spans="1:9" ht="15">
+      <c r="A11" s="19"/>
+      <c r="B11" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="16"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+    </row>
+    <row r="12" spans="1:9" ht="15">
+      <c r="A12" s="42"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+    </row>
+    <row r="13" spans="1:9" ht="15">
+      <c r="A13" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="18"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+    </row>
+    <row r="14" spans="1:9" ht="15">
+      <c r="A14" s="16"/>
+      <c r="B14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="18"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+    </row>
+    <row r="15" spans="1:9" ht="15">
+      <c r="A15" s="16"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+    </row>
+    <row r="16" spans="1:9" ht="15">
+      <c r="A16" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="18"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+    </row>
+    <row r="17" spans="1:9" ht="15">
+      <c r="A17" s="16"/>
+      <c r="B17" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+    </row>
+    <row r="18" spans="1:9" ht="15">
+      <c r="C18" s="8"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+    </row>
+    <row r="19" spans="1:9" ht="15">
+      <c r="C19" s="8"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+    </row>
+    <row r="20" spans="1:9" ht="15">
+      <c r="A20" s="15"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+    </row>
+    <row r="21" spans="1:9" ht="15">
+      <c r="A21" s="15"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+    </row>
+    <row r="22" spans="1:9" ht="15">
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+    </row>
+    <row r="23" spans="1:9" ht="15">
+      <c r="A23" s="15"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+    </row>
+    <row r="24" spans="1:9" ht="15">
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+    </row>
+    <row r="25" spans="1:9" ht="15">
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+    </row>
+    <row r="26" spans="1:9" ht="15">
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+    </row>
+    <row r="27" spans="1:9" ht="15">
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+    </row>
+    <row r="28" spans="1:9" ht="15">
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+    </row>
+    <row r="29" spans="1:9" ht="15">
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="16"/>
+    </row>
+    <row r="30" spans="1:9" ht="15">
+      <c r="A30" s="16"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+    </row>
+    <row r="31" spans="1:9" ht="15">
+      <c r="A31" s="16"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="16"/>
+    </row>
+    <row r="32" spans="1:9" ht="15">
+      <c r="A32" s="16"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+    </row>
+    <row r="33" spans="1:9" ht="15">
+      <c r="A33" s="16"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="16"/>
+    </row>
+    <row r="34" spans="1:9" ht="15">
+      <c r="A34" s="16"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="16"/>
+    </row>
+    <row r="35" spans="1:9" ht="15">
+      <c r="A35" s="16"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+    </row>
+    <row r="36" spans="1:9" ht="15">
+      <c r="A36" s="16"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16"/>
+    </row>
+    <row r="37" spans="1:9" ht="15">
+      <c r="A37" s="16"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+    </row>
+    <row r="38" spans="1:9" ht="15">
+      <c r="A38" s="16"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+    </row>
+    <row r="39" spans="1:9" ht="15">
+      <c r="A39" s="16"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="16"/>
+    </row>
+    <row r="40" spans="1:9" ht="15">
+      <c r="A40" s="16"/>
+      <c r="B40" s="16"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="16"/>
+      <c r="H40" s="16"/>
+      <c r="I40" s="16"/>
+    </row>
+    <row r="41" spans="1:9" ht="15">
+      <c r="A41" s="16"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="16"/>
+      <c r="H41" s="16"/>
+      <c r="I41" s="16"/>
+    </row>
+    <row r="42" spans="1:9" ht="15">
+      <c r="A42" s="16"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
+      <c r="I42" s="16"/>
+    </row>
+    <row r="43" spans="1:9" ht="15">
+      <c r="A43" s="16"/>
+      <c r="B43" s="16"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="16"/>
+      <c r="H43" s="16"/>
+      <c r="I43" s="16"/>
+    </row>
+    <row r="44" spans="1:9" ht="15">
+      <c r="A44" s="16"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="16"/>
+      <c r="H44" s="16"/>
+      <c r="I44" s="16"/>
+    </row>
+    <row r="45" spans="1:9" ht="15">
+      <c r="A45" s="16"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="16"/>
+      <c r="H45" s="16"/>
+      <c r="I45" s="16"/>
+    </row>
+    <row r="46" spans="1:9" ht="15">
+      <c r="A46" s="16"/>
+      <c r="B46" s="16"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="16"/>
+      <c r="H46" s="16"/>
+      <c r="I46" s="16"/>
+    </row>
+    <row r="47" spans="1:9" ht="15">
+      <c r="A47" s="16"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="16"/>
+      <c r="H47" s="16"/>
+      <c r="I47" s="16"/>
+    </row>
+    <row r="48" spans="1:9" ht="15">
+      <c r="A48" s="16"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="16"/>
+      <c r="H48" s="16"/>
+      <c r="I48" s="16"/>
+    </row>
+    <row r="49" spans="1:9" ht="15">
+      <c r="A49" s="16"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="16"/>
+      <c r="H49" s="16"/>
+      <c r="I49" s="16"/>
+    </row>
+    <row r="50" spans="1:9" ht="15">
+      <c r="A50" s="16"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="30"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="16"/>
+      <c r="H50" s="16"/>
+      <c r="I50" s="16"/>
+    </row>
+    <row r="51" spans="1:9" ht="15">
+      <c r="A51" s="16"/>
+      <c r="B51" s="16"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="30"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="16"/>
+      <c r="H51" s="16"/>
+      <c r="I51" s="16"/>
+    </row>
+    <row r="52" spans="1:9" ht="15">
+      <c r="A52" s="16"/>
+      <c r="B52" s="16"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="16"/>
+      <c r="I52" s="16"/>
+    </row>
+    <row r="53" spans="1:9" ht="15">
+      <c r="A53" s="16"/>
+      <c r="B53" s="16"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="16"/>
+      <c r="H53" s="16"/>
+      <c r="I53" s="16"/>
+    </row>
+    <row r="54" spans="1:9" ht="15">
+      <c r="A54" s="16"/>
+      <c r="B54" s="16"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="16"/>
+      <c r="H54" s="16"/>
+      <c r="I54" s="16"/>
+    </row>
+    <row r="55" spans="1:9" ht="15">
+      <c r="A55" s="16"/>
+      <c r="B55" s="16"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="16"/>
+      <c r="H55" s="16"/>
+      <c r="I55" s="16"/>
+    </row>
+    <row r="56" spans="1:9" ht="15">
+      <c r="A56" s="16"/>
+      <c r="B56" s="16"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="30"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="16"/>
+      <c r="H56" s="16"/>
+      <c r="I56" s="16"/>
+    </row>
+    <row r="57" spans="1:9" ht="15">
+      <c r="A57" s="16"/>
+      <c r="B57" s="16"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="30"/>
+      <c r="E57" s="18"/>
+      <c r="F57" s="18"/>
+      <c r="G57" s="16"/>
+      <c r="H57" s="16"/>
+      <c r="I57" s="16"/>
+    </row>
+    <row r="58" spans="1:9" ht="15">
+      <c r="A58" s="16"/>
+      <c r="B58" s="16"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="16"/>
+      <c r="H58" s="16"/>
+      <c r="I58" s="16"/>
+    </row>
+    <row r="59" spans="1:9" ht="15">
+      <c r="A59" s="16"/>
+      <c r="B59" s="16"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="18"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="16"/>
+      <c r="H59" s="16"/>
+      <c r="I59" s="16"/>
+    </row>
+    <row r="60" spans="1:9" ht="15">
+      <c r="A60" s="16"/>
+      <c r="B60" s="16"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="16"/>
+      <c r="H60" s="16"/>
+      <c r="I60" s="16"/>
+    </row>
+    <row r="61" spans="1:9" ht="15">
+      <c r="A61" s="16"/>
+      <c r="B61" s="16"/>
+      <c r="C61" s="18"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="18"/>
+      <c r="F61" s="18"/>
+      <c r="G61" s="16"/>
+      <c r="H61" s="16"/>
+      <c r="I61" s="16"/>
+    </row>
+    <row r="62" spans="1:9" ht="15">
+      <c r="A62" s="16"/>
+      <c r="B62" s="16"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="18"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="16"/>
+      <c r="H62" s="16"/>
+      <c r="I62" s="16"/>
+    </row>
+    <row r="63" spans="1:9" ht="15">
+      <c r="A63" s="16"/>
+      <c r="B63" s="16"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="18"/>
+      <c r="F63" s="18"/>
+      <c r="G63" s="16"/>
+      <c r="H63" s="16"/>
+      <c r="I63" s="16"/>
+    </row>
+    <row r="64" spans="1:9" ht="15">
+      <c r="A64" s="16"/>
+      <c r="B64" s="16"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="18"/>
+      <c r="F64" s="18"/>
+      <c r="G64" s="16"/>
+      <c r="H64" s="16"/>
+      <c r="I64" s="16"/>
+    </row>
+    <row r="65" spans="1:9" ht="15">
+      <c r="A65" s="16"/>
+      <c r="B65" s="16"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="18"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="16"/>
+      <c r="H65" s="16"/>
+      <c r="I65" s="16"/>
+    </row>
+    <row r="66" spans="1:9" ht="15">
+      <c r="A66" s="16"/>
+      <c r="B66" s="16"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="18"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="16"/>
+      <c r="H66" s="16"/>
+      <c r="I66" s="16"/>
+    </row>
+    <row r="67" spans="1:9" ht="15">
+      <c r="A67" s="16"/>
+      <c r="B67" s="16"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="18"/>
+      <c r="F67" s="18"/>
+      <c r="G67" s="16"/>
+      <c r="H67" s="16"/>
+      <c r="I67" s="16"/>
+    </row>
+    <row r="68" spans="1:9" ht="15">
+      <c r="A68" s="16"/>
+      <c r="B68" s="16"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="18"/>
+      <c r="F68" s="18"/>
+      <c r="G68" s="16"/>
+      <c r="H68" s="16"/>
+      <c r="I68" s="16"/>
+    </row>
+    <row r="69" spans="1:9" ht="15">
+      <c r="A69" s="16"/>
+      <c r="B69" s="16"/>
+      <c r="C69" s="18"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="18"/>
+      <c r="F69" s="18"/>
+      <c r="G69" s="16"/>
+      <c r="H69" s="16"/>
+      <c r="I69" s="16"/>
+    </row>
+    <row r="70" spans="1:9" ht="15">
+      <c r="A70" s="16"/>
+      <c r="B70" s="16"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="18"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="16"/>
+      <c r="H70" s="16"/>
+      <c r="I70" s="16"/>
+    </row>
+    <row r="71" spans="1:9" ht="15">
+      <c r="A71" s="16"/>
+      <c r="B71" s="16"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="18"/>
+      <c r="F71" s="18"/>
+      <c r="G71" s="16"/>
+      <c r="H71" s="16"/>
+      <c r="I71" s="16"/>
+    </row>
+    <row r="72" spans="1:9" ht="15">
+      <c r="A72" s="16"/>
+      <c r="B72" s="16"/>
+      <c r="C72" s="18"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="18"/>
+      <c r="F72" s="18"/>
+      <c r="G72" s="16"/>
+      <c r="H72" s="16"/>
+      <c r="I72" s="16"/>
+    </row>
+    <row r="73" spans="1:9" ht="15">
+      <c r="A73" s="16"/>
+      <c r="B73" s="16"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="16"/>
+      <c r="H73" s="16"/>
+      <c r="I73" s="16"/>
+    </row>
+    <row r="74" spans="1:9" ht="15">
+      <c r="A74" s="16"/>
+      <c r="B74" s="16"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="18"/>
+      <c r="F74" s="18"/>
+      <c r="G74" s="16"/>
+      <c r="H74" s="16"/>
+      <c r="I74" s="16"/>
+    </row>
+    <row r="75" spans="1:9" ht="15">
+      <c r="A75" s="16"/>
+      <c r="B75" s="16"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="18"/>
+      <c r="F75" s="18"/>
+      <c r="G75" s="16"/>
+      <c r="H75" s="16"/>
+      <c r="I75" s="16"/>
+    </row>
+    <row r="76" spans="1:9" ht="15">
+      <c r="A76" s="16"/>
+      <c r="B76" s="16"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="18"/>
+      <c r="F76" s="18"/>
+      <c r="G76" s="16"/>
+      <c r="H76" s="16"/>
+      <c r="I76" s="16"/>
+    </row>
+    <row r="77" spans="1:9" ht="15">
+      <c r="A77" s="16"/>
+      <c r="B77" s="16"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="18"/>
+      <c r="F77" s="18"/>
+      <c r="G77" s="16"/>
+      <c r="H77" s="16"/>
+      <c r="I77" s="16"/>
+    </row>
+    <row r="78" spans="1:9" ht="15">
+      <c r="A78" s="16"/>
+      <c r="B78" s="16"/>
+      <c r="C78" s="18"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="18"/>
+      <c r="F78" s="18"/>
+      <c r="G78" s="16"/>
+      <c r="H78" s="16"/>
+      <c r="I78" s="16"/>
+    </row>
+    <row r="79" spans="1:9" ht="15">
+      <c r="A79" s="16"/>
+      <c r="B79" s="16"/>
+      <c r="C79" s="18"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="18"/>
+      <c r="F79" s="18"/>
+      <c r="G79" s="16"/>
+      <c r="H79" s="16"/>
+      <c r="I79" s="16"/>
+    </row>
+    <row r="80" spans="1:9" ht="15">
+      <c r="A80" s="16"/>
+      <c r="B80" s="16"/>
+      <c r="C80" s="18"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="18"/>
+      <c r="F80" s="18"/>
+      <c r="G80" s="16"/>
+      <c r="H80" s="16"/>
+      <c r="I80" s="16"/>
+    </row>
+    <row r="81" spans="1:9" ht="15">
+      <c r="A81" s="16"/>
+      <c r="B81" s="16"/>
+      <c r="C81" s="18"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="18"/>
+      <c r="F81" s="18"/>
+      <c r="G81" s="16"/>
+      <c r="H81" s="16"/>
+      <c r="I81" s="16"/>
+    </row>
+    <row r="82" spans="1:9" ht="15">
+      <c r="A82" s="16"/>
+      <c r="B82" s="16"/>
+      <c r="C82" s="18"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="18"/>
+      <c r="F82" s="18"/>
+      <c r="G82" s="16"/>
+      <c r="H82" s="16"/>
+      <c r="I82" s="16"/>
+    </row>
+    <row r="83" spans="1:9" ht="15">
+      <c r="A83" s="16"/>
+      <c r="B83" s="16"/>
+      <c r="C83" s="18"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="18"/>
+      <c r="F83" s="18"/>
+      <c r="G83" s="16"/>
+      <c r="H83" s="16"/>
+      <c r="I83" s="16"/>
+    </row>
+    <row r="84" spans="1:9" ht="15">
+      <c r="A84" s="16"/>
+      <c r="B84" s="16"/>
+      <c r="C84" s="18"/>
+      <c r="D84" s="5"/>
+      <c r="E84" s="18"/>
+      <c r="F84" s="18"/>
+      <c r="G84" s="16"/>
+      <c r="H84" s="16"/>
+      <c r="I84" s="16"/>
+    </row>
+    <row r="85" spans="1:9" ht="15">
+      <c r="A85" s="16"/>
+      <c r="B85" s="16"/>
+      <c r="C85" s="18"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="18"/>
+      <c r="F85" s="18"/>
+      <c r="G85" s="16"/>
+      <c r="H85" s="16"/>
+      <c r="I85" s="16"/>
+    </row>
+    <row r="86" spans="1:9" ht="15">
+      <c r="A86" s="16"/>
+      <c r="B86" s="16"/>
+      <c r="C86" s="18"/>
+      <c r="D86" s="6"/>
+      <c r="E86" s="18"/>
+      <c r="F86" s="18"/>
+      <c r="G86" s="16"/>
+      <c r="H86" s="16"/>
+      <c r="I86" s="16"/>
+    </row>
+    <row r="87" spans="1:9" ht="15">
+      <c r="A87" s="16"/>
+      <c r="B87" s="16"/>
+      <c r="C87" s="18"/>
+      <c r="D87" s="6"/>
+      <c r="E87" s="18"/>
+      <c r="F87" s="18"/>
+      <c r="G87" s="16"/>
+      <c r="H87" s="16"/>
+      <c r="I87" s="16"/>
+    </row>
+    <row r="88" spans="1:9" ht="15">
+      <c r="A88" s="16"/>
+      <c r="B88" s="16"/>
+      <c r="C88" s="18"/>
+      <c r="D88" s="6"/>
+      <c r="E88" s="18"/>
+      <c r="F88" s="18"/>
+      <c r="G88" s="16"/>
+      <c r="H88" s="16"/>
+      <c r="I88" s="16"/>
+    </row>
+    <row r="89" spans="1:9" ht="15">
+      <c r="A89" s="16"/>
+      <c r="B89" s="16"/>
+      <c r="C89" s="18"/>
+      <c r="D89" s="6"/>
+      <c r="E89" s="18"/>
+      <c r="F89" s="18"/>
+      <c r="G89" s="16"/>
+      <c r="H89" s="16"/>
+      <c r="I89" s="16"/>
+    </row>
+    <row r="90" spans="1:9" ht="15">
+      <c r="A90" s="16"/>
+      <c r="B90" s="16"/>
+      <c r="C90" s="18"/>
+      <c r="D90" s="6"/>
+      <c r="E90" s="18"/>
+      <c r="F90" s="18"/>
+      <c r="G90" s="16"/>
+      <c r="H90" s="16"/>
+      <c r="I90" s="16"/>
+    </row>
+    <row r="91" spans="1:9" ht="15">
+      <c r="A91" s="16"/>
+      <c r="B91" s="16"/>
+      <c r="C91" s="18"/>
+      <c r="D91" s="6"/>
+      <c r="E91" s="18"/>
+      <c r="F91" s="18"/>
+      <c r="G91" s="16"/>
+      <c r="H91" s="16"/>
+      <c r="I91" s="16"/>
+    </row>
+    <row r="92" spans="1:9" ht="15">
+      <c r="A92" s="16"/>
+      <c r="B92" s="16"/>
+      <c r="C92" s="18"/>
+      <c r="D92" s="6"/>
+      <c r="E92" s="18"/>
+      <c r="F92" s="18"/>
+      <c r="G92" s="16"/>
+      <c r="H92" s="16"/>
+      <c r="I92" s="16"/>
+    </row>
+    <row r="93" spans="1:9" ht="15">
+      <c r="A93" s="16"/>
+      <c r="B93" s="16"/>
+      <c r="C93" s="18"/>
+      <c r="D93" s="6"/>
+      <c r="E93" s="18"/>
+      <c r="F93" s="18"/>
+      <c r="G93" s="16"/>
+      <c r="H93" s="16"/>
+      <c r="I93" s="16"/>
+    </row>
+    <row r="94" spans="1:9" ht="15">
+      <c r="A94" s="16"/>
+      <c r="B94" s="16"/>
+      <c r="C94" s="18"/>
+      <c r="D94" s="6"/>
+      <c r="E94" s="18"/>
+      <c r="F94" s="18"/>
+      <c r="G94" s="16"/>
+      <c r="H94" s="16"/>
+      <c r="I94" s="16"/>
+    </row>
+    <row r="95" spans="1:9" ht="15">
+      <c r="A95" s="16"/>
+      <c r="B95" s="16"/>
+      <c r="C95" s="18"/>
+      <c r="D95" s="5"/>
+      <c r="E95" s="18"/>
+      <c r="F95" s="18"/>
+      <c r="G95" s="16"/>
+      <c r="H95" s="16"/>
+      <c r="I95" s="16"/>
+    </row>
+    <row r="96" spans="1:9" ht="15">
+      <c r="A96" s="16"/>
+      <c r="B96" s="16"/>
+      <c r="C96" s="18"/>
+      <c r="D96" s="6"/>
+      <c r="E96" s="18"/>
+      <c r="F96" s="18"/>
+      <c r="G96" s="16"/>
+      <c r="H96" s="16"/>
+      <c r="I96" s="16"/>
+    </row>
+    <row r="97" spans="1:9" ht="15">
+      <c r="A97" s="16"/>
+      <c r="B97" s="16"/>
+      <c r="C97" s="18"/>
+      <c r="D97" s="6"/>
+      <c r="E97" s="18"/>
+      <c r="F97" s="18"/>
+      <c r="G97" s="16"/>
+      <c r="H97" s="16"/>
+      <c r="I97" s="16"/>
+    </row>
+    <row r="98" spans="1:9" ht="15">
+      <c r="A98" s="16"/>
+      <c r="B98" s="16"/>
+      <c r="C98" s="18"/>
+      <c r="D98" s="6"/>
+      <c r="E98" s="18"/>
+      <c r="F98" s="18"/>
+      <c r="G98" s="16"/>
+      <c r="H98" s="16"/>
+      <c r="I98" s="16"/>
+    </row>
+    <row r="99" spans="1:9" ht="15">
+      <c r="A99" s="16"/>
+      <c r="B99" s="16"/>
+      <c r="C99" s="18"/>
+      <c r="D99" s="6"/>
+      <c r="E99" s="18"/>
+      <c r="F99" s="18"/>
+      <c r="G99" s="16"/>
+      <c r="H99" s="16"/>
+      <c r="I99" s="16"/>
+    </row>
+    <row r="100" spans="1:9" ht="15">
+      <c r="A100" s="16"/>
+      <c r="B100" s="16"/>
+      <c r="C100" s="18"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="18"/>
+      <c r="F100" s="18"/>
+      <c r="G100" s="16"/>
+      <c r="H100" s="16"/>
+      <c r="I100" s="16"/>
+    </row>
+    <row r="101" spans="1:9" ht="15">
+      <c r="A101" s="16"/>
+      <c r="B101" s="16"/>
+      <c r="C101" s="18"/>
+      <c r="D101" s="6"/>
+      <c r="E101" s="18"/>
+      <c r="F101" s="18"/>
+      <c r="G101" s="16"/>
+      <c r="H101" s="16"/>
+      <c r="I101" s="16"/>
+    </row>
+    <row r="102" spans="1:9" ht="15">
+      <c r="A102" s="16"/>
+      <c r="B102" s="16"/>
+      <c r="C102" s="18"/>
+      <c r="D102" s="6"/>
+      <c r="E102" s="18"/>
+      <c r="F102" s="18"/>
+      <c r="G102" s="16"/>
+      <c r="H102" s="16"/>
+      <c r="I102" s="16"/>
+    </row>
+    <row r="103" spans="1:9" ht="15">
+      <c r="A103" s="16"/>
+      <c r="B103" s="16"/>
+      <c r="C103" s="18"/>
+      <c r="D103" s="6"/>
+      <c r="E103" s="18"/>
+      <c r="F103" s="18"/>
+      <c r="G103" s="16"/>
+      <c r="H103" s="16"/>
+      <c r="I103" s="16"/>
+    </row>
+    <row r="104" spans="1:9" ht="15">
+      <c r="A104" s="16"/>
+      <c r="B104" s="16"/>
+      <c r="C104" s="18"/>
+      <c r="D104" s="6"/>
+      <c r="E104" s="18"/>
+      <c r="F104" s="18"/>
+      <c r="G104" s="16"/>
+      <c r="H104" s="16"/>
+      <c r="I104" s="16"/>
+    </row>
+    <row r="105" spans="1:9" ht="15">
+      <c r="A105" s="16"/>
+      <c r="B105" s="16"/>
+      <c r="C105" s="18"/>
+      <c r="D105" s="6"/>
+      <c r="E105" s="18"/>
+      <c r="F105" s="18"/>
+      <c r="G105" s="16"/>
+      <c r="H105" s="16"/>
+      <c r="I105" s="16"/>
+    </row>
+    <row r="106" spans="1:9" ht="15">
+      <c r="A106" s="16"/>
+      <c r="B106" s="16"/>
+      <c r="C106" s="18"/>
+      <c r="D106" s="5"/>
+      <c r="E106" s="18"/>
+      <c r="F106" s="18"/>
+      <c r="G106" s="16"/>
+      <c r="H106" s="16"/>
+      <c r="I106" s="16"/>
+    </row>
+    <row r="107" spans="1:9" ht="15">
+      <c r="A107" s="16"/>
+      <c r="B107" s="16"/>
+      <c r="C107" s="18"/>
+      <c r="D107" s="6"/>
+      <c r="E107" s="18"/>
+      <c r="F107" s="18"/>
+      <c r="G107" s="16"/>
+      <c r="H107" s="16"/>
+      <c r="I107" s="16"/>
+    </row>
+    <row r="108" spans="1:9" ht="15">
+      <c r="A108" s="16"/>
+      <c r="B108" s="16"/>
+      <c r="C108" s="18"/>
+      <c r="D108" s="6"/>
+      <c r="E108" s="18"/>
+      <c r="F108" s="18"/>
+      <c r="G108" s="16"/>
+      <c r="H108" s="16"/>
+      <c r="I108" s="16"/>
+    </row>
+    <row r="109" spans="1:9" ht="15">
+      <c r="A109" s="16"/>
+      <c r="B109" s="16"/>
+      <c r="C109" s="18"/>
+      <c r="D109" s="6"/>
+      <c r="E109" s="18"/>
+      <c r="F109" s="18"/>
+      <c r="G109" s="16"/>
+      <c r="H109" s="16"/>
+      <c r="I109" s="16"/>
+    </row>
+    <row r="110" spans="1:9" ht="15">
+      <c r="A110" s="16"/>
+      <c r="B110" s="16"/>
+      <c r="C110" s="18"/>
+      <c r="D110" s="6"/>
+      <c r="E110" s="18"/>
+      <c r="F110" s="18"/>
+      <c r="G110" s="16"/>
+      <c r="H110" s="16"/>
+      <c r="I110" s="16"/>
+    </row>
+    <row r="111" spans="1:9" ht="15">
+      <c r="A111" s="16"/>
+      <c r="B111" s="16"/>
+      <c r="C111" s="18"/>
+      <c r="D111" s="6"/>
+      <c r="E111" s="18"/>
+      <c r="F111" s="18"/>
+      <c r="G111" s="16"/>
+      <c r="H111" s="16"/>
+      <c r="I111" s="16"/>
+    </row>
+    <row r="112" spans="1:9" ht="15">
+      <c r="A112" s="16"/>
+      <c r="B112" s="16"/>
+      <c r="C112" s="18"/>
+      <c r="D112" s="6"/>
+      <c r="E112" s="18"/>
+      <c r="F112" s="18"/>
+      <c r="G112" s="16"/>
+      <c r="H112" s="16"/>
+      <c r="I112" s="16"/>
+    </row>
+    <row r="113" spans="1:9" ht="15">
+      <c r="A113" s="16"/>
+      <c r="B113" s="16"/>
+      <c r="C113" s="18"/>
+      <c r="D113" s="6"/>
+      <c r="E113" s="18"/>
+      <c r="F113" s="18"/>
+      <c r="G113" s="16"/>
+      <c r="H113" s="16"/>
+      <c r="I113" s="16"/>
+    </row>
+    <row r="114" spans="1:9" ht="15">
+      <c r="A114" s="16"/>
+      <c r="B114" s="16"/>
+      <c r="C114" s="18"/>
+      <c r="D114" s="6"/>
+      <c r="E114" s="18"/>
+      <c r="F114" s="18"/>
+      <c r="G114" s="16"/>
+      <c r="H114" s="16"/>
+      <c r="I114" s="16"/>
+    </row>
+    <row r="115" spans="1:9" ht="15">
+      <c r="A115" s="16"/>
+      <c r="B115" s="16"/>
+      <c r="C115" s="18"/>
+      <c r="D115" s="6"/>
+      <c r="E115" s="18"/>
+      <c r="F115" s="18"/>
+      <c r="G115" s="16"/>
+      <c r="H115" s="16"/>
+      <c r="I115" s="16"/>
+    </row>
+    <row r="116" spans="1:9" ht="15">
+      <c r="A116" s="16"/>
+      <c r="B116" s="16"/>
+      <c r="C116" s="18"/>
+      <c r="D116" s="6"/>
+      <c r="E116" s="18"/>
+      <c r="F116" s="18"/>
+      <c r="G116" s="16"/>
+      <c r="H116" s="16"/>
+      <c r="I116" s="16"/>
+    </row>
+    <row r="117" spans="1:9" ht="15">
+      <c r="A117" s="16"/>
+      <c r="B117" s="16"/>
+      <c r="C117" s="18"/>
+      <c r="D117" s="5"/>
+      <c r="E117" s="18"/>
+      <c r="F117" s="18"/>
+      <c r="G117" s="16"/>
+      <c r="H117" s="16"/>
+      <c r="I117" s="16"/>
+    </row>
+    <row r="118" spans="1:9" ht="15">
+      <c r="A118" s="16"/>
+      <c r="B118" s="16"/>
+      <c r="C118" s="18"/>
+      <c r="D118" s="6"/>
+      <c r="E118" s="18"/>
+      <c r="F118" s="18"/>
+      <c r="G118" s="16"/>
+      <c r="H118" s="16"/>
+      <c r="I118" s="16"/>
+    </row>
+    <row r="119" spans="1:9" ht="15">
+      <c r="A119" s="16"/>
+      <c r="B119" s="16"/>
+      <c r="C119" s="18"/>
+      <c r="D119" s="6"/>
+      <c r="E119" s="18"/>
+      <c r="F119" s="18"/>
+      <c r="G119" s="16"/>
+      <c r="H119" s="16"/>
+      <c r="I119" s="16"/>
+    </row>
+    <row r="120" spans="1:9" ht="15">
+      <c r="A120" s="16"/>
+      <c r="B120" s="16"/>
+      <c r="C120" s="18"/>
+      <c r="D120" s="6"/>
+      <c r="E120" s="18"/>
+      <c r="F120" s="18"/>
+      <c r="G120" s="16"/>
+      <c r="H120" s="16"/>
+      <c r="I120" s="16"/>
+    </row>
+    <row r="121" spans="1:9" ht="15">
+      <c r="A121" s="16"/>
+      <c r="B121" s="16"/>
+      <c r="C121" s="18"/>
+      <c r="D121" s="6"/>
+      <c r="E121" s="18"/>
+      <c r="F121" s="18"/>
+      <c r="G121" s="16"/>
+      <c r="H121" s="16"/>
+      <c r="I121" s="16"/>
+    </row>
+    <row r="122" spans="1:9" ht="15">
+      <c r="A122" s="16"/>
+      <c r="B122" s="16"/>
+      <c r="C122" s="18"/>
+      <c r="D122" s="6"/>
+      <c r="E122" s="18"/>
+      <c r="F122" s="18"/>
+      <c r="G122" s="16"/>
+      <c r="H122" s="16"/>
+      <c r="I122" s="16"/>
+    </row>
+    <row r="123" spans="1:9" ht="15">
+      <c r="A123" s="16"/>
+      <c r="B123" s="16"/>
+      <c r="C123" s="18"/>
+      <c r="D123" s="6"/>
+      <c r="E123" s="18"/>
+      <c r="F123" s="18"/>
+      <c r="G123" s="16"/>
+      <c r="H123" s="16"/>
+      <c r="I123" s="16"/>
+    </row>
+    <row r="124" spans="1:9" ht="15">
+      <c r="A124" s="16"/>
+      <c r="B124" s="16"/>
+      <c r="C124" s="18"/>
+      <c r="D124" s="6"/>
+      <c r="E124" s="18"/>
+      <c r="F124" s="18"/>
+      <c r="G124" s="16"/>
+      <c r="H124" s="16"/>
+      <c r="I124" s="16"/>
+    </row>
+    <row r="125" spans="1:9" ht="15">
+      <c r="A125" s="16"/>
+      <c r="B125" s="16"/>
+      <c r="C125" s="18"/>
+      <c r="D125" s="6"/>
+      <c r="E125" s="18"/>
+      <c r="F125" s="18"/>
+      <c r="G125" s="16"/>
+      <c r="H125" s="16"/>
+      <c r="I125" s="16"/>
+    </row>
+    <row r="126" spans="1:9" ht="15">
+      <c r="A126" s="16"/>
+      <c r="B126" s="16"/>
+      <c r="C126" s="18"/>
+      <c r="D126" s="6"/>
+      <c r="E126" s="18"/>
+      <c r="F126" s="18"/>
+      <c r="G126" s="16"/>
+      <c r="H126" s="16"/>
+      <c r="I126" s="16"/>
+    </row>
+    <row r="127" spans="1:9" ht="15">
+      <c r="A127" s="16"/>
+      <c r="B127" s="16"/>
+      <c r="C127" s="18"/>
+      <c r="D127" s="6"/>
+      <c r="E127" s="18"/>
+      <c r="F127" s="18"/>
+      <c r="G127" s="16"/>
+      <c r="H127" s="16"/>
+      <c r="I127" s="16"/>
+    </row>
+    <row r="128" spans="1:9" ht="15">
+      <c r="A128" s="16"/>
+      <c r="B128" s="16"/>
+      <c r="C128" s="18"/>
+      <c r="D128" s="6"/>
+      <c r="E128" s="18"/>
+      <c r="F128" s="18"/>
+      <c r="G128" s="16"/>
+      <c r="H128" s="16"/>
+      <c r="I128" s="16"/>
+    </row>
+    <row r="129" spans="1:9" ht="15">
+      <c r="A129" s="16"/>
+      <c r="B129" s="16"/>
+      <c r="C129" s="18"/>
+      <c r="D129" s="6"/>
+      <c r="E129" s="18"/>
+      <c r="F129" s="18"/>
+      <c r="G129" s="16"/>
+      <c r="H129" s="16"/>
+      <c r="I129" s="16"/>
+    </row>
+    <row r="130" spans="1:9" ht="15">
+      <c r="A130" s="16"/>
+      <c r="B130" s="16"/>
+      <c r="C130" s="18"/>
+      <c r="D130" s="6"/>
+      <c r="E130" s="18"/>
+      <c r="F130" s="18"/>
+      <c r="G130" s="16"/>
+      <c r="H130" s="16"/>
+      <c r="I130" s="16"/>
+    </row>
+    <row r="131" spans="1:9" ht="15">
+      <c r="A131" s="16"/>
+      <c r="B131" s="16"/>
+      <c r="C131" s="18"/>
+      <c r="D131" s="6"/>
+      <c r="E131" s="18"/>
+      <c r="F131" s="18"/>
+      <c r="G131" s="16"/>
+      <c r="H131" s="16"/>
+      <c r="I131" s="16"/>
+    </row>
+    <row r="132" spans="1:9" ht="15">
+      <c r="A132" s="16"/>
+      <c r="B132" s="16"/>
+      <c r="C132" s="18"/>
+      <c r="D132" s="6"/>
+      <c r="E132" s="18"/>
+      <c r="F132" s="18"/>
+      <c r="G132" s="16"/>
+      <c r="H132" s="16"/>
+      <c r="I132" s="16"/>
+    </row>
+    <row r="133" spans="1:9" ht="15">
+      <c r="A133" s="16"/>
+      <c r="B133" s="16"/>
+      <c r="C133" s="18"/>
+      <c r="D133" s="6"/>
+      <c r="E133" s="18"/>
+      <c r="F133" s="18"/>
+      <c r="G133" s="16"/>
+      <c r="H133" s="16"/>
+      <c r="I133" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="D3:D57"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
+    <mergeCell ref="I17:I23"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>

--- a/Mapping Template BrotZeit.xlsx
+++ b/Mapping Template BrotZeit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alfa\Documents\Data Engineer\Projekt\BackZeit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D411F67-5ACF-4B13-97D8-BCE881ACABA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C12A11-F1F9-4F20-B7FB-9ADFF3AD0B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" xr2:uid="{1083ED64-F082-44F9-9F2A-19C2CA2699CD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{1083ED64-F082-44F9-9F2A-19C2CA2699CD}"/>
   </bookViews>
   <sheets>
     <sheet name="D_Filiale" sheetId="9" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="132">
   <si>
     <t>Notes</t>
   </si>
@@ -124,40 +124,22 @@
     <t>Filiale</t>
   </si>
   <si>
-    <t>FilialID</t>
-  </si>
-  <si>
     <t>Adresse</t>
   </si>
   <si>
     <t>Verkäufe</t>
   </si>
   <si>
-    <t>Zeitpunkt</t>
-  </si>
-  <si>
-    <t>Zahlart</t>
-  </si>
-  <si>
     <t>Verkäufer</t>
   </si>
   <si>
-    <t>VerkäuferID</t>
-  </si>
-  <si>
     <t>Produkt</t>
-  </si>
-  <si>
-    <t>ProduktID</t>
   </si>
   <si>
     <t>Rezept</t>
   </si>
   <si>
     <t>beinhaltet</t>
-  </si>
-  <si>
-    <t>Menge</t>
   </si>
   <si>
     <t>Zutaten</t>
@@ -334,9 +316,6 @@
     <t>[TagID] FK</t>
   </si>
   <si>
-    <t>[StundenID] FK</t>
-  </si>
-  <si>
     <t>[VerkaufsvorgangID] FK</t>
   </si>
   <si>
@@ -362,6 +341,102 @@
   </si>
   <si>
     <t>[ZeitID]</t>
+  </si>
+  <si>
+    <t>1:1 Mapping</t>
+  </si>
+  <si>
+    <t>Filiale[AdresseID].[Ort]</t>
+  </si>
+  <si>
+    <t>Falls sich der Filialname ändert wird hier der alte Wert gespeichert, um die Daten vor und nach der Änderung gut vergleichen zu können</t>
+  </si>
+  <si>
+    <t>CONCAT([FilialID], [Zeitpunkt])</t>
+  </si>
+  <si>
+    <t>b' -&gt; Barzahlung, 'k' -&gt; Kartenzahlung</t>
+  </si>
+  <si>
+    <t>Verkäufer[MitarbeiterID].[MitarbeiterName]</t>
+  </si>
+  <si>
+    <t>[KategorieName]</t>
+  </si>
+  <si>
+    <t>Rezept.[Backzeit] * Backkosten / Rezept.[Stückzahl]</t>
+  </si>
+  <si>
+    <t>Backkosten pro Stunde ist eine Konstante</t>
+  </si>
+  <si>
+    <t>Preis des Lagerortes pro Gramm ist eine Konstante je Lagerort</t>
+  </si>
+  <si>
+    <t>SUM(beinhaltet[ProduktID].[ZutatID](beinhaltet.[Menge] * Lagerkosten(Lagerort) / Rezept.[Stückzahl])</t>
+  </si>
+  <si>
+    <t>Rezept.[Zubereitungszeit] * LohnkostenBäcker / Rezept.[Stückzahl]</t>
+  </si>
+  <si>
+    <t>Lohnkosten der Bäcker pro Stunde ist eine Konstante</t>
+  </si>
+  <si>
+    <t>[FilialName_Hist]</t>
+  </si>
+  <si>
+    <t>SUM(beinhaltet[ProduktID].ZutatID)  (beinhaltet[Menge] in g * Zutat[Preis/kg] * 0.001)</t>
+  </si>
+  <si>
+    <t>Nettopreis – (Lohnkosten + Zutatenkosten + Energiekosten + Lagerkosten)</t>
+  </si>
+  <si>
+    <t>Kategorie</t>
+  </si>
+  <si>
+    <t>KategorieID</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Produkt[KategorieID].[Name]</t>
+  </si>
+  <si>
+    <t>[DatumID] FK</t>
+  </si>
+  <si>
+    <t>[ZeitID] FK</t>
+  </si>
+  <si>
+    <t>DAY(Verkauf[Zeitpunkt])</t>
+  </si>
+  <si>
+    <t>HOUR(Verkauf[Zeitpunkt])</t>
+  </si>
+  <si>
+    <t>wirdverkauft[FilialID, Zeitpunkt].[Menge]</t>
+  </si>
+  <si>
+    <t>DAY([Zeitpunkt])</t>
+  </si>
+  <si>
+    <t>LETZTEREINTRAG[AnzahlVerkäufe] + 1</t>
+  </si>
+  <si>
+    <t>LETZTEREINTRAG[Gesamtumsatz] + wirdverkauft[FilialID,Zeitpunkt].[Menge] * wirdverkauft[ProduktID].[Bruttopreis]</t>
+  </si>
+  <si>
+    <t>[Gesamtumsatz] / [AnzahlVerkäufe]</t>
+  </si>
+  <si>
+    <t>[ProduktID] FK</t>
+  </si>
+  <si>
+    <t>wirdverkauft[FilialID,Zeitpunkt].[Menge] * D_Produkt[ProduktID].[Bruttopreis]</t>
+  </si>
+  <si>
+    <t>wirdverkauft[FilialID,Zeitpunkt].[Menge] * D_Produkt[ProduktID].[Gewinnmarge]</t>
   </si>
 </sst>
 </file>
@@ -644,7 +719,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -687,14 +762,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -703,6 +784,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -735,7 +819,64 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1082,34 +1223,34 @@
     <col min="7" max="7" width="20.75" customWidth="1"/>
     <col min="8" max="8" width="17.25" customWidth="1"/>
     <col min="9" max="9" width="29.5" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" customWidth="1"/>
+    <col min="10" max="10" width="23.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="35" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="40" t="s">
+      <c r="G1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="41"/>
+      <c r="H1" s="46"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="24" t="s">
+      <c r="J1" s="27" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1120,10 +1261,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1131,62 +1272,66 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="24"/>
+      <c r="J2" s="27"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="29" t="s">
+      <c r="B3" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="H3" s="32" t="s">
-        <v>47</v>
+      <c r="G3" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="37" t="s">
+        <v>41</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="29"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="21"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
+      <c r="A4" s="29"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
       <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="21"/>
+      <c r="J4" s="29"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="30"/>
+        <v>44</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="34"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
       <c r="H5" s="10" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I5" s="10" t="s">
         <v>19</v>
@@ -1196,40 +1341,46 @@
     <row r="6" spans="1:10" ht="15">
       <c r="A6" s="10"/>
       <c r="B6" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="30"/>
+        <v>45</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="34"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
     </row>
-    <row r="7" spans="1:10" ht="15">
+    <row r="7" spans="1:10" ht="15" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="30"/>
+      <c r="D7" s="34"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
+      <c r="H7" s="10" t="s">
+        <v>113</v>
+      </c>
       <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
+      <c r="J7" s="48" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="15">
       <c r="A8" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="30"/>
+      <c r="D8" s="34"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
@@ -1237,13 +1388,13 @@
       <c r="I8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="10"/>
+      <c r="J8" s="48"/>
     </row>
     <row r="9" spans="1:10" ht="15">
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="30"/>
+      <c r="D9" s="34"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -1251,13 +1402,13 @@
       <c r="I9" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="10"/>
+      <c r="J9" s="48"/>
     </row>
     <row r="10" spans="1:10" ht="15">
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="30"/>
+      <c r="D10" s="34"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -1265,13 +1416,13 @@
       <c r="I10" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="10"/>
+      <c r="J10" s="48"/>
     </row>
     <row r="11" spans="1:10" ht="15">
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="30"/>
+      <c r="D11" s="34"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -1279,25 +1430,25 @@
       <c r="I11" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="10"/>
+      <c r="J11" s="48"/>
     </row>
     <row r="12" spans="1:10" ht="15">
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="30"/>
+      <c r="D12" s="34"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
+      <c r="J12" s="48"/>
     </row>
     <row r="13" spans="1:10" ht="15">
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="30"/>
+      <c r="D13" s="34"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -1311,7 +1462,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="30"/>
+      <c r="D14" s="34"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -1323,7 +1474,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="30"/>
+      <c r="D15" s="34"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
@@ -1337,7 +1488,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="30"/>
+      <c r="D16" s="34"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -1346,94 +1497,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
+      <c r="A17" s="47"/>
+      <c r="B17" s="47"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="21"/>
+      <c r="J17" s="29"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="21"/>
+      <c r="J18" s="29"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="22"/>
-      <c r="B19" s="22"/>
+      <c r="A19" s="47"/>
+      <c r="B19" s="47"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="21"/>
+      <c r="J19" s="29"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
+      <c r="A20" s="47"/>
+      <c r="B20" s="47"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="21"/>
+      <c r="J20" s="29"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="22"/>
-      <c r="B21" s="22"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="21"/>
+      <c r="J21" s="29"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
+      <c r="A22" s="47"/>
+      <c r="B22" s="47"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="21"/>
+      <c r="J22" s="29"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
+      <c r="A23" s="47"/>
+      <c r="B23" s="47"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="21"/>
+      <c r="J23" s="29"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="30"/>
+      <c r="D24" s="34"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -1445,7 +1596,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="30"/>
+      <c r="D25" s="34"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -1457,7 +1608,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="30"/>
+      <c r="D26" s="34"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -1469,7 +1620,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="30"/>
+      <c r="D27" s="34"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -1481,7 +1632,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="30"/>
+      <c r="D28" s="34"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -1493,7 +1644,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="30"/>
+      <c r="D29" s="34"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -1505,7 +1656,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="30"/>
+      <c r="D30" s="34"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -1517,7 +1668,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="30"/>
+      <c r="D31" s="34"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -1529,7 +1680,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="30"/>
+      <c r="D32" s="34"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -1541,7 +1692,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="30"/>
+      <c r="D33" s="34"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -1553,7 +1704,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="30"/>
+      <c r="D34" s="34"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -1565,7 +1716,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="30"/>
+      <c r="D35" s="34"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -1577,7 +1728,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="30"/>
+      <c r="D36" s="34"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -1589,7 +1740,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="30"/>
+      <c r="D37" s="34"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -1601,7 +1752,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="30"/>
+      <c r="D38" s="34"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -1613,7 +1764,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="30"/>
+      <c r="D39" s="34"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -1625,7 +1776,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="30"/>
+      <c r="D40" s="34"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -1637,7 +1788,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="30"/>
+      <c r="D41" s="34"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -1649,7 +1800,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="30"/>
+      <c r="D42" s="34"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -1661,7 +1812,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="30"/>
+      <c r="D43" s="34"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -1673,7 +1824,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="30"/>
+      <c r="D44" s="34"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -1685,7 +1836,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="30"/>
+      <c r="D45" s="34"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -1697,7 +1848,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="30"/>
+      <c r="D46" s="34"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -1709,7 +1860,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="30"/>
+      <c r="D47" s="34"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -1721,7 +1872,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="30"/>
+      <c r="D48" s="34"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -1733,7 +1884,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="30"/>
+      <c r="D49" s="34"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -1745,7 +1896,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="30"/>
+      <c r="D50" s="34"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -1757,7 +1908,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="30"/>
+      <c r="D51" s="34"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -1769,7 +1920,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="30"/>
+      <c r="D52" s="34"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -1781,7 +1932,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="30"/>
+      <c r="D53" s="34"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -1793,7 +1944,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="30"/>
+      <c r="D54" s="34"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -1805,7 +1956,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="30"/>
+      <c r="D55" s="34"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -1817,7 +1968,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="30"/>
+      <c r="D56" s="34"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -1829,7 +1980,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="30"/>
+      <c r="D57" s="34"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -2750,7 +2901,15 @@
       <c r="J133" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="24">
+    <mergeCell ref="J7:J12"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -2767,13 +2926,6 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2781,7 +2933,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F4ADF80-D98B-4509-8551-2DDB8AE878E8}">
-  <dimension ref="A1:J133"/>
+  <dimension ref="A1:J132"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -2793,34 +2945,34 @@
     <col min="7" max="7" width="20.75" customWidth="1"/>
     <col min="8" max="8" width="17.25" customWidth="1"/>
     <col min="9" max="9" width="29.5" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" customWidth="1"/>
+    <col min="10" max="10" width="32.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="35" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="40" t="s">
+      <c r="G1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="41"/>
+      <c r="H1" s="46"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="24" t="s">
+      <c r="J1" s="27" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2831,10 +2983,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2842,75 +2994,79 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="24"/>
+      <c r="J2" s="27"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="29" t="s">
+      <c r="A3" s="55" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="32" t="s">
-        <v>53</v>
+      <c r="G3" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="58" t="s">
+        <v>47</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="29"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="54"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="59"/>
       <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="21"/>
+      <c r="J4" s="29"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="30"/>
+        <v>48</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="34"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="10"/>
+      <c r="G5" s="56"/>
       <c r="H5" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="10"/>
+        <v>48</v>
+      </c>
+      <c r="I5" s="10"/>
+      <c r="J5" s="60" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="15">
       <c r="A6" s="10"/>
-      <c r="B6" s="10" t="s">
-        <v>54</v>
-      </c>
+      <c r="B6" s="10"/>
       <c r="C6" s="11"/>
-      <c r="D6" s="30"/>
+      <c r="D6" s="34"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
@@ -2922,223 +3078,223 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="30"/>
+      <c r="D7" s="34"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
+      <c r="I7" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="J7" s="10"/>
     </row>
     <row r="8" spans="1:10" ht="15">
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="30"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="34"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
       <c r="I8" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J8" s="10"/>
     </row>
     <row r="9" spans="1:10" ht="15">
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="30"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="34"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
       <c r="I9" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J9" s="10"/>
     </row>
     <row r="10" spans="1:10" ht="15">
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="30"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="34"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J10" s="10"/>
     </row>
     <row r="11" spans="1:10" ht="15">
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="30"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="34"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
-      <c r="I11" s="10" t="s">
-        <v>22</v>
-      </c>
+      <c r="I11" s="10"/>
       <c r="J11" s="10"/>
     </row>
     <row r="12" spans="1:10" ht="15">
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="30"/>
+      <c r="D12" s="34"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
+      <c r="I12" s="10" t="s">
+        <v>24</v>
+      </c>
       <c r="J12" s="10"/>
     </row>
     <row r="13" spans="1:10" ht="15">
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="30"/>
+      <c r="D13" s="34"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
-      <c r="I13" s="10" t="s">
-        <v>24</v>
-      </c>
+      <c r="I13" s="10"/>
       <c r="J13" s="10"/>
     </row>
     <row r="14" spans="1:10" ht="15">
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="30"/>
+      <c r="D14" s="34"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
+      <c r="I14" s="10" t="s">
+        <v>25</v>
+      </c>
       <c r="J14" s="10"/>
     </row>
     <row r="15" spans="1:10" ht="15">
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
-      <c r="I15" s="10" t="s">
-        <v>25</v>
-      </c>
+      <c r="I15" s="10"/>
       <c r="J15" s="10"/>
     </row>
     <row r="16" spans="1:10" ht="15">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
       <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
+      <c r="J16" s="29"/>
     </row>
     <row r="17" spans="1:10" ht="15">
       <c r="A17" s="15"/>
       <c r="B17" s="15"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="21"/>
+      <c r="J17" s="29"/>
     </row>
     <row r="18" spans="1:10" ht="15">
       <c r="A18" s="15"/>
       <c r="B18" s="15"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="21"/>
+      <c r="J18" s="29"/>
     </row>
     <row r="19" spans="1:10" ht="15">
       <c r="A19" s="15"/>
       <c r="B19" s="15"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="21"/>
+      <c r="J19" s="29"/>
     </row>
     <row r="20" spans="1:10" ht="15">
       <c r="A20" s="15"/>
       <c r="B20" s="15"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="21"/>
+      <c r="J20" s="29"/>
     </row>
     <row r="21" spans="1:10" ht="15">
       <c r="A21" s="15"/>
       <c r="B21" s="15"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="21"/>
+      <c r="J21" s="29"/>
     </row>
     <row r="22" spans="1:10" ht="15">
       <c r="A22" s="15"/>
       <c r="B22" s="15"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="21"/>
+      <c r="J22" s="29"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="15"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="21"/>
+      <c r="J23" s="10"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="30"/>
+      <c r="D24" s="34"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -3150,9 +3306,9 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
       <c r="I25" s="10"/>
@@ -3162,7 +3318,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="30"/>
+      <c r="D26" s="34"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -3174,7 +3330,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="30"/>
+      <c r="D27" s="34"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -3186,7 +3342,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="30"/>
+      <c r="D28" s="34"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -3196,11 +3352,11 @@
     </row>
     <row r="29" spans="1:10" ht="15">
       <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
+      <c r="B29" s="11"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
       <c r="G29" s="10"/>
       <c r="H29" s="10"/>
       <c r="I29" s="10"/>
@@ -3210,33 +3366,33 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="30"/>
+      <c r="D30" s="34"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
       <c r="J30" s="10"/>
     </row>
     <row r="31" spans="1:10" ht="15">
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="30"/>
+      <c r="D31" s="34"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
       <c r="J31" s="10"/>
     </row>
     <row r="32" spans="1:10" ht="15">
       <c r="A32" s="10"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
       <c r="I32" s="10"/>
@@ -3246,9 +3402,9 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
       <c r="G33" s="10"/>
       <c r="H33" s="10"/>
       <c r="I33" s="10"/>
@@ -3257,8 +3413,8 @@
     <row r="34" spans="1:10" ht="15">
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="30"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="34"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -3270,7 +3426,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="30"/>
+      <c r="D35" s="34"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -3282,7 +3438,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="30"/>
+      <c r="D36" s="34"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -3294,7 +3450,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="30"/>
+      <c r="D37" s="34"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -3306,7 +3462,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="30"/>
+      <c r="D38" s="34"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -3318,7 +3474,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="30"/>
+      <c r="D39" s="34"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -3330,7 +3486,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="30"/>
+      <c r="D40" s="34"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -3342,7 +3498,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="30"/>
+      <c r="D41" s="34"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -3354,7 +3510,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="30"/>
+      <c r="D42" s="34"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -3366,7 +3522,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="30"/>
+      <c r="D43" s="34"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -3378,7 +3534,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="30"/>
+      <c r="D44" s="34"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -3390,7 +3546,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="30"/>
+      <c r="D45" s="34"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -3402,7 +3558,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="30"/>
+      <c r="D46" s="34"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -3414,7 +3570,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="30"/>
+      <c r="D47" s="34"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -3426,7 +3582,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="30"/>
+      <c r="D48" s="34"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -3438,7 +3594,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="30"/>
+      <c r="D49" s="34"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -3450,7 +3606,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="30"/>
+      <c r="D50" s="34"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -3462,7 +3618,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="30"/>
+      <c r="D51" s="34"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -3474,7 +3630,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="30"/>
+      <c r="D52" s="34"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -3486,7 +3642,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="30"/>
+      <c r="D53" s="34"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -3498,7 +3654,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="30"/>
+      <c r="D54" s="34"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -3510,7 +3666,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="30"/>
+      <c r="D55" s="34"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -3522,7 +3678,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="30"/>
+      <c r="D56" s="34"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -3534,7 +3690,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="30"/>
+      <c r="D57" s="6"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -3642,7 +3798,7 @@
       <c r="A66" s="10"/>
       <c r="B66" s="10"/>
       <c r="C66" s="11"/>
-      <c r="D66" s="6"/>
+      <c r="D66" s="5"/>
       <c r="E66" s="11"/>
       <c r="F66" s="11"/>
       <c r="G66" s="10"/>
@@ -3654,7 +3810,7 @@
       <c r="A67" s="10"/>
       <c r="B67" s="10"/>
       <c r="C67" s="11"/>
-      <c r="D67" s="5"/>
+      <c r="D67" s="6"/>
       <c r="E67" s="11"/>
       <c r="F67" s="11"/>
       <c r="G67" s="10"/>
@@ -3714,7 +3870,7 @@
       <c r="A72" s="10"/>
       <c r="B72" s="10"/>
       <c r="C72" s="11"/>
-      <c r="D72" s="6"/>
+      <c r="D72" s="5"/>
       <c r="E72" s="11"/>
       <c r="F72" s="11"/>
       <c r="G72" s="10"/>
@@ -3726,7 +3882,7 @@
       <c r="A73" s="10"/>
       <c r="B73" s="10"/>
       <c r="C73" s="11"/>
-      <c r="D73" s="5"/>
+      <c r="D73" s="6"/>
       <c r="E73" s="11"/>
       <c r="F73" s="11"/>
       <c r="G73" s="10"/>
@@ -3846,7 +4002,7 @@
       <c r="A83" s="10"/>
       <c r="B83" s="10"/>
       <c r="C83" s="11"/>
-      <c r="D83" s="6"/>
+      <c r="D83" s="5"/>
       <c r="E83" s="11"/>
       <c r="F83" s="11"/>
       <c r="G83" s="10"/>
@@ -3858,7 +4014,7 @@
       <c r="A84" s="10"/>
       <c r="B84" s="10"/>
       <c r="C84" s="11"/>
-      <c r="D84" s="5"/>
+      <c r="D84" s="6"/>
       <c r="E84" s="11"/>
       <c r="F84" s="11"/>
       <c r="G84" s="10"/>
@@ -3978,7 +4134,7 @@
       <c r="A94" s="10"/>
       <c r="B94" s="10"/>
       <c r="C94" s="11"/>
-      <c r="D94" s="6"/>
+      <c r="D94" s="5"/>
       <c r="E94" s="11"/>
       <c r="F94" s="11"/>
       <c r="G94" s="10"/>
@@ -3990,7 +4146,7 @@
       <c r="A95" s="10"/>
       <c r="B95" s="10"/>
       <c r="C95" s="11"/>
-      <c r="D95" s="5"/>
+      <c r="D95" s="6"/>
       <c r="E95" s="11"/>
       <c r="F95" s="11"/>
       <c r="G95" s="10"/>
@@ -4110,7 +4266,7 @@
       <c r="A105" s="10"/>
       <c r="B105" s="10"/>
       <c r="C105" s="11"/>
-      <c r="D105" s="6"/>
+      <c r="D105" s="5"/>
       <c r="E105" s="11"/>
       <c r="F105" s="11"/>
       <c r="G105" s="10"/>
@@ -4122,7 +4278,7 @@
       <c r="A106" s="10"/>
       <c r="B106" s="10"/>
       <c r="C106" s="11"/>
-      <c r="D106" s="5"/>
+      <c r="D106" s="6"/>
       <c r="E106" s="11"/>
       <c r="F106" s="11"/>
       <c r="G106" s="10"/>
@@ -4242,7 +4398,7 @@
       <c r="A116" s="10"/>
       <c r="B116" s="10"/>
       <c r="C116" s="11"/>
-      <c r="D116" s="6"/>
+      <c r="D116" s="5"/>
       <c r="E116" s="11"/>
       <c r="F116" s="11"/>
       <c r="G116" s="10"/>
@@ -4254,7 +4410,7 @@
       <c r="A117" s="10"/>
       <c r="B117" s="10"/>
       <c r="C117" s="11"/>
-      <c r="D117" s="5"/>
+      <c r="D117" s="6"/>
       <c r="E117" s="11"/>
       <c r="F117" s="11"/>
       <c r="G117" s="10"/>
@@ -4442,28 +4598,20 @@
       <c r="I132" s="10"/>
       <c r="J132" s="10"/>
     </row>
-    <row r="133" spans="1:10" ht="15">
-      <c r="A133" s="10"/>
-      <c r="B133" s="10"/>
-      <c r="C133" s="11"/>
-      <c r="D133" s="6"/>
-      <c r="E133" s="11"/>
-      <c r="F133" s="11"/>
-      <c r="G133" s="10"/>
-      <c r="H133" s="10"/>
-      <c r="I133" s="10"/>
-      <c r="J133" s="10"/>
-    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="20">
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="J16:J22"/>
+    <mergeCell ref="E16:E22"/>
+    <mergeCell ref="F16:F22"/>
+    <mergeCell ref="G16:G22"/>
+    <mergeCell ref="H16:H22"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D57"/>
+    <mergeCell ref="D3:D56"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="A1:B1"/>
@@ -4472,11 +4620,6 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4484,12 +4627,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36DBACEB-1C96-48F4-AAF8-DD33C824A79C}">
-  <dimension ref="A1:J133"/>
+  <dimension ref="A1:J132"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="24.125" customWidth="1"/>
-    <col min="3" max="3" width="32.625" customWidth="1"/>
+    <col min="3" max="3" width="36.125" customWidth="1"/>
     <col min="4" max="4" width="53.75" customWidth="1"/>
     <col min="5" max="5" width="21.5" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="22.375" hidden="1" customWidth="1"/>
@@ -4500,30 +4643,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="35" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="40" t="s">
+      <c r="G1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="41"/>
+      <c r="H1" s="46"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="24" t="s">
+      <c r="J1" s="27" t="s">
         <v>0</v>
       </c>
     </row>
@@ -4534,10 +4677,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -4545,307 +4688,309 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="24"/>
+      <c r="J2" s="27"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="29" t="s">
+      <c r="A3" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="I3" s="10" t="s">
+      <c r="G3" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="61" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="34"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="63" t="s">
+        <v>54</v>
+      </c>
       <c r="I4" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="21"/>
+        <v>19</v>
+      </c>
+      <c r="J4" s="10"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
-      <c r="B5" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="30"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="34"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
-      <c r="H5" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>19</v>
-      </c>
+      <c r="H5" s="63"/>
+      <c r="I5" s="10"/>
       <c r="J5" s="10"/>
     </row>
     <row r="6" spans="1:10" ht="15">
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="30"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="34"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="12"/>
+      <c r="H6" s="63"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
     </row>
     <row r="7" spans="1:10" ht="15">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="30"/>
+      <c r="A7" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="61"/>
+      <c r="D7" s="34"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="J7" s="10"/>
     </row>
     <row r="8" spans="1:10" ht="15">
-      <c r="A8" s="10" t="s">
-        <v>40</v>
-      </c>
+      <c r="A8" s="10"/>
       <c r="B8" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="30"/>
+        <v>53</v>
+      </c>
+      <c r="C8" s="61"/>
+      <c r="D8" s="34"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
+      <c r="H8" s="63"/>
       <c r="I8" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J8" s="10"/>
     </row>
     <row r="9" spans="1:10" ht="15">
       <c r="A9" s="10"/>
-      <c r="B9" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="30"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="34"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
       <c r="I9" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J9" s="10"/>
     </row>
     <row r="10" spans="1:10" ht="15">
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="30"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="34"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J10" s="10"/>
     </row>
     <row r="11" spans="1:10" ht="15">
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="30"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="34"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
-      <c r="I11" s="10" t="s">
-        <v>22</v>
-      </c>
+      <c r="I11" s="10"/>
       <c r="J11" s="10"/>
     </row>
     <row r="12" spans="1:10" ht="15">
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="30"/>
+      <c r="D12" s="34"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
+      <c r="I12" s="10" t="s">
+        <v>24</v>
+      </c>
       <c r="J12" s="10"/>
     </row>
     <row r="13" spans="1:10" ht="15">
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="30"/>
+      <c r="D13" s="34"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
-      <c r="I13" s="10" t="s">
-        <v>24</v>
-      </c>
+      <c r="I13" s="10"/>
       <c r="J13" s="10"/>
     </row>
     <row r="14" spans="1:10" ht="15">
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="30"/>
+      <c r="D14" s="34"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
+      <c r="I14" s="10" t="s">
+        <v>25</v>
+      </c>
       <c r="J14" s="10"/>
     </row>
     <row r="15" spans="1:10" ht="15">
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
-      <c r="I15" s="10" t="s">
-        <v>25</v>
-      </c>
+      <c r="I15" s="10"/>
       <c r="J15" s="10"/>
     </row>
     <row r="16" spans="1:10" ht="15">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
+      <c r="A16" s="47"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
       <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
+      <c r="J16" s="29"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
+      <c r="A17" s="47"/>
+      <c r="B17" s="47"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="21"/>
+      <c r="J17" s="29"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="21"/>
+      <c r="J18" s="29"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="22"/>
-      <c r="B19" s="22"/>
+      <c r="A19" s="47"/>
+      <c r="B19" s="47"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="21"/>
+      <c r="J19" s="29"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
+      <c r="A20" s="47"/>
+      <c r="B20" s="47"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="21"/>
+      <c r="J20" s="29"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="22"/>
-      <c r="B21" s="22"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="21"/>
+      <c r="J21" s="29"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
+      <c r="A22" s="47"/>
+      <c r="B22" s="47"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="21"/>
+      <c r="J22" s="29"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="21"/>
+      <c r="J23" s="10"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="30"/>
+      <c r="D24" s="34"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -4857,9 +5002,9 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
       <c r="I25" s="10"/>
@@ -4869,7 +5014,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="30"/>
+      <c r="D26" s="34"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -4881,7 +5026,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="30"/>
+      <c r="D27" s="34"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -4893,7 +5038,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="30"/>
+      <c r="D28" s="34"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -4903,11 +5048,11 @@
     </row>
     <row r="29" spans="1:10" ht="15">
       <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
+      <c r="B29" s="11"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
       <c r="G29" s="10"/>
       <c r="H29" s="10"/>
       <c r="I29" s="10"/>
@@ -4917,33 +5062,33 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="30"/>
+      <c r="D30" s="34"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
       <c r="J30" s="10"/>
     </row>
     <row r="31" spans="1:10" ht="15">
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="30"/>
+      <c r="D31" s="34"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
       <c r="J31" s="10"/>
     </row>
     <row r="32" spans="1:10" ht="15">
       <c r="A32" s="10"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
       <c r="I32" s="10"/>
@@ -4953,9 +5098,9 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
       <c r="G33" s="10"/>
       <c r="H33" s="10"/>
       <c r="I33" s="10"/>
@@ -4964,8 +5109,8 @@
     <row r="34" spans="1:10" ht="15">
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="30"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="34"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -4977,7 +5122,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="30"/>
+      <c r="D35" s="34"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -4989,7 +5134,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="30"/>
+      <c r="D36" s="34"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -5001,7 +5146,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="30"/>
+      <c r="D37" s="34"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -5009,11 +5154,11 @@
       <c r="I37" s="10"/>
       <c r="J37" s="10"/>
     </row>
-    <row r="38" spans="1:10" ht="15">
+    <row r="38" spans="1:10">
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="30"/>
+      <c r="D38" s="34"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -5025,7 +5170,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="30"/>
+      <c r="D39" s="34"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -5037,7 +5182,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="30"/>
+      <c r="D40" s="34"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -5049,7 +5194,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="30"/>
+      <c r="D41" s="34"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -5061,7 +5206,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="30"/>
+      <c r="D42" s="34"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -5073,7 +5218,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="30"/>
+      <c r="D43" s="34"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -5085,7 +5230,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="30"/>
+      <c r="D44" s="34"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -5097,7 +5242,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="30"/>
+      <c r="D45" s="34"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -5109,7 +5254,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="30"/>
+      <c r="D46" s="34"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -5121,7 +5266,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="30"/>
+      <c r="D47" s="34"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -5133,7 +5278,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="30"/>
+      <c r="D48" s="34"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -5145,7 +5290,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="30"/>
+      <c r="D49" s="34"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -5157,7 +5302,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="30"/>
+      <c r="D50" s="34"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -5169,7 +5314,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="30"/>
+      <c r="D51" s="34"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -5181,7 +5326,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="30"/>
+      <c r="D52" s="34"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -5193,7 +5338,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="30"/>
+      <c r="D53" s="34"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -5205,7 +5350,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="30"/>
+      <c r="D54" s="34"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -5217,7 +5362,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="30"/>
+      <c r="D55" s="34"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -5229,7 +5374,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="30"/>
+      <c r="D56" s="34"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -5241,7 +5386,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="30"/>
+      <c r="D57" s="6"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -5349,7 +5494,7 @@
       <c r="A66" s="10"/>
       <c r="B66" s="10"/>
       <c r="C66" s="11"/>
-      <c r="D66" s="6"/>
+      <c r="D66" s="5"/>
       <c r="E66" s="11"/>
       <c r="F66" s="11"/>
       <c r="G66" s="10"/>
@@ -5361,7 +5506,7 @@
       <c r="A67" s="10"/>
       <c r="B67" s="10"/>
       <c r="C67" s="11"/>
-      <c r="D67" s="5"/>
+      <c r="D67" s="6"/>
       <c r="E67" s="11"/>
       <c r="F67" s="11"/>
       <c r="G67" s="10"/>
@@ -5421,7 +5566,7 @@
       <c r="A72" s="10"/>
       <c r="B72" s="10"/>
       <c r="C72" s="11"/>
-      <c r="D72" s="6"/>
+      <c r="D72" s="5"/>
       <c r="E72" s="11"/>
       <c r="F72" s="11"/>
       <c r="G72" s="10"/>
@@ -5433,7 +5578,7 @@
       <c r="A73" s="10"/>
       <c r="B73" s="10"/>
       <c r="C73" s="11"/>
-      <c r="D73" s="5"/>
+      <c r="D73" s="6"/>
       <c r="E73" s="11"/>
       <c r="F73" s="11"/>
       <c r="G73" s="10"/>
@@ -5553,7 +5698,7 @@
       <c r="A83" s="10"/>
       <c r="B83" s="10"/>
       <c r="C83" s="11"/>
-      <c r="D83" s="6"/>
+      <c r="D83" s="5"/>
       <c r="E83" s="11"/>
       <c r="F83" s="11"/>
       <c r="G83" s="10"/>
@@ -5565,7 +5710,7 @@
       <c r="A84" s="10"/>
       <c r="B84" s="10"/>
       <c r="C84" s="11"/>
-      <c r="D84" s="5"/>
+      <c r="D84" s="6"/>
       <c r="E84" s="11"/>
       <c r="F84" s="11"/>
       <c r="G84" s="10"/>
@@ -5685,7 +5830,7 @@
       <c r="A94" s="10"/>
       <c r="B94" s="10"/>
       <c r="C94" s="11"/>
-      <c r="D94" s="6"/>
+      <c r="D94" s="5"/>
       <c r="E94" s="11"/>
       <c r="F94" s="11"/>
       <c r="G94" s="10"/>
@@ -5697,7 +5842,7 @@
       <c r="A95" s="10"/>
       <c r="B95" s="10"/>
       <c r="C95" s="11"/>
-      <c r="D95" s="5"/>
+      <c r="D95" s="6"/>
       <c r="E95" s="11"/>
       <c r="F95" s="11"/>
       <c r="G95" s="10"/>
@@ -5817,7 +5962,7 @@
       <c r="A105" s="10"/>
       <c r="B105" s="10"/>
       <c r="C105" s="11"/>
-      <c r="D105" s="6"/>
+      <c r="D105" s="5"/>
       <c r="E105" s="11"/>
       <c r="F105" s="11"/>
       <c r="G105" s="10"/>
@@ -5829,7 +5974,7 @@
       <c r="A106" s="10"/>
       <c r="B106" s="10"/>
       <c r="C106" s="11"/>
-      <c r="D106" s="5"/>
+      <c r="D106" s="6"/>
       <c r="E106" s="11"/>
       <c r="F106" s="11"/>
       <c r="G106" s="10"/>
@@ -5949,7 +6094,7 @@
       <c r="A116" s="10"/>
       <c r="B116" s="10"/>
       <c r="C116" s="11"/>
-      <c r="D116" s="6"/>
+      <c r="D116" s="5"/>
       <c r="E116" s="11"/>
       <c r="F116" s="11"/>
       <c r="G116" s="10"/>
@@ -5961,7 +6106,7 @@
       <c r="A117" s="10"/>
       <c r="B117" s="10"/>
       <c r="C117" s="11"/>
-      <c r="D117" s="5"/>
+      <c r="D117" s="6"/>
       <c r="E117" s="11"/>
       <c r="F117" s="11"/>
       <c r="G117" s="10"/>
@@ -6149,43 +6294,25 @@
       <c r="I132" s="10"/>
       <c r="J132" s="10"/>
     </row>
-    <row r="133" spans="1:10" ht="15">
-      <c r="A133" s="10"/>
-      <c r="B133" s="10"/>
-      <c r="C133" s="11"/>
-      <c r="D133" s="6"/>
-      <c r="E133" s="11"/>
-      <c r="F133" s="11"/>
-      <c r="G133" s="10"/>
-      <c r="H133" s="10"/>
-      <c r="I133" s="10"/>
-      <c r="J133" s="10"/>
-    </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="17">
+    <mergeCell ref="C4:C8"/>
+    <mergeCell ref="H4:H8"/>
+    <mergeCell ref="J16:J22"/>
+    <mergeCell ref="A16:A22"/>
+    <mergeCell ref="B16:B22"/>
+    <mergeCell ref="E16:E22"/>
+    <mergeCell ref="F16:F22"/>
+    <mergeCell ref="G16:G22"/>
+    <mergeCell ref="H16:H22"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D57"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="D3:D56"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6209,30 +6336,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="35" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="40" t="s">
+      <c r="G1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="41"/>
+      <c r="H1" s="46"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="24" t="s">
+      <c r="J1" s="27" t="s">
         <v>0</v>
       </c>
     </row>
@@ -6243,10 +6370,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -6254,56 +6381,56 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="24"/>
+      <c r="J2" s="27"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="29" t="s">
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="H3" s="32" t="s">
-        <v>64</v>
+      <c r="G3" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="37" t="s">
+        <v>58</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="29"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
       <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="21"/>
+      <c r="J4" s="29"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="10"/>
       <c r="C5" s="11"/>
-      <c r="D5" s="30"/>
+      <c r="D5" s="34"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
       <c r="H5" s="10" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="I5" s="10" t="s">
         <v>19</v>
@@ -6314,12 +6441,12 @@
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
       <c r="C6" s="11"/>
-      <c r="D6" s="30"/>
+      <c r="D6" s="34"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
@@ -6328,12 +6455,12 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="30"/>
+      <c r="D7" s="34"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
       <c r="H7" s="10" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
@@ -6342,12 +6469,12 @@
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="30"/>
+      <c r="D8" s="34"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
       <c r="H8" s="10" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>20</v>
@@ -6358,7 +6485,7 @@
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="30"/>
+      <c r="D9" s="34"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -6372,7 +6499,7 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="30"/>
+      <c r="D10" s="34"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -6386,7 +6513,7 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="30"/>
+      <c r="D11" s="34"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -6400,7 +6527,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="30"/>
+      <c r="D12" s="34"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -6412,7 +6539,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="30"/>
+      <c r="D13" s="34"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -6426,7 +6553,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="30"/>
+      <c r="D14" s="34"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -6438,7 +6565,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="30"/>
+      <c r="D15" s="34"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
@@ -6452,7 +6579,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="30"/>
+      <c r="D16" s="34"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -6461,94 +6588,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
+      <c r="A17" s="47"/>
+      <c r="B17" s="47"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="21"/>
+      <c r="J17" s="29"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="21"/>
+      <c r="J18" s="29"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="22"/>
-      <c r="B19" s="22"/>
+      <c r="A19" s="47"/>
+      <c r="B19" s="47"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="21"/>
+      <c r="J19" s="29"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
+      <c r="A20" s="47"/>
+      <c r="B20" s="47"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="21"/>
+      <c r="J20" s="29"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="22"/>
-      <c r="B21" s="22"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="21"/>
+      <c r="J21" s="29"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
+      <c r="A22" s="47"/>
+      <c r="B22" s="47"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="21"/>
+      <c r="J22" s="29"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
+      <c r="A23" s="47"/>
+      <c r="B23" s="47"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="21"/>
+      <c r="J23" s="29"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="30"/>
+      <c r="D24" s="34"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -6560,7 +6687,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="30"/>
+      <c r="D25" s="34"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -6572,7 +6699,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="30"/>
+      <c r="D26" s="34"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -6584,7 +6711,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="30"/>
+      <c r="D27" s="34"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -6596,7 +6723,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="30"/>
+      <c r="D28" s="34"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -6608,7 +6735,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="30"/>
+      <c r="D29" s="34"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -6620,7 +6747,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="30"/>
+      <c r="D30" s="34"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -6632,7 +6759,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="30"/>
+      <c r="D31" s="34"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -6644,7 +6771,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="30"/>
+      <c r="D32" s="34"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -6656,7 +6783,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="30"/>
+      <c r="D33" s="34"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -6668,7 +6795,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="30"/>
+      <c r="D34" s="34"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -6680,7 +6807,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="30"/>
+      <c r="D35" s="34"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -6692,7 +6819,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="30"/>
+      <c r="D36" s="34"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -6704,7 +6831,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="30"/>
+      <c r="D37" s="34"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -6716,7 +6843,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="30"/>
+      <c r="D38" s="34"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -6728,7 +6855,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="30"/>
+      <c r="D39" s="34"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -6740,7 +6867,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="30"/>
+      <c r="D40" s="34"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -6752,7 +6879,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="30"/>
+      <c r="D41" s="34"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -6764,7 +6891,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="30"/>
+      <c r="D42" s="34"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -6776,7 +6903,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="30"/>
+      <c r="D43" s="34"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -6788,7 +6915,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="30"/>
+      <c r="D44" s="34"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -6800,7 +6927,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="30"/>
+      <c r="D45" s="34"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -6812,7 +6939,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="30"/>
+      <c r="D46" s="34"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -6824,7 +6951,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="30"/>
+      <c r="D47" s="34"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -6836,7 +6963,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="30"/>
+      <c r="D48" s="34"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -6848,7 +6975,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="30"/>
+      <c r="D49" s="34"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -6860,7 +6987,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="30"/>
+      <c r="D50" s="34"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -6872,7 +6999,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="30"/>
+      <c r="D51" s="34"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -6884,7 +7011,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="30"/>
+      <c r="D52" s="34"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -6896,7 +7023,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="30"/>
+      <c r="D53" s="34"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -6908,7 +7035,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="30"/>
+      <c r="D54" s="34"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -6920,7 +7047,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="30"/>
+      <c r="D55" s="34"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -6932,7 +7059,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="30"/>
+      <c r="D56" s="34"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -6944,7 +7071,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="30"/>
+      <c r="D57" s="34"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -7866,6 +7993,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -7882,13 +8016,6 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7912,30 +8039,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="35" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="40" t="s">
+      <c r="G1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="41"/>
+      <c r="H1" s="46"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="24" t="s">
+      <c r="J1" s="27" t="s">
         <v>0</v>
       </c>
     </row>
@@ -7946,10 +8073,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -7957,56 +8084,56 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="24"/>
+      <c r="J2" s="27"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="29" t="s">
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" s="32" t="s">
-        <v>68</v>
+      <c r="G3" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="37" t="s">
+        <v>62</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="29"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
       <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="21"/>
+      <c r="J4" s="29"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="10"/>
       <c r="C5" s="11"/>
-      <c r="D5" s="30"/>
+      <c r="D5" s="34"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
       <c r="H5" s="10" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="I5" s="10" t="s">
         <v>19</v>
@@ -8017,12 +8144,12 @@
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
       <c r="C6" s="11"/>
-      <c r="D6" s="30"/>
+      <c r="D6" s="34"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
@@ -8031,7 +8158,7 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="30"/>
+      <c r="D7" s="34"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
@@ -8043,7 +8170,7 @@
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="30"/>
+      <c r="D8" s="34"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
@@ -8057,7 +8184,7 @@
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="30"/>
+      <c r="D9" s="34"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -8071,7 +8198,7 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="30"/>
+      <c r="D10" s="34"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -8085,7 +8212,7 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="30"/>
+      <c r="D11" s="34"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -8099,7 +8226,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="30"/>
+      <c r="D12" s="34"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -8111,7 +8238,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="30"/>
+      <c r="D13" s="34"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -8125,7 +8252,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="30"/>
+      <c r="D14" s="34"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -8137,7 +8264,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="30"/>
+      <c r="D15" s="34"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
@@ -8151,7 +8278,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="30"/>
+      <c r="D16" s="34"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -8160,94 +8287,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
+      <c r="A17" s="47"/>
+      <c r="B17" s="47"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="21"/>
+      <c r="J17" s="29"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="21"/>
+      <c r="J18" s="29"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="22"/>
-      <c r="B19" s="22"/>
+      <c r="A19" s="47"/>
+      <c r="B19" s="47"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="21"/>
+      <c r="J19" s="29"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
+      <c r="A20" s="47"/>
+      <c r="B20" s="47"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="21"/>
+      <c r="J20" s="29"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="22"/>
-      <c r="B21" s="22"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="21"/>
+      <c r="J21" s="29"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
+      <c r="A22" s="47"/>
+      <c r="B22" s="47"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="21"/>
+      <c r="J22" s="29"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
+      <c r="A23" s="47"/>
+      <c r="B23" s="47"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="21"/>
+      <c r="J23" s="29"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="30"/>
+      <c r="D24" s="34"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -8259,7 +8386,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="30"/>
+      <c r="D25" s="34"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -8271,7 +8398,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="30"/>
+      <c r="D26" s="34"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -8283,7 +8410,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="30"/>
+      <c r="D27" s="34"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -8295,7 +8422,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="30"/>
+      <c r="D28" s="34"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -8307,7 +8434,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="30"/>
+      <c r="D29" s="34"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -8319,7 +8446,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="30"/>
+      <c r="D30" s="34"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -8331,7 +8458,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="30"/>
+      <c r="D31" s="34"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -8343,7 +8470,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="30"/>
+      <c r="D32" s="34"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -8355,7 +8482,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="30"/>
+      <c r="D33" s="34"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -8367,7 +8494,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="30"/>
+      <c r="D34" s="34"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -8379,7 +8506,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="30"/>
+      <c r="D35" s="34"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -8391,7 +8518,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="30"/>
+      <c r="D36" s="34"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -8403,7 +8530,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="30"/>
+      <c r="D37" s="34"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -8415,7 +8542,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="30"/>
+      <c r="D38" s="34"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -8427,7 +8554,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="30"/>
+      <c r="D39" s="34"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -8439,7 +8566,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="30"/>
+      <c r="D40" s="34"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -8451,7 +8578,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="30"/>
+      <c r="D41" s="34"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -8463,7 +8590,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="30"/>
+      <c r="D42" s="34"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -8475,7 +8602,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="30"/>
+      <c r="D43" s="34"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -8487,7 +8614,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="30"/>
+      <c r="D44" s="34"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -8499,7 +8626,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="30"/>
+      <c r="D45" s="34"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -8511,7 +8638,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="30"/>
+      <c r="D46" s="34"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -8523,7 +8650,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="30"/>
+      <c r="D47" s="34"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -8535,7 +8662,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="30"/>
+      <c r="D48" s="34"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -8547,7 +8674,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="30"/>
+      <c r="D49" s="34"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -8559,7 +8686,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="30"/>
+      <c r="D50" s="34"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -8571,7 +8698,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="30"/>
+      <c r="D51" s="34"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -8583,7 +8710,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="30"/>
+      <c r="D52" s="34"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -8595,7 +8722,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="30"/>
+      <c r="D53" s="34"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -8607,7 +8734,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="30"/>
+      <c r="D54" s="34"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -8619,7 +8746,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="30"/>
+      <c r="D55" s="34"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -8631,7 +8758,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="30"/>
+      <c r="D56" s="34"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -8643,7 +8770,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="30"/>
+      <c r="D57" s="34"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -9565,6 +9692,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -9581,13 +9715,6 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9607,34 +9734,34 @@
     <col min="7" max="7" width="20.75" customWidth="1"/>
     <col min="8" max="8" width="17.25" customWidth="1"/>
     <col min="9" max="9" width="29.5" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" customWidth="1"/>
+    <col min="10" max="10" width="42.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="35" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="40" t="s">
+      <c r="G1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="41"/>
+      <c r="H1" s="46"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="24" t="s">
+      <c r="J1" s="27" t="s">
         <v>0</v>
       </c>
     </row>
@@ -9645,10 +9772,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -9656,349 +9783,348 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="24"/>
+      <c r="J2" s="27"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" s="32" t="s">
-        <v>70</v>
+      <c r="G3" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>64</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="21"/>
+        <v>18</v>
+      </c>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" spans="1:10" ht="15">
       <c r="B4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="28"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="31"/>
+        <v>65</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" s="34"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="36"/>
       <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
+      <c r="H4" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="I4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="21"/>
+        <v>19</v>
+      </c>
+      <c r="J4" s="4"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="B5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="30"/>
+        <v>67</v>
+      </c>
+      <c r="C5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="34"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="I5" s="4"/>
       <c r="J5" s="4"/>
     </row>
     <row r="6" spans="1:10" ht="15">
       <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="30"/>
+        <v>68</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" s="34"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10" ht="15">
-      <c r="B7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="30"/>
+    <row r="7" spans="1:10" ht="60">
+      <c r="C7" s="66" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="34"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="4"/>
-      <c r="H7" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-    </row>
-    <row r="8" spans="1:10" ht="15">
-      <c r="C8" s="7"/>
-      <c r="D8" s="30"/>
+      <c r="H7" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="65" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="30">
+      <c r="C8" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="34"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" s="4"/>
-    </row>
-    <row r="9" spans="1:10" ht="15">
-      <c r="A9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="30"/>
+        <v>21</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="30">
+      <c r="C9" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" s="34"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="4"/>
+        <v>23</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="10" spans="1:10" ht="15">
-      <c r="B10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="30"/>
+      <c r="C10" s="68" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" s="34"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="4"/>
-      <c r="H10" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" s="4"/>
-    </row>
-    <row r="11" spans="1:10" ht="15">
-      <c r="B11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="30"/>
+      <c r="H10" s="67" t="s">
+        <v>72</v>
+      </c>
+      <c r="I10" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="62"/>
+    </row>
+    <row r="11" spans="1:10" ht="15" customHeight="1">
+      <c r="C11" s="68"/>
+      <c r="D11" s="34"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="4"/>
-      <c r="H11" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="4"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="62"/>
     </row>
     <row r="12" spans="1:10" ht="15">
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="30"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="34"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-    </row>
-    <row r="13" spans="1:10" ht="15">
-      <c r="B13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="30"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="62"/>
+    </row>
+    <row r="13" spans="1:10" ht="45">
+      <c r="C13" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="D13" s="34"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>24</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="I13" s="4"/>
       <c r="J13" s="4"/>
     </row>
     <row r="14" spans="1:10" ht="15">
-      <c r="C14" s="7"/>
-      <c r="D14" s="30"/>
+      <c r="B14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" s="34"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
+      <c r="H14" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="J14" s="4"/>
     </row>
     <row r="15" spans="1:10" ht="15">
-      <c r="A15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="30"/>
+      <c r="C15" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="D15" s="34"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4" t="s">
-        <v>25</v>
-      </c>
+      <c r="H15" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="I15" s="4"/>
       <c r="J15" s="4"/>
     </row>
     <row r="16" spans="1:10" ht="15">
-      <c r="B16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="30"/>
+      <c r="D16" s="34"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="51"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="B17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="21"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="51"/>
     </row>
     <row r="18" spans="1:10" ht="15">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
       <c r="B18" t="s">
-        <v>86</v>
-      </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="21"/>
+        <v>74</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="51"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="C19" s="8"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="21"/>
+      <c r="B19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="51"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" t="s">
-        <v>36</v>
-      </c>
       <c r="B20" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="21"/>
+        <v>76</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="51"/>
     </row>
     <row r="21" spans="1:10" ht="15">
       <c r="B21" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="21"/>
+        <v>77</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="51"/>
     </row>
     <row r="22" spans="1:10" ht="15">
       <c r="B22" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="21"/>
+        <v>78</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="51"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="B23" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" s="8"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="4"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="21"/>
       <c r="J23" s="21"/>
     </row>
     <row r="24" spans="1:10" ht="15">
+      <c r="A24" t="s">
+        <v>32</v>
+      </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C24" s="7"/>
-      <c r="D24" s="30"/>
+      <c r="D24" s="34"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
-      <c r="G24" s="4"/>
+      <c r="G24" s="21"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
     </row>
     <row r="25" spans="1:10" ht="15">
       <c r="B25" t="s">
-        <v>90</v>
-      </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="30"/>
+        <v>79</v>
+      </c>
+      <c r="C25" s="8"/>
+      <c r="D25" s="34"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="4"/>
@@ -10008,10 +10134,10 @@
     </row>
     <row r="26" spans="1:10" ht="15">
       <c r="B26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="30"/>
+        <v>64</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="D26" s="34"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -10021,10 +10147,10 @@
     </row>
     <row r="27" spans="1:10" ht="15">
       <c r="B27" t="s">
-        <v>92</v>
-      </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="30"/>
+        <v>80</v>
+      </c>
+      <c r="C27" s="8"/>
+      <c r="D27" s="34"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
@@ -10033,10 +10159,8 @@
       <c r="J27" s="4"/>
     </row>
     <row r="28" spans="1:10" ht="15">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="30"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="34"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -10045,10 +10169,14 @@
       <c r="J28" s="4"/>
     </row>
     <row r="29" spans="1:10" ht="15">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="30"/>
+      <c r="A29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="8"/>
+      <c r="D29" s="34"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -10057,34 +10185,37 @@
       <c r="J29" s="4"/>
     </row>
     <row r="30" spans="1:10" ht="15">
-      <c r="A30" s="4"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="30"/>
+      <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="34"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
+      <c r="I30" s="7"/>
       <c r="J30" s="4"/>
     </row>
     <row r="31" spans="1:10" ht="15">
-      <c r="A31" s="4"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="30"/>
+      <c r="B31" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" s="8"/>
+      <c r="D31" s="34"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="4"/>
       <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
+      <c r="I31" s="4"/>
       <c r="J31" s="4"/>
     </row>
     <row r="32" spans="1:10" ht="15">
-      <c r="A32" s="4"/>
-      <c r="B32" s="7"/>
+      <c r="B32" t="s">
+        <v>82</v>
+      </c>
       <c r="C32" s="7"/>
-      <c r="D32" s="30"/>
+      <c r="D32" s="34"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="4"/>
@@ -10093,10 +10224,11 @@
       <c r="J32" s="4"/>
     </row>
     <row r="33" spans="1:10" ht="15">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="30"/>
+      <c r="B33" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" s="7"/>
+      <c r="D33" s="34"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
@@ -10105,10 +10237,11 @@
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="1:10" ht="15">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="30"/>
+      <c r="B34" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="7"/>
+      <c r="D34" s="34"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
       <c r="G34" s="4"/>
@@ -10117,10 +10250,11 @@
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="1:10" ht="15">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
+      <c r="B35" t="s">
+        <v>85</v>
+      </c>
       <c r="C35" s="7"/>
-      <c r="D35" s="30"/>
+      <c r="D35" s="34"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
       <c r="G35" s="4"/>
@@ -10129,10 +10263,11 @@
       <c r="J35" s="4"/>
     </row>
     <row r="36" spans="1:10" ht="15">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
+      <c r="B36" t="s">
+        <v>86</v>
+      </c>
       <c r="C36" s="7"/>
-      <c r="D36" s="30"/>
+      <c r="D36" s="34"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="4"/>
@@ -10144,7 +10279,7 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="30"/>
+      <c r="D37" s="34"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="4"/>
@@ -10153,10 +10288,14 @@
       <c r="J37" s="4"/>
     </row>
     <row r="38" spans="1:10" ht="15">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
+      <c r="A38" t="s">
+        <v>116</v>
+      </c>
+      <c r="B38" t="s">
+        <v>117</v>
+      </c>
       <c r="C38" s="7"/>
-      <c r="D38" s="30"/>
+      <c r="D38" s="34"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="4"/>
@@ -10165,10 +10304,11 @@
       <c r="J38" s="4"/>
     </row>
     <row r="39" spans="1:10" ht="15">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
+      <c r="B39" t="s">
+        <v>118</v>
+      </c>
       <c r="C39" s="7"/>
-      <c r="D39" s="30"/>
+      <c r="D39" s="34"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="4"/>
@@ -10177,10 +10317,9 @@
       <c r="J39" s="4"/>
     </row>
     <row r="40" spans="1:10" ht="15">
-      <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="7"/>
-      <c r="D40" s="30"/>
+      <c r="D40" s="34"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="4"/>
@@ -10189,10 +10328,9 @@
       <c r="J40" s="4"/>
     </row>
     <row r="41" spans="1:10" ht="15">
-      <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="30"/>
+      <c r="D41" s="34"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="4"/>
@@ -10204,7 +10342,7 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="30"/>
+      <c r="D42" s="34"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="4"/>
@@ -10216,7 +10354,7 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="30"/>
+      <c r="D43" s="34"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="4"/>
@@ -10228,7 +10366,7 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="7"/>
-      <c r="D44" s="30"/>
+      <c r="D44" s="34"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="4"/>
@@ -10240,7 +10378,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="30"/>
+      <c r="D45" s="34"/>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
       <c r="G45" s="4"/>
@@ -10252,7 +10390,7 @@
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="7"/>
-      <c r="D46" s="30"/>
+      <c r="D46" s="34"/>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
       <c r="G46" s="4"/>
@@ -10264,7 +10402,7 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="7"/>
-      <c r="D47" s="30"/>
+      <c r="D47" s="34"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
       <c r="G47" s="4"/>
@@ -10276,7 +10414,7 @@
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="7"/>
-      <c r="D48" s="30"/>
+      <c r="D48" s="34"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
       <c r="G48" s="4"/>
@@ -10288,7 +10426,7 @@
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="7"/>
-      <c r="D49" s="30"/>
+      <c r="D49" s="34"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
       <c r="G49" s="4"/>
@@ -10300,7 +10438,7 @@
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="30"/>
+      <c r="D50" s="34"/>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
       <c r="G50" s="4"/>
@@ -10312,7 +10450,7 @@
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="7"/>
-      <c r="D51" s="30"/>
+      <c r="D51" s="34"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
       <c r="G51" s="4"/>
@@ -10324,7 +10462,7 @@
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="7"/>
-      <c r="D52" s="30"/>
+      <c r="D52" s="34"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
       <c r="G52" s="4"/>
@@ -10336,7 +10474,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="30"/>
+      <c r="D53" s="34"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="4"/>
@@ -10348,7 +10486,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="30"/>
+      <c r="D54" s="34"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
       <c r="G54" s="4"/>
@@ -10360,7 +10498,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="7"/>
-      <c r="D55" s="30"/>
+      <c r="D55" s="34"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
       <c r="G55" s="4"/>
@@ -10372,7 +10510,7 @@
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="7"/>
-      <c r="D56" s="30"/>
+      <c r="D56" s="34"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
       <c r="G56" s="4"/>
@@ -10384,7 +10522,7 @@
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="7"/>
-      <c r="D57" s="30"/>
+      <c r="D57" s="34"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
       <c r="G57" s="4"/>
@@ -11295,36 +11433,29 @@
     <row r="133" spans="1:10" ht="15">
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
-      <c r="C133" s="7"/>
       <c r="D133" s="6"/>
       <c r="E133" s="7"/>
       <c r="F133" s="7"/>
       <c r="G133" s="4"/>
       <c r="H133" s="4"/>
-      <c r="I133" s="4"/>
-      <c r="J133" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="D3:D57"/>
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
+  <mergeCells count="15">
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="H10:H12"/>
+    <mergeCell ref="J10:J12"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="D3:D57"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11333,12 +11464,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94A74049-1771-468B-813D-A487483CB510}">
-  <dimension ref="A1:I133"/>
+  <dimension ref="A1:I136"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="29.75" customWidth="1"/>
     <col min="2" max="2" width="45.25" customWidth="1"/>
-    <col min="3" max="3" width="32.625" customWidth="1"/>
+    <col min="3" max="3" width="39.75" customWidth="1"/>
     <col min="4" max="4" width="59.125" customWidth="1"/>
     <col min="5" max="5" width="20" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="17.25" hidden="1" customWidth="1"/>
@@ -11347,27 +11478,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="35" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="40" t="s">
+      <c r="G1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="41"/>
-      <c r="I1" s="24" t="s">
+      <c r="H1" s="46"/>
+      <c r="I1" s="27" t="s">
         <v>0</v>
       </c>
     </row>
@@ -11378,160 +11509,156 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="24"/>
+      <c r="I2" s="27"/>
     </row>
     <row r="3" spans="1:9" ht="15">
       <c r="A3" s="14" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="23"/>
-      <c r="F3" s="31"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="36"/>
       <c r="G3" s="14" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="I3" s="21"/>
-    </row>
-    <row r="4" spans="1:9" ht="14.25" customHeight="1">
+        <v>88</v>
+      </c>
+      <c r="I3" s="29"/>
+    </row>
+    <row r="4" spans="1:9" ht="15" customHeight="1">
       <c r="A4" s="14"/>
       <c r="B4" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="31"/>
+        <v>41</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" s="34"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="36"/>
       <c r="G4" s="13"/>
       <c r="H4" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="I4" s="21"/>
-    </row>
-    <row r="5" spans="1:9" ht="15">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="I5" s="4"/>
+        <v>89</v>
+      </c>
+      <c r="I4" s="29"/>
+    </row>
+    <row r="5" spans="1:9" ht="15" customHeight="1">
+      <c r="A5" s="25"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="I5" s="21"/>
     </row>
     <row r="6" spans="1:9" ht="15">
       <c r="A6" s="14"/>
       <c r="B6" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="30"/>
+        <v>49</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="34"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:9" ht="15">
       <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="30"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="34"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" ht="15">
-      <c r="A8" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="30"/>
+      <c r="C8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D8" s="34"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9" ht="15">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="30"/>
+    <row r="9" spans="1:9" ht="38.25" customHeight="1">
+      <c r="C9" s="69" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" s="34"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="I9" s="4"/>
     </row>
-    <row r="10" spans="1:9" ht="15">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="30"/>
+    <row r="10" spans="1:9" ht="42.75" customHeight="1">
+      <c r="C10" s="70" t="s">
+        <v>131</v>
+      </c>
+      <c r="D10" s="34"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="H10" s="4" t="s">
+        <v>92</v>
+      </c>
       <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" ht="15">
       <c r="A11" s="14"/>
       <c r="B11" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="30"/>
+        <v>48</v>
+      </c>
+      <c r="D11" s="34"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
       <c r="I11" s="4"/>
     </row>
     <row r="12" spans="1:9" ht="15">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="30"/>
+      <c r="A12" s="14"/>
+      <c r="D12" s="34"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="4"/>
@@ -11539,10 +11666,13 @@
       <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:9" ht="15">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="30"/>
+      <c r="A13" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="34"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="4"/>
@@ -11550,10 +11680,11 @@
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:9" ht="15">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="30"/>
+      <c r="A14" s="25"/>
+      <c r="B14" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="34"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="4"/>
@@ -11561,10 +11692,12 @@
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="15">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
+      <c r="A15" s="25"/>
+      <c r="B15" s="25" t="s">
+        <v>64</v>
+      </c>
       <c r="C15" s="7"/>
-      <c r="D15" s="30"/>
+      <c r="D15" s="34"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="4"/>
@@ -11572,109 +11705,99 @@
       <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:9" ht="15">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
+      <c r="A16" s="25"/>
+      <c r="B16" s="25" t="s">
+        <v>80</v>
+      </c>
       <c r="C16" s="7"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
       <c r="G16" s="4"/>
-      <c r="H16" s="21"/>
+      <c r="H16" s="4"/>
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" ht="15">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
+      <c r="A17" s="21"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
       <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9" ht="15">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
+      <c r="A18" s="21"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="29"/>
     </row>
     <row r="19" spans="1:9" ht="15">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="29"/>
     </row>
     <row r="20" spans="1:9" ht="15">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="29"/>
     </row>
     <row r="21" spans="1:9" ht="15">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="29"/>
     </row>
     <row r="22" spans="1:9" ht="15">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="29"/>
     </row>
     <row r="23" spans="1:9" ht="15">
-      <c r="A23" s="15"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="21"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="29"/>
     </row>
     <row r="24" spans="1:9" ht="15">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="29"/>
     </row>
     <row r="25" spans="1:9" ht="15">
       <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
+      <c r="B25" s="15"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="30"/>
+      <c r="D25" s="34"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="4"/>
@@ -11683,11 +11806,11 @@
     </row>
     <row r="26" spans="1:9" ht="15">
       <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
+      <c r="B26" s="15"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
@@ -11696,7 +11819,7 @@
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="7"/>
-      <c r="D27" s="30"/>
+      <c r="D27" s="34"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
@@ -11707,7 +11830,7 @@
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="30"/>
+      <c r="D28" s="34"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -11718,7 +11841,7 @@
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="30"/>
+      <c r="D29" s="34"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -11727,31 +11850,31 @@
     </row>
     <row r="30" spans="1:9" ht="15">
       <c r="A30" s="4"/>
-      <c r="B30" s="7"/>
+      <c r="B30" s="4"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
       <c r="G30" s="4"/>
-      <c r="H30" s="7"/>
+      <c r="H30" s="4"/>
       <c r="I30" s="4"/>
     </row>
     <row r="31" spans="1:9" ht="15">
       <c r="A31" s="4"/>
-      <c r="B31" s="7"/>
+      <c r="B31" s="4"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="30"/>
+      <c r="D31" s="34"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
+      <c r="H31" s="7"/>
       <c r="I31" s="4"/>
     </row>
     <row r="32" spans="1:9" ht="15">
       <c r="A32" s="4"/>
-      <c r="B32" s="7"/>
+      <c r="B32" s="4"/>
       <c r="C32" s="7"/>
-      <c r="D32" s="30"/>
+      <c r="D32" s="34"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="4"/>
@@ -11760,31 +11883,31 @@
     </row>
     <row r="33" spans="1:9" ht="15">
       <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
     </row>
     <row r="34" spans="1:9" ht="15">
       <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
+      <c r="B34" s="7"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
     </row>
     <row r="35" spans="1:9" ht="15">
       <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="30"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="34"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
       <c r="G35" s="4"/>
@@ -11795,7 +11918,7 @@
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="7"/>
-      <c r="D36" s="30"/>
+      <c r="D36" s="34"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="4"/>
@@ -11806,7 +11929,7 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="30"/>
+      <c r="D37" s="34"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="4"/>
@@ -11817,7 +11940,7 @@
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="7"/>
-      <c r="D38" s="30"/>
+      <c r="D38" s="34"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="4"/>
@@ -11828,7 +11951,7 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="7"/>
-      <c r="D39" s="30"/>
+      <c r="D39" s="34"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="4"/>
@@ -11839,7 +11962,7 @@
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="7"/>
-      <c r="D40" s="30"/>
+      <c r="D40" s="34"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="4"/>
@@ -11850,7 +11973,7 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="30"/>
+      <c r="D41" s="34"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="4"/>
@@ -11861,7 +11984,7 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="30"/>
+      <c r="D42" s="34"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="4"/>
@@ -11872,7 +11995,7 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="30"/>
+      <c r="D43" s="34"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="4"/>
@@ -11883,7 +12006,7 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="7"/>
-      <c r="D44" s="30"/>
+      <c r="D44" s="34"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="4"/>
@@ -11894,7 +12017,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="30"/>
+      <c r="D45" s="34"/>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
       <c r="G45" s="4"/>
@@ -11905,7 +12028,7 @@
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="7"/>
-      <c r="D46" s="30"/>
+      <c r="D46" s="34"/>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
       <c r="G46" s="4"/>
@@ -11916,7 +12039,7 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="7"/>
-      <c r="D47" s="30"/>
+      <c r="D47" s="34"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
       <c r="G47" s="4"/>
@@ -11927,7 +12050,7 @@
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="7"/>
-      <c r="D48" s="30"/>
+      <c r="D48" s="34"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
       <c r="G48" s="4"/>
@@ -11938,7 +12061,7 @@
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="7"/>
-      <c r="D49" s="30"/>
+      <c r="D49" s="34"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
       <c r="G49" s="4"/>
@@ -11949,7 +12072,7 @@
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="30"/>
+      <c r="D50" s="34"/>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
       <c r="G50" s="4"/>
@@ -11960,7 +12083,7 @@
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="7"/>
-      <c r="D51" s="30"/>
+      <c r="D51" s="34"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
       <c r="G51" s="4"/>
@@ -11971,7 +12094,7 @@
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="7"/>
-      <c r="D52" s="30"/>
+      <c r="D52" s="34"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
       <c r="G52" s="4"/>
@@ -11982,7 +12105,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="30"/>
+      <c r="D53" s="34"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="4"/>
@@ -11993,7 +12116,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="30"/>
+      <c r="D54" s="34"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
       <c r="G54" s="4"/>
@@ -12004,7 +12127,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="7"/>
-      <c r="D55" s="30"/>
+      <c r="D55" s="34"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
       <c r="G55" s="4"/>
@@ -12015,7 +12138,7 @@
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="7"/>
-      <c r="D56" s="30"/>
+      <c r="D56" s="34"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
       <c r="G56" s="4"/>
@@ -12026,7 +12149,7 @@
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="7"/>
-      <c r="D57" s="30"/>
+      <c r="D57" s="34"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
       <c r="G57" s="4"/>
@@ -12037,7 +12160,7 @@
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="7"/>
-      <c r="D58" s="6"/>
+      <c r="D58" s="34"/>
       <c r="E58" s="7"/>
       <c r="F58" s="7"/>
       <c r="G58" s="4"/>
@@ -12136,7 +12259,7 @@
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="7"/>
-      <c r="D67" s="5"/>
+      <c r="D67" s="6"/>
       <c r="E67" s="7"/>
       <c r="F67" s="7"/>
       <c r="G67" s="4"/>
@@ -12147,7 +12270,7 @@
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="7"/>
-      <c r="D68" s="6"/>
+      <c r="D68" s="5"/>
       <c r="E68" s="7"/>
       <c r="F68" s="7"/>
       <c r="G68" s="4"/>
@@ -12202,7 +12325,7 @@
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="7"/>
-      <c r="D73" s="5"/>
+      <c r="D73" s="6"/>
       <c r="E73" s="7"/>
       <c r="F73" s="7"/>
       <c r="G73" s="4"/>
@@ -12213,7 +12336,7 @@
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="7"/>
-      <c r="D74" s="6"/>
+      <c r="D74" s="5"/>
       <c r="E74" s="7"/>
       <c r="F74" s="7"/>
       <c r="G74" s="4"/>
@@ -12323,7 +12446,7 @@
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="7"/>
-      <c r="D84" s="5"/>
+      <c r="D84" s="6"/>
       <c r="E84" s="7"/>
       <c r="F84" s="7"/>
       <c r="G84" s="4"/>
@@ -12334,7 +12457,7 @@
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="7"/>
-      <c r="D85" s="6"/>
+      <c r="D85" s="5"/>
       <c r="E85" s="7"/>
       <c r="F85" s="7"/>
       <c r="G85" s="4"/>
@@ -12444,7 +12567,7 @@
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="7"/>
-      <c r="D95" s="5"/>
+      <c r="D95" s="6"/>
       <c r="E95" s="7"/>
       <c r="F95" s="7"/>
       <c r="G95" s="4"/>
@@ -12455,7 +12578,7 @@
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="7"/>
-      <c r="D96" s="6"/>
+      <c r="D96" s="5"/>
       <c r="E96" s="7"/>
       <c r="F96" s="7"/>
       <c r="G96" s="4"/>
@@ -12565,7 +12688,7 @@
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="7"/>
-      <c r="D106" s="5"/>
+      <c r="D106" s="6"/>
       <c r="E106" s="7"/>
       <c r="F106" s="7"/>
       <c r="G106" s="4"/>
@@ -12576,7 +12699,7 @@
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="7"/>
-      <c r="D107" s="6"/>
+      <c r="D107" s="5"/>
       <c r="E107" s="7"/>
       <c r="F107" s="7"/>
       <c r="G107" s="4"/>
@@ -12686,7 +12809,7 @@
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="7"/>
-      <c r="D117" s="5"/>
+      <c r="D117" s="6"/>
       <c r="E117" s="7"/>
       <c r="F117" s="7"/>
       <c r="G117" s="4"/>
@@ -12697,7 +12820,7 @@
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="7"/>
-      <c r="D118" s="6"/>
+      <c r="D118" s="5"/>
       <c r="E118" s="7"/>
       <c r="F118" s="7"/>
       <c r="G118" s="4"/>
@@ -12866,26 +12989,41 @@
       <c r="E133" s="7"/>
       <c r="F133" s="7"/>
       <c r="G133" s="4"/>
+      <c r="H133" s="4"/>
       <c r="I133" s="4"/>
     </row>
+    <row r="134" spans="1:9" ht="15">
+      <c r="A134" s="4"/>
+      <c r="B134" s="4"/>
+      <c r="C134" s="7"/>
+      <c r="D134" s="6"/>
+      <c r="E134" s="7"/>
+      <c r="F134" s="7"/>
+      <c r="G134" s="4"/>
+      <c r="I134" s="4"/>
+    </row>
+    <row r="135" spans="1:9" ht="15">
+      <c r="B135" s="4"/>
+    </row>
+    <row r="136" spans="1:9" ht="15">
+      <c r="B136" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="14">
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="D3:D58"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I18:I24"/>
+    <mergeCell ref="E18:E24"/>
+    <mergeCell ref="F18:F24"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="D3:D57"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I17:I23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H16:H22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12907,27 +13045,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="35" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="40" t="s">
+      <c r="G1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="41"/>
-      <c r="I1" s="24" t="s">
+      <c r="H1" s="46"/>
+      <c r="I1" s="27" t="s">
         <v>0</v>
       </c>
     </row>
@@ -12938,136 +13076,127 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="24"/>
+      <c r="I2" s="27"/>
     </row>
     <row r="3" spans="1:9" ht="15">
       <c r="A3" s="19" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="23"/>
-      <c r="F3" s="31"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="36"/>
       <c r="G3" s="19" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="I3" s="21"/>
+        <v>88</v>
+      </c>
+      <c r="I3" s="29"/>
     </row>
     <row r="4" spans="1:9" ht="14.25" customHeight="1">
       <c r="A4" s="19"/>
       <c r="B4" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="31"/>
+        <v>49</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="34"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="36"/>
       <c r="G4" s="16"/>
       <c r="H4" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="I4" s="21"/>
+        <v>90</v>
+      </c>
+      <c r="I4" s="29"/>
     </row>
     <row r="5" spans="1:9" ht="15">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19" t="s">
-        <v>31</v>
-      </c>
       <c r="C5" s="18"/>
-      <c r="D5" s="30"/>
+      <c r="D5" s="34"/>
       <c r="E5" s="18"/>
       <c r="F5" s="18"/>
       <c r="G5" s="16"/>
       <c r="H5" s="16" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="I5" s="16"/>
     </row>
     <row r="6" spans="1:9" ht="15">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="30"/>
+      <c r="C6" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" s="34"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
       <c r="G6" s="16"/>
       <c r="H6" s="16" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="I6" s="16"/>
     </row>
-    <row r="7" spans="1:9" ht="15">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="30"/>
+    <row r="7" spans="1:9" ht="60">
+      <c r="C7" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D7" s="34"/>
       <c r="E7" s="18"/>
       <c r="F7" s="18"/>
       <c r="G7" s="16"/>
       <c r="H7" s="16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="I7" s="16"/>
     </row>
     <row r="8" spans="1:9" ht="15">
-      <c r="A8" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="30"/>
+      <c r="C8" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="34"/>
       <c r="E8" s="18"/>
       <c r="F8" s="18"/>
       <c r="G8" s="16"/>
-      <c r="H8" s="16" t="s">
-        <v>61</v>
+      <c r="H8" s="21" t="s">
+        <v>55</v>
       </c>
       <c r="I8" s="16"/>
     </row>
     <row r="9" spans="1:9" ht="15">
       <c r="A9" s="19"/>
       <c r="B9" s="19" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="C9" s="16"/>
-      <c r="D9" s="30"/>
+      <c r="D9" s="34"/>
       <c r="E9" s="18"/>
       <c r="F9" s="18"/>
       <c r="G9" s="16"/>
-      <c r="H9" s="16" t="s">
-        <v>98</v>
-      </c>
       <c r="I9" s="16"/>
     </row>
     <row r="10" spans="1:9" ht="15">
       <c r="A10" s="19"/>
       <c r="B10" s="19" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C10" s="18"/>
-      <c r="D10" s="30"/>
+      <c r="D10" s="34"/>
       <c r="E10" s="18"/>
       <c r="F10" s="18"/>
       <c r="G10" s="16"/>
@@ -13076,11 +13205,8 @@
     </row>
     <row r="11" spans="1:9" ht="15">
       <c r="A11" s="19"/>
-      <c r="B11" s="19" t="s">
-        <v>38</v>
-      </c>
       <c r="C11" s="16"/>
-      <c r="D11" s="30"/>
+      <c r="D11" s="34"/>
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
       <c r="G11" s="16"/>
@@ -13088,10 +13214,14 @@
       <c r="I11" s="16"/>
     </row>
     <row r="12" spans="1:9" ht="15">
-      <c r="A12" s="42"/>
-      <c r="B12" s="42"/>
+      <c r="A12" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>41</v>
+      </c>
       <c r="C12" s="18"/>
-      <c r="D12" s="30"/>
+      <c r="D12" s="34"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="16"/>
@@ -13099,14 +13229,12 @@
       <c r="I12" s="16"/>
     </row>
     <row r="13" spans="1:9" ht="15">
-      <c r="A13" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>56</v>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19" t="s">
+        <v>49</v>
       </c>
       <c r="C13" s="18"/>
-      <c r="D13" s="30"/>
+      <c r="D13" s="34"/>
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
       <c r="G13" s="16"/>
@@ -13114,12 +13242,12 @@
       <c r="I13" s="16"/>
     </row>
     <row r="14" spans="1:9" ht="15">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16" t="s">
-        <v>57</v>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19" t="s">
+        <v>64</v>
       </c>
       <c r="C14" s="18"/>
-      <c r="D14" s="30"/>
+      <c r="D14" s="34"/>
       <c r="E14" s="18"/>
       <c r="F14" s="18"/>
       <c r="G14" s="16"/>
@@ -13127,9 +13255,12 @@
       <c r="I14" s="16"/>
     </row>
     <row r="15" spans="1:9" ht="15">
-      <c r="A15" s="16"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19" t="s">
+        <v>80</v>
+      </c>
       <c r="C15" s="18"/>
-      <c r="D15" s="30"/>
+      <c r="D15" s="34"/>
       <c r="E15" s="18"/>
       <c r="F15" s="18"/>
       <c r="G15" s="16"/>
@@ -13137,14 +13268,10 @@
       <c r="I15" s="16"/>
     </row>
     <row r="16" spans="1:9" ht="15">
-      <c r="A16" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>58</v>
-      </c>
+      <c r="A16" s="26"/>
+      <c r="B16" s="26"/>
       <c r="C16" s="18"/>
-      <c r="D16" s="30"/>
+      <c r="D16" s="34"/>
       <c r="E16" s="16"/>
       <c r="F16" s="16"/>
       <c r="G16" s="16"/>
@@ -13152,85 +13279,94 @@
       <c r="I16" s="16"/>
     </row>
     <row r="17" spans="1:9" ht="15">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16" t="s">
-        <v>59</v>
+      <c r="A17" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>50</v>
       </c>
       <c r="C17" s="8"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
     </row>
     <row r="18" spans="1:9" ht="15">
+      <c r="A18" s="16"/>
+      <c r="B18" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="C18" s="8"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
     </row>
     <row r="19" spans="1:9" ht="15">
+      <c r="A19" s="16"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
     </row>
     <row r="20" spans="1:9" ht="15">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
+      <c r="A20" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>52</v>
+      </c>
       <c r="C20" s="8"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
     </row>
     <row r="21" spans="1:9" ht="15">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
+      <c r="A21" s="16"/>
+      <c r="B21" s="16" t="s">
+        <v>53</v>
+      </c>
       <c r="C21" s="8"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
     </row>
     <row r="22" spans="1:9" ht="15">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
     </row>
     <row r="23" spans="1:9" ht="15">
-      <c r="A23" s="15"/>
-      <c r="B23" s="15"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
     </row>
     <row r="24" spans="1:9" ht="15">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
       <c r="C24" s="18"/>
-      <c r="D24" s="30"/>
+      <c r="D24" s="34"/>
       <c r="E24" s="18"/>
       <c r="F24" s="18"/>
       <c r="G24" s="16"/>
@@ -13241,7 +13377,7 @@
       <c r="A25" s="16"/>
       <c r="B25" s="16"/>
       <c r="C25" s="18"/>
-      <c r="D25" s="30"/>
+      <c r="D25" s="34"/>
       <c r="E25" s="18"/>
       <c r="F25" s="18"/>
       <c r="G25" s="16"/>
@@ -13252,7 +13388,7 @@
       <c r="A26" s="16"/>
       <c r="B26" s="16"/>
       <c r="C26" s="18"/>
-      <c r="D26" s="30"/>
+      <c r="D26" s="34"/>
       <c r="E26" s="16"/>
       <c r="F26" s="16"/>
       <c r="G26" s="16"/>
@@ -13263,7 +13399,7 @@
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
       <c r="C27" s="18"/>
-      <c r="D27" s="30"/>
+      <c r="D27" s="34"/>
       <c r="E27" s="16"/>
       <c r="F27" s="16"/>
       <c r="G27" s="16"/>
@@ -13274,7 +13410,7 @@
       <c r="A28" s="16"/>
       <c r="B28" s="16"/>
       <c r="C28" s="18"/>
-      <c r="D28" s="30"/>
+      <c r="D28" s="34"/>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
       <c r="G28" s="16"/>
@@ -13285,7 +13421,7 @@
       <c r="A29" s="16"/>
       <c r="B29" s="16"/>
       <c r="C29" s="18"/>
-      <c r="D29" s="30"/>
+      <c r="D29" s="34"/>
       <c r="E29" s="16"/>
       <c r="F29" s="16"/>
       <c r="G29" s="16"/>
@@ -13296,7 +13432,7 @@
       <c r="A30" s="16"/>
       <c r="B30" s="18"/>
       <c r="C30" s="18"/>
-      <c r="D30" s="30"/>
+      <c r="D30" s="34"/>
       <c r="E30" s="18"/>
       <c r="F30" s="18"/>
       <c r="G30" s="16"/>
@@ -13307,7 +13443,7 @@
       <c r="A31" s="16"/>
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
-      <c r="D31" s="30"/>
+      <c r="D31" s="34"/>
       <c r="E31" s="18"/>
       <c r="F31" s="18"/>
       <c r="G31" s="16"/>
@@ -13318,7 +13454,7 @@
       <c r="A32" s="16"/>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
-      <c r="D32" s="30"/>
+      <c r="D32" s="34"/>
       <c r="E32" s="18"/>
       <c r="F32" s="18"/>
       <c r="G32" s="16"/>
@@ -13329,7 +13465,7 @@
       <c r="A33" s="16"/>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
-      <c r="D33" s="30"/>
+      <c r="D33" s="34"/>
       <c r="E33" s="16"/>
       <c r="F33" s="16"/>
       <c r="G33" s="16"/>
@@ -13340,7 +13476,7 @@
       <c r="A34" s="16"/>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
-      <c r="D34" s="30"/>
+      <c r="D34" s="34"/>
       <c r="E34" s="18"/>
       <c r="F34" s="18"/>
       <c r="G34" s="16"/>
@@ -13351,7 +13487,7 @@
       <c r="A35" s="16"/>
       <c r="B35" s="16"/>
       <c r="C35" s="18"/>
-      <c r="D35" s="30"/>
+      <c r="D35" s="34"/>
       <c r="E35" s="18"/>
       <c r="F35" s="18"/>
       <c r="G35" s="16"/>
@@ -13362,7 +13498,7 @@
       <c r="A36" s="16"/>
       <c r="B36" s="16"/>
       <c r="C36" s="18"/>
-      <c r="D36" s="30"/>
+      <c r="D36" s="34"/>
       <c r="E36" s="18"/>
       <c r="F36" s="18"/>
       <c r="G36" s="16"/>
@@ -13373,7 +13509,7 @@
       <c r="A37" s="16"/>
       <c r="B37" s="16"/>
       <c r="C37" s="18"/>
-      <c r="D37" s="30"/>
+      <c r="D37" s="34"/>
       <c r="E37" s="18"/>
       <c r="F37" s="18"/>
       <c r="G37" s="16"/>
@@ -13384,7 +13520,7 @@
       <c r="A38" s="16"/>
       <c r="B38" s="16"/>
       <c r="C38" s="18"/>
-      <c r="D38" s="30"/>
+      <c r="D38" s="34"/>
       <c r="E38" s="18"/>
       <c r="F38" s="18"/>
       <c r="G38" s="16"/>
@@ -13395,7 +13531,7 @@
       <c r="A39" s="16"/>
       <c r="B39" s="16"/>
       <c r="C39" s="18"/>
-      <c r="D39" s="30"/>
+      <c r="D39" s="34"/>
       <c r="E39" s="18"/>
       <c r="F39" s="18"/>
       <c r="G39" s="16"/>
@@ -13406,7 +13542,7 @@
       <c r="A40" s="16"/>
       <c r="B40" s="16"/>
       <c r="C40" s="18"/>
-      <c r="D40" s="30"/>
+      <c r="D40" s="34"/>
       <c r="E40" s="18"/>
       <c r="F40" s="18"/>
       <c r="G40" s="16"/>
@@ -13417,7 +13553,7 @@
       <c r="A41" s="16"/>
       <c r="B41" s="16"/>
       <c r="C41" s="18"/>
-      <c r="D41" s="30"/>
+      <c r="D41" s="34"/>
       <c r="E41" s="18"/>
       <c r="F41" s="18"/>
       <c r="G41" s="16"/>
@@ -13428,7 +13564,7 @@
       <c r="A42" s="16"/>
       <c r="B42" s="16"/>
       <c r="C42" s="18"/>
-      <c r="D42" s="30"/>
+      <c r="D42" s="34"/>
       <c r="E42" s="18"/>
       <c r="F42" s="18"/>
       <c r="G42" s="16"/>
@@ -13439,7 +13575,7 @@
       <c r="A43" s="16"/>
       <c r="B43" s="16"/>
       <c r="C43" s="18"/>
-      <c r="D43" s="30"/>
+      <c r="D43" s="34"/>
       <c r="E43" s="18"/>
       <c r="F43" s="18"/>
       <c r="G43" s="16"/>
@@ -13450,7 +13586,7 @@
       <c r="A44" s="16"/>
       <c r="B44" s="16"/>
       <c r="C44" s="18"/>
-      <c r="D44" s="30"/>
+      <c r="D44" s="34"/>
       <c r="E44" s="18"/>
       <c r="F44" s="18"/>
       <c r="G44" s="16"/>
@@ -13461,7 +13597,7 @@
       <c r="A45" s="16"/>
       <c r="B45" s="16"/>
       <c r="C45" s="18"/>
-      <c r="D45" s="30"/>
+      <c r="D45" s="34"/>
       <c r="E45" s="18"/>
       <c r="F45" s="18"/>
       <c r="G45" s="16"/>
@@ -13472,7 +13608,7 @@
       <c r="A46" s="16"/>
       <c r="B46" s="16"/>
       <c r="C46" s="18"/>
-      <c r="D46" s="30"/>
+      <c r="D46" s="34"/>
       <c r="E46" s="18"/>
       <c r="F46" s="18"/>
       <c r="G46" s="16"/>
@@ -13483,7 +13619,7 @@
       <c r="A47" s="16"/>
       <c r="B47" s="16"/>
       <c r="C47" s="18"/>
-      <c r="D47" s="30"/>
+      <c r="D47" s="34"/>
       <c r="E47" s="18"/>
       <c r="F47" s="18"/>
       <c r="G47" s="16"/>
@@ -13494,7 +13630,7 @@
       <c r="A48" s="16"/>
       <c r="B48" s="16"/>
       <c r="C48" s="18"/>
-      <c r="D48" s="30"/>
+      <c r="D48" s="34"/>
       <c r="E48" s="18"/>
       <c r="F48" s="18"/>
       <c r="G48" s="16"/>
@@ -13505,7 +13641,7 @@
       <c r="A49" s="16"/>
       <c r="B49" s="16"/>
       <c r="C49" s="18"/>
-      <c r="D49" s="30"/>
+      <c r="D49" s="34"/>
       <c r="E49" s="18"/>
       <c r="F49" s="18"/>
       <c r="G49" s="16"/>
@@ -13516,7 +13652,7 @@
       <c r="A50" s="16"/>
       <c r="B50" s="16"/>
       <c r="C50" s="18"/>
-      <c r="D50" s="30"/>
+      <c r="D50" s="34"/>
       <c r="E50" s="18"/>
       <c r="F50" s="18"/>
       <c r="G50" s="16"/>
@@ -13527,7 +13663,7 @@
       <c r="A51" s="16"/>
       <c r="B51" s="16"/>
       <c r="C51" s="18"/>
-      <c r="D51" s="30"/>
+      <c r="D51" s="34"/>
       <c r="E51" s="18"/>
       <c r="F51" s="18"/>
       <c r="G51" s="16"/>
@@ -13538,7 +13674,7 @@
       <c r="A52" s="16"/>
       <c r="B52" s="16"/>
       <c r="C52" s="18"/>
-      <c r="D52" s="30"/>
+      <c r="D52" s="34"/>
       <c r="E52" s="18"/>
       <c r="F52" s="18"/>
       <c r="G52" s="16"/>
@@ -13549,7 +13685,7 @@
       <c r="A53" s="16"/>
       <c r="B53" s="16"/>
       <c r="C53" s="18"/>
-      <c r="D53" s="30"/>
+      <c r="D53" s="34"/>
       <c r="E53" s="18"/>
       <c r="F53" s="18"/>
       <c r="G53" s="16"/>
@@ -13560,7 +13696,7 @@
       <c r="A54" s="16"/>
       <c r="B54" s="16"/>
       <c r="C54" s="18"/>
-      <c r="D54" s="30"/>
+      <c r="D54" s="34"/>
       <c r="E54" s="18"/>
       <c r="F54" s="18"/>
       <c r="G54" s="16"/>
@@ -13571,7 +13707,7 @@
       <c r="A55" s="16"/>
       <c r="B55" s="16"/>
       <c r="C55" s="18"/>
-      <c r="D55" s="30"/>
+      <c r="D55" s="34"/>
       <c r="E55" s="18"/>
       <c r="F55" s="18"/>
       <c r="G55" s="16"/>
@@ -13582,7 +13718,7 @@
       <c r="A56" s="16"/>
       <c r="B56" s="16"/>
       <c r="C56" s="18"/>
-      <c r="D56" s="30"/>
+      <c r="D56" s="34"/>
       <c r="E56" s="18"/>
       <c r="F56" s="18"/>
       <c r="G56" s="16"/>
@@ -13593,7 +13729,7 @@
       <c r="A57" s="16"/>
       <c r="B57" s="16"/>
       <c r="C57" s="18"/>
-      <c r="D57" s="30"/>
+      <c r="D57" s="34"/>
       <c r="E57" s="18"/>
       <c r="F57" s="18"/>
       <c r="G57" s="16"/>
@@ -14438,6 +14574,11 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="D3:D57"/>
     <mergeCell ref="E3:E4"/>
@@ -14448,11 +14589,6 @@
     <mergeCell ref="G17:G23"/>
     <mergeCell ref="H17:H23"/>
     <mergeCell ref="I17:I23"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/Mapping Template BrotZeit.xlsx
+++ b/Mapping Template BrotZeit.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alfa\Documents\Data Engineer\Projekt\BackZeit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C12A11-F1F9-4F20-B7FB-9ADFF3AD0B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628A7AF5-BA8B-4BEB-94BE-93C6F47F5A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{1083ED64-F082-44F9-9F2A-19C2CA2699CD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{1083ED64-F082-44F9-9F2A-19C2CA2699CD}"/>
   </bookViews>
   <sheets>
     <sheet name="D_Filiale" sheetId="9" r:id="rId1"/>
     <sheet name="D_Verkaufsvorgang" sheetId="8" r:id="rId2"/>
     <sheet name="D_Verkäufer" sheetId="7" r:id="rId3"/>
-    <sheet name="D_Tag" sheetId="6" r:id="rId4"/>
-    <sheet name="D_Stunde" sheetId="5" r:id="rId5"/>
+    <sheet name="D_Datum" sheetId="6" r:id="rId4"/>
+    <sheet name="D_Zeit" sheetId="5" r:id="rId5"/>
     <sheet name="D_Produkt" sheetId="1" r:id="rId6"/>
     <sheet name="F_Verkäufe" sheetId="4" r:id="rId7"/>
     <sheet name="F_Verkäuferumsatz" sheetId="10" r:id="rId8"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="138">
   <si>
     <t>Notes</t>
   </si>
@@ -352,9 +352,6 @@
     <t>Falls sich der Filialname ändert wird hier der alte Wert gespeichert, um die Daten vor und nach der Änderung gut vergleichen zu können</t>
   </si>
   <si>
-    <t>CONCAT([FilialID], [Zeitpunkt])</t>
-  </si>
-  <si>
     <t>b' -&gt; Barzahlung, 'k' -&gt; Kartenzahlung</t>
   </si>
   <si>
@@ -424,19 +421,40 @@
     <t>LETZTEREINTRAG[AnzahlVerkäufe] + 1</t>
   </si>
   <si>
-    <t>LETZTEREINTRAG[Gesamtumsatz] + wirdverkauft[FilialID,Zeitpunkt].[Menge] * wirdverkauft[ProduktID].[Bruttopreis]</t>
-  </si>
-  <si>
     <t>[Gesamtumsatz] / [AnzahlVerkäufe]</t>
   </si>
   <si>
     <t>[ProduktID] FK</t>
   </si>
   <si>
-    <t>wirdverkauft[FilialID,Zeitpunkt].[Menge] * D_Produkt[ProduktID].[Bruttopreis]</t>
+    <t>wirdverkauft[FilialID,Zeitpunkt].[Menge] * D_Produkt[ProduktID].[Gewinnmarge]</t>
   </si>
   <si>
-    <t>wirdverkauft[FilialID,Zeitpunkt].[Menge] * D_Produkt[ProduktID].[Gewinnmarge]</t>
+    <t>[Wochentag]</t>
+  </si>
+  <si>
+    <t>[MonatLang]</t>
+  </si>
+  <si>
+    <t>[MonatKurz]</t>
+  </si>
+  <si>
+    <t>[Zeitpunk]</t>
+  </si>
+  <si>
+    <t>Identity(1,1)</t>
+  </si>
+  <si>
+    <t>LETZTEREINTRAG[Gesamtumsatz] + [VerkaufsvorgangID].[Umsatz]</t>
+  </si>
+  <si>
+    <t>wirdverkauft[FilialID,Zeitpunkt, ProduktID].[Menge] * D_Produkt[ProduktID].[Bruttopreis]</t>
+  </si>
+  <si>
+    <t>Neue Identity(1,1)</t>
+  </si>
+  <si>
+    <t>SUM(Produkte) (wirdverkauft[FilialID,Zeitpunkt, ProduktID].[Menge] * Produkt[ProduktID].[Bruttopreis])</t>
   </si>
 </sst>
 </file>
@@ -719,7 +737,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -771,11 +789,44 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -784,9 +835,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -819,63 +867,35 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1227,30 +1247,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="44" t="s">
+      <c r="F1" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="45" t="s">
+      <c r="G1" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="46"/>
+      <c r="H1" s="62"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="27" t="s">
+      <c r="J1" s="45" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1261,10 +1281,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1272,51 +1292,51 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="27"/>
+      <c r="J2" s="45"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="36" t="s">
+      <c r="F3" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="37" t="s">
+      <c r="G3" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="37" t="s">
+      <c r="H3" s="53" t="s">
         <v>41</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="29"/>
+      <c r="J3" s="42"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="29"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
+      <c r="A4" s="42"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
       <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="29"/>
+      <c r="J4" s="42"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
@@ -1326,7 +1346,7 @@
       <c r="C5" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="34"/>
+      <c r="D5" s="51"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
@@ -1346,7 +1366,7 @@
       <c r="C6" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D6" s="34"/>
+      <c r="D6" s="51"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
@@ -1360,15 +1380,15 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="34"/>
+      <c r="D7" s="51"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
       <c r="H7" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I7" s="10"/>
-      <c r="J7" s="48" t="s">
+      <c r="J7" s="41" t="s">
         <v>102</v>
       </c>
     </row>
@@ -1380,7 +1400,7 @@
         <v>46</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="34"/>
+      <c r="D8" s="51"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
@@ -1388,13 +1408,13 @@
       <c r="I8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="48"/>
+      <c r="J8" s="41"/>
     </row>
     <row r="9" spans="1:10" ht="15">
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="34"/>
+      <c r="D9" s="51"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -1402,13 +1422,13 @@
       <c r="I9" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="48"/>
+      <c r="J9" s="41"/>
     </row>
     <row r="10" spans="1:10" ht="15">
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="34"/>
+      <c r="D10" s="51"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -1416,13 +1436,13 @@
       <c r="I10" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="48"/>
+      <c r="J10" s="41"/>
     </row>
     <row r="11" spans="1:10" ht="15">
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="34"/>
+      <c r="D11" s="51"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -1430,25 +1450,25 @@
       <c r="I11" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="48"/>
+      <c r="J11" s="41"/>
     </row>
     <row r="12" spans="1:10" ht="15">
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="34"/>
+      <c r="D12" s="51"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
-      <c r="J12" s="48"/>
+      <c r="J12" s="41"/>
     </row>
     <row r="13" spans="1:10" ht="15">
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="34"/>
+      <c r="D13" s="51"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -1462,7 +1482,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="34"/>
+      <c r="D14" s="51"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -1474,7 +1494,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="34"/>
+      <c r="D15" s="51"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
@@ -1488,7 +1508,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="34"/>
+      <c r="D16" s="51"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -1497,94 +1517,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="47"/>
-      <c r="B17" s="47"/>
+      <c r="A17" s="43"/>
+      <c r="B17" s="43"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="29"/>
+      <c r="J17" s="42"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="47"/>
-      <c r="B18" s="47"/>
+      <c r="A18" s="43"/>
+      <c r="B18" s="43"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="29"/>
+      <c r="J18" s="42"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="47"/>
-      <c r="B19" s="47"/>
+      <c r="A19" s="43"/>
+      <c r="B19" s="43"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="29"/>
+      <c r="J19" s="42"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="47"/>
-      <c r="B20" s="47"/>
+      <c r="A20" s="43"/>
+      <c r="B20" s="43"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="29"/>
+      <c r="J20" s="42"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
+      <c r="A21" s="43"/>
+      <c r="B21" s="43"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="29"/>
+      <c r="J21" s="42"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="47"/>
-      <c r="B22" s="47"/>
+      <c r="A22" s="43"/>
+      <c r="B22" s="43"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="29"/>
+      <c r="J22" s="42"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="47"/>
-      <c r="B23" s="47"/>
+      <c r="A23" s="43"/>
+      <c r="B23" s="43"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="29"/>
+      <c r="J23" s="42"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="34"/>
+      <c r="D24" s="51"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -1596,7 +1616,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="34"/>
+      <c r="D25" s="51"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -1608,7 +1628,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="34"/>
+      <c r="D26" s="51"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -1620,7 +1640,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="34"/>
+      <c r="D27" s="51"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -1632,7 +1652,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="34"/>
+      <c r="D28" s="51"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -1644,7 +1664,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="34"/>
+      <c r="D29" s="51"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -1656,7 +1676,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="34"/>
+      <c r="D30" s="51"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -1668,7 +1688,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="34"/>
+      <c r="D31" s="51"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -1680,7 +1700,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="34"/>
+      <c r="D32" s="51"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -1692,7 +1712,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="34"/>
+      <c r="D33" s="51"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -1704,7 +1724,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="34"/>
+      <c r="D34" s="51"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -1716,7 +1736,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="34"/>
+      <c r="D35" s="51"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -1728,7 +1748,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="34"/>
+      <c r="D36" s="51"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -1740,7 +1760,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="34"/>
+      <c r="D37" s="51"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -1752,7 +1772,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="34"/>
+      <c r="D38" s="51"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -1764,7 +1784,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="34"/>
+      <c r="D39" s="51"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -1776,7 +1796,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="34"/>
+      <c r="D40" s="51"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -1788,7 +1808,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="34"/>
+      <c r="D41" s="51"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -1800,7 +1820,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="34"/>
+      <c r="D42" s="51"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -1812,7 +1832,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="34"/>
+      <c r="D43" s="51"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -1824,7 +1844,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="34"/>
+      <c r="D44" s="51"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -1836,7 +1856,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="34"/>
+      <c r="D45" s="51"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -1848,7 +1868,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="34"/>
+      <c r="D46" s="51"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -1860,7 +1880,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="34"/>
+      <c r="D47" s="51"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -1872,7 +1892,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="34"/>
+      <c r="D48" s="51"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -1884,7 +1904,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="34"/>
+      <c r="D49" s="51"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -1896,7 +1916,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="34"/>
+      <c r="D50" s="51"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -1908,7 +1928,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="34"/>
+      <c r="D51" s="51"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -1920,7 +1940,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="34"/>
+      <c r="D52" s="51"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -1932,7 +1952,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="34"/>
+      <c r="D53" s="51"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -1944,7 +1964,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="34"/>
+      <c r="D54" s="51"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -1956,7 +1976,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="34"/>
+      <c r="D55" s="51"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -1968,7 +1988,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="34"/>
+      <c r="D56" s="51"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -1980,7 +2000,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="34"/>
+      <c r="D57" s="51"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -2902,14 +2922,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="J7:J12"/>
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -2926,6 +2938,14 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J7:J12"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2949,30 +2969,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="44" t="s">
+      <c r="F1" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="45" t="s">
+      <c r="G1" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="46"/>
+      <c r="H1" s="62"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="27" t="s">
+      <c r="J1" s="45" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2983,10 +3003,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2994,119 +3014,132 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="27"/>
+      <c r="J2" s="45"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="50" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="D3" s="50" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="69" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="68" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="33" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" s="51"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" s="10"/>
+      <c r="J4" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="57" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" s="58" t="s">
-        <v>47</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="29"/>
-    </row>
-    <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="56"/>
-      <c r="B4" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="29"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="34"/>
+      <c r="D5" s="51"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="56"/>
+      <c r="G5" s="10"/>
       <c r="H5" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I5" s="10"/>
-      <c r="J5" s="60" t="s">
-        <v>104</v>
-      </c>
+      <c r="J5" s="10"/>
     </row>
     <row r="6" spans="1:10" ht="15">
       <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="34"/>
+      <c r="B6" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" s="51"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
+      <c r="H6" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="J6" s="10"/>
     </row>
-    <row r="7" spans="1:10" ht="15">
+    <row r="7" spans="1:10" ht="67.5" customHeight="1">
       <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="34"/>
+      <c r="C7" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="D7" s="51"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
+      <c r="H7" s="72" t="s">
+        <v>93</v>
+      </c>
       <c r="I7" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J7" s="10"/>
     </row>
-    <row r="8" spans="1:10" ht="15">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" s="10"/>
+    <row r="8" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A8" s="27"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="72"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
     </row>
     <row r="9" spans="1:10" ht="15">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
+      <c r="A9" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>41</v>
+      </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="34"/>
+      <c r="D9" s="51"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -3117,10 +3150,12 @@
       <c r="J9" s="10"/>
     </row>
     <row r="10" spans="1:10" ht="15">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="30" t="s">
+        <v>49</v>
+      </c>
       <c r="C10" s="10"/>
-      <c r="D10" s="34"/>
+      <c r="D10" s="51"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -3131,10 +3166,12 @@
       <c r="J10" s="10"/>
     </row>
     <row r="11" spans="1:10" ht="15">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="30" t="s">
+        <v>64</v>
+      </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="34"/>
+      <c r="D11" s="51"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -3143,10 +3180,12 @@
       <c r="J11" s="10"/>
     </row>
     <row r="12" spans="1:10" ht="15">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
+      <c r="A12" s="30"/>
+      <c r="B12" s="30" t="s">
+        <v>80</v>
+      </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="34"/>
+      <c r="D12" s="51"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -3160,7 +3199,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="34"/>
+      <c r="D13" s="51"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -3169,10 +3208,14 @@
       <c r="J13" s="10"/>
     </row>
     <row r="14" spans="1:10" ht="15">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
+        <v>64</v>
+      </c>
       <c r="C14" s="11"/>
-      <c r="D14" s="34"/>
+      <c r="D14" s="51"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -3183,10 +3226,11 @@
       <c r="J14" s="10"/>
     </row>
     <row r="15" spans="1:10" ht="15">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
+      <c r="B15" t="s">
+        <v>65</v>
+      </c>
       <c r="C15" s="11"/>
-      <c r="D15" s="34"/>
+      <c r="D15" s="51"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
@@ -3195,94 +3239,96 @@
       <c r="J15" s="10"/>
     </row>
     <row r="16" spans="1:10" ht="15">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
+      <c r="B16" t="s">
+        <v>67</v>
+      </c>
       <c r="C16" s="8"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
       <c r="I16" s="10"/>
-      <c r="J16" s="29"/>
+      <c r="J16" s="42"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
+      <c r="B17" t="s">
+        <v>68</v>
+      </c>
       <c r="C17" s="8"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="29"/>
+      <c r="J17" s="42"/>
     </row>
     <row r="18" spans="1:10" ht="15">
       <c r="A18" s="15"/>
       <c r="B18" s="15"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="29"/>
+      <c r="J18" s="42"/>
     </row>
     <row r="19" spans="1:10" ht="15">
       <c r="A19" s="15"/>
       <c r="B19" s="15"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="29"/>
+      <c r="J19" s="42"/>
     </row>
     <row r="20" spans="1:10" ht="15">
       <c r="A20" s="15"/>
       <c r="B20" s="15"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="29"/>
+      <c r="J20" s="42"/>
     </row>
     <row r="21" spans="1:10" ht="15">
       <c r="A21" s="15"/>
       <c r="B21" s="15"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="29"/>
+      <c r="J21" s="42"/>
     </row>
     <row r="22" spans="1:10" ht="15">
       <c r="A22" s="15"/>
       <c r="B22" s="15"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="29"/>
+      <c r="J22" s="42"/>
     </row>
     <row r="23" spans="1:10" ht="15">
       <c r="A23" s="10"/>
       <c r="B23" s="10"/>
       <c r="C23" s="11"/>
-      <c r="D23" s="34"/>
+      <c r="D23" s="51"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="10"/>
@@ -3294,7 +3340,7 @@
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="34"/>
+      <c r="D24" s="51"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -3306,7 +3352,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="34"/>
+      <c r="D25" s="51"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
@@ -3318,7 +3364,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="34"/>
+      <c r="D26" s="51"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -3330,7 +3376,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="34"/>
+      <c r="D27" s="51"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -3342,7 +3388,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="34"/>
+      <c r="D28" s="51"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -3354,7 +3400,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="34"/>
+      <c r="D29" s="51"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
       <c r="G29" s="10"/>
@@ -3366,7 +3412,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="34"/>
+      <c r="D30" s="51"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -3378,7 +3424,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="34"/>
+      <c r="D31" s="51"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -3390,7 +3436,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
-      <c r="D32" s="34"/>
+      <c r="D32" s="51"/>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
@@ -3402,7 +3448,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="34"/>
+      <c r="D33" s="51"/>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
       <c r="G33" s="10"/>
@@ -3414,7 +3460,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="11"/>
-      <c r="D34" s="34"/>
+      <c r="D34" s="51"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -3426,7 +3472,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="34"/>
+      <c r="D35" s="51"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -3438,7 +3484,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="34"/>
+      <c r="D36" s="51"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -3450,7 +3496,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="34"/>
+      <c r="D37" s="51"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -3462,7 +3508,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="34"/>
+      <c r="D38" s="51"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -3470,11 +3516,11 @@
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
     </row>
-    <row r="39" spans="1:10" ht="15">
+    <row r="39" spans="1:10">
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="34"/>
+      <c r="D39" s="51"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -3486,7 +3532,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="34"/>
+      <c r="D40" s="51"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -3498,7 +3544,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="34"/>
+      <c r="D41" s="51"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -3510,7 +3556,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="34"/>
+      <c r="D42" s="51"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -3522,7 +3568,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="34"/>
+      <c r="D43" s="51"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -3534,7 +3580,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="34"/>
+      <c r="D44" s="51"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -3546,7 +3592,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="34"/>
+      <c r="D45" s="51"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -3558,7 +3604,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="34"/>
+      <c r="D46" s="51"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -3570,7 +3616,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="34"/>
+      <c r="D47" s="51"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -3582,7 +3628,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="34"/>
+      <c r="D48" s="51"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -3594,7 +3640,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="34"/>
+      <c r="D49" s="51"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -3606,7 +3652,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="34"/>
+      <c r="D50" s="51"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -3618,7 +3664,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="34"/>
+      <c r="D51" s="51"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -3630,7 +3676,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="34"/>
+      <c r="D52" s="51"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -3642,7 +3688,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="34"/>
+      <c r="D53" s="51"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -3654,7 +3700,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="34"/>
+      <c r="D54" s="51"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -3666,7 +3712,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="34"/>
+      <c r="D55" s="51"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -3678,7 +3724,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="34"/>
+      <c r="D56" s="51"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -4599,27 +4645,20 @@
       <c r="J132" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="J16:J22"/>
-    <mergeCell ref="E16:E22"/>
-    <mergeCell ref="F16:F22"/>
-    <mergeCell ref="G16:G22"/>
-    <mergeCell ref="H16:H22"/>
+  <mergeCells count="13">
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D56"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="J3:J4"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J16:J22"/>
+    <mergeCell ref="E16:E22"/>
+    <mergeCell ref="F16:F22"/>
+    <mergeCell ref="G16:G22"/>
+    <mergeCell ref="H16:H22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4643,30 +4682,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="44" t="s">
+      <c r="F1" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="45" t="s">
+      <c r="G1" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="46"/>
+      <c r="H1" s="62"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="27" t="s">
+      <c r="J1" s="45" t="s">
         <v>0</v>
       </c>
     </row>
@@ -4677,10 +4716,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -4688,19 +4727,19 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="27"/>
+      <c r="J2" s="45"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="C3" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="50" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="22" t="s">
@@ -4709,30 +4748,30 @@
       <c r="F3" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="52" t="s">
+      <c r="G3" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="50" t="s">
+      <c r="H3" s="32" t="s">
         <v>50</v>
       </c>
       <c r="I3" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="51"/>
+      <c r="J3" s="33"/>
     </row>
     <row r="4" spans="1:10" ht="15">
       <c r="A4" s="10"/>
       <c r="B4" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="61" t="s">
-        <v>105</v>
-      </c>
-      <c r="D4" s="34"/>
+      <c r="C4" s="63" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="51"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="10"/>
-      <c r="H4" s="63" t="s">
+      <c r="H4" s="64" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="10" t="s">
@@ -4743,24 +4782,24 @@
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="10"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="34"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="51"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
-      <c r="H5" s="63"/>
+      <c r="H5" s="64"/>
       <c r="I5" s="10"/>
       <c r="J5" s="10"/>
     </row>
     <row r="6" spans="1:10" ht="15">
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="34"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="51"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="63"/>
+      <c r="H6" s="64"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
     </row>
@@ -4771,12 +4810,12 @@
       <c r="B7" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="61"/>
-      <c r="D7" s="34"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="51"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
-      <c r="H7" s="63"/>
+      <c r="H7" s="64"/>
       <c r="I7" s="10" t="s">
         <v>20</v>
       </c>
@@ -4787,12 +4826,12 @@
       <c r="B8" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="61"/>
-      <c r="D8" s="34"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="51"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
-      <c r="H8" s="63"/>
+      <c r="H8" s="64"/>
       <c r="I8" s="10" t="s">
         <v>21</v>
       </c>
@@ -4802,7 +4841,7 @@
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="11"/>
-      <c r="D9" s="34"/>
+      <c r="D9" s="51"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -4816,7 +4855,7 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
-      <c r="D10" s="34"/>
+      <c r="D10" s="51"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -4830,7 +4869,7 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="11"/>
-      <c r="D11" s="34"/>
+      <c r="D11" s="51"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -4842,7 +4881,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="34"/>
+      <c r="D12" s="51"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -4856,7 +4895,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="34"/>
+      <c r="D13" s="51"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -4868,7 +4907,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="34"/>
+      <c r="D14" s="51"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -4882,7 +4921,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="34"/>
+      <c r="D15" s="51"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
@@ -4891,94 +4930,94 @@
       <c r="J15" s="10"/>
     </row>
     <row r="16" spans="1:10" ht="15">
-      <c r="A16" s="47"/>
-      <c r="B16" s="47"/>
+      <c r="A16" s="43"/>
+      <c r="B16" s="43"/>
       <c r="C16" s="8"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
       <c r="I16" s="10"/>
-      <c r="J16" s="29"/>
+      <c r="J16" s="42"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="47"/>
-      <c r="B17" s="47"/>
+      <c r="A17" s="43"/>
+      <c r="B17" s="43"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="29"/>
+      <c r="J17" s="42"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="47"/>
-      <c r="B18" s="47"/>
+      <c r="A18" s="43"/>
+      <c r="B18" s="43"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="29"/>
+      <c r="J18" s="42"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="47"/>
-      <c r="B19" s="47"/>
+      <c r="A19" s="43"/>
+      <c r="B19" s="43"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="29"/>
+      <c r="J19" s="42"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="47"/>
-      <c r="B20" s="47"/>
+      <c r="A20" s="43"/>
+      <c r="B20" s="43"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="29"/>
+      <c r="J20" s="42"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
+      <c r="A21" s="43"/>
+      <c r="B21" s="43"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="29"/>
+      <c r="J21" s="42"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="47"/>
-      <c r="B22" s="47"/>
+      <c r="A22" s="43"/>
+      <c r="B22" s="43"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="29"/>
+      <c r="J22" s="42"/>
     </row>
     <row r="23" spans="1:10" ht="15">
       <c r="A23" s="10"/>
       <c r="B23" s="10"/>
       <c r="C23" s="11"/>
-      <c r="D23" s="34"/>
+      <c r="D23" s="51"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="10"/>
@@ -4990,7 +5029,7 @@
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="34"/>
+      <c r="D24" s="51"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -5002,7 +5041,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="34"/>
+      <c r="D25" s="51"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
@@ -5014,7 +5053,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="34"/>
+      <c r="D26" s="51"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -5026,7 +5065,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="34"/>
+      <c r="D27" s="51"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -5038,7 +5077,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="34"/>
+      <c r="D28" s="51"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -5050,7 +5089,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="34"/>
+      <c r="D29" s="51"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
       <c r="G29" s="10"/>
@@ -5062,7 +5101,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="34"/>
+      <c r="D30" s="51"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -5074,7 +5113,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="34"/>
+      <c r="D31" s="51"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -5086,7 +5125,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
-      <c r="D32" s="34"/>
+      <c r="D32" s="51"/>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
@@ -5098,7 +5137,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="34"/>
+      <c r="D33" s="51"/>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
       <c r="G33" s="10"/>
@@ -5110,7 +5149,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="11"/>
-      <c r="D34" s="34"/>
+      <c r="D34" s="51"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -5122,7 +5161,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="34"/>
+      <c r="D35" s="51"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -5134,7 +5173,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="34"/>
+      <c r="D36" s="51"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -5146,7 +5185,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="34"/>
+      <c r="D37" s="51"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -5154,11 +5193,11 @@
       <c r="I37" s="10"/>
       <c r="J37" s="10"/>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" ht="15">
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="34"/>
+      <c r="D38" s="51"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -5170,7 +5209,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="34"/>
+      <c r="D39" s="51"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -5182,7 +5221,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="34"/>
+      <c r="D40" s="51"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -5194,7 +5233,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="34"/>
+      <c r="D41" s="51"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -5206,7 +5245,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="34"/>
+      <c r="D42" s="51"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -5218,7 +5257,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="34"/>
+      <c r="D43" s="51"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -5230,7 +5269,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="34"/>
+      <c r="D44" s="51"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -5242,7 +5281,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="34"/>
+      <c r="D45" s="51"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -5254,7 +5293,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="34"/>
+      <c r="D46" s="51"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -5266,7 +5305,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="34"/>
+      <c r="D47" s="51"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -5278,7 +5317,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="34"/>
+      <c r="D48" s="51"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -5290,7 +5329,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="34"/>
+      <c r="D49" s="51"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -5302,7 +5341,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="34"/>
+      <c r="D50" s="51"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -5314,7 +5353,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="34"/>
+      <c r="D51" s="51"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -5326,7 +5365,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="34"/>
+      <c r="D52" s="51"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -5338,7 +5377,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="34"/>
+      <c r="D53" s="51"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -5350,7 +5389,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="34"/>
+      <c r="D54" s="51"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -5362,7 +5401,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="34"/>
+      <c r="D55" s="51"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -5374,7 +5413,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="34"/>
+      <c r="D56" s="51"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -6296,6 +6335,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="D3:D56"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:H1"/>
     <mergeCell ref="C4:C8"/>
     <mergeCell ref="H4:H8"/>
     <mergeCell ref="J16:J22"/>
@@ -6305,14 +6352,6 @@
     <mergeCell ref="F16:F22"/>
     <mergeCell ref="G16:G22"/>
     <mergeCell ref="H16:H22"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="D3:D56"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6336,30 +6375,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="44" t="s">
+      <c r="F1" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="45" t="s">
+      <c r="G1" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="46"/>
+      <c r="H1" s="62"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="27" t="s">
+      <c r="J1" s="45" t="s">
         <v>0</v>
       </c>
     </row>
@@ -6370,10 +6409,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -6381,51 +6420,51 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="27"/>
+      <c r="J2" s="45"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="33" t="s">
+      <c r="A3" s="46"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="36" t="s">
+      <c r="F3" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="37" t="s">
+      <c r="G3" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="37" t="s">
+      <c r="H3" s="53" t="s">
         <v>58</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="29"/>
+      <c r="J3" s="42"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="29"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
+      <c r="A4" s="42"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
       <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="29"/>
+      <c r="J4" s="42"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="10"/>
       <c r="C5" s="11"/>
-      <c r="D5" s="34"/>
+      <c r="D5" s="51"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
@@ -6441,7 +6480,7 @@
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
       <c r="C6" s="11"/>
-      <c r="D6" s="34"/>
+      <c r="D6" s="51"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
@@ -6455,7 +6494,7 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="34"/>
+      <c r="D7" s="51"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
@@ -6469,7 +6508,7 @@
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="34"/>
+      <c r="D8" s="51"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
@@ -6485,11 +6524,13 @@
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="34"/>
+      <c r="D9" s="51"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
+      <c r="H9" s="10" t="s">
+        <v>129</v>
+      </c>
       <c r="I9" s="10" t="s">
         <v>21</v>
       </c>
@@ -6499,11 +6540,13 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="34"/>
+      <c r="D10" s="51"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
+      <c r="H10" s="10" t="s">
+        <v>130</v>
+      </c>
       <c r="I10" s="10" t="s">
         <v>23</v>
       </c>
@@ -6513,11 +6556,13 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="34"/>
+      <c r="D11" s="51"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
+      <c r="H11" s="10" t="s">
+        <v>131</v>
+      </c>
       <c r="I11" s="10" t="s">
         <v>22</v>
       </c>
@@ -6527,7 +6572,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="34"/>
+      <c r="D12" s="51"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -6539,7 +6584,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="34"/>
+      <c r="D13" s="51"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -6553,7 +6598,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="34"/>
+      <c r="D14" s="51"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -6565,7 +6610,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="34"/>
+      <c r="D15" s="51"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
@@ -6579,7 +6624,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="34"/>
+      <c r="D16" s="51"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -6588,94 +6633,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="47"/>
-      <c r="B17" s="47"/>
+      <c r="A17" s="43"/>
+      <c r="B17" s="43"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="29"/>
+      <c r="J17" s="42"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="47"/>
-      <c r="B18" s="47"/>
+      <c r="A18" s="43"/>
+      <c r="B18" s="43"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="29"/>
+      <c r="J18" s="42"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="47"/>
-      <c r="B19" s="47"/>
+      <c r="A19" s="43"/>
+      <c r="B19" s="43"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="29"/>
+      <c r="J19" s="42"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="47"/>
-      <c r="B20" s="47"/>
+      <c r="A20" s="43"/>
+      <c r="B20" s="43"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="29"/>
+      <c r="J20" s="42"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
+      <c r="A21" s="43"/>
+      <c r="B21" s="43"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="29"/>
+      <c r="J21" s="42"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="47"/>
-      <c r="B22" s="47"/>
+      <c r="A22" s="43"/>
+      <c r="B22" s="43"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="29"/>
+      <c r="J22" s="42"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="47"/>
-      <c r="B23" s="47"/>
+      <c r="A23" s="43"/>
+      <c r="B23" s="43"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="29"/>
+      <c r="J23" s="42"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="34"/>
+      <c r="D24" s="51"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -6687,7 +6732,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="34"/>
+      <c r="D25" s="51"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -6699,7 +6744,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="34"/>
+      <c r="D26" s="51"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -6711,7 +6756,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="34"/>
+      <c r="D27" s="51"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -6723,7 +6768,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="34"/>
+      <c r="D28" s="51"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -6735,7 +6780,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="34"/>
+      <c r="D29" s="51"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -6747,7 +6792,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="34"/>
+      <c r="D30" s="51"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -6759,7 +6804,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="34"/>
+      <c r="D31" s="51"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -6771,7 +6816,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="34"/>
+      <c r="D32" s="51"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -6783,7 +6828,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="34"/>
+      <c r="D33" s="51"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -6795,7 +6840,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="34"/>
+      <c r="D34" s="51"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -6807,7 +6852,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="34"/>
+      <c r="D35" s="51"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -6819,7 +6864,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="34"/>
+      <c r="D36" s="51"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -6831,7 +6876,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="34"/>
+      <c r="D37" s="51"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -6843,7 +6888,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="34"/>
+      <c r="D38" s="51"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -6855,7 +6900,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="34"/>
+      <c r="D39" s="51"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -6867,7 +6912,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="34"/>
+      <c r="D40" s="51"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -6879,7 +6924,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="34"/>
+      <c r="D41" s="51"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -6891,7 +6936,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="34"/>
+      <c r="D42" s="51"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -6903,7 +6948,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="34"/>
+      <c r="D43" s="51"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -6915,7 +6960,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="34"/>
+      <c r="D44" s="51"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -6927,7 +6972,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="34"/>
+      <c r="D45" s="51"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -6939,7 +6984,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="34"/>
+      <c r="D46" s="51"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -6951,7 +6996,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="34"/>
+      <c r="D47" s="51"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -6963,7 +7008,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="34"/>
+      <c r="D48" s="51"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -6975,7 +7020,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="34"/>
+      <c r="D49" s="51"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -6987,7 +7032,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="34"/>
+      <c r="D50" s="51"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -6999,7 +7044,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="34"/>
+      <c r="D51" s="51"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -7011,7 +7056,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="34"/>
+      <c r="D52" s="51"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -7023,7 +7068,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="34"/>
+      <c r="D53" s="51"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -7035,7 +7080,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="34"/>
+      <c r="D54" s="51"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -7047,7 +7092,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="34"/>
+      <c r="D55" s="51"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -7059,7 +7104,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="34"/>
+      <c r="D56" s="51"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -7071,7 +7116,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="34"/>
+      <c r="D57" s="51"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -7993,13 +8038,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -8016,6 +8054,13 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8039,30 +8084,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="44" t="s">
+      <c r="F1" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="45" t="s">
+      <c r="G1" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="46"/>
+      <c r="H1" s="62"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="27" t="s">
+      <c r="J1" s="45" t="s">
         <v>0</v>
       </c>
     </row>
@@ -8073,10 +8118,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -8084,51 +8129,51 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="27"/>
+      <c r="J2" s="45"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="33" t="s">
+      <c r="A3" s="46"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="36" t="s">
+      <c r="F3" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="37" t="s">
+      <c r="G3" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="37" t="s">
+      <c r="H3" s="53" t="s">
         <v>62</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="29"/>
+      <c r="J3" s="42"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="29"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
+      <c r="A4" s="42"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
       <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="29"/>
+      <c r="J4" s="42"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="10"/>
       <c r="C5" s="11"/>
-      <c r="D5" s="34"/>
+      <c r="D5" s="51"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
@@ -8144,7 +8189,7 @@
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
       <c r="C6" s="11"/>
-      <c r="D6" s="34"/>
+      <c r="D6" s="51"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
@@ -8158,7 +8203,7 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="34"/>
+      <c r="D7" s="51"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
@@ -8170,7 +8215,7 @@
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="34"/>
+      <c r="D8" s="51"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
@@ -8184,7 +8229,7 @@
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="34"/>
+      <c r="D9" s="51"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -8198,7 +8243,7 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="34"/>
+      <c r="D10" s="51"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -8212,7 +8257,7 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="34"/>
+      <c r="D11" s="51"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -8226,7 +8271,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="34"/>
+      <c r="D12" s="51"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -8238,7 +8283,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="34"/>
+      <c r="D13" s="51"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -8252,7 +8297,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="34"/>
+      <c r="D14" s="51"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -8264,7 +8309,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="34"/>
+      <c r="D15" s="51"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
@@ -8278,7 +8323,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="34"/>
+      <c r="D16" s="51"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -8287,94 +8332,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="47"/>
-      <c r="B17" s="47"/>
+      <c r="A17" s="43"/>
+      <c r="B17" s="43"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="29"/>
+      <c r="J17" s="42"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="47"/>
-      <c r="B18" s="47"/>
+      <c r="A18" s="43"/>
+      <c r="B18" s="43"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="29"/>
+      <c r="J18" s="42"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="47"/>
-      <c r="B19" s="47"/>
+      <c r="A19" s="43"/>
+      <c r="B19" s="43"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="29"/>
+      <c r="J19" s="42"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="47"/>
-      <c r="B20" s="47"/>
+      <c r="A20" s="43"/>
+      <c r="B20" s="43"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="29"/>
+      <c r="J20" s="42"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
+      <c r="A21" s="43"/>
+      <c r="B21" s="43"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="29"/>
+      <c r="J21" s="42"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="47"/>
-      <c r="B22" s="47"/>
+      <c r="A22" s="43"/>
+      <c r="B22" s="43"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="29"/>
+      <c r="J22" s="42"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="47"/>
-      <c r="B23" s="47"/>
+      <c r="A23" s="43"/>
+      <c r="B23" s="43"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="29"/>
+      <c r="J23" s="42"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="34"/>
+      <c r="D24" s="51"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -8386,7 +8431,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="34"/>
+      <c r="D25" s="51"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -8398,7 +8443,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="34"/>
+      <c r="D26" s="51"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -8410,7 +8455,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="34"/>
+      <c r="D27" s="51"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -8422,7 +8467,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="34"/>
+      <c r="D28" s="51"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -8434,7 +8479,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="34"/>
+      <c r="D29" s="51"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -8446,7 +8491,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="34"/>
+      <c r="D30" s="51"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -8458,7 +8503,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="34"/>
+      <c r="D31" s="51"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -8470,7 +8515,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="34"/>
+      <c r="D32" s="51"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -8482,7 +8527,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="34"/>
+      <c r="D33" s="51"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -8494,7 +8539,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="34"/>
+      <c r="D34" s="51"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -8506,7 +8551,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="34"/>
+      <c r="D35" s="51"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -8518,7 +8563,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="34"/>
+      <c r="D36" s="51"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -8530,7 +8575,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="34"/>
+      <c r="D37" s="51"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -8542,7 +8587,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="34"/>
+      <c r="D38" s="51"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -8554,7 +8599,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="34"/>
+      <c r="D39" s="51"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -8566,7 +8611,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="34"/>
+      <c r="D40" s="51"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -8578,7 +8623,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="34"/>
+      <c r="D41" s="51"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -8590,7 +8635,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="34"/>
+      <c r="D42" s="51"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -8602,7 +8647,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="34"/>
+      <c r="D43" s="51"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -8614,7 +8659,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="34"/>
+      <c r="D44" s="51"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -8626,7 +8671,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="34"/>
+      <c r="D45" s="51"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -8638,7 +8683,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="34"/>
+      <c r="D46" s="51"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -8650,7 +8695,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="34"/>
+      <c r="D47" s="51"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -8662,7 +8707,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="34"/>
+      <c r="D48" s="51"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -8674,7 +8719,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="34"/>
+      <c r="D49" s="51"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -8686,7 +8731,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="34"/>
+      <c r="D50" s="51"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -8698,7 +8743,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="34"/>
+      <c r="D51" s="51"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -8710,7 +8755,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="34"/>
+      <c r="D52" s="51"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -8722,7 +8767,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="34"/>
+      <c r="D53" s="51"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -8734,7 +8779,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="34"/>
+      <c r="D54" s="51"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -8746,7 +8791,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="34"/>
+      <c r="D55" s="51"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -8758,7 +8803,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="34"/>
+      <c r="D56" s="51"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -8770,7 +8815,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="34"/>
+      <c r="D57" s="51"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -9692,13 +9737,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -9715,6 +9753,13 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9738,30 +9783,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="44" t="s">
+      <c r="F1" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="45" t="s">
+      <c r="G1" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="46"/>
+      <c r="H1" s="62"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="27" t="s">
+      <c r="J1" s="45" t="s">
         <v>0</v>
       </c>
     </row>
@@ -9772,10 +9817,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -9783,7 +9828,7 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="27"/>
+      <c r="J2" s="45"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A3" t="s">
@@ -9795,13 +9840,13 @@
       <c r="C3" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="36" t="s">
+      <c r="F3" s="52" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="25" t="s">
@@ -9813,7 +9858,7 @@
       <c r="I3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="51"/>
+      <c r="J3" s="33"/>
     </row>
     <row r="4" spans="1:10" ht="15">
       <c r="B4" t="s">
@@ -9822,9 +9867,9 @@
       <c r="C4" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="36"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="52"/>
       <c r="G4" s="21"/>
       <c r="H4" s="4" t="s">
         <v>65</v>
@@ -9841,7 +9886,7 @@
       <c r="C5" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="34"/>
+      <c r="D5" s="51"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="4"/>
@@ -9858,7 +9903,7 @@
       <c r="C6" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D6" s="34"/>
+      <c r="D6" s="51"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="4"/>
@@ -9869,28 +9914,28 @@
       <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:10" ht="60">
-      <c r="C7" s="66" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" s="34"/>
+      <c r="C7" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="51"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="4"/>
-      <c r="H7" s="65" t="s">
+      <c r="H7" s="37" t="s">
         <v>69</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J7" s="65" t="s">
-        <v>109</v>
+      <c r="J7" s="37" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30">
       <c r="C8" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="D8" s="34"/>
+        <v>106</v>
+      </c>
+      <c r="D8" s="51"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="4"/>
@@ -9901,14 +9946,14 @@
         <v>21</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="30">
       <c r="C9" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="D9" s="34"/>
+        <v>110</v>
+      </c>
+      <c r="D9" s="51"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="4"/>
@@ -9919,52 +9964,52 @@
         <v>23</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15">
-      <c r="C10" s="68" t="s">
-        <v>114</v>
-      </c>
-      <c r="D10" s="34"/>
+      <c r="C10" s="65" t="s">
+        <v>113</v>
+      </c>
+      <c r="D10" s="51"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="4"/>
-      <c r="H10" s="67" t="s">
+      <c r="H10" s="66" t="s">
         <v>72</v>
       </c>
       <c r="I10" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="J10" s="62"/>
+      <c r="J10" s="67"/>
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1">
-      <c r="C11" s="68"/>
-      <c r="D11" s="34"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="51"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="4"/>
-      <c r="H11" s="67"/>
+      <c r="H11" s="66"/>
       <c r="I11" s="21"/>
-      <c r="J11" s="62"/>
+      <c r="J11" s="67"/>
     </row>
     <row r="12" spans="1:10" ht="15">
-      <c r="C12" s="68"/>
-      <c r="D12" s="34"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="51"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="67"/>
+      <c r="H12" s="66"/>
       <c r="I12" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="62"/>
+      <c r="J12" s="67"/>
     </row>
     <row r="13" spans="1:10" ht="45">
       <c r="C13" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="D13" s="34"/>
+        <v>114</v>
+      </c>
+      <c r="D13" s="51"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="4"/>
@@ -9981,7 +10026,7 @@
       <c r="C14" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D14" s="34"/>
+      <c r="D14" s="51"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="4"/>
@@ -9995,35 +10040,35 @@
     </row>
     <row r="15" spans="1:10" ht="15">
       <c r="C15" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="D15" s="34"/>
+        <v>118</v>
+      </c>
+      <c r="D15" s="51"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="4"/>
-      <c r="H15" s="64" t="s">
-        <v>106</v>
+      <c r="H15" s="36" t="s">
+        <v>105</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
     </row>
     <row r="16" spans="1:10" ht="15">
-      <c r="D16" s="34"/>
+      <c r="D16" s="51"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="21"/>
       <c r="I16" s="21"/>
-      <c r="J16" s="51"/>
+      <c r="J16" s="33"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="D17" s="34"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
       <c r="I17" s="21"/>
-      <c r="J17" s="51"/>
+      <c r="J17" s="33"/>
     </row>
     <row r="18" spans="1:10" ht="15">
       <c r="A18" t="s">
@@ -10033,73 +10078,75 @@
         <v>74</v>
       </c>
       <c r="C18" s="7"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
       <c r="I18" s="21"/>
-      <c r="J18" s="51"/>
+      <c r="J18" s="33"/>
     </row>
     <row r="19" spans="1:10" ht="15">
       <c r="B19" t="s">
         <v>75</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
+      <c r="C19" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="51"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
       <c r="I19" s="21"/>
-      <c r="J19" s="51"/>
+      <c r="J19" s="33"/>
     </row>
     <row r="20" spans="1:10" ht="15">
       <c r="B20" t="s">
         <v>76</v>
       </c>
       <c r="C20" s="7"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
       <c r="I20" s="21"/>
-      <c r="J20" s="51"/>
+      <c r="J20" s="33"/>
     </row>
     <row r="21" spans="1:10" ht="15">
       <c r="B21" t="s">
         <v>77</v>
       </c>
       <c r="C21" s="7"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
       <c r="I21" s="21"/>
-      <c r="J21" s="51"/>
+      <c r="J21" s="33"/>
     </row>
     <row r="22" spans="1:10" ht="15">
       <c r="B22" t="s">
         <v>78</v>
       </c>
       <c r="C22" s="7"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="33"/>
       <c r="I22" s="21"/>
-      <c r="J22" s="51"/>
+      <c r="J22" s="33"/>
     </row>
     <row r="23" spans="1:10" ht="15">
       <c r="C23" s="7"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="33"/>
       <c r="I23" s="21"/>
       <c r="J23" s="21"/>
     </row>
@@ -10111,7 +10158,7 @@
         <v>74</v>
       </c>
       <c r="C24" s="7"/>
-      <c r="D24" s="34"/>
+      <c r="D24" s="51"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
       <c r="G24" s="21"/>
@@ -10124,7 +10171,7 @@
         <v>79</v>
       </c>
       <c r="C25" s="8"/>
-      <c r="D25" s="34"/>
+      <c r="D25" s="51"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="4"/>
@@ -10137,7 +10184,7 @@
         <v>64</v>
       </c>
       <c r="C26" s="8"/>
-      <c r="D26" s="34"/>
+      <c r="D26" s="51"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -10150,7 +10197,7 @@
         <v>80</v>
       </c>
       <c r="C27" s="8"/>
-      <c r="D27" s="34"/>
+      <c r="D27" s="51"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
@@ -10160,7 +10207,7 @@
     </row>
     <row r="28" spans="1:10" ht="15">
       <c r="C28" s="8"/>
-      <c r="D28" s="34"/>
+      <c r="D28" s="51"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -10176,7 +10223,7 @@
         <v>64</v>
       </c>
       <c r="C29" s="8"/>
-      <c r="D29" s="34"/>
+      <c r="D29" s="51"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -10189,7 +10236,7 @@
         <v>79</v>
       </c>
       <c r="C30" s="8"/>
-      <c r="D30" s="34"/>
+      <c r="D30" s="51"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="4"/>
@@ -10202,7 +10249,7 @@
         <v>81</v>
       </c>
       <c r="C31" s="8"/>
-      <c r="D31" s="34"/>
+      <c r="D31" s="51"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="4"/>
@@ -10215,7 +10262,7 @@
         <v>82</v>
       </c>
       <c r="C32" s="7"/>
-      <c r="D32" s="34"/>
+      <c r="D32" s="51"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="4"/>
@@ -10228,7 +10275,7 @@
         <v>83</v>
       </c>
       <c r="C33" s="7"/>
-      <c r="D33" s="34"/>
+      <c r="D33" s="51"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
@@ -10241,7 +10288,7 @@
         <v>84</v>
       </c>
       <c r="C34" s="7"/>
-      <c r="D34" s="34"/>
+      <c r="D34" s="51"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
       <c r="G34" s="4"/>
@@ -10254,7 +10301,7 @@
         <v>85</v>
       </c>
       <c r="C35" s="7"/>
-      <c r="D35" s="34"/>
+      <c r="D35" s="51"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
       <c r="G35" s="4"/>
@@ -10267,7 +10314,7 @@
         <v>86</v>
       </c>
       <c r="C36" s="7"/>
-      <c r="D36" s="34"/>
+      <c r="D36" s="51"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="4"/>
@@ -10279,7 +10326,7 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="34"/>
+      <c r="D37" s="51"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="4"/>
@@ -10289,13 +10336,13 @@
     </row>
     <row r="38" spans="1:10" ht="15">
       <c r="A38" t="s">
+        <v>115</v>
+      </c>
+      <c r="B38" t="s">
         <v>116</v>
       </c>
-      <c r="B38" t="s">
-        <v>117</v>
-      </c>
       <c r="C38" s="7"/>
-      <c r="D38" s="34"/>
+      <c r="D38" s="51"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="4"/>
@@ -10305,10 +10352,10 @@
     </row>
     <row r="39" spans="1:10" ht="15">
       <c r="B39" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C39" s="7"/>
-      <c r="D39" s="34"/>
+      <c r="D39" s="51"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="4"/>
@@ -10319,7 +10366,7 @@
     <row r="40" spans="1:10" ht="15">
       <c r="B40" s="4"/>
       <c r="C40" s="7"/>
-      <c r="D40" s="34"/>
+      <c r="D40" s="51"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="4"/>
@@ -10330,7 +10377,7 @@
     <row r="41" spans="1:10" ht="15">
       <c r="B41" s="4"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="34"/>
+      <c r="D41" s="51"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="4"/>
@@ -10342,7 +10389,7 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="34"/>
+      <c r="D42" s="51"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="4"/>
@@ -10354,7 +10401,7 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="34"/>
+      <c r="D43" s="51"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="4"/>
@@ -10366,7 +10413,7 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="7"/>
-      <c r="D44" s="34"/>
+      <c r="D44" s="51"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="4"/>
@@ -10378,7 +10425,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="34"/>
+      <c r="D45" s="51"/>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
       <c r="G45" s="4"/>
@@ -10390,7 +10437,7 @@
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="7"/>
-      <c r="D46" s="34"/>
+      <c r="D46" s="51"/>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
       <c r="G46" s="4"/>
@@ -10402,7 +10449,7 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="7"/>
-      <c r="D47" s="34"/>
+      <c r="D47" s="51"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
       <c r="G47" s="4"/>
@@ -10414,7 +10461,7 @@
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="7"/>
-      <c r="D48" s="34"/>
+      <c r="D48" s="51"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
       <c r="G48" s="4"/>
@@ -10426,7 +10473,7 @@
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="7"/>
-      <c r="D49" s="34"/>
+      <c r="D49" s="51"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
       <c r="G49" s="4"/>
@@ -10438,7 +10485,7 @@
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="34"/>
+      <c r="D50" s="51"/>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
       <c r="G50" s="4"/>
@@ -10450,7 +10497,7 @@
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="7"/>
-      <c r="D51" s="34"/>
+      <c r="D51" s="51"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
       <c r="G51" s="4"/>
@@ -10462,7 +10509,7 @@
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="7"/>
-      <c r="D52" s="34"/>
+      <c r="D52" s="51"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
       <c r="G52" s="4"/>
@@ -10474,7 +10521,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="34"/>
+      <c r="D53" s="51"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="4"/>
@@ -10486,7 +10533,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="34"/>
+      <c r="D54" s="51"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
       <c r="G54" s="4"/>
@@ -10498,7 +10545,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="7"/>
-      <c r="D55" s="34"/>
+      <c r="D55" s="51"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
       <c r="G55" s="4"/>
@@ -10510,7 +10557,7 @@
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="7"/>
-      <c r="D56" s="34"/>
+      <c r="D56" s="51"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
       <c r="G56" s="4"/>
@@ -10522,7 +10569,7 @@
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="7"/>
-      <c r="D57" s="34"/>
+      <c r="D57" s="51"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
       <c r="G57" s="4"/>
@@ -11478,27 +11525,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="44" t="s">
+      <c r="F1" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="45" t="s">
+      <c r="G1" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="46"/>
-      <c r="I1" s="27" t="s">
+      <c r="H1" s="62"/>
+      <c r="I1" s="45" t="s">
         <v>0</v>
       </c>
     </row>
@@ -11509,17 +11556,17 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="27"/>
+      <c r="I2" s="45"/>
     </row>
     <row r="3" spans="1:9" ht="15">
       <c r="A3" s="14" t="s">
@@ -11531,18 +11578,18 @@
       <c r="C3" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="35"/>
-      <c r="F3" s="36"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="52"/>
       <c r="G3" s="14" t="s">
         <v>87</v>
       </c>
       <c r="H3" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="I3" s="29"/>
+      <c r="I3" s="42"/>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1">
       <c r="A4" s="14"/>
@@ -11552,25 +11599,25 @@
       <c r="C4" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="36"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="52"/>
       <c r="G4" s="13"/>
       <c r="H4" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="I4" s="29"/>
+      <c r="I4" s="42"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1">
       <c r="A5" s="25"/>
       <c r="B5" s="25"/>
       <c r="C5" s="20"/>
-      <c r="D5" s="34"/>
+      <c r="D5" s="51"/>
       <c r="E5" s="22"/>
       <c r="F5" s="24"/>
       <c r="G5" s="21"/>
       <c r="H5" s="21" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I5" s="21"/>
     </row>
@@ -11580,14 +11627,14 @@
         <v>49</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D6" s="34"/>
+        <v>121</v>
+      </c>
+      <c r="D6" s="51"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I6" s="4"/>
     </row>
@@ -11595,22 +11642,22 @@
       <c r="A7" s="14"/>
       <c r="B7" s="25"/>
       <c r="C7" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="D7" s="34"/>
+        <v>122</v>
+      </c>
+      <c r="D7" s="51"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="C8" t="s">
-        <v>124</v>
-      </c>
-      <c r="D8" s="34"/>
+        <v>123</v>
+      </c>
+      <c r="D8" s="51"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="4"/>
@@ -11619,11 +11666,11 @@
       </c>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9" ht="38.25" customHeight="1">
-      <c r="C9" s="69" t="s">
-        <v>130</v>
-      </c>
-      <c r="D9" s="34"/>
+    <row r="9" spans="1:9" ht="52.5" customHeight="1">
+      <c r="C9" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="D9" s="51"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="4"/>
@@ -11633,10 +11680,10 @@
       <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" ht="42.75" customHeight="1">
-      <c r="C10" s="70" t="s">
-        <v>131</v>
-      </c>
-      <c r="D10" s="34"/>
+      <c r="C10" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" s="51"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="4"/>
@@ -11650,7 +11697,7 @@
       <c r="B11" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="34"/>
+      <c r="D11" s="51"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="4"/>
@@ -11658,7 +11705,7 @@
     </row>
     <row r="12" spans="1:9" ht="15">
       <c r="A12" s="14"/>
-      <c r="D12" s="34"/>
+      <c r="D12" s="51"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="4"/>
@@ -11672,7 +11719,7 @@
       <c r="B13" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="34"/>
+      <c r="D13" s="51"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="4"/>
@@ -11684,7 +11731,7 @@
       <c r="B14" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="34"/>
+      <c r="D14" s="51"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="4"/>
@@ -11697,7 +11744,7 @@
         <v>64</v>
       </c>
       <c r="C15" s="7"/>
-      <c r="D15" s="34"/>
+      <c r="D15" s="51"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="4"/>
@@ -11710,7 +11757,7 @@
         <v>80</v>
       </c>
       <c r="C16" s="7"/>
-      <c r="D16" s="34"/>
+      <c r="D16" s="51"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="4"/>
@@ -11720,84 +11767,84 @@
     <row r="17" spans="1:9" ht="15">
       <c r="A17" s="21"/>
       <c r="C17" s="7"/>
-      <c r="D17" s="34"/>
+      <c r="D17" s="51"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="21"/>
-      <c r="H17" s="51"/>
+      <c r="H17" s="33"/>
       <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9" ht="15">
       <c r="A18" s="21"/>
       <c r="C18" s="7"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="29"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="42"/>
     </row>
     <row r="19" spans="1:9" ht="15">
       <c r="C19" s="4"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="29"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="42"/>
     </row>
     <row r="20" spans="1:9" ht="15">
       <c r="C20" s="7"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="29"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="42"/>
     </row>
     <row r="21" spans="1:9" ht="15">
       <c r="C21" s="4"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="29"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="42"/>
     </row>
     <row r="22" spans="1:9" ht="15">
       <c r="C22" s="7"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="29"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="42"/>
     </row>
     <row r="23" spans="1:9" ht="15">
       <c r="C23" s="7"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="29"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="42"/>
     </row>
     <row r="24" spans="1:9" ht="15">
       <c r="A24" s="15"/>
       <c r="B24" s="15"/>
       <c r="C24" s="8"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="33"/>
       <c r="H24" s="21"/>
-      <c r="I24" s="29"/>
+      <c r="I24" s="42"/>
     </row>
     <row r="25" spans="1:9" ht="15">
       <c r="A25" s="4"/>
       <c r="B25" s="15"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="34"/>
+      <c r="D25" s="51"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="4"/>
@@ -11808,7 +11855,7 @@
       <c r="A26" s="4"/>
       <c r="B26" s="15"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="34"/>
+      <c r="D26" s="51"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
       <c r="G26" s="4"/>
@@ -11819,7 +11866,7 @@
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="7"/>
-      <c r="D27" s="34"/>
+      <c r="D27" s="51"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
@@ -11830,7 +11877,7 @@
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="34"/>
+      <c r="D28" s="51"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -11841,7 +11888,7 @@
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="34"/>
+      <c r="D29" s="51"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -11852,7 +11899,7 @@
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="34"/>
+      <c r="D30" s="51"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
@@ -11863,7 +11910,7 @@
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="34"/>
+      <c r="D31" s="51"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="4"/>
@@ -11874,7 +11921,7 @@
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="7"/>
-      <c r="D32" s="34"/>
+      <c r="D32" s="51"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="4"/>
@@ -11885,7 +11932,7 @@
       <c r="A33" s="4"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="34"/>
+      <c r="D33" s="51"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
       <c r="G33" s="4"/>
@@ -11896,7 +11943,7 @@
       <c r="A34" s="4"/>
       <c r="B34" s="7"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="34"/>
+      <c r="D34" s="51"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
@@ -11907,7 +11954,7 @@
       <c r="A35" s="4"/>
       <c r="B35" s="7"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="34"/>
+      <c r="D35" s="51"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
       <c r="G35" s="4"/>
@@ -11918,7 +11965,7 @@
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="7"/>
-      <c r="D36" s="34"/>
+      <c r="D36" s="51"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="4"/>
@@ -11929,7 +11976,7 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="34"/>
+      <c r="D37" s="51"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="4"/>
@@ -11940,7 +11987,7 @@
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="7"/>
-      <c r="D38" s="34"/>
+      <c r="D38" s="51"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="4"/>
@@ -11951,7 +11998,7 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="7"/>
-      <c r="D39" s="34"/>
+      <c r="D39" s="51"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="4"/>
@@ -11962,7 +12009,7 @@
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="7"/>
-      <c r="D40" s="34"/>
+      <c r="D40" s="51"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="4"/>
@@ -11973,7 +12020,7 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="34"/>
+      <c r="D41" s="51"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="4"/>
@@ -11984,7 +12031,7 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="34"/>
+      <c r="D42" s="51"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="4"/>
@@ -11995,7 +12042,7 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="34"/>
+      <c r="D43" s="51"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="4"/>
@@ -12006,7 +12053,7 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="7"/>
-      <c r="D44" s="34"/>
+      <c r="D44" s="51"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="4"/>
@@ -12017,7 +12064,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="34"/>
+      <c r="D45" s="51"/>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
       <c r="G45" s="4"/>
@@ -12028,7 +12075,7 @@
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="7"/>
-      <c r="D46" s="34"/>
+      <c r="D46" s="51"/>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
       <c r="G46" s="4"/>
@@ -12039,7 +12086,7 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="7"/>
-      <c r="D47" s="34"/>
+      <c r="D47" s="51"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
       <c r="G47" s="4"/>
@@ -12050,7 +12097,7 @@
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="7"/>
-      <c r="D48" s="34"/>
+      <c r="D48" s="51"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
       <c r="G48" s="4"/>
@@ -12061,7 +12108,7 @@
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="7"/>
-      <c r="D49" s="34"/>
+      <c r="D49" s="51"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
       <c r="G49" s="4"/>
@@ -12072,7 +12119,7 @@
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="34"/>
+      <c r="D50" s="51"/>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
       <c r="G50" s="4"/>
@@ -12083,7 +12130,7 @@
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="7"/>
-      <c r="D51" s="34"/>
+      <c r="D51" s="51"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
       <c r="G51" s="4"/>
@@ -12094,7 +12141,7 @@
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="7"/>
-      <c r="D52" s="34"/>
+      <c r="D52" s="51"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
       <c r="G52" s="4"/>
@@ -12105,7 +12152,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="34"/>
+      <c r="D53" s="51"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="4"/>
@@ -12116,7 +12163,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="34"/>
+      <c r="D54" s="51"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
       <c r="G54" s="4"/>
@@ -12127,7 +12174,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="7"/>
-      <c r="D55" s="34"/>
+      <c r="D55" s="51"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
       <c r="G55" s="4"/>
@@ -12138,7 +12185,7 @@
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="7"/>
-      <c r="D56" s="34"/>
+      <c r="D56" s="51"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
       <c r="G56" s="4"/>
@@ -12149,7 +12196,7 @@
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="7"/>
-      <c r="D57" s="34"/>
+      <c r="D57" s="51"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
       <c r="G57" s="4"/>
@@ -12160,7 +12207,7 @@
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="7"/>
-      <c r="D58" s="34"/>
+      <c r="D58" s="51"/>
       <c r="E58" s="7"/>
       <c r="F58" s="7"/>
       <c r="G58" s="4"/>
@@ -13010,6 +13057,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="D3:D58"/>
     <mergeCell ref="E3:E4"/>
@@ -13019,11 +13071,6 @@
     <mergeCell ref="I18:I24"/>
     <mergeCell ref="E18:E24"/>
     <mergeCell ref="F18:F24"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13045,27 +13092,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="44" t="s">
+      <c r="F1" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="45" t="s">
+      <c r="G1" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="46"/>
-      <c r="I1" s="27" t="s">
+      <c r="H1" s="62"/>
+      <c r="I1" s="45" t="s">
         <v>0</v>
       </c>
     </row>
@@ -13076,17 +13123,17 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="27"/>
+      <c r="I2" s="45"/>
     </row>
     <row r="3" spans="1:9" ht="15">
       <c r="A3" s="19" t="s">
@@ -13098,18 +13145,18 @@
       <c r="C3" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="35"/>
-      <c r="F3" s="36"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="52"/>
       <c r="G3" s="19" t="s">
         <v>97</v>
       </c>
       <c r="H3" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="I3" s="29"/>
+      <c r="I3" s="42"/>
     </row>
     <row r="4" spans="1:9" ht="14.25" customHeight="1">
       <c r="A4" s="19"/>
@@ -13117,20 +13164,20 @@
         <v>49</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="36"/>
+        <v>124</v>
+      </c>
+      <c r="D4" s="51"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="52"/>
       <c r="G4" s="16"/>
       <c r="H4" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="29"/>
+      <c r="I4" s="42"/>
     </row>
     <row r="5" spans="1:9" ht="15">
       <c r="C5" s="18"/>
-      <c r="D5" s="34"/>
+      <c r="D5" s="51"/>
       <c r="E5" s="18"/>
       <c r="F5" s="18"/>
       <c r="G5" s="16"/>
@@ -13141,9 +13188,9 @@
     </row>
     <row r="6" spans="1:9" ht="15">
       <c r="C6" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6" s="34"/>
+        <v>125</v>
+      </c>
+      <c r="D6" s="51"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
       <c r="G6" s="16"/>
@@ -13152,11 +13199,11 @@
       </c>
       <c r="I6" s="16"/>
     </row>
-    <row r="7" spans="1:9" ht="60">
+    <row r="7" spans="1:9" ht="30">
       <c r="C7" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="D7" s="34"/>
+        <v>134</v>
+      </c>
+      <c r="D7" s="51"/>
       <c r="E7" s="18"/>
       <c r="F7" s="18"/>
       <c r="G7" s="16"/>
@@ -13167,9 +13214,9 @@
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="C8" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D8" s="34"/>
+        <v>126</v>
+      </c>
+      <c r="D8" s="51"/>
       <c r="E8" s="18"/>
       <c r="F8" s="18"/>
       <c r="G8" s="16"/>
@@ -13184,7 +13231,7 @@
         <v>48</v>
       </c>
       <c r="C9" s="16"/>
-      <c r="D9" s="34"/>
+      <c r="D9" s="51"/>
       <c r="E9" s="18"/>
       <c r="F9" s="18"/>
       <c r="G9" s="16"/>
@@ -13196,7 +13243,7 @@
         <v>41</v>
       </c>
       <c r="C10" s="18"/>
-      <c r="D10" s="34"/>
+      <c r="D10" s="51"/>
       <c r="E10" s="18"/>
       <c r="F10" s="18"/>
       <c r="G10" s="16"/>
@@ -13206,7 +13253,7 @@
     <row r="11" spans="1:9" ht="15">
       <c r="A11" s="19"/>
       <c r="C11" s="16"/>
-      <c r="D11" s="34"/>
+      <c r="D11" s="51"/>
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
       <c r="G11" s="16"/>
@@ -13221,7 +13268,7 @@
         <v>41</v>
       </c>
       <c r="C12" s="18"/>
-      <c r="D12" s="34"/>
+      <c r="D12" s="51"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="16"/>
@@ -13234,7 +13281,7 @@
         <v>49</v>
       </c>
       <c r="C13" s="18"/>
-      <c r="D13" s="34"/>
+      <c r="D13" s="51"/>
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
       <c r="G13" s="16"/>
@@ -13247,7 +13294,7 @@
         <v>64</v>
       </c>
       <c r="C14" s="18"/>
-      <c r="D14" s="34"/>
+      <c r="D14" s="51"/>
       <c r="E14" s="18"/>
       <c r="F14" s="18"/>
       <c r="G14" s="16"/>
@@ -13260,7 +13307,7 @@
         <v>80</v>
       </c>
       <c r="C15" s="18"/>
-      <c r="D15" s="34"/>
+      <c r="D15" s="51"/>
       <c r="E15" s="18"/>
       <c r="F15" s="18"/>
       <c r="G15" s="16"/>
@@ -13271,7 +13318,7 @@
       <c r="A16" s="26"/>
       <c r="B16" s="26"/>
       <c r="C16" s="18"/>
-      <c r="D16" s="34"/>
+      <c r="D16" s="51"/>
       <c r="E16" s="16"/>
       <c r="F16" s="16"/>
       <c r="G16" s="16"/>
@@ -13286,12 +13333,12 @@
         <v>50</v>
       </c>
       <c r="C17" s="8"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="29"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
     </row>
     <row r="18" spans="1:9" ht="15">
       <c r="A18" s="16"/>
@@ -13299,22 +13346,22 @@
         <v>51</v>
       </c>
       <c r="C18" s="8"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
     </row>
     <row r="19" spans="1:9" ht="15">
       <c r="A19" s="16"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
     </row>
     <row r="20" spans="1:9" ht="15">
       <c r="A20" s="16" t="s">
@@ -13324,12 +13371,12 @@
         <v>52</v>
       </c>
       <c r="C20" s="8"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
     </row>
     <row r="21" spans="1:9" ht="15">
       <c r="A21" s="16"/>
@@ -13337,36 +13384,36 @@
         <v>53</v>
       </c>
       <c r="C21" s="8"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="29"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
     </row>
     <row r="22" spans="1:9" ht="15">
       <c r="C22" s="8"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
     </row>
     <row r="23" spans="1:9" ht="15">
       <c r="C23" s="8"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
     </row>
     <row r="24" spans="1:9" ht="15">
       <c r="A24" s="15"/>
       <c r="B24" s="15"/>
       <c r="C24" s="18"/>
-      <c r="D24" s="34"/>
+      <c r="D24" s="51"/>
       <c r="E24" s="18"/>
       <c r="F24" s="18"/>
       <c r="G24" s="16"/>
@@ -13377,7 +13424,7 @@
       <c r="A25" s="16"/>
       <c r="B25" s="16"/>
       <c r="C25" s="18"/>
-      <c r="D25" s="34"/>
+      <c r="D25" s="51"/>
       <c r="E25" s="18"/>
       <c r="F25" s="18"/>
       <c r="G25" s="16"/>
@@ -13388,7 +13435,7 @@
       <c r="A26" s="16"/>
       <c r="B26" s="16"/>
       <c r="C26" s="18"/>
-      <c r="D26" s="34"/>
+      <c r="D26" s="51"/>
       <c r="E26" s="16"/>
       <c r="F26" s="16"/>
       <c r="G26" s="16"/>
@@ -13399,7 +13446,7 @@
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
       <c r="C27" s="18"/>
-      <c r="D27" s="34"/>
+      <c r="D27" s="51"/>
       <c r="E27" s="16"/>
       <c r="F27" s="16"/>
       <c r="G27" s="16"/>
@@ -13410,7 +13457,7 @@
       <c r="A28" s="16"/>
       <c r="B28" s="16"/>
       <c r="C28" s="18"/>
-      <c r="D28" s="34"/>
+      <c r="D28" s="51"/>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
       <c r="G28" s="16"/>
@@ -13421,7 +13468,7 @@
       <c r="A29" s="16"/>
       <c r="B29" s="16"/>
       <c r="C29" s="18"/>
-      <c r="D29" s="34"/>
+      <c r="D29" s="51"/>
       <c r="E29" s="16"/>
       <c r="F29" s="16"/>
       <c r="G29" s="16"/>
@@ -13432,7 +13479,7 @@
       <c r="A30" s="16"/>
       <c r="B30" s="18"/>
       <c r="C30" s="18"/>
-      <c r="D30" s="34"/>
+      <c r="D30" s="51"/>
       <c r="E30" s="18"/>
       <c r="F30" s="18"/>
       <c r="G30" s="16"/>
@@ -13443,7 +13490,7 @@
       <c r="A31" s="16"/>
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
-      <c r="D31" s="34"/>
+      <c r="D31" s="51"/>
       <c r="E31" s="18"/>
       <c r="F31" s="18"/>
       <c r="G31" s="16"/>
@@ -13454,7 +13501,7 @@
       <c r="A32" s="16"/>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
-      <c r="D32" s="34"/>
+      <c r="D32" s="51"/>
       <c r="E32" s="18"/>
       <c r="F32" s="18"/>
       <c r="G32" s="16"/>
@@ -13465,7 +13512,7 @@
       <c r="A33" s="16"/>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
-      <c r="D33" s="34"/>
+      <c r="D33" s="51"/>
       <c r="E33" s="16"/>
       <c r="F33" s="16"/>
       <c r="G33" s="16"/>
@@ -13476,7 +13523,7 @@
       <c r="A34" s="16"/>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
-      <c r="D34" s="34"/>
+      <c r="D34" s="51"/>
       <c r="E34" s="18"/>
       <c r="F34" s="18"/>
       <c r="G34" s="16"/>
@@ -13487,7 +13534,7 @@
       <c r="A35" s="16"/>
       <c r="B35" s="16"/>
       <c r="C35" s="18"/>
-      <c r="D35" s="34"/>
+      <c r="D35" s="51"/>
       <c r="E35" s="18"/>
       <c r="F35" s="18"/>
       <c r="G35" s="16"/>
@@ -13498,7 +13545,7 @@
       <c r="A36" s="16"/>
       <c r="B36" s="16"/>
       <c r="C36" s="18"/>
-      <c r="D36" s="34"/>
+      <c r="D36" s="51"/>
       <c r="E36" s="18"/>
       <c r="F36" s="18"/>
       <c r="G36" s="16"/>
@@ -13509,7 +13556,7 @@
       <c r="A37" s="16"/>
       <c r="B37" s="16"/>
       <c r="C37" s="18"/>
-      <c r="D37" s="34"/>
+      <c r="D37" s="51"/>
       <c r="E37" s="18"/>
       <c r="F37" s="18"/>
       <c r="G37" s="16"/>
@@ -13520,7 +13567,7 @@
       <c r="A38" s="16"/>
       <c r="B38" s="16"/>
       <c r="C38" s="18"/>
-      <c r="D38" s="34"/>
+      <c r="D38" s="51"/>
       <c r="E38" s="18"/>
       <c r="F38" s="18"/>
       <c r="G38" s="16"/>
@@ -13531,7 +13578,7 @@
       <c r="A39" s="16"/>
       <c r="B39" s="16"/>
       <c r="C39" s="18"/>
-      <c r="D39" s="34"/>
+      <c r="D39" s="51"/>
       <c r="E39" s="18"/>
       <c r="F39" s="18"/>
       <c r="G39" s="16"/>
@@ -13542,7 +13589,7 @@
       <c r="A40" s="16"/>
       <c r="B40" s="16"/>
       <c r="C40" s="18"/>
-      <c r="D40" s="34"/>
+      <c r="D40" s="51"/>
       <c r="E40" s="18"/>
       <c r="F40" s="18"/>
       <c r="G40" s="16"/>
@@ -13553,7 +13600,7 @@
       <c r="A41" s="16"/>
       <c r="B41" s="16"/>
       <c r="C41" s="18"/>
-      <c r="D41" s="34"/>
+      <c r="D41" s="51"/>
       <c r="E41" s="18"/>
       <c r="F41" s="18"/>
       <c r="G41" s="16"/>
@@ -13564,7 +13611,7 @@
       <c r="A42" s="16"/>
       <c r="B42" s="16"/>
       <c r="C42" s="18"/>
-      <c r="D42" s="34"/>
+      <c r="D42" s="51"/>
       <c r="E42" s="18"/>
       <c r="F42" s="18"/>
       <c r="G42" s="16"/>
@@ -13575,7 +13622,7 @@
       <c r="A43" s="16"/>
       <c r="B43" s="16"/>
       <c r="C43" s="18"/>
-      <c r="D43" s="34"/>
+      <c r="D43" s="51"/>
       <c r="E43" s="18"/>
       <c r="F43" s="18"/>
       <c r="G43" s="16"/>
@@ -13586,7 +13633,7 @@
       <c r="A44" s="16"/>
       <c r="B44" s="16"/>
       <c r="C44" s="18"/>
-      <c r="D44" s="34"/>
+      <c r="D44" s="51"/>
       <c r="E44" s="18"/>
       <c r="F44" s="18"/>
       <c r="G44" s="16"/>
@@ -13597,7 +13644,7 @@
       <c r="A45" s="16"/>
       <c r="B45" s="16"/>
       <c r="C45" s="18"/>
-      <c r="D45" s="34"/>
+      <c r="D45" s="51"/>
       <c r="E45" s="18"/>
       <c r="F45" s="18"/>
       <c r="G45" s="16"/>
@@ -13608,7 +13655,7 @@
       <c r="A46" s="16"/>
       <c r="B46" s="16"/>
       <c r="C46" s="18"/>
-      <c r="D46" s="34"/>
+      <c r="D46" s="51"/>
       <c r="E46" s="18"/>
       <c r="F46" s="18"/>
       <c r="G46" s="16"/>
@@ -13619,7 +13666,7 @@
       <c r="A47" s="16"/>
       <c r="B47" s="16"/>
       <c r="C47" s="18"/>
-      <c r="D47" s="34"/>
+      <c r="D47" s="51"/>
       <c r="E47" s="18"/>
       <c r="F47" s="18"/>
       <c r="G47" s="16"/>
@@ -13630,7 +13677,7 @@
       <c r="A48" s="16"/>
       <c r="B48" s="16"/>
       <c r="C48" s="18"/>
-      <c r="D48" s="34"/>
+      <c r="D48" s="51"/>
       <c r="E48" s="18"/>
       <c r="F48" s="18"/>
       <c r="G48" s="16"/>
@@ -13641,7 +13688,7 @@
       <c r="A49" s="16"/>
       <c r="B49" s="16"/>
       <c r="C49" s="18"/>
-      <c r="D49" s="34"/>
+      <c r="D49" s="51"/>
       <c r="E49" s="18"/>
       <c r="F49" s="18"/>
       <c r="G49" s="16"/>
@@ -13652,7 +13699,7 @@
       <c r="A50" s="16"/>
       <c r="B50" s="16"/>
       <c r="C50" s="18"/>
-      <c r="D50" s="34"/>
+      <c r="D50" s="51"/>
       <c r="E50" s="18"/>
       <c r="F50" s="18"/>
       <c r="G50" s="16"/>
@@ -13663,7 +13710,7 @@
       <c r="A51" s="16"/>
       <c r="B51" s="16"/>
       <c r="C51" s="18"/>
-      <c r="D51" s="34"/>
+      <c r="D51" s="51"/>
       <c r="E51" s="18"/>
       <c r="F51" s="18"/>
       <c r="G51" s="16"/>
@@ -13674,7 +13721,7 @@
       <c r="A52" s="16"/>
       <c r="B52" s="16"/>
       <c r="C52" s="18"/>
-      <c r="D52" s="34"/>
+      <c r="D52" s="51"/>
       <c r="E52" s="18"/>
       <c r="F52" s="18"/>
       <c r="G52" s="16"/>
@@ -13685,7 +13732,7 @@
       <c r="A53" s="16"/>
       <c r="B53" s="16"/>
       <c r="C53" s="18"/>
-      <c r="D53" s="34"/>
+      <c r="D53" s="51"/>
       <c r="E53" s="18"/>
       <c r="F53" s="18"/>
       <c r="G53" s="16"/>
@@ -13696,7 +13743,7 @@
       <c r="A54" s="16"/>
       <c r="B54" s="16"/>
       <c r="C54" s="18"/>
-      <c r="D54" s="34"/>
+      <c r="D54" s="51"/>
       <c r="E54" s="18"/>
       <c r="F54" s="18"/>
       <c r="G54" s="16"/>
@@ -13707,7 +13754,7 @@
       <c r="A55" s="16"/>
       <c r="B55" s="16"/>
       <c r="C55" s="18"/>
-      <c r="D55" s="34"/>
+      <c r="D55" s="51"/>
       <c r="E55" s="18"/>
       <c r="F55" s="18"/>
       <c r="G55" s="16"/>
@@ -13718,7 +13765,7 @@
       <c r="A56" s="16"/>
       <c r="B56" s="16"/>
       <c r="C56" s="18"/>
-      <c r="D56" s="34"/>
+      <c r="D56" s="51"/>
       <c r="E56" s="18"/>
       <c r="F56" s="18"/>
       <c r="G56" s="16"/>
@@ -13729,7 +13776,7 @@
       <c r="A57" s="16"/>
       <c r="B57" s="16"/>
       <c r="C57" s="18"/>
-      <c r="D57" s="34"/>
+      <c r="D57" s="51"/>
       <c r="E57" s="18"/>
       <c r="F57" s="18"/>
       <c r="G57" s="16"/>
@@ -14574,11 +14621,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="D3:D57"/>
     <mergeCell ref="E3:E4"/>
@@ -14590,6 +14632,11 @@
     <mergeCell ref="H17:H23"/>
     <mergeCell ref="I17:I23"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Mapping Template BrotZeit.xlsx
+++ b/Mapping Template BrotZeit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alfa\Documents\Data Engineer\Projekt\BackZeit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628A7AF5-BA8B-4BEB-94BE-93C6F47F5A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60082A9A-A166-489E-9181-539AB3A52E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{1083ED64-F082-44F9-9F2A-19C2CA2699CD}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{1083ED64-F082-44F9-9F2A-19C2CA2699CD}"/>
   </bookViews>
   <sheets>
     <sheet name="D_Filiale" sheetId="9" r:id="rId1"/>
@@ -815,18 +815,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -835,6 +843,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -868,6 +879,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -881,21 +896,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1247,30 +1247,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="58" t="s">
+      <c r="D1" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="60" t="s">
+      <c r="E1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="60" t="s">
+      <c r="F1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="61" t="s">
+      <c r="G1" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="62"/>
+      <c r="H1" s="65"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="45" t="s">
+      <c r="J1" s="46" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1281,10 +1281,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1292,51 +1292,51 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="45"/>
+      <c r="J2" s="46"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="48" t="s">
+      <c r="C3" s="50" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="E3" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="52" t="s">
+      <c r="F3" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="53" t="s">
+      <c r="G3" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="53" t="s">
+      <c r="H3" s="56" t="s">
         <v>41</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="42"/>
+      <c r="J3" s="48"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="42"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
       <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="42"/>
+      <c r="J4" s="48"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
@@ -1346,7 +1346,7 @@
       <c r="C5" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="51"/>
+      <c r="D5" s="53"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
@@ -1366,7 +1366,7 @@
       <c r="C6" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D6" s="51"/>
+      <c r="D6" s="53"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
@@ -1380,7 +1380,7 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="51"/>
+      <c r="D7" s="53"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
@@ -1388,7 +1388,7 @@
         <v>112</v>
       </c>
       <c r="I7" s="10"/>
-      <c r="J7" s="41" t="s">
+      <c r="J7" s="66" t="s">
         <v>102</v>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
         <v>46</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="51"/>
+      <c r="D8" s="53"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
@@ -1408,13 +1408,13 @@
       <c r="I8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="41"/>
+      <c r="J8" s="66"/>
     </row>
     <row r="9" spans="1:10" ht="15">
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="51"/>
+      <c r="D9" s="53"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -1422,13 +1422,13 @@
       <c r="I9" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="41"/>
+      <c r="J9" s="66"/>
     </row>
     <row r="10" spans="1:10" ht="15">
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="51"/>
+      <c r="D10" s="53"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -1436,13 +1436,13 @@
       <c r="I10" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="41"/>
+      <c r="J10" s="66"/>
     </row>
     <row r="11" spans="1:10" ht="15">
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="51"/>
+      <c r="D11" s="53"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -1450,25 +1450,25 @@
       <c r="I11" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="41"/>
+      <c r="J11" s="66"/>
     </row>
     <row r="12" spans="1:10" ht="15">
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="51"/>
+      <c r="D12" s="53"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
-      <c r="J12" s="41"/>
+      <c r="J12" s="66"/>
     </row>
     <row r="13" spans="1:10" ht="15">
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="51"/>
+      <c r="D13" s="53"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -1482,7 +1482,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="51"/>
+      <c r="D14" s="53"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -1494,7 +1494,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="51"/>
+      <c r="D15" s="53"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
@@ -1508,7 +1508,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="51"/>
+      <c r="D16" s="53"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -1517,94 +1517,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="43"/>
-      <c r="B17" s="43"/>
+      <c r="A17" s="67"/>
+      <c r="B17" s="67"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="42"/>
+      <c r="J17" s="48"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="43"/>
-      <c r="B18" s="43"/>
+      <c r="A18" s="67"/>
+      <c r="B18" s="67"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="42"/>
+      <c r="J18" s="48"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="43"/>
-      <c r="B19" s="43"/>
+      <c r="A19" s="67"/>
+      <c r="B19" s="67"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="42"/>
+      <c r="J19" s="48"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="43"/>
-      <c r="B20" s="43"/>
+      <c r="A20" s="67"/>
+      <c r="B20" s="67"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="42"/>
+      <c r="J20" s="48"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="43"/>
-      <c r="B21" s="43"/>
+      <c r="A21" s="67"/>
+      <c r="B21" s="67"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="42"/>
+      <c r="J21" s="48"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="43"/>
-      <c r="B22" s="43"/>
+      <c r="A22" s="67"/>
+      <c r="B22" s="67"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="42"/>
+      <c r="J22" s="48"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="43"/>
-      <c r="B23" s="43"/>
+      <c r="A23" s="67"/>
+      <c r="B23" s="67"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="48"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="42"/>
+      <c r="J23" s="48"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="51"/>
+      <c r="D24" s="53"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -1616,7 +1616,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="51"/>
+      <c r="D25" s="53"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -1628,7 +1628,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="51"/>
+      <c r="D26" s="53"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -1640,7 +1640,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="51"/>
+      <c r="D27" s="53"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -1652,7 +1652,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="51"/>
+      <c r="D28" s="53"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -1664,7 +1664,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="51"/>
+      <c r="D29" s="53"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -1676,7 +1676,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="51"/>
+      <c r="D30" s="53"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -1688,7 +1688,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="51"/>
+      <c r="D31" s="53"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -1700,7 +1700,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="51"/>
+      <c r="D32" s="53"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -1712,7 +1712,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="51"/>
+      <c r="D33" s="53"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -1724,7 +1724,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="51"/>
+      <c r="D34" s="53"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -1736,7 +1736,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="51"/>
+      <c r="D35" s="53"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -1748,7 +1748,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="51"/>
+      <c r="D36" s="53"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -1760,7 +1760,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="51"/>
+      <c r="D37" s="53"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -1772,7 +1772,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="51"/>
+      <c r="D38" s="53"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -1784,7 +1784,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="51"/>
+      <c r="D39" s="53"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -1796,7 +1796,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="51"/>
+      <c r="D40" s="53"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -1808,7 +1808,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="51"/>
+      <c r="D41" s="53"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -1820,7 +1820,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="51"/>
+      <c r="D42" s="53"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -1832,7 +1832,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="51"/>
+      <c r="D43" s="53"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -1844,7 +1844,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="51"/>
+      <c r="D44" s="53"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -1856,7 +1856,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="51"/>
+      <c r="D45" s="53"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -1868,7 +1868,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="51"/>
+      <c r="D46" s="53"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -1880,7 +1880,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="51"/>
+      <c r="D47" s="53"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -1892,7 +1892,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="51"/>
+      <c r="D48" s="53"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -1904,7 +1904,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="51"/>
+      <c r="D49" s="53"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -1916,7 +1916,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="51"/>
+      <c r="D50" s="53"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -1928,7 +1928,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="51"/>
+      <c r="D51" s="53"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -1940,7 +1940,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="51"/>
+      <c r="D52" s="53"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -1952,7 +1952,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="51"/>
+      <c r="D53" s="53"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -1964,7 +1964,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="51"/>
+      <c r="D54" s="53"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -1976,7 +1976,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="51"/>
+      <c r="D55" s="53"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -1988,7 +1988,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="51"/>
+      <c r="D56" s="53"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -2000,7 +2000,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="51"/>
+      <c r="D57" s="53"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -2922,6 +2922,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="J7:J12"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -2938,14 +2946,6 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J7:J12"/>
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2969,30 +2969,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="58" t="s">
+      <c r="D1" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="60" t="s">
+      <c r="E1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="60" t="s">
+      <c r="F1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="61" t="s">
+      <c r="G1" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="62"/>
+      <c r="H1" s="65"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="45" t="s">
+      <c r="J1" s="46" t="s">
         <v>0</v>
       </c>
     </row>
@@ -3003,10 +3003,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -3014,16 +3014,16 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="45"/>
+      <c r="J2" s="46"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="44" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="52" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="28" t="s">
@@ -3032,10 +3032,10 @@
       <c r="F3" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="69" t="s">
+      <c r="G3" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="68" t="s">
+      <c r="H3" s="41" t="s">
         <v>47</v>
       </c>
       <c r="I3" s="27" t="s">
@@ -3053,10 +3053,10 @@
       <c r="C4" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D4" s="51"/>
+      <c r="D4" s="53"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="70"/>
+      <c r="G4" s="43"/>
       <c r="H4" s="10" t="s">
         <v>48</v>
       </c>
@@ -3073,7 +3073,7 @@
       <c r="C5" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="51"/>
+      <c r="D5" s="53"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
@@ -3091,7 +3091,7 @@
       <c r="C6" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D6" s="51"/>
+      <c r="D6" s="53"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
@@ -3108,11 +3108,11 @@
       <c r="C7" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="D7" s="51"/>
+      <c r="D7" s="53"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
-      <c r="H7" s="72" t="s">
+      <c r="H7" s="45" t="s">
         <v>93</v>
       </c>
       <c r="I7" s="10" t="s">
@@ -3123,11 +3123,11 @@
     <row r="8" spans="1:10" ht="14.25" customHeight="1">
       <c r="A8" s="27"/>
       <c r="C8" s="28"/>
-      <c r="D8" s="51"/>
+      <c r="D8" s="53"/>
       <c r="E8" s="28"/>
       <c r="F8" s="28"/>
       <c r="G8" s="27"/>
-      <c r="H8" s="72"/>
+      <c r="H8" s="45"/>
       <c r="I8" s="27"/>
       <c r="J8" s="27"/>
     </row>
@@ -3139,7 +3139,7 @@
         <v>41</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="51"/>
+      <c r="D9" s="53"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -3155,7 +3155,7 @@
         <v>49</v>
       </c>
       <c r="C10" s="10"/>
-      <c r="D10" s="51"/>
+      <c r="D10" s="53"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -3171,7 +3171,7 @@
         <v>64</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="51"/>
+      <c r="D11" s="53"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -3185,7 +3185,7 @@
         <v>80</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="51"/>
+      <c r="D12" s="53"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -3199,7 +3199,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="51"/>
+      <c r="D13" s="53"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -3215,7 +3215,7 @@
         <v>64</v>
       </c>
       <c r="C14" s="11"/>
-      <c r="D14" s="51"/>
+      <c r="D14" s="53"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -3230,7 +3230,7 @@
         <v>65</v>
       </c>
       <c r="C15" s="11"/>
-      <c r="D15" s="51"/>
+      <c r="D15" s="53"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
@@ -3243,92 +3243,92 @@
         <v>67</v>
       </c>
       <c r="C16" s="8"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="48"/>
       <c r="I16" s="10"/>
-      <c r="J16" s="42"/>
+      <c r="J16" s="48"/>
     </row>
     <row r="17" spans="1:10" ht="15">
       <c r="B17" t="s">
         <v>68</v>
       </c>
       <c r="C17" s="8"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="42"/>
+      <c r="J17" s="48"/>
     </row>
     <row r="18" spans="1:10" ht="15">
       <c r="A18" s="15"/>
       <c r="B18" s="15"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="42"/>
+      <c r="J18" s="48"/>
     </row>
     <row r="19" spans="1:10" ht="15">
       <c r="A19" s="15"/>
       <c r="B19" s="15"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="42"/>
+      <c r="J19" s="48"/>
     </row>
     <row r="20" spans="1:10" ht="15">
       <c r="A20" s="15"/>
       <c r="B20" s="15"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="42"/>
+      <c r="J20" s="48"/>
     </row>
     <row r="21" spans="1:10" ht="15">
       <c r="A21" s="15"/>
       <c r="B21" s="15"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="42"/>
+      <c r="J21" s="48"/>
     </row>
     <row r="22" spans="1:10" ht="15">
       <c r="A22" s="15"/>
       <c r="B22" s="15"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="42"/>
+      <c r="J22" s="48"/>
     </row>
     <row r="23" spans="1:10" ht="15">
       <c r="A23" s="10"/>
       <c r="B23" s="10"/>
       <c r="C23" s="11"/>
-      <c r="D23" s="51"/>
+      <c r="D23" s="53"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="10"/>
@@ -3340,7 +3340,7 @@
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="51"/>
+      <c r="D24" s="53"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -3352,7 +3352,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="51"/>
+      <c r="D25" s="53"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
@@ -3364,7 +3364,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="51"/>
+      <c r="D26" s="53"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -3376,7 +3376,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="51"/>
+      <c r="D27" s="53"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -3388,7 +3388,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="51"/>
+      <c r="D28" s="53"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -3400,7 +3400,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="51"/>
+      <c r="D29" s="53"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
       <c r="G29" s="10"/>
@@ -3412,7 +3412,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="51"/>
+      <c r="D30" s="53"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -3424,7 +3424,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="51"/>
+      <c r="D31" s="53"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -3436,7 +3436,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
-      <c r="D32" s="51"/>
+      <c r="D32" s="53"/>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
@@ -3448,7 +3448,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="51"/>
+      <c r="D33" s="53"/>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
       <c r="G33" s="10"/>
@@ -3460,7 +3460,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="11"/>
-      <c r="D34" s="51"/>
+      <c r="D34" s="53"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -3472,7 +3472,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="51"/>
+      <c r="D35" s="53"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -3484,7 +3484,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="51"/>
+      <c r="D36" s="53"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -3496,7 +3496,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="51"/>
+      <c r="D37" s="53"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -3508,7 +3508,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="51"/>
+      <c r="D38" s="53"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -3516,11 +3516,11 @@
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" ht="15">
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="51"/>
+      <c r="D39" s="53"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -3532,7 +3532,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="51"/>
+      <c r="D40" s="53"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -3544,7 +3544,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="51"/>
+      <c r="D41" s="53"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -3556,7 +3556,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="51"/>
+      <c r="D42" s="53"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -3568,7 +3568,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="51"/>
+      <c r="D43" s="53"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -3580,7 +3580,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="51"/>
+      <c r="D44" s="53"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -3592,7 +3592,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="51"/>
+      <c r="D45" s="53"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -3604,7 +3604,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="51"/>
+      <c r="D46" s="53"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -3616,7 +3616,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="51"/>
+      <c r="D47" s="53"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -3628,7 +3628,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="51"/>
+      <c r="D48" s="53"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -3640,7 +3640,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="51"/>
+      <c r="D49" s="53"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -3652,7 +3652,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="51"/>
+      <c r="D50" s="53"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -3664,7 +3664,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="51"/>
+      <c r="D51" s="53"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -3676,7 +3676,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="51"/>
+      <c r="D52" s="53"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -3688,7 +3688,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="51"/>
+      <c r="D53" s="53"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -3700,7 +3700,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="51"/>
+      <c r="D54" s="53"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -3712,7 +3712,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="51"/>
+      <c r="D55" s="53"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -3724,7 +3724,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="51"/>
+      <c r="D56" s="53"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -4682,30 +4682,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="58" t="s">
+      <c r="D1" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="60" t="s">
+      <c r="E1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="60" t="s">
+      <c r="F1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="61" t="s">
+      <c r="G1" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="62"/>
+      <c r="H1" s="65"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="45" t="s">
+      <c r="J1" s="46" t="s">
         <v>0</v>
       </c>
     </row>
@@ -4716,10 +4716,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -4727,7 +4727,7 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="45"/>
+      <c r="J2" s="46"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A3" s="32" t="s">
@@ -4739,7 +4739,7 @@
       <c r="C3" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="52" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="22" t="s">
@@ -4764,14 +4764,14 @@
       <c r="B4" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="63" t="s">
+      <c r="C4" s="68" t="s">
         <v>104</v>
       </c>
-      <c r="D4" s="51"/>
+      <c r="D4" s="53"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="10"/>
-      <c r="H4" s="64" t="s">
+      <c r="H4" s="69" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="10" t="s">
@@ -4782,24 +4782,24 @@
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="10"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="51"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="53"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
-      <c r="H5" s="64"/>
+      <c r="H5" s="69"/>
       <c r="I5" s="10"/>
       <c r="J5" s="10"/>
     </row>
     <row r="6" spans="1:10" ht="15">
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="51"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="53"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="64"/>
+      <c r="H6" s="69"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
     </row>
@@ -4810,12 +4810,12 @@
       <c r="B7" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="63"/>
-      <c r="D7" s="51"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="53"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
-      <c r="H7" s="64"/>
+      <c r="H7" s="69"/>
       <c r="I7" s="10" t="s">
         <v>20</v>
       </c>
@@ -4826,12 +4826,12 @@
       <c r="B8" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="63"/>
-      <c r="D8" s="51"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="53"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
-      <c r="H8" s="64"/>
+      <c r="H8" s="69"/>
       <c r="I8" s="10" t="s">
         <v>21</v>
       </c>
@@ -4841,7 +4841,7 @@
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="11"/>
-      <c r="D9" s="51"/>
+      <c r="D9" s="53"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -4855,7 +4855,7 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
-      <c r="D10" s="51"/>
+      <c r="D10" s="53"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -4869,7 +4869,7 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="11"/>
-      <c r="D11" s="51"/>
+      <c r="D11" s="53"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -4881,7 +4881,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="51"/>
+      <c r="D12" s="53"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -4895,7 +4895,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="51"/>
+      <c r="D13" s="53"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -4907,7 +4907,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="51"/>
+      <c r="D14" s="53"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -4921,7 +4921,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="51"/>
+      <c r="D15" s="53"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
@@ -4930,94 +4930,94 @@
       <c r="J15" s="10"/>
     </row>
     <row r="16" spans="1:10" ht="15">
-      <c r="A16" s="43"/>
-      <c r="B16" s="43"/>
+      <c r="A16" s="67"/>
+      <c r="B16" s="67"/>
       <c r="C16" s="8"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="48"/>
       <c r="I16" s="10"/>
-      <c r="J16" s="42"/>
+      <c r="J16" s="48"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="43"/>
-      <c r="B17" s="43"/>
+      <c r="A17" s="67"/>
+      <c r="B17" s="67"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="42"/>
+      <c r="J17" s="48"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="43"/>
-      <c r="B18" s="43"/>
+      <c r="A18" s="67"/>
+      <c r="B18" s="67"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="42"/>
+      <c r="J18" s="48"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="43"/>
-      <c r="B19" s="43"/>
+      <c r="A19" s="67"/>
+      <c r="B19" s="67"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="42"/>
+      <c r="J19" s="48"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="43"/>
-      <c r="B20" s="43"/>
+      <c r="A20" s="67"/>
+      <c r="B20" s="67"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="42"/>
+      <c r="J20" s="48"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="43"/>
-      <c r="B21" s="43"/>
+      <c r="A21" s="67"/>
+      <c r="B21" s="67"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="42"/>
+      <c r="J21" s="48"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="43"/>
-      <c r="B22" s="43"/>
+      <c r="A22" s="67"/>
+      <c r="B22" s="67"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="42"/>
+      <c r="J22" s="48"/>
     </row>
     <row r="23" spans="1:10" ht="15">
       <c r="A23" s="10"/>
       <c r="B23" s="10"/>
       <c r="C23" s="11"/>
-      <c r="D23" s="51"/>
+      <c r="D23" s="53"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="10"/>
@@ -5029,7 +5029,7 @@
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="51"/>
+      <c r="D24" s="53"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -5041,7 +5041,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="51"/>
+      <c r="D25" s="53"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
@@ -5053,7 +5053,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="51"/>
+      <c r="D26" s="53"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -5065,7 +5065,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="51"/>
+      <c r="D27" s="53"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -5077,7 +5077,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="51"/>
+      <c r="D28" s="53"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -5089,7 +5089,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="51"/>
+      <c r="D29" s="53"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
       <c r="G29" s="10"/>
@@ -5101,7 +5101,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="51"/>
+      <c r="D30" s="53"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -5113,7 +5113,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="51"/>
+      <c r="D31" s="53"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -5125,7 +5125,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
-      <c r="D32" s="51"/>
+      <c r="D32" s="53"/>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
@@ -5137,7 +5137,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="51"/>
+      <c r="D33" s="53"/>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
       <c r="G33" s="10"/>
@@ -5149,7 +5149,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="11"/>
-      <c r="D34" s="51"/>
+      <c r="D34" s="53"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -5161,7 +5161,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="51"/>
+      <c r="D35" s="53"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -5173,7 +5173,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="51"/>
+      <c r="D36" s="53"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -5185,7 +5185,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="51"/>
+      <c r="D37" s="53"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -5197,7 +5197,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="51"/>
+      <c r="D38" s="53"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -5209,7 +5209,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="51"/>
+      <c r="D39" s="53"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -5221,7 +5221,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="51"/>
+      <c r="D40" s="53"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -5233,7 +5233,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="51"/>
+      <c r="D41" s="53"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -5245,7 +5245,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="51"/>
+      <c r="D42" s="53"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -5257,7 +5257,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="51"/>
+      <c r="D43" s="53"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -5269,7 +5269,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="51"/>
+      <c r="D44" s="53"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -5281,7 +5281,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="51"/>
+      <c r="D45" s="53"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -5293,7 +5293,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="51"/>
+      <c r="D46" s="53"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -5305,7 +5305,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="51"/>
+      <c r="D47" s="53"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -5317,7 +5317,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="51"/>
+      <c r="D48" s="53"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -5329,7 +5329,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="51"/>
+      <c r="D49" s="53"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -5341,7 +5341,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="51"/>
+      <c r="D50" s="53"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -5353,7 +5353,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="51"/>
+      <c r="D51" s="53"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -5365,7 +5365,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="51"/>
+      <c r="D52" s="53"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -5377,7 +5377,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="51"/>
+      <c r="D53" s="53"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -5389,7 +5389,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="51"/>
+      <c r="D54" s="53"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -5401,7 +5401,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="51"/>
+      <c r="D55" s="53"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -5413,7 +5413,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="51"/>
+      <c r="D56" s="53"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -6335,6 +6335,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="H16:H22"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="D3:D56"/>
     <mergeCell ref="A1:B1"/>
@@ -6351,7 +6352,6 @@
     <mergeCell ref="E16:E22"/>
     <mergeCell ref="F16:F22"/>
     <mergeCell ref="G16:G22"/>
-    <mergeCell ref="H16:H22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6375,30 +6375,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="58" t="s">
+      <c r="D1" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="60" t="s">
+      <c r="E1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="60" t="s">
+      <c r="F1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="61" t="s">
+      <c r="G1" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="62"/>
+      <c r="H1" s="65"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="45" t="s">
+      <c r="J1" s="46" t="s">
         <v>0</v>
       </c>
     </row>
@@ -6409,10 +6409,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -6420,51 +6420,51 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="45"/>
+      <c r="J2" s="46"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="46"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="50" t="s">
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="E3" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="52" t="s">
+      <c r="F3" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="53" t="s">
+      <c r="G3" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="53" t="s">
+      <c r="H3" s="56" t="s">
         <v>58</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="42"/>
+      <c r="J3" s="48"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="42"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
       <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="42"/>
+      <c r="J4" s="48"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="10"/>
       <c r="C5" s="11"/>
-      <c r="D5" s="51"/>
+      <c r="D5" s="53"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
@@ -6480,7 +6480,7 @@
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
       <c r="C6" s="11"/>
-      <c r="D6" s="51"/>
+      <c r="D6" s="53"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
@@ -6494,7 +6494,7 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="51"/>
+      <c r="D7" s="53"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
@@ -6508,7 +6508,7 @@
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="51"/>
+      <c r="D8" s="53"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
@@ -6524,7 +6524,7 @@
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="51"/>
+      <c r="D9" s="53"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -6540,7 +6540,7 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="51"/>
+      <c r="D10" s="53"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -6556,7 +6556,7 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="51"/>
+      <c r="D11" s="53"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -6572,7 +6572,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="51"/>
+      <c r="D12" s="53"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -6584,7 +6584,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="51"/>
+      <c r="D13" s="53"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -6598,7 +6598,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="51"/>
+      <c r="D14" s="53"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -6610,7 +6610,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="51"/>
+      <c r="D15" s="53"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
@@ -6624,7 +6624,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="51"/>
+      <c r="D16" s="53"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -6633,94 +6633,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="43"/>
-      <c r="B17" s="43"/>
+      <c r="A17" s="67"/>
+      <c r="B17" s="67"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="42"/>
+      <c r="J17" s="48"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="43"/>
-      <c r="B18" s="43"/>
+      <c r="A18" s="67"/>
+      <c r="B18" s="67"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="42"/>
+      <c r="J18" s="48"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="43"/>
-      <c r="B19" s="43"/>
+      <c r="A19" s="67"/>
+      <c r="B19" s="67"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="42"/>
+      <c r="J19" s="48"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="43"/>
-      <c r="B20" s="43"/>
+      <c r="A20" s="67"/>
+      <c r="B20" s="67"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="42"/>
+      <c r="J20" s="48"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="43"/>
-      <c r="B21" s="43"/>
+      <c r="A21" s="67"/>
+      <c r="B21" s="67"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="42"/>
+      <c r="J21" s="48"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="43"/>
-      <c r="B22" s="43"/>
+      <c r="A22" s="67"/>
+      <c r="B22" s="67"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="42"/>
+      <c r="J22" s="48"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="43"/>
-      <c r="B23" s="43"/>
+      <c r="A23" s="67"/>
+      <c r="B23" s="67"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="48"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="42"/>
+      <c r="J23" s="48"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="51"/>
+      <c r="D24" s="53"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -6732,7 +6732,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="51"/>
+      <c r="D25" s="53"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -6744,7 +6744,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="51"/>
+      <c r="D26" s="53"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -6756,7 +6756,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="51"/>
+      <c r="D27" s="53"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -6768,7 +6768,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="51"/>
+      <c r="D28" s="53"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -6780,7 +6780,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="51"/>
+      <c r="D29" s="53"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -6792,7 +6792,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="51"/>
+      <c r="D30" s="53"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -6804,7 +6804,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="51"/>
+      <c r="D31" s="53"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -6816,7 +6816,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="51"/>
+      <c r="D32" s="53"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -6828,7 +6828,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="51"/>
+      <c r="D33" s="53"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -6840,7 +6840,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="51"/>
+      <c r="D34" s="53"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -6852,7 +6852,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="51"/>
+      <c r="D35" s="53"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -6864,7 +6864,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="51"/>
+      <c r="D36" s="53"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -6876,7 +6876,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="51"/>
+      <c r="D37" s="53"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -6888,7 +6888,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="51"/>
+      <c r="D38" s="53"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -6900,7 +6900,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="51"/>
+      <c r="D39" s="53"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -6912,7 +6912,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="51"/>
+      <c r="D40" s="53"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -6924,7 +6924,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="51"/>
+      <c r="D41" s="53"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -6936,7 +6936,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="51"/>
+      <c r="D42" s="53"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -6948,7 +6948,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="51"/>
+      <c r="D43" s="53"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -6960,7 +6960,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="51"/>
+      <c r="D44" s="53"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -6972,7 +6972,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="51"/>
+      <c r="D45" s="53"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -6984,7 +6984,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="51"/>
+      <c r="D46" s="53"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -6996,7 +6996,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="51"/>
+      <c r="D47" s="53"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -7008,7 +7008,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="51"/>
+      <c r="D48" s="53"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -7020,7 +7020,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="51"/>
+      <c r="D49" s="53"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -7032,7 +7032,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="51"/>
+      <c r="D50" s="53"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -7044,7 +7044,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="51"/>
+      <c r="D51" s="53"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -7056,7 +7056,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="51"/>
+      <c r="D52" s="53"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -7068,7 +7068,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="51"/>
+      <c r="D53" s="53"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -7080,7 +7080,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="51"/>
+      <c r="D54" s="53"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -7092,7 +7092,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="51"/>
+      <c r="D55" s="53"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -7104,7 +7104,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="51"/>
+      <c r="D56" s="53"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -7116,7 +7116,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="51"/>
+      <c r="D57" s="53"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -8038,6 +8038,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -8054,13 +8061,6 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8084,30 +8084,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="58" t="s">
+      <c r="D1" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="60" t="s">
+      <c r="E1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="60" t="s">
+      <c r="F1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="61" t="s">
+      <c r="G1" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="62"/>
+      <c r="H1" s="65"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="45" t="s">
+      <c r="J1" s="46" t="s">
         <v>0</v>
       </c>
     </row>
@@ -8118,10 +8118,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -8129,51 +8129,51 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="45"/>
+      <c r="J2" s="46"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="46"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="50" t="s">
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="E3" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="52" t="s">
+      <c r="F3" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="53" t="s">
+      <c r="G3" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="53" t="s">
+      <c r="H3" s="56" t="s">
         <v>62</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="42"/>
+      <c r="J3" s="48"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="42"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
       <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="42"/>
+      <c r="J4" s="48"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="10"/>
       <c r="C5" s="11"/>
-      <c r="D5" s="51"/>
+      <c r="D5" s="53"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
@@ -8189,7 +8189,7 @@
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
       <c r="C6" s="11"/>
-      <c r="D6" s="51"/>
+      <c r="D6" s="53"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
@@ -8203,7 +8203,7 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="51"/>
+      <c r="D7" s="53"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
@@ -8215,7 +8215,7 @@
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="51"/>
+      <c r="D8" s="53"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
@@ -8229,7 +8229,7 @@
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="51"/>
+      <c r="D9" s="53"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -8243,7 +8243,7 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="51"/>
+      <c r="D10" s="53"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -8257,7 +8257,7 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="51"/>
+      <c r="D11" s="53"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -8271,7 +8271,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="51"/>
+      <c r="D12" s="53"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -8283,7 +8283,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="51"/>
+      <c r="D13" s="53"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -8297,7 +8297,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="51"/>
+      <c r="D14" s="53"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -8309,7 +8309,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="51"/>
+      <c r="D15" s="53"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
@@ -8323,7 +8323,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="51"/>
+      <c r="D16" s="53"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -8332,94 +8332,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="43"/>
-      <c r="B17" s="43"/>
+      <c r="A17" s="67"/>
+      <c r="B17" s="67"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="42"/>
+      <c r="J17" s="48"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="43"/>
-      <c r="B18" s="43"/>
+      <c r="A18" s="67"/>
+      <c r="B18" s="67"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="42"/>
+      <c r="J18" s="48"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="43"/>
-      <c r="B19" s="43"/>
+      <c r="A19" s="67"/>
+      <c r="B19" s="67"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="42"/>
+      <c r="J19" s="48"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="43"/>
-      <c r="B20" s="43"/>
+      <c r="A20" s="67"/>
+      <c r="B20" s="67"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="42"/>
+      <c r="J20" s="48"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="43"/>
-      <c r="B21" s="43"/>
+      <c r="A21" s="67"/>
+      <c r="B21" s="67"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="42"/>
+      <c r="J21" s="48"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="43"/>
-      <c r="B22" s="43"/>
+      <c r="A22" s="67"/>
+      <c r="B22" s="67"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="42"/>
+      <c r="J22" s="48"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="43"/>
-      <c r="B23" s="43"/>
+      <c r="A23" s="67"/>
+      <c r="B23" s="67"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="48"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="42"/>
+      <c r="J23" s="48"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="51"/>
+      <c r="D24" s="53"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -8431,7 +8431,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="51"/>
+      <c r="D25" s="53"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -8443,7 +8443,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="51"/>
+      <c r="D26" s="53"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -8455,7 +8455,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="51"/>
+      <c r="D27" s="53"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -8467,7 +8467,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="51"/>
+      <c r="D28" s="53"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -8479,7 +8479,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="51"/>
+      <c r="D29" s="53"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -8491,7 +8491,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="51"/>
+      <c r="D30" s="53"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -8503,7 +8503,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="51"/>
+      <c r="D31" s="53"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -8515,7 +8515,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="51"/>
+      <c r="D32" s="53"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -8527,7 +8527,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="51"/>
+      <c r="D33" s="53"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -8539,7 +8539,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="51"/>
+      <c r="D34" s="53"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -8551,7 +8551,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="51"/>
+      <c r="D35" s="53"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -8563,7 +8563,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="51"/>
+      <c r="D36" s="53"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -8575,7 +8575,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="51"/>
+      <c r="D37" s="53"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -8587,7 +8587,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="51"/>
+      <c r="D38" s="53"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -8599,7 +8599,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="51"/>
+      <c r="D39" s="53"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -8611,7 +8611,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="51"/>
+      <c r="D40" s="53"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -8623,7 +8623,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="51"/>
+      <c r="D41" s="53"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -8635,7 +8635,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="51"/>
+      <c r="D42" s="53"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -8647,7 +8647,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="51"/>
+      <c r="D43" s="53"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -8659,7 +8659,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="51"/>
+      <c r="D44" s="53"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -8671,7 +8671,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="51"/>
+      <c r="D45" s="53"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -8683,7 +8683,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="51"/>
+      <c r="D46" s="53"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -8695,7 +8695,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="51"/>
+      <c r="D47" s="53"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -8707,7 +8707,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="51"/>
+      <c r="D48" s="53"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -8719,7 +8719,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="51"/>
+      <c r="D49" s="53"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -8731,7 +8731,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="51"/>
+      <c r="D50" s="53"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -8743,7 +8743,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="51"/>
+      <c r="D51" s="53"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -8755,7 +8755,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="51"/>
+      <c r="D52" s="53"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -8767,7 +8767,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="51"/>
+      <c r="D53" s="53"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -8779,7 +8779,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="51"/>
+      <c r="D54" s="53"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -8791,7 +8791,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="51"/>
+      <c r="D55" s="53"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -8803,7 +8803,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="51"/>
+      <c r="D56" s="53"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -8815,7 +8815,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="51"/>
+      <c r="D57" s="53"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -9737,6 +9737,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -9753,13 +9760,6 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9783,30 +9783,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="58" t="s">
+      <c r="D1" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="60" t="s">
+      <c r="E1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="60" t="s">
+      <c r="F1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="61" t="s">
+      <c r="G1" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="62"/>
+      <c r="H1" s="65"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="45" t="s">
+      <c r="J1" s="46" t="s">
         <v>0</v>
       </c>
     </row>
@@ -9817,10 +9817,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -9828,7 +9828,7 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="45"/>
+      <c r="J2" s="46"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A3" t="s">
@@ -9840,13 +9840,13 @@
       <c r="C3" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="E3" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="52" t="s">
+      <c r="F3" s="55" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="25" t="s">
@@ -9867,9 +9867,9 @@
       <c r="C4" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D4" s="51"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="52"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="55"/>
       <c r="G4" s="21"/>
       <c r="H4" s="4" t="s">
         <v>65</v>
@@ -9886,7 +9886,7 @@
       <c r="C5" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="51"/>
+      <c r="D5" s="53"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="4"/>
@@ -9903,7 +9903,7 @@
       <c r="C6" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D6" s="51"/>
+      <c r="D6" s="53"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="4"/>
@@ -9917,7 +9917,7 @@
       <c r="C7" s="38" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="51"/>
+      <c r="D7" s="53"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="4"/>
@@ -9935,7 +9935,7 @@
       <c r="C8" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="D8" s="51"/>
+      <c r="D8" s="53"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="4"/>
@@ -9953,7 +9953,7 @@
       <c r="C9" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="D9" s="51"/>
+      <c r="D9" s="53"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="4"/>
@@ -9968,48 +9968,48 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="15">
-      <c r="C10" s="65" t="s">
+      <c r="C10" s="70" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="51"/>
+      <c r="D10" s="53"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="4"/>
-      <c r="H10" s="66" t="s">
+      <c r="H10" s="71" t="s">
         <v>72</v>
       </c>
       <c r="I10" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="J10" s="67"/>
+      <c r="J10" s="72"/>
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1">
-      <c r="C11" s="65"/>
-      <c r="D11" s="51"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="53"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="4"/>
-      <c r="H11" s="66"/>
+      <c r="H11" s="71"/>
       <c r="I11" s="21"/>
-      <c r="J11" s="67"/>
+      <c r="J11" s="72"/>
     </row>
     <row r="12" spans="1:10" ht="15">
-      <c r="C12" s="65"/>
-      <c r="D12" s="51"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="53"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="66"/>
+      <c r="H12" s="71"/>
       <c r="I12" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="67"/>
+      <c r="J12" s="72"/>
     </row>
     <row r="13" spans="1:10" ht="45">
       <c r="C13" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="D13" s="51"/>
+      <c r="D13" s="53"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="4"/>
@@ -10026,7 +10026,7 @@
       <c r="C14" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D14" s="51"/>
+      <c r="D14" s="53"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="4"/>
@@ -10042,7 +10042,7 @@
       <c r="C15" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="D15" s="51"/>
+      <c r="D15" s="53"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="4"/>
@@ -10053,7 +10053,7 @@
       <c r="J15" s="4"/>
     </row>
     <row r="16" spans="1:10" ht="15">
-      <c r="D16" s="51"/>
+      <c r="D16" s="53"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -10062,9 +10062,9 @@
       <c r="J16" s="33"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="D17" s="51"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
       <c r="G17" s="33"/>
       <c r="H17" s="33"/>
       <c r="I17" s="21"/>
@@ -10078,9 +10078,9 @@
         <v>74</v>
       </c>
       <c r="C18" s="7"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
       <c r="G18" s="33"/>
       <c r="H18" s="33"/>
       <c r="I18" s="21"/>
@@ -10093,9 +10093,9 @@
       <c r="C19" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="51"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
       <c r="G19" s="33"/>
       <c r="H19" s="33"/>
       <c r="I19" s="21"/>
@@ -10106,9 +10106,9 @@
         <v>76</v>
       </c>
       <c r="C20" s="7"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
       <c r="G20" s="33"/>
       <c r="H20" s="33"/>
       <c r="I20" s="21"/>
@@ -10119,9 +10119,9 @@
         <v>77</v>
       </c>
       <c r="C21" s="7"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
       <c r="G21" s="33"/>
       <c r="H21" s="33"/>
       <c r="I21" s="21"/>
@@ -10132,9 +10132,9 @@
         <v>78</v>
       </c>
       <c r="C22" s="7"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
       <c r="G22" s="33"/>
       <c r="H22" s="33"/>
       <c r="I22" s="21"/>
@@ -10142,9 +10142,9 @@
     </row>
     <row r="23" spans="1:10" ht="15">
       <c r="C23" s="7"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
       <c r="G23" s="33"/>
       <c r="H23" s="33"/>
       <c r="I23" s="21"/>
@@ -10158,7 +10158,7 @@
         <v>74</v>
       </c>
       <c r="C24" s="7"/>
-      <c r="D24" s="51"/>
+      <c r="D24" s="53"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
       <c r="G24" s="21"/>
@@ -10171,7 +10171,7 @@
         <v>79</v>
       </c>
       <c r="C25" s="8"/>
-      <c r="D25" s="51"/>
+      <c r="D25" s="53"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="4"/>
@@ -10184,7 +10184,7 @@
         <v>64</v>
       </c>
       <c r="C26" s="8"/>
-      <c r="D26" s="51"/>
+      <c r="D26" s="53"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -10197,7 +10197,7 @@
         <v>80</v>
       </c>
       <c r="C27" s="8"/>
-      <c r="D27" s="51"/>
+      <c r="D27" s="53"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
@@ -10207,7 +10207,7 @@
     </row>
     <row r="28" spans="1:10" ht="15">
       <c r="C28" s="8"/>
-      <c r="D28" s="51"/>
+      <c r="D28" s="53"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -10223,7 +10223,7 @@
         <v>64</v>
       </c>
       <c r="C29" s="8"/>
-      <c r="D29" s="51"/>
+      <c r="D29" s="53"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -10236,7 +10236,7 @@
         <v>79</v>
       </c>
       <c r="C30" s="8"/>
-      <c r="D30" s="51"/>
+      <c r="D30" s="53"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="4"/>
@@ -10249,7 +10249,7 @@
         <v>81</v>
       </c>
       <c r="C31" s="8"/>
-      <c r="D31" s="51"/>
+      <c r="D31" s="53"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="4"/>
@@ -10262,7 +10262,7 @@
         <v>82</v>
       </c>
       <c r="C32" s="7"/>
-      <c r="D32" s="51"/>
+      <c r="D32" s="53"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="4"/>
@@ -10275,7 +10275,7 @@
         <v>83</v>
       </c>
       <c r="C33" s="7"/>
-      <c r="D33" s="51"/>
+      <c r="D33" s="53"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
@@ -10288,7 +10288,7 @@
         <v>84</v>
       </c>
       <c r="C34" s="7"/>
-      <c r="D34" s="51"/>
+      <c r="D34" s="53"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
       <c r="G34" s="4"/>
@@ -10301,7 +10301,7 @@
         <v>85</v>
       </c>
       <c r="C35" s="7"/>
-      <c r="D35" s="51"/>
+      <c r="D35" s="53"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
       <c r="G35" s="4"/>
@@ -10314,7 +10314,7 @@
         <v>86</v>
       </c>
       <c r="C36" s="7"/>
-      <c r="D36" s="51"/>
+      <c r="D36" s="53"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="4"/>
@@ -10326,7 +10326,7 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="51"/>
+      <c r="D37" s="53"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="4"/>
@@ -10342,7 +10342,7 @@
         <v>116</v>
       </c>
       <c r="C38" s="7"/>
-      <c r="D38" s="51"/>
+      <c r="D38" s="53"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="4"/>
@@ -10355,7 +10355,7 @@
         <v>117</v>
       </c>
       <c r="C39" s="7"/>
-      <c r="D39" s="51"/>
+      <c r="D39" s="53"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="4"/>
@@ -10366,7 +10366,7 @@
     <row r="40" spans="1:10" ht="15">
       <c r="B40" s="4"/>
       <c r="C40" s="7"/>
-      <c r="D40" s="51"/>
+      <c r="D40" s="53"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="4"/>
@@ -10377,7 +10377,7 @@
     <row r="41" spans="1:10" ht="15">
       <c r="B41" s="4"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="51"/>
+      <c r="D41" s="53"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="4"/>
@@ -10389,7 +10389,7 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="51"/>
+      <c r="D42" s="53"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="4"/>
@@ -10401,7 +10401,7 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="51"/>
+      <c r="D43" s="53"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="4"/>
@@ -10413,7 +10413,7 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="7"/>
-      <c r="D44" s="51"/>
+      <c r="D44" s="53"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="4"/>
@@ -10425,7 +10425,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="51"/>
+      <c r="D45" s="53"/>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
       <c r="G45" s="4"/>
@@ -10437,7 +10437,7 @@
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="7"/>
-      <c r="D46" s="51"/>
+      <c r="D46" s="53"/>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
       <c r="G46" s="4"/>
@@ -10449,7 +10449,7 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="7"/>
-      <c r="D47" s="51"/>
+      <c r="D47" s="53"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
       <c r="G47" s="4"/>
@@ -10461,7 +10461,7 @@
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="7"/>
-      <c r="D48" s="51"/>
+      <c r="D48" s="53"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
       <c r="G48" s="4"/>
@@ -10473,7 +10473,7 @@
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="7"/>
-      <c r="D49" s="51"/>
+      <c r="D49" s="53"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
       <c r="G49" s="4"/>
@@ -10485,7 +10485,7 @@
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="51"/>
+      <c r="D50" s="53"/>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
       <c r="G50" s="4"/>
@@ -10497,7 +10497,7 @@
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="7"/>
-      <c r="D51" s="51"/>
+      <c r="D51" s="53"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
       <c r="G51" s="4"/>
@@ -10509,7 +10509,7 @@
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="7"/>
-      <c r="D52" s="51"/>
+      <c r="D52" s="53"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
       <c r="G52" s="4"/>
@@ -10521,7 +10521,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="51"/>
+      <c r="D53" s="53"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="4"/>
@@ -10533,7 +10533,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="51"/>
+      <c r="D54" s="53"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
       <c r="G54" s="4"/>
@@ -10545,7 +10545,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="7"/>
-      <c r="D55" s="51"/>
+      <c r="D55" s="53"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
       <c r="G55" s="4"/>
@@ -10557,7 +10557,7 @@
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="7"/>
-      <c r="D56" s="51"/>
+      <c r="D56" s="53"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
       <c r="G56" s="4"/>
@@ -10569,7 +10569,7 @@
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="7"/>
-      <c r="D57" s="51"/>
+      <c r="D57" s="53"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
       <c r="G57" s="4"/>
@@ -11525,27 +11525,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="58" t="s">
+      <c r="D1" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="60" t="s">
+      <c r="E1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="60" t="s">
+      <c r="F1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="61" t="s">
+      <c r="G1" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="62"/>
-      <c r="I1" s="45" t="s">
+      <c r="H1" s="65"/>
+      <c r="I1" s="46" t="s">
         <v>0</v>
       </c>
     </row>
@@ -11556,17 +11556,17 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="45"/>
+      <c r="I2" s="46"/>
     </row>
     <row r="3" spans="1:9" ht="15">
       <c r="A3" s="14" t="s">
@@ -11578,18 +11578,18 @@
       <c r="C3" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="44"/>
-      <c r="F3" s="52"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="55"/>
       <c r="G3" s="14" t="s">
         <v>87</v>
       </c>
       <c r="H3" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="I3" s="42"/>
+      <c r="I3" s="48"/>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1">
       <c r="A4" s="14"/>
@@ -11599,20 +11599,20 @@
       <c r="C4" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="D4" s="51"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="52"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="55"/>
       <c r="G4" s="13"/>
       <c r="H4" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="I4" s="42"/>
+      <c r="I4" s="48"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1">
       <c r="A5" s="25"/>
       <c r="B5" s="25"/>
       <c r="C5" s="20"/>
-      <c r="D5" s="51"/>
+      <c r="D5" s="53"/>
       <c r="E5" s="22"/>
       <c r="F5" s="24"/>
       <c r="G5" s="21"/>
@@ -11629,7 +11629,7 @@
       <c r="C6" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="D6" s="51"/>
+      <c r="D6" s="53"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="4"/>
@@ -11644,7 +11644,7 @@
       <c r="C7" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="D7" s="51"/>
+      <c r="D7" s="53"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="4"/>
@@ -11657,7 +11657,7 @@
       <c r="C8" t="s">
         <v>123</v>
       </c>
-      <c r="D8" s="51"/>
+      <c r="D8" s="53"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="4"/>
@@ -11670,7 +11670,7 @@
       <c r="C9" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="D9" s="51"/>
+      <c r="D9" s="53"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="4"/>
@@ -11683,7 +11683,7 @@
       <c r="C10" s="40" t="s">
         <v>128</v>
       </c>
-      <c r="D10" s="51"/>
+      <c r="D10" s="53"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="4"/>
@@ -11697,7 +11697,7 @@
       <c r="B11" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="51"/>
+      <c r="D11" s="53"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="4"/>
@@ -11705,7 +11705,7 @@
     </row>
     <row r="12" spans="1:9" ht="15">
       <c r="A12" s="14"/>
-      <c r="D12" s="51"/>
+      <c r="D12" s="53"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="4"/>
@@ -11719,7 +11719,7 @@
       <c r="B13" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="51"/>
+      <c r="D13" s="53"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="4"/>
@@ -11731,7 +11731,7 @@
       <c r="B14" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="51"/>
+      <c r="D14" s="53"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="4"/>
@@ -11744,7 +11744,7 @@
         <v>64</v>
       </c>
       <c r="C15" s="7"/>
-      <c r="D15" s="51"/>
+      <c r="D15" s="53"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="4"/>
@@ -11757,7 +11757,7 @@
         <v>80</v>
       </c>
       <c r="C16" s="7"/>
-      <c r="D16" s="51"/>
+      <c r="D16" s="53"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="4"/>
@@ -11767,7 +11767,7 @@
     <row r="17" spans="1:9" ht="15">
       <c r="A17" s="21"/>
       <c r="C17" s="7"/>
-      <c r="D17" s="51"/>
+      <c r="D17" s="53"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="21"/>
@@ -11777,74 +11777,74 @@
     <row r="18" spans="1:9" ht="15">
       <c r="A18" s="21"/>
       <c r="C18" s="7"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
       <c r="G18" s="33"/>
       <c r="H18" s="33"/>
-      <c r="I18" s="42"/>
+      <c r="I18" s="48"/>
     </row>
     <row r="19" spans="1:9" ht="15">
       <c r="C19" s="4"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
       <c r="G19" s="33"/>
       <c r="H19" s="33"/>
-      <c r="I19" s="42"/>
+      <c r="I19" s="48"/>
     </row>
     <row r="20" spans="1:9" ht="15">
       <c r="C20" s="7"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
       <c r="G20" s="33"/>
       <c r="H20" s="33"/>
-      <c r="I20" s="42"/>
+      <c r="I20" s="48"/>
     </row>
     <row r="21" spans="1:9" ht="15">
       <c r="C21" s="4"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
       <c r="G21" s="33"/>
       <c r="H21" s="33"/>
-      <c r="I21" s="42"/>
+      <c r="I21" s="48"/>
     </row>
     <row r="22" spans="1:9" ht="15">
       <c r="C22" s="7"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
       <c r="G22" s="33"/>
       <c r="H22" s="33"/>
-      <c r="I22" s="42"/>
+      <c r="I22" s="48"/>
     </row>
     <row r="23" spans="1:9" ht="15">
       <c r="C23" s="7"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
       <c r="G23" s="33"/>
       <c r="H23" s="33"/>
-      <c r="I23" s="42"/>
+      <c r="I23" s="48"/>
     </row>
     <row r="24" spans="1:9" ht="15">
       <c r="A24" s="15"/>
       <c r="B24" s="15"/>
       <c r="C24" s="8"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
       <c r="G24" s="33"/>
       <c r="H24" s="21"/>
-      <c r="I24" s="42"/>
+      <c r="I24" s="48"/>
     </row>
     <row r="25" spans="1:9" ht="15">
       <c r="A25" s="4"/>
       <c r="B25" s="15"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="51"/>
+      <c r="D25" s="53"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="4"/>
@@ -11855,7 +11855,7 @@
       <c r="A26" s="4"/>
       <c r="B26" s="15"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="51"/>
+      <c r="D26" s="53"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
       <c r="G26" s="4"/>
@@ -11866,7 +11866,7 @@
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="7"/>
-      <c r="D27" s="51"/>
+      <c r="D27" s="53"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
@@ -11877,7 +11877,7 @@
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="51"/>
+      <c r="D28" s="53"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -11888,7 +11888,7 @@
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="51"/>
+      <c r="D29" s="53"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -11899,7 +11899,7 @@
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="51"/>
+      <c r="D30" s="53"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
@@ -11910,7 +11910,7 @@
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="51"/>
+      <c r="D31" s="53"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="4"/>
@@ -11921,7 +11921,7 @@
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="7"/>
-      <c r="D32" s="51"/>
+      <c r="D32" s="53"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="4"/>
@@ -11932,7 +11932,7 @@
       <c r="A33" s="4"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="51"/>
+      <c r="D33" s="53"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
       <c r="G33" s="4"/>
@@ -11943,7 +11943,7 @@
       <c r="A34" s="4"/>
       <c r="B34" s="7"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="51"/>
+      <c r="D34" s="53"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
@@ -11954,7 +11954,7 @@
       <c r="A35" s="4"/>
       <c r="B35" s="7"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="51"/>
+      <c r="D35" s="53"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
       <c r="G35" s="4"/>
@@ -11965,7 +11965,7 @@
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="7"/>
-      <c r="D36" s="51"/>
+      <c r="D36" s="53"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="4"/>
@@ -11976,7 +11976,7 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="51"/>
+      <c r="D37" s="53"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="4"/>
@@ -11987,7 +11987,7 @@
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="7"/>
-      <c r="D38" s="51"/>
+      <c r="D38" s="53"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="4"/>
@@ -11998,7 +11998,7 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="7"/>
-      <c r="D39" s="51"/>
+      <c r="D39" s="53"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="4"/>
@@ -12009,7 +12009,7 @@
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="7"/>
-      <c r="D40" s="51"/>
+      <c r="D40" s="53"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="4"/>
@@ -12020,7 +12020,7 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="51"/>
+      <c r="D41" s="53"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="4"/>
@@ -12031,7 +12031,7 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="51"/>
+      <c r="D42" s="53"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="4"/>
@@ -12042,7 +12042,7 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="51"/>
+      <c r="D43" s="53"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="4"/>
@@ -12053,7 +12053,7 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="7"/>
-      <c r="D44" s="51"/>
+      <c r="D44" s="53"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="4"/>
@@ -12064,7 +12064,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="51"/>
+      <c r="D45" s="53"/>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
       <c r="G45" s="4"/>
@@ -12075,7 +12075,7 @@
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="7"/>
-      <c r="D46" s="51"/>
+      <c r="D46" s="53"/>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
       <c r="G46" s="4"/>
@@ -12086,7 +12086,7 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="7"/>
-      <c r="D47" s="51"/>
+      <c r="D47" s="53"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
       <c r="G47" s="4"/>
@@ -12097,7 +12097,7 @@
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="7"/>
-      <c r="D48" s="51"/>
+      <c r="D48" s="53"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
       <c r="G48" s="4"/>
@@ -12108,7 +12108,7 @@
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="7"/>
-      <c r="D49" s="51"/>
+      <c r="D49" s="53"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
       <c r="G49" s="4"/>
@@ -12119,7 +12119,7 @@
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="51"/>
+      <c r="D50" s="53"/>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
       <c r="G50" s="4"/>
@@ -12130,7 +12130,7 @@
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="7"/>
-      <c r="D51" s="51"/>
+      <c r="D51" s="53"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
       <c r="G51" s="4"/>
@@ -12141,7 +12141,7 @@
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="7"/>
-      <c r="D52" s="51"/>
+      <c r="D52" s="53"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
       <c r="G52" s="4"/>
@@ -12152,7 +12152,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="51"/>
+      <c r="D53" s="53"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="4"/>
@@ -12163,7 +12163,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="51"/>
+      <c r="D54" s="53"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
       <c r="G54" s="4"/>
@@ -12174,7 +12174,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="7"/>
-      <c r="D55" s="51"/>
+      <c r="D55" s="53"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
       <c r="G55" s="4"/>
@@ -12185,7 +12185,7 @@
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="7"/>
-      <c r="D56" s="51"/>
+      <c r="D56" s="53"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
       <c r="G56" s="4"/>
@@ -12196,7 +12196,7 @@
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="7"/>
-      <c r="D57" s="51"/>
+      <c r="D57" s="53"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
       <c r="G57" s="4"/>
@@ -12207,7 +12207,7 @@
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="7"/>
-      <c r="D58" s="51"/>
+      <c r="D58" s="53"/>
       <c r="E58" s="7"/>
       <c r="F58" s="7"/>
       <c r="G58" s="4"/>
@@ -13057,11 +13057,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="D3:D58"/>
     <mergeCell ref="E3:E4"/>
@@ -13071,6 +13066,11 @@
     <mergeCell ref="I18:I24"/>
     <mergeCell ref="E18:E24"/>
     <mergeCell ref="F18:F24"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13092,27 +13092,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="58" t="s">
+      <c r="D1" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="60" t="s">
+      <c r="E1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="60" t="s">
+      <c r="F1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="61" t="s">
+      <c r="G1" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="62"/>
-      <c r="I1" s="45" t="s">
+      <c r="H1" s="65"/>
+      <c r="I1" s="46" t="s">
         <v>0</v>
       </c>
     </row>
@@ -13123,17 +13123,17 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="45"/>
+      <c r="I2" s="46"/>
     </row>
     <row r="3" spans="1:9" ht="15">
       <c r="A3" s="19" t="s">
@@ -13145,18 +13145,18 @@
       <c r="C3" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="44"/>
-      <c r="F3" s="52"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="55"/>
       <c r="G3" s="19" t="s">
         <v>97</v>
       </c>
       <c r="H3" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="I3" s="42"/>
+      <c r="I3" s="48"/>
     </row>
     <row r="4" spans="1:9" ht="14.25" customHeight="1">
       <c r="A4" s="19"/>
@@ -13166,18 +13166,18 @@
       <c r="C4" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="D4" s="51"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="52"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="55"/>
       <c r="G4" s="16"/>
       <c r="H4" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="42"/>
+      <c r="I4" s="48"/>
     </row>
     <row r="5" spans="1:9" ht="15">
       <c r="C5" s="18"/>
-      <c r="D5" s="51"/>
+      <c r="D5" s="53"/>
       <c r="E5" s="18"/>
       <c r="F5" s="18"/>
       <c r="G5" s="16"/>
@@ -13190,7 +13190,7 @@
       <c r="C6" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="D6" s="51"/>
+      <c r="D6" s="53"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
       <c r="G6" s="16"/>
@@ -13203,7 +13203,7 @@
       <c r="C7" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="D7" s="51"/>
+      <c r="D7" s="53"/>
       <c r="E7" s="18"/>
       <c r="F7" s="18"/>
       <c r="G7" s="16"/>
@@ -13216,7 +13216,7 @@
       <c r="C8" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D8" s="51"/>
+      <c r="D8" s="53"/>
       <c r="E8" s="18"/>
       <c r="F8" s="18"/>
       <c r="G8" s="16"/>
@@ -13231,7 +13231,7 @@
         <v>48</v>
       </c>
       <c r="C9" s="16"/>
-      <c r="D9" s="51"/>
+      <c r="D9" s="53"/>
       <c r="E9" s="18"/>
       <c r="F9" s="18"/>
       <c r="G9" s="16"/>
@@ -13243,7 +13243,7 @@
         <v>41</v>
       </c>
       <c r="C10" s="18"/>
-      <c r="D10" s="51"/>
+      <c r="D10" s="53"/>
       <c r="E10" s="18"/>
       <c r="F10" s="18"/>
       <c r="G10" s="16"/>
@@ -13253,7 +13253,7 @@
     <row r="11" spans="1:9" ht="15">
       <c r="A11" s="19"/>
       <c r="C11" s="16"/>
-      <c r="D11" s="51"/>
+      <c r="D11" s="53"/>
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
       <c r="G11" s="16"/>
@@ -13268,7 +13268,7 @@
         <v>41</v>
       </c>
       <c r="C12" s="18"/>
-      <c r="D12" s="51"/>
+      <c r="D12" s="53"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="16"/>
@@ -13281,7 +13281,7 @@
         <v>49</v>
       </c>
       <c r="C13" s="18"/>
-      <c r="D13" s="51"/>
+      <c r="D13" s="53"/>
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
       <c r="G13" s="16"/>
@@ -13294,7 +13294,7 @@
         <v>64</v>
       </c>
       <c r="C14" s="18"/>
-      <c r="D14" s="51"/>
+      <c r="D14" s="53"/>
       <c r="E14" s="18"/>
       <c r="F14" s="18"/>
       <c r="G14" s="16"/>
@@ -13307,7 +13307,7 @@
         <v>80</v>
       </c>
       <c r="C15" s="18"/>
-      <c r="D15" s="51"/>
+      <c r="D15" s="53"/>
       <c r="E15" s="18"/>
       <c r="F15" s="18"/>
       <c r="G15" s="16"/>
@@ -13318,7 +13318,7 @@
       <c r="A16" s="26"/>
       <c r="B16" s="26"/>
       <c r="C16" s="18"/>
-      <c r="D16" s="51"/>
+      <c r="D16" s="53"/>
       <c r="E16" s="16"/>
       <c r="F16" s="16"/>
       <c r="G16" s="16"/>
@@ -13333,12 +13333,12 @@
         <v>50</v>
       </c>
       <c r="C17" s="8"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="48"/>
     </row>
     <row r="18" spans="1:9" ht="15">
       <c r="A18" s="16"/>
@@ -13346,22 +13346,22 @@
         <v>51</v>
       </c>
       <c r="C18" s="8"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="48"/>
     </row>
     <row r="19" spans="1:9" ht="15">
       <c r="A19" s="16"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
     </row>
     <row r="20" spans="1:9" ht="15">
       <c r="A20" s="16" t="s">
@@ -13371,12 +13371,12 @@
         <v>52</v>
       </c>
       <c r="C20" s="8"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="48"/>
     </row>
     <row r="21" spans="1:9" ht="15">
       <c r="A21" s="16"/>
@@ -13384,36 +13384,36 @@
         <v>53</v>
       </c>
       <c r="C21" s="8"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="42"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="48"/>
     </row>
     <row r="22" spans="1:9" ht="15">
       <c r="C22" s="8"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="42"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="48"/>
     </row>
     <row r="23" spans="1:9" ht="15">
       <c r="C23" s="8"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="48"/>
     </row>
     <row r="24" spans="1:9" ht="15">
       <c r="A24" s="15"/>
       <c r="B24" s="15"/>
       <c r="C24" s="18"/>
-      <c r="D24" s="51"/>
+      <c r="D24" s="53"/>
       <c r="E24" s="18"/>
       <c r="F24" s="18"/>
       <c r="G24" s="16"/>
@@ -13424,7 +13424,7 @@
       <c r="A25" s="16"/>
       <c r="B25" s="16"/>
       <c r="C25" s="18"/>
-      <c r="D25" s="51"/>
+      <c r="D25" s="53"/>
       <c r="E25" s="18"/>
       <c r="F25" s="18"/>
       <c r="G25" s="16"/>
@@ -13435,7 +13435,7 @@
       <c r="A26" s="16"/>
       <c r="B26" s="16"/>
       <c r="C26" s="18"/>
-      <c r="D26" s="51"/>
+      <c r="D26" s="53"/>
       <c r="E26" s="16"/>
       <c r="F26" s="16"/>
       <c r="G26" s="16"/>
@@ -13446,7 +13446,7 @@
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
       <c r="C27" s="18"/>
-      <c r="D27" s="51"/>
+      <c r="D27" s="53"/>
       <c r="E27" s="16"/>
       <c r="F27" s="16"/>
       <c r="G27" s="16"/>
@@ -13457,7 +13457,7 @@
       <c r="A28" s="16"/>
       <c r="B28" s="16"/>
       <c r="C28" s="18"/>
-      <c r="D28" s="51"/>
+      <c r="D28" s="53"/>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
       <c r="G28" s="16"/>
@@ -13468,7 +13468,7 @@
       <c r="A29" s="16"/>
       <c r="B29" s="16"/>
       <c r="C29" s="18"/>
-      <c r="D29" s="51"/>
+      <c r="D29" s="53"/>
       <c r="E29" s="16"/>
       <c r="F29" s="16"/>
       <c r="G29" s="16"/>
@@ -13479,7 +13479,7 @@
       <c r="A30" s="16"/>
       <c r="B30" s="18"/>
       <c r="C30" s="18"/>
-      <c r="D30" s="51"/>
+      <c r="D30" s="53"/>
       <c r="E30" s="18"/>
       <c r="F30" s="18"/>
       <c r="G30" s="16"/>
@@ -13490,7 +13490,7 @@
       <c r="A31" s="16"/>
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
-      <c r="D31" s="51"/>
+      <c r="D31" s="53"/>
       <c r="E31" s="18"/>
       <c r="F31" s="18"/>
       <c r="G31" s="16"/>
@@ -13501,7 +13501,7 @@
       <c r="A32" s="16"/>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
-      <c r="D32" s="51"/>
+      <c r="D32" s="53"/>
       <c r="E32" s="18"/>
       <c r="F32" s="18"/>
       <c r="G32" s="16"/>
@@ -13512,7 +13512,7 @@
       <c r="A33" s="16"/>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
-      <c r="D33" s="51"/>
+      <c r="D33" s="53"/>
       <c r="E33" s="16"/>
       <c r="F33" s="16"/>
       <c r="G33" s="16"/>
@@ -13523,7 +13523,7 @@
       <c r="A34" s="16"/>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
-      <c r="D34" s="51"/>
+      <c r="D34" s="53"/>
       <c r="E34" s="18"/>
       <c r="F34" s="18"/>
       <c r="G34" s="16"/>
@@ -13534,7 +13534,7 @@
       <c r="A35" s="16"/>
       <c r="B35" s="16"/>
       <c r="C35" s="18"/>
-      <c r="D35" s="51"/>
+      <c r="D35" s="53"/>
       <c r="E35" s="18"/>
       <c r="F35" s="18"/>
       <c r="G35" s="16"/>
@@ -13545,7 +13545,7 @@
       <c r="A36" s="16"/>
       <c r="B36" s="16"/>
       <c r="C36" s="18"/>
-      <c r="D36" s="51"/>
+      <c r="D36" s="53"/>
       <c r="E36" s="18"/>
       <c r="F36" s="18"/>
       <c r="G36" s="16"/>
@@ -13556,7 +13556,7 @@
       <c r="A37" s="16"/>
       <c r="B37" s="16"/>
       <c r="C37" s="18"/>
-      <c r="D37" s="51"/>
+      <c r="D37" s="53"/>
       <c r="E37" s="18"/>
       <c r="F37" s="18"/>
       <c r="G37" s="16"/>
@@ -13567,7 +13567,7 @@
       <c r="A38" s="16"/>
       <c r="B38" s="16"/>
       <c r="C38" s="18"/>
-      <c r="D38" s="51"/>
+      <c r="D38" s="53"/>
       <c r="E38" s="18"/>
       <c r="F38" s="18"/>
       <c r="G38" s="16"/>
@@ -13578,7 +13578,7 @@
       <c r="A39" s="16"/>
       <c r="B39" s="16"/>
       <c r="C39" s="18"/>
-      <c r="D39" s="51"/>
+      <c r="D39" s="53"/>
       <c r="E39" s="18"/>
       <c r="F39" s="18"/>
       <c r="G39" s="16"/>
@@ -13589,7 +13589,7 @@
       <c r="A40" s="16"/>
       <c r="B40" s="16"/>
       <c r="C40" s="18"/>
-      <c r="D40" s="51"/>
+      <c r="D40" s="53"/>
       <c r="E40" s="18"/>
       <c r="F40" s="18"/>
       <c r="G40" s="16"/>
@@ -13600,7 +13600,7 @@
       <c r="A41" s="16"/>
       <c r="B41" s="16"/>
       <c r="C41" s="18"/>
-      <c r="D41" s="51"/>
+      <c r="D41" s="53"/>
       <c r="E41" s="18"/>
       <c r="F41" s="18"/>
       <c r="G41" s="16"/>
@@ -13611,7 +13611,7 @@
       <c r="A42" s="16"/>
       <c r="B42" s="16"/>
       <c r="C42" s="18"/>
-      <c r="D42" s="51"/>
+      <c r="D42" s="53"/>
       <c r="E42" s="18"/>
       <c r="F42" s="18"/>
       <c r="G42" s="16"/>
@@ -13622,7 +13622,7 @@
       <c r="A43" s="16"/>
       <c r="B43" s="16"/>
       <c r="C43" s="18"/>
-      <c r="D43" s="51"/>
+      <c r="D43" s="53"/>
       <c r="E43" s="18"/>
       <c r="F43" s="18"/>
       <c r="G43" s="16"/>
@@ -13633,7 +13633,7 @@
       <c r="A44" s="16"/>
       <c r="B44" s="16"/>
       <c r="C44" s="18"/>
-      <c r="D44" s="51"/>
+      <c r="D44" s="53"/>
       <c r="E44" s="18"/>
       <c r="F44" s="18"/>
       <c r="G44" s="16"/>
@@ -13644,7 +13644,7 @@
       <c r="A45" s="16"/>
       <c r="B45" s="16"/>
       <c r="C45" s="18"/>
-      <c r="D45" s="51"/>
+      <c r="D45" s="53"/>
       <c r="E45" s="18"/>
       <c r="F45" s="18"/>
       <c r="G45" s="16"/>
@@ -13655,7 +13655,7 @@
       <c r="A46" s="16"/>
       <c r="B46" s="16"/>
       <c r="C46" s="18"/>
-      <c r="D46" s="51"/>
+      <c r="D46" s="53"/>
       <c r="E46" s="18"/>
       <c r="F46" s="18"/>
       <c r="G46" s="16"/>
@@ -13666,7 +13666,7 @@
       <c r="A47" s="16"/>
       <c r="B47" s="16"/>
       <c r="C47" s="18"/>
-      <c r="D47" s="51"/>
+      <c r="D47" s="53"/>
       <c r="E47" s="18"/>
       <c r="F47" s="18"/>
       <c r="G47" s="16"/>
@@ -13677,7 +13677,7 @@
       <c r="A48" s="16"/>
       <c r="B48" s="16"/>
       <c r="C48" s="18"/>
-      <c r="D48" s="51"/>
+      <c r="D48" s="53"/>
       <c r="E48" s="18"/>
       <c r="F48" s="18"/>
       <c r="G48" s="16"/>
@@ -13688,7 +13688,7 @@
       <c r="A49" s="16"/>
       <c r="B49" s="16"/>
       <c r="C49" s="18"/>
-      <c r="D49" s="51"/>
+      <c r="D49" s="53"/>
       <c r="E49" s="18"/>
       <c r="F49" s="18"/>
       <c r="G49" s="16"/>
@@ -13699,7 +13699,7 @@
       <c r="A50" s="16"/>
       <c r="B50" s="16"/>
       <c r="C50" s="18"/>
-      <c r="D50" s="51"/>
+      <c r="D50" s="53"/>
       <c r="E50" s="18"/>
       <c r="F50" s="18"/>
       <c r="G50" s="16"/>
@@ -13710,7 +13710,7 @@
       <c r="A51" s="16"/>
       <c r="B51" s="16"/>
       <c r="C51" s="18"/>
-      <c r="D51" s="51"/>
+      <c r="D51" s="53"/>
       <c r="E51" s="18"/>
       <c r="F51" s="18"/>
       <c r="G51" s="16"/>
@@ -13721,7 +13721,7 @@
       <c r="A52" s="16"/>
       <c r="B52" s="16"/>
       <c r="C52" s="18"/>
-      <c r="D52" s="51"/>
+      <c r="D52" s="53"/>
       <c r="E52" s="18"/>
       <c r="F52" s="18"/>
       <c r="G52" s="16"/>
@@ -13732,7 +13732,7 @@
       <c r="A53" s="16"/>
       <c r="B53" s="16"/>
       <c r="C53" s="18"/>
-      <c r="D53" s="51"/>
+      <c r="D53" s="53"/>
       <c r="E53" s="18"/>
       <c r="F53" s="18"/>
       <c r="G53" s="16"/>
@@ -13743,7 +13743,7 @@
       <c r="A54" s="16"/>
       <c r="B54" s="16"/>
       <c r="C54" s="18"/>
-      <c r="D54" s="51"/>
+      <c r="D54" s="53"/>
       <c r="E54" s="18"/>
       <c r="F54" s="18"/>
       <c r="G54" s="16"/>
@@ -13754,7 +13754,7 @@
       <c r="A55" s="16"/>
       <c r="B55" s="16"/>
       <c r="C55" s="18"/>
-      <c r="D55" s="51"/>
+      <c r="D55" s="53"/>
       <c r="E55" s="18"/>
       <c r="F55" s="18"/>
       <c r="G55" s="16"/>
@@ -13765,7 +13765,7 @@
       <c r="A56" s="16"/>
       <c r="B56" s="16"/>
       <c r="C56" s="18"/>
-      <c r="D56" s="51"/>
+      <c r="D56" s="53"/>
       <c r="E56" s="18"/>
       <c r="F56" s="18"/>
       <c r="G56" s="16"/>
@@ -13776,7 +13776,7 @@
       <c r="A57" s="16"/>
       <c r="B57" s="16"/>
       <c r="C57" s="18"/>
-      <c r="D57" s="51"/>
+      <c r="D57" s="53"/>
       <c r="E57" s="18"/>
       <c r="F57" s="18"/>
       <c r="G57" s="16"/>
@@ -14621,6 +14621,11 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="D3:D57"/>
     <mergeCell ref="E3:E4"/>
@@ -14632,11 +14637,6 @@
     <mergeCell ref="H17:H23"/>
     <mergeCell ref="I17:I23"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Mapping Template BrotZeit.xlsx
+++ b/Mapping Template BrotZeit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alfa\Documents\Data Engineer\Projekt\BackZeit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60082A9A-A166-489E-9181-539AB3A52E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0B6E85-2CE2-4704-8C1C-867E8B58C07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{1083ED64-F082-44F9-9F2A-19C2CA2699CD}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{1083ED64-F082-44F9-9F2A-19C2CA2699CD}"/>
   </bookViews>
   <sheets>
     <sheet name="D_Filiale" sheetId="9" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="137">
   <si>
     <t>Notes</t>
   </si>
@@ -311,9 +311,6 @@
   </si>
   <si>
     <t>[FilialID] FK</t>
-  </si>
-  <si>
-    <t>[TagID] FK</t>
   </si>
   <si>
     <t>[VerkaufsvorgangID] FK</t>
@@ -830,11 +827,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -843,9 +847,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -878,10 +879,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1247,30 +1244,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="D1" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="63" t="s">
+      <c r="E1" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="63" t="s">
+      <c r="F1" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="64" t="s">
+      <c r="G1" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="65"/>
+      <c r="H1" s="67"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="46" t="s">
+      <c r="J1" s="50" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1281,10 +1278,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1292,51 +1289,51 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="46"/>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="50" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="52" t="s">
+      <c r="C3" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="54" t="s">
+      <c r="E3" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="55" t="s">
+      <c r="F3" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="56" t="s">
+      <c r="G3" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="56" t="s">
+      <c r="H3" s="58" t="s">
         <v>41</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="48"/>
+      <c r="J3" s="47"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="48"/>
-      <c r="B4" s="49"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
+      <c r="A4" s="47"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
       <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="48"/>
+      <c r="J4" s="47"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
@@ -1344,9 +1341,9 @@
         <v>44</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" s="53"/>
+        <v>99</v>
+      </c>
+      <c r="D5" s="56"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
@@ -1364,9 +1361,9 @@
         <v>45</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="D6" s="53"/>
+        <v>100</v>
+      </c>
+      <c r="D6" s="56"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
@@ -1380,16 +1377,16 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="53"/>
+      <c r="D7" s="56"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
       <c r="H7" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I7" s="10"/>
-      <c r="J7" s="66" t="s">
-        <v>102</v>
+      <c r="J7" s="46" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15">
@@ -1400,7 +1397,7 @@
         <v>46</v>
       </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="53"/>
+      <c r="D8" s="56"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
@@ -1408,13 +1405,13 @@
       <c r="I8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="66"/>
+      <c r="J8" s="46"/>
     </row>
     <row r="9" spans="1:10" ht="15">
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="53"/>
+      <c r="D9" s="56"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -1422,13 +1419,13 @@
       <c r="I9" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="66"/>
+      <c r="J9" s="46"/>
     </row>
     <row r="10" spans="1:10" ht="15">
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="53"/>
+      <c r="D10" s="56"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -1436,13 +1433,13 @@
       <c r="I10" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="66"/>
+      <c r="J10" s="46"/>
     </row>
     <row r="11" spans="1:10" ht="15">
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="53"/>
+      <c r="D11" s="56"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -1450,25 +1447,25 @@
       <c r="I11" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="66"/>
+      <c r="J11" s="46"/>
     </row>
     <row r="12" spans="1:10" ht="15">
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="53"/>
+      <c r="D12" s="56"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
-      <c r="J12" s="66"/>
+      <c r="J12" s="46"/>
     </row>
     <row r="13" spans="1:10" ht="15">
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="53"/>
+      <c r="D13" s="56"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -1482,7 +1479,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="53"/>
+      <c r="D14" s="56"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -1494,7 +1491,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="53"/>
+      <c r="D15" s="56"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
@@ -1508,7 +1505,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="53"/>
+      <c r="D16" s="56"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -1517,94 +1514,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="67"/>
-      <c r="B17" s="67"/>
+      <c r="A17" s="48"/>
+      <c r="B17" s="48"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="48"/>
+      <c r="J17" s="47"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="67"/>
-      <c r="B18" s="67"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="48"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="48"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="48"/>
+      <c r="J18" s="47"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="67"/>
-      <c r="B19" s="67"/>
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="48"/>
+      <c r="J19" s="47"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="67"/>
-      <c r="B20" s="67"/>
+      <c r="A20" s="48"/>
+      <c r="B20" s="48"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="48"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="48"/>
+      <c r="J20" s="47"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="67"/>
-      <c r="B21" s="67"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="48"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="48"/>
-      <c r="H21" s="48"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="47"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="48"/>
+      <c r="J21" s="47"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="67"/>
-      <c r="B22" s="67"/>
+      <c r="A22" s="48"/>
+      <c r="B22" s="48"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="48"/>
+      <c r="J22" s="47"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="67"/>
-      <c r="B23" s="67"/>
+      <c r="A23" s="48"/>
+      <c r="B23" s="48"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="48"/>
-      <c r="H23" s="48"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="47"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="48"/>
+      <c r="J23" s="47"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="53"/>
+      <c r="D24" s="56"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -1616,7 +1613,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="53"/>
+      <c r="D25" s="56"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -1628,7 +1625,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="53"/>
+      <c r="D26" s="56"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -1640,7 +1637,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="53"/>
+      <c r="D27" s="56"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -1652,7 +1649,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="53"/>
+      <c r="D28" s="56"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -1664,7 +1661,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="53"/>
+      <c r="D29" s="56"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -1676,7 +1673,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="53"/>
+      <c r="D30" s="56"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -1688,7 +1685,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="53"/>
+      <c r="D31" s="56"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -1700,7 +1697,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="53"/>
+      <c r="D32" s="56"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -1712,7 +1709,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="53"/>
+      <c r="D33" s="56"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -1724,7 +1721,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="53"/>
+      <c r="D34" s="56"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -1736,7 +1733,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="53"/>
+      <c r="D35" s="56"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -1748,7 +1745,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="53"/>
+      <c r="D36" s="56"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -1760,7 +1757,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="53"/>
+      <c r="D37" s="56"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -1772,7 +1769,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="53"/>
+      <c r="D38" s="56"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -1784,7 +1781,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="53"/>
+      <c r="D39" s="56"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -1796,7 +1793,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="53"/>
+      <c r="D40" s="56"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -1808,7 +1805,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="53"/>
+      <c r="D41" s="56"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -1820,7 +1817,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="53"/>
+      <c r="D42" s="56"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -1832,7 +1829,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="53"/>
+      <c r="D43" s="56"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -1844,7 +1841,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="53"/>
+      <c r="D44" s="56"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -1856,7 +1853,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="53"/>
+      <c r="D45" s="56"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -1868,7 +1865,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="53"/>
+      <c r="D46" s="56"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -1880,7 +1877,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="53"/>
+      <c r="D47" s="56"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -1892,7 +1889,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="53"/>
+      <c r="D48" s="56"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -1904,7 +1901,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="53"/>
+      <c r="D49" s="56"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -1916,7 +1913,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="53"/>
+      <c r="D50" s="56"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -1928,7 +1925,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="53"/>
+      <c r="D51" s="56"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -1940,7 +1937,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="53"/>
+      <c r="D52" s="56"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -1952,7 +1949,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="53"/>
+      <c r="D53" s="56"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -1964,7 +1961,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="53"/>
+      <c r="D54" s="56"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -1976,7 +1973,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="53"/>
+      <c r="D55" s="56"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -1988,7 +1985,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="53"/>
+      <c r="D56" s="56"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -2000,7 +1997,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="53"/>
+      <c r="D57" s="56"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -2922,14 +2919,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="J7:J12"/>
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -2946,6 +2935,14 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J7:J12"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2969,30 +2966,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="D1" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="63" t="s">
+      <c r="E1" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="63" t="s">
+      <c r="F1" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="64" t="s">
+      <c r="G1" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="65"/>
+      <c r="H1" s="67"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="46" t="s">
+      <c r="J1" s="50" t="s">
         <v>0</v>
       </c>
     </row>
@@ -3003,10 +3000,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -3014,16 +3011,16 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="46"/>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A3" s="44" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>136</v>
-      </c>
-      <c r="D3" s="52" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="55" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="28" t="s">
@@ -3042,7 +3039,7 @@
         <v>17</v>
       </c>
       <c r="J3" s="33" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15">
@@ -3051,9 +3048,9 @@
         <v>48</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" s="53"/>
+        <v>99</v>
+      </c>
+      <c r="D4" s="56"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="43"/>
@@ -3062,7 +3059,7 @@
       </c>
       <c r="I4" s="10"/>
       <c r="J4" s="35" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15">
@@ -3071,9 +3068,9 @@
         <v>41</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" s="53"/>
+        <v>99</v>
+      </c>
+      <c r="D5" s="56"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
@@ -3089,14 +3086,14 @@
         <v>49</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="D6" s="53"/>
+        <v>99</v>
+      </c>
+      <c r="D6" s="56"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I6" s="10" t="s">
         <v>20</v>
@@ -3106,14 +3103,14 @@
     <row r="7" spans="1:10" ht="67.5" customHeight="1">
       <c r="A7" s="10"/>
       <c r="C7" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="D7" s="53"/>
+        <v>136</v>
+      </c>
+      <c r="D7" s="56"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
       <c r="H7" s="45" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I7" s="10" t="s">
         <v>21</v>
@@ -3123,7 +3120,7 @@
     <row r="8" spans="1:10" ht="14.25" customHeight="1">
       <c r="A8" s="27"/>
       <c r="C8" s="28"/>
-      <c r="D8" s="53"/>
+      <c r="D8" s="56"/>
       <c r="E8" s="28"/>
       <c r="F8" s="28"/>
       <c r="G8" s="27"/>
@@ -3133,13 +3130,13 @@
     </row>
     <row r="9" spans="1:10" ht="15">
       <c r="A9" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B9" s="30" t="s">
         <v>41</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="53"/>
+      <c r="D9" s="56"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -3155,7 +3152,7 @@
         <v>49</v>
       </c>
       <c r="C10" s="10"/>
-      <c r="D10" s="53"/>
+      <c r="D10" s="56"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -3171,7 +3168,7 @@
         <v>64</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="53"/>
+      <c r="D11" s="56"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -3185,7 +3182,7 @@
         <v>80</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="53"/>
+      <c r="D12" s="56"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -3199,7 +3196,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="53"/>
+      <c r="D13" s="56"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -3215,7 +3212,7 @@
         <v>64</v>
       </c>
       <c r="C14" s="11"/>
-      <c r="D14" s="53"/>
+      <c r="D14" s="56"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -3230,7 +3227,7 @@
         <v>65</v>
       </c>
       <c r="C15" s="11"/>
-      <c r="D15" s="53"/>
+      <c r="D15" s="56"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
@@ -3243,92 +3240,92 @@
         <v>67</v>
       </c>
       <c r="C16" s="8"/>
-      <c r="D16" s="53"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
       <c r="I16" s="10"/>
-      <c r="J16" s="48"/>
+      <c r="J16" s="47"/>
     </row>
     <row r="17" spans="1:10" ht="15">
       <c r="B17" t="s">
         <v>68</v>
       </c>
       <c r="C17" s="8"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="48"/>
+      <c r="J17" s="47"/>
     </row>
     <row r="18" spans="1:10" ht="15">
       <c r="A18" s="15"/>
       <c r="B18" s="15"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="48"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="48"/>
+      <c r="J18" s="47"/>
     </row>
     <row r="19" spans="1:10" ht="15">
       <c r="A19" s="15"/>
       <c r="B19" s="15"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="48"/>
+      <c r="J19" s="47"/>
     </row>
     <row r="20" spans="1:10" ht="15">
       <c r="A20" s="15"/>
       <c r="B20" s="15"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="48"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="48"/>
+      <c r="J20" s="47"/>
     </row>
     <row r="21" spans="1:10" ht="15">
       <c r="A21" s="15"/>
       <c r="B21" s="15"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="48"/>
-      <c r="H21" s="48"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="47"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="48"/>
+      <c r="J21" s="47"/>
     </row>
     <row r="22" spans="1:10" ht="15">
       <c r="A22" s="15"/>
       <c r="B22" s="15"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="48"/>
+      <c r="J22" s="47"/>
     </row>
     <row r="23" spans="1:10" ht="15">
       <c r="A23" s="10"/>
       <c r="B23" s="10"/>
       <c r="C23" s="11"/>
-      <c r="D23" s="53"/>
+      <c r="D23" s="56"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="10"/>
@@ -3340,7 +3337,7 @@
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="53"/>
+      <c r="D24" s="56"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -3352,7 +3349,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="53"/>
+      <c r="D25" s="56"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
@@ -3364,7 +3361,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="53"/>
+      <c r="D26" s="56"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -3376,7 +3373,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="53"/>
+      <c r="D27" s="56"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -3388,7 +3385,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="53"/>
+      <c r="D28" s="56"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -3400,7 +3397,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="53"/>
+      <c r="D29" s="56"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
       <c r="G29" s="10"/>
@@ -3412,7 +3409,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="53"/>
+      <c r="D30" s="56"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -3424,7 +3421,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="53"/>
+      <c r="D31" s="56"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -3436,7 +3433,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
-      <c r="D32" s="53"/>
+      <c r="D32" s="56"/>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
@@ -3448,7 +3445,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="53"/>
+      <c r="D33" s="56"/>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
       <c r="G33" s="10"/>
@@ -3460,7 +3457,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="11"/>
-      <c r="D34" s="53"/>
+      <c r="D34" s="56"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -3472,7 +3469,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="53"/>
+      <c r="D35" s="56"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -3484,7 +3481,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="53"/>
+      <c r="D36" s="56"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -3496,7 +3493,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="53"/>
+      <c r="D37" s="56"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -3508,7 +3505,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="53"/>
+      <c r="D38" s="56"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -3520,7 +3517,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="53"/>
+      <c r="D39" s="56"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -3532,7 +3529,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="53"/>
+      <c r="D40" s="56"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -3544,7 +3541,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="53"/>
+      <c r="D41" s="56"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -3556,7 +3553,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="53"/>
+      <c r="D42" s="56"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -3568,7 +3565,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="53"/>
+      <c r="D43" s="56"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -3580,7 +3577,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="53"/>
+      <c r="D44" s="56"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -3592,7 +3589,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="53"/>
+      <c r="D45" s="56"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -3604,7 +3601,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="53"/>
+      <c r="D46" s="56"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -3616,7 +3613,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="53"/>
+      <c r="D47" s="56"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -3628,7 +3625,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="53"/>
+      <c r="D48" s="56"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -3640,7 +3637,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="53"/>
+      <c r="D49" s="56"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -3652,7 +3649,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="53"/>
+      <c r="D50" s="56"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -3664,7 +3661,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="53"/>
+      <c r="D51" s="56"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -3676,7 +3673,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="53"/>
+      <c r="D52" s="56"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -3688,7 +3685,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="53"/>
+      <c r="D53" s="56"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -3700,7 +3697,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="53"/>
+      <c r="D54" s="56"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -3712,7 +3709,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="53"/>
+      <c r="D55" s="56"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -3724,7 +3721,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="53"/>
+      <c r="D56" s="56"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -4682,30 +4679,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="D1" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="63" t="s">
+      <c r="E1" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="63" t="s">
+      <c r="F1" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="64" t="s">
+      <c r="G1" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="65"/>
+      <c r="H1" s="67"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="46" t="s">
+      <c r="J1" s="50" t="s">
         <v>0</v>
       </c>
     </row>
@@ -4716,10 +4713,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -4727,7 +4724,7 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="46"/>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A3" s="32" t="s">
@@ -4737,9 +4734,9 @@
         <v>50</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" s="55" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="22" t="s">
@@ -4765,9 +4762,9 @@
         <v>51</v>
       </c>
       <c r="C4" s="68" t="s">
-        <v>104</v>
-      </c>
-      <c r="D4" s="53"/>
+        <v>103</v>
+      </c>
+      <c r="D4" s="56"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="10"/>
@@ -4783,7 +4780,7 @@
       <c r="A5" s="10"/>
       <c r="B5" s="10"/>
       <c r="C5" s="68"/>
-      <c r="D5" s="53"/>
+      <c r="D5" s="56"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
@@ -4795,7 +4792,7 @@
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
       <c r="C6" s="68"/>
-      <c r="D6" s="53"/>
+      <c r="D6" s="56"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
@@ -4811,7 +4808,7 @@
         <v>52</v>
       </c>
       <c r="C7" s="68"/>
-      <c r="D7" s="53"/>
+      <c r="D7" s="56"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
@@ -4827,7 +4824,7 @@
         <v>53</v>
       </c>
       <c r="C8" s="68"/>
-      <c r="D8" s="53"/>
+      <c r="D8" s="56"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
@@ -4841,7 +4838,7 @@
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="11"/>
-      <c r="D9" s="53"/>
+      <c r="D9" s="56"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -4855,7 +4852,7 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
-      <c r="D10" s="53"/>
+      <c r="D10" s="56"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -4869,7 +4866,7 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="11"/>
-      <c r="D11" s="53"/>
+      <c r="D11" s="56"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -4881,7 +4878,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="53"/>
+      <c r="D12" s="56"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -4895,7 +4892,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="53"/>
+      <c r="D13" s="56"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -4907,7 +4904,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="53"/>
+      <c r="D14" s="56"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -4921,7 +4918,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="53"/>
+      <c r="D15" s="56"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
@@ -4930,94 +4927,94 @@
       <c r="J15" s="10"/>
     </row>
     <row r="16" spans="1:10" ht="15">
-      <c r="A16" s="67"/>
-      <c r="B16" s="67"/>
+      <c r="A16" s="48"/>
+      <c r="B16" s="48"/>
       <c r="C16" s="8"/>
-      <c r="D16" s="53"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
       <c r="I16" s="10"/>
-      <c r="J16" s="48"/>
+      <c r="J16" s="47"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="67"/>
-      <c r="B17" s="67"/>
+      <c r="A17" s="48"/>
+      <c r="B17" s="48"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="48"/>
+      <c r="J17" s="47"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="67"/>
-      <c r="B18" s="67"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="48"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="48"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="48"/>
+      <c r="J18" s="47"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="67"/>
-      <c r="B19" s="67"/>
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="48"/>
+      <c r="J19" s="47"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="67"/>
-      <c r="B20" s="67"/>
+      <c r="A20" s="48"/>
+      <c r="B20" s="48"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="48"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="48"/>
+      <c r="J20" s="47"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="67"/>
-      <c r="B21" s="67"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="48"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="48"/>
-      <c r="H21" s="48"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="47"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="48"/>
+      <c r="J21" s="47"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="67"/>
-      <c r="B22" s="67"/>
+      <c r="A22" s="48"/>
+      <c r="B22" s="48"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="48"/>
+      <c r="J22" s="47"/>
     </row>
     <row r="23" spans="1:10" ht="15">
       <c r="A23" s="10"/>
       <c r="B23" s="10"/>
       <c r="C23" s="11"/>
-      <c r="D23" s="53"/>
+      <c r="D23" s="56"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="10"/>
@@ -5029,7 +5026,7 @@
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="53"/>
+      <c r="D24" s="56"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -5041,7 +5038,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="53"/>
+      <c r="D25" s="56"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
@@ -5053,7 +5050,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="53"/>
+      <c r="D26" s="56"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -5065,7 +5062,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="53"/>
+      <c r="D27" s="56"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -5077,7 +5074,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="53"/>
+      <c r="D28" s="56"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -5089,7 +5086,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="53"/>
+      <c r="D29" s="56"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
       <c r="G29" s="10"/>
@@ -5101,7 +5098,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="53"/>
+      <c r="D30" s="56"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -5113,7 +5110,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="53"/>
+      <c r="D31" s="56"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -5125,7 +5122,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
-      <c r="D32" s="53"/>
+      <c r="D32" s="56"/>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
@@ -5137,7 +5134,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="53"/>
+      <c r="D33" s="56"/>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
       <c r="G33" s="10"/>
@@ -5149,7 +5146,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="11"/>
-      <c r="D34" s="53"/>
+      <c r="D34" s="56"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -5161,7 +5158,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="53"/>
+      <c r="D35" s="56"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -5173,7 +5170,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="53"/>
+      <c r="D36" s="56"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -5185,7 +5182,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="53"/>
+      <c r="D37" s="56"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -5197,7 +5194,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="53"/>
+      <c r="D38" s="56"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -5209,7 +5206,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="53"/>
+      <c r="D39" s="56"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -5221,7 +5218,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="53"/>
+      <c r="D40" s="56"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -5233,7 +5230,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="53"/>
+      <c r="D41" s="56"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -5245,7 +5242,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="53"/>
+      <c r="D42" s="56"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -5257,7 +5254,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="53"/>
+      <c r="D43" s="56"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -5269,7 +5266,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="53"/>
+      <c r="D44" s="56"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -5281,7 +5278,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="53"/>
+      <c r="D45" s="56"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -5293,7 +5290,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="53"/>
+      <c r="D46" s="56"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -5305,7 +5302,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="53"/>
+      <c r="D47" s="56"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -5317,7 +5314,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="53"/>
+      <c r="D48" s="56"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -5329,7 +5326,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="53"/>
+      <c r="D49" s="56"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -5341,7 +5338,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="53"/>
+      <c r="D50" s="56"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -5353,7 +5350,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="53"/>
+      <c r="D51" s="56"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -5365,7 +5362,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="53"/>
+      <c r="D52" s="56"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -5377,7 +5374,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="53"/>
+      <c r="D53" s="56"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -5389,7 +5386,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="53"/>
+      <c r="D54" s="56"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -5401,7 +5398,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="53"/>
+      <c r="D55" s="56"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -5413,7 +5410,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="53"/>
+      <c r="D56" s="56"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -6335,6 +6332,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="G16:G22"/>
     <mergeCell ref="H16:H22"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="D3:D56"/>
@@ -6351,7 +6349,6 @@
     <mergeCell ref="B16:B22"/>
     <mergeCell ref="E16:E22"/>
     <mergeCell ref="F16:F22"/>
-    <mergeCell ref="G16:G22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6375,30 +6372,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="D1" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="63" t="s">
+      <c r="E1" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="63" t="s">
+      <c r="F1" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="64" t="s">
+      <c r="G1" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="65"/>
+      <c r="H1" s="67"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="46" t="s">
+      <c r="J1" s="50" t="s">
         <v>0</v>
       </c>
     </row>
@@ -6409,10 +6406,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -6420,51 +6417,51 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="46"/>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="52" t="s">
+      <c r="A3" s="51"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="54" t="s">
+      <c r="E3" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="55" t="s">
+      <c r="F3" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="56" t="s">
+      <c r="G3" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="56" t="s">
+      <c r="H3" s="58" t="s">
         <v>58</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="48"/>
+      <c r="J3" s="47"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="48"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
+      <c r="A4" s="47"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
       <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="48"/>
+      <c r="J4" s="47"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="10"/>
       <c r="C5" s="11"/>
-      <c r="D5" s="53"/>
+      <c r="D5" s="56"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
@@ -6480,7 +6477,7 @@
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
       <c r="C6" s="11"/>
-      <c r="D6" s="53"/>
+      <c r="D6" s="56"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
@@ -6494,7 +6491,7 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="53"/>
+      <c r="D7" s="56"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
@@ -6508,12 +6505,12 @@
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="53"/>
+      <c r="D8" s="56"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
       <c r="H8" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>20</v>
@@ -6524,12 +6521,12 @@
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="53"/>
+      <c r="D9" s="56"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
       <c r="H9" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I9" s="10" t="s">
         <v>21</v>
@@ -6540,12 +6537,12 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="53"/>
+      <c r="D10" s="56"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>23</v>
@@ -6556,12 +6553,12 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="53"/>
+      <c r="D11" s="56"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I11" s="10" t="s">
         <v>22</v>
@@ -6572,7 +6569,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="53"/>
+      <c r="D12" s="56"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -6584,7 +6581,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="53"/>
+      <c r="D13" s="56"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -6598,7 +6595,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="53"/>
+      <c r="D14" s="56"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -6610,7 +6607,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="53"/>
+      <c r="D15" s="56"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
@@ -6624,7 +6621,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="53"/>
+      <c r="D16" s="56"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -6633,94 +6630,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="67"/>
-      <c r="B17" s="67"/>
+      <c r="A17" s="48"/>
+      <c r="B17" s="48"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="48"/>
+      <c r="J17" s="47"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="67"/>
-      <c r="B18" s="67"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="48"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="48"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="48"/>
+      <c r="J18" s="47"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="67"/>
-      <c r="B19" s="67"/>
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="48"/>
+      <c r="J19" s="47"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="67"/>
-      <c r="B20" s="67"/>
+      <c r="A20" s="48"/>
+      <c r="B20" s="48"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="48"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="48"/>
+      <c r="J20" s="47"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="67"/>
-      <c r="B21" s="67"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="48"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="48"/>
-      <c r="H21" s="48"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="47"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="48"/>
+      <c r="J21" s="47"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="67"/>
-      <c r="B22" s="67"/>
+      <c r="A22" s="48"/>
+      <c r="B22" s="48"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="48"/>
+      <c r="J22" s="47"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="67"/>
-      <c r="B23" s="67"/>
+      <c r="A23" s="48"/>
+      <c r="B23" s="48"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="48"/>
-      <c r="H23" s="48"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="47"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="48"/>
+      <c r="J23" s="47"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="53"/>
+      <c r="D24" s="56"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -6732,7 +6729,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="53"/>
+      <c r="D25" s="56"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -6744,7 +6741,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="53"/>
+      <c r="D26" s="56"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -6756,7 +6753,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="53"/>
+      <c r="D27" s="56"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -6768,7 +6765,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="53"/>
+      <c r="D28" s="56"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -6780,7 +6777,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="53"/>
+      <c r="D29" s="56"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -6792,7 +6789,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="53"/>
+      <c r="D30" s="56"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -6804,7 +6801,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="53"/>
+      <c r="D31" s="56"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -6816,7 +6813,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="53"/>
+      <c r="D32" s="56"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -6828,7 +6825,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="53"/>
+      <c r="D33" s="56"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -6840,7 +6837,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="53"/>
+      <c r="D34" s="56"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -6852,7 +6849,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="53"/>
+      <c r="D35" s="56"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -6864,7 +6861,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="53"/>
+      <c r="D36" s="56"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -6876,7 +6873,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="53"/>
+      <c r="D37" s="56"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -6888,7 +6885,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="53"/>
+      <c r="D38" s="56"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -6900,7 +6897,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="53"/>
+      <c r="D39" s="56"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -6912,7 +6909,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="53"/>
+      <c r="D40" s="56"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -6924,7 +6921,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="53"/>
+      <c r="D41" s="56"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -6936,7 +6933,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="53"/>
+      <c r="D42" s="56"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -6948,7 +6945,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="53"/>
+      <c r="D43" s="56"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -6960,7 +6957,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="53"/>
+      <c r="D44" s="56"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -6972,7 +6969,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="53"/>
+      <c r="D45" s="56"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -6984,7 +6981,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="53"/>
+      <c r="D46" s="56"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -6996,7 +6993,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="53"/>
+      <c r="D47" s="56"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -7008,7 +7005,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="53"/>
+      <c r="D48" s="56"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -7020,7 +7017,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="53"/>
+      <c r="D49" s="56"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -7032,7 +7029,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="53"/>
+      <c r="D50" s="56"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -7044,7 +7041,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="53"/>
+      <c r="D51" s="56"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -7056,7 +7053,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="53"/>
+      <c r="D52" s="56"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -7068,7 +7065,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="53"/>
+      <c r="D53" s="56"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -7080,7 +7077,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="53"/>
+      <c r="D54" s="56"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -7092,7 +7089,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="53"/>
+      <c r="D55" s="56"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -7104,7 +7101,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="53"/>
+      <c r="D56" s="56"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -7116,7 +7113,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="53"/>
+      <c r="D57" s="56"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -8038,13 +8035,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -8061,6 +8051,13 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8084,30 +8081,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="D1" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="63" t="s">
+      <c r="E1" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="63" t="s">
+      <c r="F1" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="64" t="s">
+      <c r="G1" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="65"/>
+      <c r="H1" s="67"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="46" t="s">
+      <c r="J1" s="50" t="s">
         <v>0</v>
       </c>
     </row>
@@ -8118,10 +8115,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -8129,51 +8126,51 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="46"/>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="52" t="s">
+      <c r="A3" s="51"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="54" t="s">
+      <c r="E3" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="55" t="s">
+      <c r="F3" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="56" t="s">
+      <c r="G3" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="56" t="s">
+      <c r="H3" s="58" t="s">
         <v>62</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="48"/>
+      <c r="J3" s="47"/>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="48"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
+      <c r="A4" s="47"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
       <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="48"/>
+      <c r="J4" s="47"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="10"/>
       <c r="B5" s="10"/>
       <c r="C5" s="11"/>
-      <c r="D5" s="53"/>
+      <c r="D5" s="56"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
@@ -8189,12 +8186,12 @@
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
       <c r="C6" s="11"/>
-      <c r="D6" s="53"/>
+      <c r="D6" s="56"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
@@ -8203,7 +8200,7 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="53"/>
+      <c r="D7" s="56"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
@@ -8215,7 +8212,7 @@
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="53"/>
+      <c r="D8" s="56"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
@@ -8229,7 +8226,7 @@
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="53"/>
+      <c r="D9" s="56"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -8243,7 +8240,7 @@
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="53"/>
+      <c r="D10" s="56"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
@@ -8257,7 +8254,7 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="53"/>
+      <c r="D11" s="56"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
@@ -8271,7 +8268,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="53"/>
+      <c r="D12" s="56"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -8283,7 +8280,7 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="53"/>
+      <c r="D13" s="56"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="10"/>
@@ -8297,7 +8294,7 @@
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="53"/>
+      <c r="D14" s="56"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="10"/>
@@ -8309,7 +8306,7 @@
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="53"/>
+      <c r="D15" s="56"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="10"/>
@@ -8323,7 +8320,7 @@
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="53"/>
+      <c r="D16" s="56"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -8332,94 +8329,94 @@
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="67"/>
-      <c r="B17" s="67"/>
+      <c r="A17" s="48"/>
+      <c r="B17" s="48"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="48"/>
+      <c r="J17" s="47"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="67"/>
-      <c r="B18" s="67"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="48"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="48"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="48"/>
+      <c r="J18" s="47"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="67"/>
-      <c r="B19" s="67"/>
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="48"/>
+      <c r="J19" s="47"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="67"/>
-      <c r="B20" s="67"/>
+      <c r="A20" s="48"/>
+      <c r="B20" s="48"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="48"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="48"/>
+      <c r="J20" s="47"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="67"/>
-      <c r="B21" s="67"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="48"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="48"/>
-      <c r="H21" s="48"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="47"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="48"/>
+      <c r="J21" s="47"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="67"/>
-      <c r="B22" s="67"/>
+      <c r="A22" s="48"/>
+      <c r="B22" s="48"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="48"/>
+      <c r="J22" s="47"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="67"/>
-      <c r="B23" s="67"/>
+      <c r="A23" s="48"/>
+      <c r="B23" s="48"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="48"/>
-      <c r="H23" s="48"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="47"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="48"/>
+      <c r="J23" s="47"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="53"/>
+      <c r="D24" s="56"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="10"/>
@@ -8431,7 +8428,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="53"/>
+      <c r="D25" s="56"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="10"/>
@@ -8443,7 +8440,7 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="53"/>
+      <c r="D26" s="56"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -8455,7 +8452,7 @@
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="53"/>
+      <c r="D27" s="56"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -8467,7 +8464,7 @@
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="53"/>
+      <c r="D28" s="56"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -8479,7 +8476,7 @@
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="53"/>
+      <c r="D29" s="56"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -8491,7 +8488,7 @@
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="53"/>
+      <c r="D30" s="56"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="10"/>
@@ -8503,7 +8500,7 @@
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="53"/>
+      <c r="D31" s="56"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="10"/>
@@ -8515,7 +8512,7 @@
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="53"/>
+      <c r="D32" s="56"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="10"/>
@@ -8527,7 +8524,7 @@
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="53"/>
+      <c r="D33" s="56"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
@@ -8539,7 +8536,7 @@
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="53"/>
+      <c r="D34" s="56"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="10"/>
@@ -8551,7 +8548,7 @@
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="53"/>
+      <c r="D35" s="56"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="10"/>
@@ -8563,7 +8560,7 @@
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="53"/>
+      <c r="D36" s="56"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="10"/>
@@ -8575,7 +8572,7 @@
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="53"/>
+      <c r="D37" s="56"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="10"/>
@@ -8587,7 +8584,7 @@
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="53"/>
+      <c r="D38" s="56"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="10"/>
@@ -8599,7 +8596,7 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="53"/>
+      <c r="D39" s="56"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="10"/>
@@ -8611,7 +8608,7 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="53"/>
+      <c r="D40" s="56"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="10"/>
@@ -8623,7 +8620,7 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="53"/>
+      <c r="D41" s="56"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="10"/>
@@ -8635,7 +8632,7 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="53"/>
+      <c r="D42" s="56"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="10"/>
@@ -8647,7 +8644,7 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="53"/>
+      <c r="D43" s="56"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="10"/>
@@ -8659,7 +8656,7 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="53"/>
+      <c r="D44" s="56"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="10"/>
@@ -8671,7 +8668,7 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="53"/>
+      <c r="D45" s="56"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="10"/>
@@ -8683,7 +8680,7 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="53"/>
+      <c r="D46" s="56"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="10"/>
@@ -8695,7 +8692,7 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="53"/>
+      <c r="D47" s="56"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="10"/>
@@ -8707,7 +8704,7 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="53"/>
+      <c r="D48" s="56"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="10"/>
@@ -8719,7 +8716,7 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="53"/>
+      <c r="D49" s="56"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="10"/>
@@ -8731,7 +8728,7 @@
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="53"/>
+      <c r="D50" s="56"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="10"/>
@@ -8743,7 +8740,7 @@
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="53"/>
+      <c r="D51" s="56"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="10"/>
@@ -8755,7 +8752,7 @@
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="53"/>
+      <c r="D52" s="56"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="10"/>
@@ -8767,7 +8764,7 @@
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="53"/>
+      <c r="D53" s="56"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="10"/>
@@ -8779,7 +8776,7 @@
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="53"/>
+      <c r="D54" s="56"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="10"/>
@@ -8791,7 +8788,7 @@
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="53"/>
+      <c r="D55" s="56"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="10"/>
@@ -8803,7 +8800,7 @@
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="53"/>
+      <c r="D56" s="56"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="10"/>
@@ -8815,7 +8812,7 @@
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="53"/>
+      <c r="D57" s="56"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="10"/>
@@ -9737,13 +9734,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="J17:J23"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="H17:H23"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -9760,6 +9750,13 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J17:J23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="H17:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9783,30 +9780,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="D1" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="63" t="s">
+      <c r="E1" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="63" t="s">
+      <c r="F1" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="64" t="s">
+      <c r="G1" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="65"/>
+      <c r="H1" s="67"/>
       <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="46" t="s">
+      <c r="J1" s="50" t="s">
         <v>0</v>
       </c>
     </row>
@@ -9817,10 +9814,10 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -9828,7 +9825,7 @@
         <v>5</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="J2" s="46"/>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1">
       <c r="A3" t="s">
@@ -9838,15 +9835,15 @@
         <v>64</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="54" t="s">
+      <c r="E3" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="55" t="s">
+      <c r="F3" s="57" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="25" t="s">
@@ -9865,11 +9862,11 @@
         <v>65</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" s="53"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="55"/>
+        <v>99</v>
+      </c>
+      <c r="D4" s="56"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="57"/>
       <c r="G4" s="21"/>
       <c r="H4" s="4" t="s">
         <v>65</v>
@@ -9884,9 +9881,9 @@
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" s="53"/>
+        <v>99</v>
+      </c>
+      <c r="D5" s="56"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="4"/>
@@ -9901,9 +9898,9 @@
         <v>68</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D6" s="53"/>
+        <v>99</v>
+      </c>
+      <c r="D6" s="56"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="4"/>
@@ -9915,9 +9912,9 @@
     </row>
     <row r="7" spans="1:10" ht="60">
       <c r="C7" s="38" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="53"/>
+        <v>108</v>
+      </c>
+      <c r="D7" s="56"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="4"/>
@@ -9928,14 +9925,14 @@
         <v>20</v>
       </c>
       <c r="J7" s="37" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30">
       <c r="C8" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="D8" s="53"/>
+        <v>105</v>
+      </c>
+      <c r="D8" s="56"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="4"/>
@@ -9946,14 +9943,14 @@
         <v>21</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="30">
       <c r="C9" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="D9" s="53"/>
+        <v>109</v>
+      </c>
+      <c r="D9" s="56"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="4"/>
@@ -9964,14 +9961,14 @@
         <v>23</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15">
       <c r="C10" s="70" t="s">
-        <v>113</v>
-      </c>
-      <c r="D10" s="53"/>
+        <v>112</v>
+      </c>
+      <c r="D10" s="56"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="4"/>
@@ -9985,7 +9982,7 @@
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1">
       <c r="C11" s="70"/>
-      <c r="D11" s="53"/>
+      <c r="D11" s="56"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="4"/>
@@ -9995,7 +9992,7 @@
     </row>
     <row r="12" spans="1:10" ht="15">
       <c r="C12" s="70"/>
-      <c r="D12" s="53"/>
+      <c r="D12" s="56"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="4"/>
@@ -10007,9 +10004,9 @@
     </row>
     <row r="13" spans="1:10" ht="45">
       <c r="C13" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="D13" s="53"/>
+        <v>113</v>
+      </c>
+      <c r="D13" s="56"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="4"/>
@@ -10024,9 +10021,9 @@
         <v>66</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" s="53"/>
+        <v>99</v>
+      </c>
+      <c r="D14" s="56"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="4"/>
@@ -10040,20 +10037,20 @@
     </row>
     <row r="15" spans="1:10" ht="15">
       <c r="C15" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="D15" s="53"/>
+        <v>117</v>
+      </c>
+      <c r="D15" s="56"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="4"/>
       <c r="H15" s="36" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
     </row>
     <row r="16" spans="1:10" ht="15">
-      <c r="D16" s="53"/>
+      <c r="D16" s="56"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -10062,9 +10059,9 @@
       <c r="J16" s="33"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="D17" s="53"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="49"/>
       <c r="G17" s="33"/>
       <c r="H17" s="33"/>
       <c r="I17" s="21"/>
@@ -10078,9 +10075,9 @@
         <v>74</v>
       </c>
       <c r="C18" s="7"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="49"/>
       <c r="G18" s="33"/>
       <c r="H18" s="33"/>
       <c r="I18" s="21"/>
@@ -10093,9 +10090,9 @@
       <c r="C19" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="53"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
       <c r="G19" s="33"/>
       <c r="H19" s="33"/>
       <c r="I19" s="21"/>
@@ -10106,9 +10103,9 @@
         <v>76</v>
       </c>
       <c r="C20" s="7"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
       <c r="G20" s="33"/>
       <c r="H20" s="33"/>
       <c r="I20" s="21"/>
@@ -10119,9 +10116,9 @@
         <v>77</v>
       </c>
       <c r="C21" s="7"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
       <c r="G21" s="33"/>
       <c r="H21" s="33"/>
       <c r="I21" s="21"/>
@@ -10132,9 +10129,9 @@
         <v>78</v>
       </c>
       <c r="C22" s="7"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
       <c r="G22" s="33"/>
       <c r="H22" s="33"/>
       <c r="I22" s="21"/>
@@ -10142,9 +10139,9 @@
     </row>
     <row r="23" spans="1:10" ht="15">
       <c r="C23" s="7"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
       <c r="G23" s="33"/>
       <c r="H23" s="33"/>
       <c r="I23" s="21"/>
@@ -10158,7 +10155,7 @@
         <v>74</v>
       </c>
       <c r="C24" s="7"/>
-      <c r="D24" s="53"/>
+      <c r="D24" s="56"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
       <c r="G24" s="21"/>
@@ -10171,7 +10168,7 @@
         <v>79</v>
       </c>
       <c r="C25" s="8"/>
-      <c r="D25" s="53"/>
+      <c r="D25" s="56"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="4"/>
@@ -10184,7 +10181,7 @@
         <v>64</v>
       </c>
       <c r="C26" s="8"/>
-      <c r="D26" s="53"/>
+      <c r="D26" s="56"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -10197,7 +10194,7 @@
         <v>80</v>
       </c>
       <c r="C27" s="8"/>
-      <c r="D27" s="53"/>
+      <c r="D27" s="56"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
@@ -10207,7 +10204,7 @@
     </row>
     <row r="28" spans="1:10" ht="15">
       <c r="C28" s="8"/>
-      <c r="D28" s="53"/>
+      <c r="D28" s="56"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -10223,7 +10220,7 @@
         <v>64</v>
       </c>
       <c r="C29" s="8"/>
-      <c r="D29" s="53"/>
+      <c r="D29" s="56"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -10236,7 +10233,7 @@
         <v>79</v>
       </c>
       <c r="C30" s="8"/>
-      <c r="D30" s="53"/>
+      <c r="D30" s="56"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="4"/>
@@ -10249,7 +10246,7 @@
         <v>81</v>
       </c>
       <c r="C31" s="8"/>
-      <c r="D31" s="53"/>
+      <c r="D31" s="56"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="4"/>
@@ -10262,7 +10259,7 @@
         <v>82</v>
       </c>
       <c r="C32" s="7"/>
-      <c r="D32" s="53"/>
+      <c r="D32" s="56"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="4"/>
@@ -10275,7 +10272,7 @@
         <v>83</v>
       </c>
       <c r="C33" s="7"/>
-      <c r="D33" s="53"/>
+      <c r="D33" s="56"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
@@ -10288,7 +10285,7 @@
         <v>84</v>
       </c>
       <c r="C34" s="7"/>
-      <c r="D34" s="53"/>
+      <c r="D34" s="56"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
       <c r="G34" s="4"/>
@@ -10301,7 +10298,7 @@
         <v>85</v>
       </c>
       <c r="C35" s="7"/>
-      <c r="D35" s="53"/>
+      <c r="D35" s="56"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
       <c r="G35" s="4"/>
@@ -10314,7 +10311,7 @@
         <v>86</v>
       </c>
       <c r="C36" s="7"/>
-      <c r="D36" s="53"/>
+      <c r="D36" s="56"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="4"/>
@@ -10326,7 +10323,7 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="53"/>
+      <c r="D37" s="56"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="4"/>
@@ -10336,13 +10333,13 @@
     </row>
     <row r="38" spans="1:10" ht="15">
       <c r="A38" t="s">
+        <v>114</v>
+      </c>
+      <c r="B38" t="s">
         <v>115</v>
       </c>
-      <c r="B38" t="s">
-        <v>116</v>
-      </c>
       <c r="C38" s="7"/>
-      <c r="D38" s="53"/>
+      <c r="D38" s="56"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="4"/>
@@ -10352,10 +10349,10 @@
     </row>
     <row r="39" spans="1:10" ht="15">
       <c r="B39" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C39" s="7"/>
-      <c r="D39" s="53"/>
+      <c r="D39" s="56"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="4"/>
@@ -10366,7 +10363,7 @@
     <row r="40" spans="1:10" ht="15">
       <c r="B40" s="4"/>
       <c r="C40" s="7"/>
-      <c r="D40" s="53"/>
+      <c r="D40" s="56"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="4"/>
@@ -10377,7 +10374,7 @@
     <row r="41" spans="1:10" ht="15">
       <c r="B41" s="4"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="53"/>
+      <c r="D41" s="56"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="4"/>
@@ -10389,7 +10386,7 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="53"/>
+      <c r="D42" s="56"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="4"/>
@@ -10401,7 +10398,7 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="53"/>
+      <c r="D43" s="56"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="4"/>
@@ -10413,7 +10410,7 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="7"/>
-      <c r="D44" s="53"/>
+      <c r="D44" s="56"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="4"/>
@@ -10425,7 +10422,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="53"/>
+      <c r="D45" s="56"/>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
       <c r="G45" s="4"/>
@@ -10437,7 +10434,7 @@
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="7"/>
-      <c r="D46" s="53"/>
+      <c r="D46" s="56"/>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
       <c r="G46" s="4"/>
@@ -10449,7 +10446,7 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="7"/>
-      <c r="D47" s="53"/>
+      <c r="D47" s="56"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
       <c r="G47" s="4"/>
@@ -10461,7 +10458,7 @@
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="7"/>
-      <c r="D48" s="53"/>
+      <c r="D48" s="56"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
       <c r="G48" s="4"/>
@@ -10473,7 +10470,7 @@
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="7"/>
-      <c r="D49" s="53"/>
+      <c r="D49" s="56"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
       <c r="G49" s="4"/>
@@ -10485,7 +10482,7 @@
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="53"/>
+      <c r="D50" s="56"/>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
       <c r="G50" s="4"/>
@@ -10497,7 +10494,7 @@
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="7"/>
-      <c r="D51" s="53"/>
+      <c r="D51" s="56"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
       <c r="G51" s="4"/>
@@ -10509,7 +10506,7 @@
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="7"/>
-      <c r="D52" s="53"/>
+      <c r="D52" s="56"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
       <c r="G52" s="4"/>
@@ -10521,7 +10518,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="53"/>
+      <c r="D53" s="56"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="4"/>
@@ -10533,7 +10530,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="53"/>
+      <c r="D54" s="56"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
       <c r="G54" s="4"/>
@@ -10545,7 +10542,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="7"/>
-      <c r="D55" s="53"/>
+      <c r="D55" s="56"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
       <c r="G55" s="4"/>
@@ -10557,7 +10554,7 @@
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="7"/>
-      <c r="D56" s="53"/>
+      <c r="D56" s="56"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
       <c r="G56" s="4"/>
@@ -10569,7 +10566,7 @@
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="7"/>
-      <c r="D57" s="53"/>
+      <c r="D57" s="56"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
       <c r="G57" s="4"/>
@@ -11525,27 +11522,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="D1" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="63" t="s">
+      <c r="E1" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="63" t="s">
+      <c r="F1" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="64" t="s">
+      <c r="G1" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="65"/>
-      <c r="I1" s="46" t="s">
+      <c r="H1" s="67"/>
+      <c r="I1" s="50" t="s">
         <v>0</v>
       </c>
     </row>
@@ -11556,40 +11553,40 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="46"/>
+      <c r="I2" s="50"/>
     </row>
     <row r="3" spans="1:9" ht="15">
       <c r="A3" s="14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>50</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="54"/>
-      <c r="F3" s="55"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="57"/>
       <c r="G3" s="14" t="s">
         <v>87</v>
       </c>
       <c r="H3" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="I3" s="48"/>
+      <c r="I3" s="47"/>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1">
       <c r="A4" s="14"/>
@@ -11597,27 +11594,27 @@
         <v>41</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" s="53"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="55"/>
+        <v>99</v>
+      </c>
+      <c r="D4" s="56"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="57"/>
       <c r="G4" s="13"/>
       <c r="H4" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="I4" s="48"/>
+      <c r="I4" s="47"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1">
       <c r="A5" s="25"/>
       <c r="B5" s="25"/>
       <c r="C5" s="20"/>
-      <c r="D5" s="53"/>
+      <c r="D5" s="56"/>
       <c r="E5" s="22"/>
       <c r="F5" s="24"/>
       <c r="G5" s="21"/>
       <c r="H5" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I5" s="21"/>
     </row>
@@ -11627,14 +11624,14 @@
         <v>49</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="D6" s="53"/>
+        <v>120</v>
+      </c>
+      <c r="D6" s="56"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I6" s="4"/>
     </row>
@@ -11642,53 +11639,53 @@
       <c r="A7" s="14"/>
       <c r="B7" s="25"/>
       <c r="C7" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" s="53"/>
+        <v>121</v>
+      </c>
+      <c r="D7" s="56"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="C8" t="s">
-        <v>123</v>
-      </c>
-      <c r="D8" s="53"/>
+        <v>122</v>
+      </c>
+      <c r="D8" s="56"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:9" ht="52.5" customHeight="1">
       <c r="C9" s="39" t="s">
-        <v>135</v>
-      </c>
-      <c r="D9" s="53"/>
+        <v>134</v>
+      </c>
+      <c r="D9" s="56"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" ht="42.75" customHeight="1">
       <c r="C10" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="D10" s="53"/>
+        <v>127</v>
+      </c>
+      <c r="D10" s="56"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I10" s="4"/>
     </row>
@@ -11697,7 +11694,7 @@
       <c r="B11" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="53"/>
+      <c r="D11" s="56"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="4"/>
@@ -11705,7 +11702,7 @@
     </row>
     <row r="12" spans="1:9" ht="15">
       <c r="A12" s="14"/>
-      <c r="D12" s="53"/>
+      <c r="D12" s="56"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="4"/>
@@ -11714,12 +11711,12 @@
     </row>
     <row r="13" spans="1:9" ht="15">
       <c r="A13" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B13" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="53"/>
+      <c r="D13" s="56"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="4"/>
@@ -11731,7 +11728,7 @@
       <c r="B14" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="53"/>
+      <c r="D14" s="56"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="4"/>
@@ -11744,7 +11741,7 @@
         <v>64</v>
       </c>
       <c r="C15" s="7"/>
-      <c r="D15" s="53"/>
+      <c r="D15" s="56"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="4"/>
@@ -11757,7 +11754,7 @@
         <v>80</v>
       </c>
       <c r="C16" s="7"/>
-      <c r="D16" s="53"/>
+      <c r="D16" s="56"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="4"/>
@@ -11767,7 +11764,7 @@
     <row r="17" spans="1:9" ht="15">
       <c r="A17" s="21"/>
       <c r="C17" s="7"/>
-      <c r="D17" s="53"/>
+      <c r="D17" s="56"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="21"/>
@@ -11777,74 +11774,74 @@
     <row r="18" spans="1:9" ht="15">
       <c r="A18" s="21"/>
       <c r="C18" s="7"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="49"/>
       <c r="G18" s="33"/>
       <c r="H18" s="33"/>
-      <c r="I18" s="48"/>
+      <c r="I18" s="47"/>
     </row>
     <row r="19" spans="1:9" ht="15">
       <c r="C19" s="4"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
       <c r="G19" s="33"/>
       <c r="H19" s="33"/>
-      <c r="I19" s="48"/>
+      <c r="I19" s="47"/>
     </row>
     <row r="20" spans="1:9" ht="15">
       <c r="C20" s="7"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
       <c r="G20" s="33"/>
       <c r="H20" s="33"/>
-      <c r="I20" s="48"/>
+      <c r="I20" s="47"/>
     </row>
     <row r="21" spans="1:9" ht="15">
       <c r="C21" s="4"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
       <c r="G21" s="33"/>
       <c r="H21" s="33"/>
-      <c r="I21" s="48"/>
+      <c r="I21" s="47"/>
     </row>
     <row r="22" spans="1:9" ht="15">
       <c r="C22" s="7"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
       <c r="G22" s="33"/>
       <c r="H22" s="33"/>
-      <c r="I22" s="48"/>
+      <c r="I22" s="47"/>
     </row>
     <row r="23" spans="1:9" ht="15">
       <c r="C23" s="7"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
       <c r="G23" s="33"/>
       <c r="H23" s="33"/>
-      <c r="I23" s="48"/>
+      <c r="I23" s="47"/>
     </row>
     <row r="24" spans="1:9" ht="15">
       <c r="A24" s="15"/>
       <c r="B24" s="15"/>
       <c r="C24" s="8"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="49"/>
       <c r="G24" s="33"/>
       <c r="H24" s="21"/>
-      <c r="I24" s="48"/>
+      <c r="I24" s="47"/>
     </row>
     <row r="25" spans="1:9" ht="15">
       <c r="A25" s="4"/>
       <c r="B25" s="15"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="53"/>
+      <c r="D25" s="56"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="4"/>
@@ -11855,7 +11852,7 @@
       <c r="A26" s="4"/>
       <c r="B26" s="15"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="53"/>
+      <c r="D26" s="56"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
       <c r="G26" s="4"/>
@@ -11866,7 +11863,7 @@
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="7"/>
-      <c r="D27" s="53"/>
+      <c r="D27" s="56"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
@@ -11877,7 +11874,7 @@
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="53"/>
+      <c r="D28" s="56"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -11888,7 +11885,7 @@
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="53"/>
+      <c r="D29" s="56"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -11899,7 +11896,7 @@
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="53"/>
+      <c r="D30" s="56"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
@@ -11910,7 +11907,7 @@
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="53"/>
+      <c r="D31" s="56"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="4"/>
@@ -11921,7 +11918,7 @@
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="7"/>
-      <c r="D32" s="53"/>
+      <c r="D32" s="56"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="4"/>
@@ -11932,7 +11929,7 @@
       <c r="A33" s="4"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="53"/>
+      <c r="D33" s="56"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
       <c r="G33" s="4"/>
@@ -11943,7 +11940,7 @@
       <c r="A34" s="4"/>
       <c r="B34" s="7"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="53"/>
+      <c r="D34" s="56"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
@@ -11954,7 +11951,7 @@
       <c r="A35" s="4"/>
       <c r="B35" s="7"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="53"/>
+      <c r="D35" s="56"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
       <c r="G35" s="4"/>
@@ -11965,7 +11962,7 @@
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="7"/>
-      <c r="D36" s="53"/>
+      <c r="D36" s="56"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="4"/>
@@ -11976,7 +11973,7 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="53"/>
+      <c r="D37" s="56"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="4"/>
@@ -11987,7 +11984,7 @@
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="7"/>
-      <c r="D38" s="53"/>
+      <c r="D38" s="56"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="4"/>
@@ -11998,7 +11995,7 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="7"/>
-      <c r="D39" s="53"/>
+      <c r="D39" s="56"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="4"/>
@@ -12009,7 +12006,7 @@
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="7"/>
-      <c r="D40" s="53"/>
+      <c r="D40" s="56"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="4"/>
@@ -12020,7 +12017,7 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="53"/>
+      <c r="D41" s="56"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="4"/>
@@ -12031,7 +12028,7 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="53"/>
+      <c r="D42" s="56"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="4"/>
@@ -12042,7 +12039,7 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="53"/>
+      <c r="D43" s="56"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="4"/>
@@ -12053,7 +12050,7 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="7"/>
-      <c r="D44" s="53"/>
+      <c r="D44" s="56"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="4"/>
@@ -12064,7 +12061,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="53"/>
+      <c r="D45" s="56"/>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
       <c r="G45" s="4"/>
@@ -12075,7 +12072,7 @@
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="7"/>
-      <c r="D46" s="53"/>
+      <c r="D46" s="56"/>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
       <c r="G46" s="4"/>
@@ -12086,7 +12083,7 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="7"/>
-      <c r="D47" s="53"/>
+      <c r="D47" s="56"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
       <c r="G47" s="4"/>
@@ -12097,7 +12094,7 @@
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="7"/>
-      <c r="D48" s="53"/>
+      <c r="D48" s="56"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
       <c r="G48" s="4"/>
@@ -12108,7 +12105,7 @@
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="7"/>
-      <c r="D49" s="53"/>
+      <c r="D49" s="56"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
       <c r="G49" s="4"/>
@@ -12119,7 +12116,7 @@
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="53"/>
+      <c r="D50" s="56"/>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
       <c r="G50" s="4"/>
@@ -12130,7 +12127,7 @@
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="7"/>
-      <c r="D51" s="53"/>
+      <c r="D51" s="56"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
       <c r="G51" s="4"/>
@@ -12141,7 +12138,7 @@
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="7"/>
-      <c r="D52" s="53"/>
+      <c r="D52" s="56"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
       <c r="G52" s="4"/>
@@ -12152,7 +12149,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="53"/>
+      <c r="D53" s="56"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="4"/>
@@ -12163,7 +12160,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="53"/>
+      <c r="D54" s="56"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
       <c r="G54" s="4"/>
@@ -12174,7 +12171,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="7"/>
-      <c r="D55" s="53"/>
+      <c r="D55" s="56"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
       <c r="G55" s="4"/>
@@ -12185,7 +12182,7 @@
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="7"/>
-      <c r="D56" s="53"/>
+      <c r="D56" s="56"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
       <c r="G56" s="4"/>
@@ -12196,7 +12193,7 @@
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="7"/>
-      <c r="D57" s="53"/>
+      <c r="D57" s="56"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
       <c r="G57" s="4"/>
@@ -12207,7 +12204,7 @@
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="7"/>
-      <c r="D58" s="53"/>
+      <c r="D58" s="56"/>
       <c r="E58" s="7"/>
       <c r="F58" s="7"/>
       <c r="G58" s="4"/>
@@ -13057,6 +13054,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="D3:D58"/>
     <mergeCell ref="E3:E4"/>
@@ -13066,11 +13068,6 @@
     <mergeCell ref="I18:I24"/>
     <mergeCell ref="E18:E24"/>
     <mergeCell ref="F18:F24"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13092,27 +13089,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.65" customHeight="1" thickBot="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="D1" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="63" t="s">
+      <c r="E1" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="63" t="s">
+      <c r="F1" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="64" t="s">
+      <c r="G1" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="65"/>
-      <c r="I1" s="46" t="s">
+      <c r="H1" s="67"/>
+      <c r="I1" s="50" t="s">
         <v>0</v>
       </c>
     </row>
@@ -13123,40 +13120,40 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="46"/>
+      <c r="I2" s="50"/>
     </row>
     <row r="3" spans="1:9" ht="15">
       <c r="A3" s="19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B3" s="19" t="s">
         <v>50</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="54"/>
-      <c r="F3" s="55"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="57"/>
       <c r="G3" s="19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H3" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="I3" s="48"/>
+      <c r="I3" s="47"/>
     </row>
     <row r="4" spans="1:9" ht="14.25" customHeight="1">
       <c r="A4" s="19"/>
@@ -13164,33 +13161,33 @@
         <v>49</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="D4" s="53"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="55"/>
+        <v>123</v>
+      </c>
+      <c r="D4" s="56"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="57"/>
       <c r="G4" s="16"/>
       <c r="H4" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="I4" s="48"/>
+        <v>118</v>
+      </c>
+      <c r="I4" s="47"/>
     </row>
     <row r="5" spans="1:9" ht="15">
       <c r="C5" s="18"/>
-      <c r="D5" s="53"/>
+      <c r="D5" s="56"/>
       <c r="E5" s="18"/>
       <c r="F5" s="18"/>
       <c r="G5" s="16"/>
       <c r="H5" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I5" s="16"/>
     </row>
     <row r="6" spans="1:9" ht="15">
       <c r="C6" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="D6" s="53"/>
+        <v>124</v>
+      </c>
+      <c r="D6" s="56"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
       <c r="G6" s="16"/>
@@ -13201,9 +13198,9 @@
     </row>
     <row r="7" spans="1:9" ht="30">
       <c r="C7" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="D7" s="53"/>
+        <v>133</v>
+      </c>
+      <c r="D7" s="56"/>
       <c r="E7" s="18"/>
       <c r="F7" s="18"/>
       <c r="G7" s="16"/>
@@ -13214,9 +13211,9 @@
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="C8" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="D8" s="53"/>
+        <v>125</v>
+      </c>
+      <c r="D8" s="56"/>
       <c r="E8" s="18"/>
       <c r="F8" s="18"/>
       <c r="G8" s="16"/>
@@ -13231,7 +13228,7 @@
         <v>48</v>
       </c>
       <c r="C9" s="16"/>
-      <c r="D9" s="53"/>
+      <c r="D9" s="56"/>
       <c r="E9" s="18"/>
       <c r="F9" s="18"/>
       <c r="G9" s="16"/>
@@ -13243,7 +13240,7 @@
         <v>41</v>
       </c>
       <c r="C10" s="18"/>
-      <c r="D10" s="53"/>
+      <c r="D10" s="56"/>
       <c r="E10" s="18"/>
       <c r="F10" s="18"/>
       <c r="G10" s="16"/>
@@ -13253,7 +13250,7 @@
     <row r="11" spans="1:9" ht="15">
       <c r="A11" s="19"/>
       <c r="C11" s="16"/>
-      <c r="D11" s="53"/>
+      <c r="D11" s="56"/>
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
       <c r="G11" s="16"/>
@@ -13262,13 +13259,13 @@
     </row>
     <row r="12" spans="1:9" ht="15">
       <c r="A12" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>41</v>
       </c>
       <c r="C12" s="18"/>
-      <c r="D12" s="53"/>
+      <c r="D12" s="56"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="16"/>
@@ -13281,7 +13278,7 @@
         <v>49</v>
       </c>
       <c r="C13" s="18"/>
-      <c r="D13" s="53"/>
+      <c r="D13" s="56"/>
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
       <c r="G13" s="16"/>
@@ -13294,7 +13291,7 @@
         <v>64</v>
       </c>
       <c r="C14" s="18"/>
-      <c r="D14" s="53"/>
+      <c r="D14" s="56"/>
       <c r="E14" s="18"/>
       <c r="F14" s="18"/>
       <c r="G14" s="16"/>
@@ -13307,7 +13304,7 @@
         <v>80</v>
       </c>
       <c r="C15" s="18"/>
-      <c r="D15" s="53"/>
+      <c r="D15" s="56"/>
       <c r="E15" s="18"/>
       <c r="F15" s="18"/>
       <c r="G15" s="16"/>
@@ -13318,7 +13315,7 @@
       <c r="A16" s="26"/>
       <c r="B16" s="26"/>
       <c r="C16" s="18"/>
-      <c r="D16" s="53"/>
+      <c r="D16" s="56"/>
       <c r="E16" s="16"/>
       <c r="F16" s="16"/>
       <c r="G16" s="16"/>
@@ -13333,12 +13330,12 @@
         <v>50</v>
       </c>
       <c r="C17" s="8"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
-      <c r="I17" s="48"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="47"/>
     </row>
     <row r="18" spans="1:9" ht="15">
       <c r="A18" s="16"/>
@@ -13346,22 +13343,22 @@
         <v>51</v>
       </c>
       <c r="C18" s="8"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="48"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
     </row>
     <row r="19" spans="1:9" ht="15">
       <c r="A19" s="16"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="47"/>
     </row>
     <row r="20" spans="1:9" ht="15">
       <c r="A20" s="16" t="s">
@@ -13371,12 +13368,12 @@
         <v>52</v>
       </c>
       <c r="C20" s="8"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="48"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="47"/>
     </row>
     <row r="21" spans="1:9" ht="15">
       <c r="A21" s="16"/>
@@ -13384,36 +13381,36 @@
         <v>53</v>
       </c>
       <c r="C21" s="8"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="48"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="48"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="47"/>
+      <c r="I21" s="47"/>
     </row>
     <row r="22" spans="1:9" ht="15">
       <c r="C22" s="8"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="48"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
     </row>
     <row r="23" spans="1:9" ht="15">
       <c r="C23" s="8"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="48"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="48"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="47"/>
     </row>
     <row r="24" spans="1:9" ht="15">
       <c r="A24" s="15"/>
       <c r="B24" s="15"/>
       <c r="C24" s="18"/>
-      <c r="D24" s="53"/>
+      <c r="D24" s="56"/>
       <c r="E24" s="18"/>
       <c r="F24" s="18"/>
       <c r="G24" s="16"/>
@@ -13424,7 +13421,7 @@
       <c r="A25" s="16"/>
       <c r="B25" s="16"/>
       <c r="C25" s="18"/>
-      <c r="D25" s="53"/>
+      <c r="D25" s="56"/>
       <c r="E25" s="18"/>
       <c r="F25" s="18"/>
       <c r="G25" s="16"/>
@@ -13435,7 +13432,7 @@
       <c r="A26" s="16"/>
       <c r="B26" s="16"/>
       <c r="C26" s="18"/>
-      <c r="D26" s="53"/>
+      <c r="D26" s="56"/>
       <c r="E26" s="16"/>
       <c r="F26" s="16"/>
       <c r="G26" s="16"/>
@@ -13446,7 +13443,7 @@
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
       <c r="C27" s="18"/>
-      <c r="D27" s="53"/>
+      <c r="D27" s="56"/>
       <c r="E27" s="16"/>
       <c r="F27" s="16"/>
       <c r="G27" s="16"/>
@@ -13457,7 +13454,7 @@
       <c r="A28" s="16"/>
       <c r="B28" s="16"/>
       <c r="C28" s="18"/>
-      <c r="D28" s="53"/>
+      <c r="D28" s="56"/>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
       <c r="G28" s="16"/>
@@ -13468,7 +13465,7 @@
       <c r="A29" s="16"/>
       <c r="B29" s="16"/>
       <c r="C29" s="18"/>
-      <c r="D29" s="53"/>
+      <c r="D29" s="56"/>
       <c r="E29" s="16"/>
       <c r="F29" s="16"/>
       <c r="G29" s="16"/>
@@ -13479,7 +13476,7 @@
       <c r="A30" s="16"/>
       <c r="B30" s="18"/>
       <c r="C30" s="18"/>
-      <c r="D30" s="53"/>
+      <c r="D30" s="56"/>
       <c r="E30" s="18"/>
       <c r="F30" s="18"/>
       <c r="G30" s="16"/>
@@ -13490,7 +13487,7 @@
       <c r="A31" s="16"/>
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
-      <c r="D31" s="53"/>
+      <c r="D31" s="56"/>
       <c r="E31" s="18"/>
       <c r="F31" s="18"/>
       <c r="G31" s="16"/>
@@ -13501,7 +13498,7 @@
       <c r="A32" s="16"/>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
-      <c r="D32" s="53"/>
+      <c r="D32" s="56"/>
       <c r="E32" s="18"/>
       <c r="F32" s="18"/>
       <c r="G32" s="16"/>
@@ -13512,7 +13509,7 @@
       <c r="A33" s="16"/>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
-      <c r="D33" s="53"/>
+      <c r="D33" s="56"/>
       <c r="E33" s="16"/>
       <c r="F33" s="16"/>
       <c r="G33" s="16"/>
@@ -13523,7 +13520,7 @@
       <c r="A34" s="16"/>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
-      <c r="D34" s="53"/>
+      <c r="D34" s="56"/>
       <c r="E34" s="18"/>
       <c r="F34" s="18"/>
       <c r="G34" s="16"/>
@@ -13534,7 +13531,7 @@
       <c r="A35" s="16"/>
       <c r="B35" s="16"/>
       <c r="C35" s="18"/>
-      <c r="D35" s="53"/>
+      <c r="D35" s="56"/>
       <c r="E35" s="18"/>
       <c r="F35" s="18"/>
       <c r="G35" s="16"/>
@@ -13545,7 +13542,7 @@
       <c r="A36" s="16"/>
       <c r="B36" s="16"/>
       <c r="C36" s="18"/>
-      <c r="D36" s="53"/>
+      <c r="D36" s="56"/>
       <c r="E36" s="18"/>
       <c r="F36" s="18"/>
       <c r="G36" s="16"/>
@@ -13556,7 +13553,7 @@
       <c r="A37" s="16"/>
       <c r="B37" s="16"/>
       <c r="C37" s="18"/>
-      <c r="D37" s="53"/>
+      <c r="D37" s="56"/>
       <c r="E37" s="18"/>
       <c r="F37" s="18"/>
       <c r="G37" s="16"/>
@@ -13567,7 +13564,7 @@
       <c r="A38" s="16"/>
       <c r="B38" s="16"/>
       <c r="C38" s="18"/>
-      <c r="D38" s="53"/>
+      <c r="D38" s="56"/>
       <c r="E38" s="18"/>
       <c r="F38" s="18"/>
       <c r="G38" s="16"/>
@@ -13578,7 +13575,7 @@
       <c r="A39" s="16"/>
       <c r="B39" s="16"/>
       <c r="C39" s="18"/>
-      <c r="D39" s="53"/>
+      <c r="D39" s="56"/>
       <c r="E39" s="18"/>
       <c r="F39" s="18"/>
       <c r="G39" s="16"/>
@@ -13589,7 +13586,7 @@
       <c r="A40" s="16"/>
       <c r="B40" s="16"/>
       <c r="C40" s="18"/>
-      <c r="D40" s="53"/>
+      <c r="D40" s="56"/>
       <c r="E40" s="18"/>
       <c r="F40" s="18"/>
       <c r="G40" s="16"/>
@@ -13600,7 +13597,7 @@
       <c r="A41" s="16"/>
       <c r="B41" s="16"/>
       <c r="C41" s="18"/>
-      <c r="D41" s="53"/>
+      <c r="D41" s="56"/>
       <c r="E41" s="18"/>
       <c r="F41" s="18"/>
       <c r="G41" s="16"/>
@@ -13611,7 +13608,7 @@
       <c r="A42" s="16"/>
       <c r="B42" s="16"/>
       <c r="C42" s="18"/>
-      <c r="D42" s="53"/>
+      <c r="D42" s="56"/>
       <c r="E42" s="18"/>
       <c r="F42" s="18"/>
       <c r="G42" s="16"/>
@@ -13622,7 +13619,7 @@
       <c r="A43" s="16"/>
       <c r="B43" s="16"/>
       <c r="C43" s="18"/>
-      <c r="D43" s="53"/>
+      <c r="D43" s="56"/>
       <c r="E43" s="18"/>
       <c r="F43" s="18"/>
       <c r="G43" s="16"/>
@@ -13633,7 +13630,7 @@
       <c r="A44" s="16"/>
       <c r="B44" s="16"/>
       <c r="C44" s="18"/>
-      <c r="D44" s="53"/>
+      <c r="D44" s="56"/>
       <c r="E44" s="18"/>
       <c r="F44" s="18"/>
       <c r="G44" s="16"/>
@@ -13644,7 +13641,7 @@
       <c r="A45" s="16"/>
       <c r="B45" s="16"/>
       <c r="C45" s="18"/>
-      <c r="D45" s="53"/>
+      <c r="D45" s="56"/>
       <c r="E45" s="18"/>
       <c r="F45" s="18"/>
       <c r="G45" s="16"/>
@@ -13655,7 +13652,7 @@
       <c r="A46" s="16"/>
       <c r="B46" s="16"/>
       <c r="C46" s="18"/>
-      <c r="D46" s="53"/>
+      <c r="D46" s="56"/>
       <c r="E46" s="18"/>
       <c r="F46" s="18"/>
       <c r="G46" s="16"/>
@@ -13666,7 +13663,7 @@
       <c r="A47" s="16"/>
       <c r="B47" s="16"/>
       <c r="C47" s="18"/>
-      <c r="D47" s="53"/>
+      <c r="D47" s="56"/>
       <c r="E47" s="18"/>
       <c r="F47" s="18"/>
       <c r="G47" s="16"/>
@@ -13677,7 +13674,7 @@
       <c r="A48" s="16"/>
       <c r="B48" s="16"/>
       <c r="C48" s="18"/>
-      <c r="D48" s="53"/>
+      <c r="D48" s="56"/>
       <c r="E48" s="18"/>
       <c r="F48" s="18"/>
       <c r="G48" s="16"/>
@@ -13688,7 +13685,7 @@
       <c r="A49" s="16"/>
       <c r="B49" s="16"/>
       <c r="C49" s="18"/>
-      <c r="D49" s="53"/>
+      <c r="D49" s="56"/>
       <c r="E49" s="18"/>
       <c r="F49" s="18"/>
       <c r="G49" s="16"/>
@@ -13699,7 +13696,7 @@
       <c r="A50" s="16"/>
       <c r="B50" s="16"/>
       <c r="C50" s="18"/>
-      <c r="D50" s="53"/>
+      <c r="D50" s="56"/>
       <c r="E50" s="18"/>
       <c r="F50" s="18"/>
       <c r="G50" s="16"/>
@@ -13710,7 +13707,7 @@
       <c r="A51" s="16"/>
       <c r="B51" s="16"/>
       <c r="C51" s="18"/>
-      <c r="D51" s="53"/>
+      <c r="D51" s="56"/>
       <c r="E51" s="18"/>
       <c r="F51" s="18"/>
       <c r="G51" s="16"/>
@@ -13721,7 +13718,7 @@
       <c r="A52" s="16"/>
       <c r="B52" s="16"/>
       <c r="C52" s="18"/>
-      <c r="D52" s="53"/>
+      <c r="D52" s="56"/>
       <c r="E52" s="18"/>
       <c r="F52" s="18"/>
       <c r="G52" s="16"/>
@@ -13732,7 +13729,7 @@
       <c r="A53" s="16"/>
       <c r="B53" s="16"/>
       <c r="C53" s="18"/>
-      <c r="D53" s="53"/>
+      <c r="D53" s="56"/>
       <c r="E53" s="18"/>
       <c r="F53" s="18"/>
       <c r="G53" s="16"/>
@@ -13743,7 +13740,7 @@
       <c r="A54" s="16"/>
       <c r="B54" s="16"/>
       <c r="C54" s="18"/>
-      <c r="D54" s="53"/>
+      <c r="D54" s="56"/>
       <c r="E54" s="18"/>
       <c r="F54" s="18"/>
       <c r="G54" s="16"/>
@@ -13754,7 +13751,7 @@
       <c r="A55" s="16"/>
       <c r="B55" s="16"/>
       <c r="C55" s="18"/>
-      <c r="D55" s="53"/>
+      <c r="D55" s="56"/>
       <c r="E55" s="18"/>
       <c r="F55" s="18"/>
       <c r="G55" s="16"/>
@@ -13765,7 +13762,7 @@
       <c r="A56" s="16"/>
       <c r="B56" s="16"/>
       <c r="C56" s="18"/>
-      <c r="D56" s="53"/>
+      <c r="D56" s="56"/>
       <c r="E56" s="18"/>
       <c r="F56" s="18"/>
       <c r="G56" s="16"/>
@@ -13776,7 +13773,7 @@
       <c r="A57" s="16"/>
       <c r="B57" s="16"/>
       <c r="C57" s="18"/>
-      <c r="D57" s="53"/>
+      <c r="D57" s="56"/>
       <c r="E57" s="18"/>
       <c r="F57" s="18"/>
       <c r="G57" s="16"/>
@@ -14621,11 +14618,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="D3:D57"/>
     <mergeCell ref="E3:E4"/>
@@ -14637,6 +14629,11 @@
     <mergeCell ref="H17:H23"/>
     <mergeCell ref="I17:I23"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Mapping Template BrotZeit.xlsx
+++ b/Mapping Template BrotZeit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alfa\Documents\Data Engineer\Projekt\BackZeit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{806E9E10-A2FA-4230-8215-5AD092E35747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3255F7B-00C9-43E9-A892-CD758785137E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="3300" windowWidth="21600" windowHeight="11385" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="D_Filiale" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="142">
   <si>
     <t>Source DB / csv / ….</t>
   </si>
@@ -77,9 +77,6 @@
   </si>
   <si>
     <t>1:1 Mapping</t>
-  </si>
-  <si>
-    <t>SELECT …..  (view, stored proc im Source-system)</t>
   </si>
   <si>
     <t>RAW_sourceTableName</t>
@@ -367,9 +364,6 @@
     <t>Verkauf</t>
   </si>
   <si>
-    <t>SELECT …..</t>
-  </si>
-  <si>
     <t>F_Verkäufe</t>
   </si>
   <si>
@@ -444,12 +438,364 @@
   <si>
     <t>[Gewinnbetrag]</t>
   </si>
+  <si>
+    <t>USE DWH_BackZeit;
+GO
+-- Entfernen der Stored Procedure, falls sie existiert
+IF OBJECT_ID('sp_FillFactVerkaeuferumsatz', 'P') IS NOT NULL
+    BEGIN
+        DROP PROCEDURE sp_FillFactVerkaeuferumsatz;
+    END
+GO
+-- Erstellen der Stored Procedure
+CREATE PROCEDURE sp_FillFactVerkaeuferumsatz
+AS
+BEGIN
+    WITH BisherigeWerte AS
+        (SELECT bdbv.VerkäuferID AS VerkäuferID, SUM(vv.Umsatz) AS bisherigeUmsätze, COUNT(vv.VerkaufsvorgangID) AS bisherigeVerkäufe
+            FROM D_Verkaufsvorgang AS vv
+            Inner JOIN
+            BDB_BackZeit.bdb_Kassensystem.Verkauf AS bdbv
+            ON vv.Zeitpunkt = bdbv.Zeitpunkt AND vv.FilialID = bdbv.FilialID
+        GROUP BY bdbv.VerkäuferID)
+    INSERT INTO F_Verkäuferumsatz (DatumID, VerkäuferID, VerkaufsvorgangID, Gesamtumsatz, AnzahlVerkäufe)
+    SELECT  CONVERT(INT, CONVERT(CHAR(8), vv.Zeitpunkt, 112)),
+            v.VerkäuferID,
+            vv.VerkaufsvorgangID,
+            bw.bisherigeUmsätze,
+            bw.bisherigeVerkäufe
+    FROM   D_Verkäufer AS v
+           Inner JOIN
+           BDB_BackZeit.bdb_Kassensystem.Verkauf AS bdbv
+           ON bdbv.VerkäuferID = v.VerkäuferID
+           INNER JOIN
+           D_Verkaufsvorgang AS vv
+           ON vv.Zeitpunkt = bdbv.Zeitpunkt AND vv.FilialID = bdbv.FilialID
+           INNER JOIN
+           BisherigeWerte AS bw
+           ON bw.VerkäuferID = v.VerkäuferID
+END
+GO
+EXEC sp_FillFactVerkaeuferumsatz;
+SELECT *
+FROM   F_Verkäuferumsatz;
+--DELETE F_Verkäuferumsatz;
+    SELECT …..</t>
+  </si>
+  <si>
+    <t>USE DWH_BackZeit;
+GO
+-- Entfernen der Stored Procedure, falls sie existiert
+IF OBJECT_ID('dbo.ETL_F_Verkaeufe', 'P') IS NOT NULL
+BEGIN
+    DROP PROCEDURE dbo.ETL_F_Verkaeufe;
+END
+GO
+-- Erstellen der Stored Procedure
+CREATE PROCEDURE dbo.ETL_F_Verkaeufe
+AS
+BEGIN
+    SET NOCOUNT ON;
+    INSERT INTO DWH_BackZeit.dbo.F_Verkäufe (DatumID, ZeitID, ProduktID, FilialID, VerkäuferID, AnzahlProdukte, Umsatz, Gewinn)
+    SELECT
+        CONVERT(INT, CONVERT(CHAR(8), CAST(v.Zeitpunkt AS DATE), 112)) AS DatumID,
+        DATEPART(HOUR, v.Zeitpunkt) AS ZeitID,
+        w.ProduktID,
+        v.FilialID,
+        v.VerkäuferID,
+        -- AnzahlProdukte
+        CAST(w.Menge AS SMALLINT) AS AnzahlProdukte,
+        --Umsatz
+        CAST( w.Menge * p.Nettopreis AS DECIMAL(7,2)) AS Umsatz,
+        -- Gewinn
+        CAST(w.Menge * dp.Gewinnbetrag AS DECIMAL(7,2)) AS Gewinn
+    FROM BDB_BackZeit.bdb_Kassensystem.Verkauf v
+    INNER JOIN BDB_BackZeit.bdb_Kassensystem.wirdVerkauft w
+        ON v.Zeitpunkt = w.Zeitpunkt
+        AND v.FilialID = w.FilialID
+    INNER JOIN BDB_BackZeit.bdb_Kassensystem.Produkt p
+        ON w.ProduktID = p.ProduktID
+    INNER JOIN DWH_BackZeit.dbo.D_Produkt dp
+        ON w.ProduktID = dp.ProduktID
+    -- Verhindert, dass bereits geladene Verkäufe erneut eingefügt werden
+    WHERE NOT EXISTS
+    (
+        SELECT 1
+        FROM DWH_BackZeit.dbo.F_Verkäufe f
+        WHERE f.DatumID =
+              CONVERT(INT, CONVERT(CHAR(8), CAST(v.Zeitpunkt AS DATE), 112))
+          AND f.ZeitID = DATEPART(HOUR, v.Zeitpunkt)
+          AND f.ProduktID = w.ProduktID
+          AND f.FilialID = v.FilialID
+          AND f.VerkäuferID = v.VerkäuferID
+    );
+END;
+GO
+EXEC dbo.ETL_F_Verkaeufe;
+GO
+SELECT * FROM DWH_BackZeit.dbo.F_Verkäufe
+--DELETE DWH_BackZeit.dbo.F_Verkäufe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">--- ETL für Dimension Verkäufer
+USE BDB_BackZeit;
+GO
+-- Stored Procedure entfernen, falls sie bereits existiert
+IF OBJECT_ID('sp_FillDimVerkäufer', 'P') IS NOT NULL
+    BEGIN
+        DROP PROCEDURE sp_FillDimVerkäufer;
+    END
+GO
+-- Stored Procedure erstellen
+CREATE PROCEDURE sp_FillDimVerkäufer
+AS
+BEGIN
+INSERT INTO DWH_BackZeit.dbo.D_Verkäufer(VerkäuferID, VerkäuferName)
+SELECT
+    v.VerkäuferID,
+    m.MitarbeiterName
+FROM bdb_Kassensystem.Verkäufer AS v
+INNER JOIN bdb_Personal.Mitarbeiter AS m
+    ON v.MitarbeiterID = m.MitarbeiterID
+WHERE
+    NOT EXISTS
+        (SELECT 1
+        FROM DWH_BackZeit.dbo.D_Verkäufer AS dv
+            WHERE dv.VerkäuferID = v.VerkäuferID
+        );
+END
+GO
+-- Stored Procedure ausführen
+EXECUTE sp_FillDimVerkäufer;
+GO
+-- Ergebnis kontrollieren
+SELECT *
+FROM   DWH_BackZeit.dbo.D_Verkäufer;
+</t>
+  </si>
+  <si>
+    <t>USE DWH_BackZeit;
+GO
+-- Stored Procedure entfernen, falls sie bereits existiert
+IF OBJECT_ID('sp_FillDimProdukt', 'P') IS NOT NULL
+    BEGIN
+        DROP PROCEDURE sp_FillDimProdukt;
+    END
+GO
+-- Stored Procedure erstellen
+CREATE PROCEDURE sp_FillDimProdukt
+AS
+BEGIN
+    SET NOCOUNT ON;
+    /*
+        Für jedes Produkt wird zunächst die aktuellste
+        Rezeptversion ermittelt.
+    */;
+    WITH AktuelleRezeptVersion
+    AS   (SELECT   ProduktID,
+                   MAX(RezeptVersion) AS RezeptVersion
+          FROM     BDB_BackZeit.bdb_Rezepte.Rezept
+          GROUP BY ProduktID),
+         AktuelleRezepte
+    AS   (SELECT r.ProduktID,
+                 r.Zubereitungsdauer,
+                 r.Backzeit,
+                 r.Stückzahl
+          FROM   BDB_BackZeit.bdb_Rezepte.Rezept AS r
+                 INNER JOIN
+                 AktuelleRezeptVersion AS ar
+                 ON r.ProduktID = ar.ProduktID
+                    AND r.RezeptVersion = ar.RezeptVersion),
+         -- Kostenberechnung pro Produkt (aggregiert über alle Zutaten)
+         ProduktKosten
+    AS   (SELECT   b.ProduktID,
+                   SUM(z.LagerkostenProg * b.Menge) AS GesamtLagerkosten,
+                   SUM(z.PreisProKg * b.Menge * 0.0001) AS GesamtZutatenkosten
+            FROM     BDB_BackZeit.bdb_Rezepte.beinhaltet AS b
+                     INNER JOIN
+                     BDB_BackZeit.bdb_Rezepte.Zutat AS z
+                     ON b.ZutatID = z.ZutatID
+            GROUP BY b.ProduktID)
+    INSERT INTO D_Produkt (ProduktID, ProduktName, Bruttopreis, Nettopreis, Lagerkosten, Backkosten, Lohnkosten, Zutatenkosten, KategorieID, KategorieName)
+    SELECT   p.ProduktID,
+             p.ProduktName,
+             p.Bruttopreis,
+             p.Nettopreis,
+             pc.GesamtLagerkosten / r.Stückzahl,  -- Lagerkosten pro Stück
+             r.Backzeit * 5 / r.Stückzahl,        -- Backkosten pro Stück
+             r.Zubereitungsdauer * 1 / r.Stückzahl, -- Lohnkosten pro Stück
+             pc.GesamtZutatenkosten / r.Stückzahl, -- Zutatenkosten pro Stück
+             p.KategorieID,
+             k.KategorieName
+    FROM     BDB_BackZeit.bdb_Kassensystem.Produkt AS p
+             INNER JOIN
+             AktuelleRezepte AS r
+             ON p.ProduktID = r.ProduktID
+             INNER JOIN
+             ProduktKosten AS pc
+             ON p.ProduktID = pc.ProduktID
+             INNER JOIN
+             BDB_BackZeit.bdb_Kassensystem.Kategorie AS k
+             ON p.KategorieID = k.KategorieID;
+END
+GO
+-- Stored Procedure ausführen
+EXECUTE sp_FillDimProdukt;
+GO
+-- Ergebnis kontrollieren
+SELECT *
+FROM   D_Produkt</t>
+  </si>
+  <si>
+    <t>--- ETL für Dimension Filiale
+USE BDB_BackZeit;
+GO
+-- Stored Procedure entfernen, falls sie bereits existiert
+IF OBJECT_ID('sp_FillDimFiliale', 'P') IS NOT NULL
+    BEGIN
+        DROP PROCEDURE sp_FillDimFiliale;
+    END
+GO
+-- Stored Procedure erstellen
+CREATE PROCEDURE sp_FillDimFiliale
+AS
+BEGIN
+INSERT INTO DWH_BackZeit.dbo.D_Filiale (FilialID, FilialName, FilialOrt)
+SELECT
+    f.FilialID,
+    f.Filialname,
+    CONCAT(a.AdresseID, '.', a.Ort) AS FilialOrt
+FROM
+    BDB_BackZeit.bdb_Immobilienverwaltung.Filiale AS f
+JOIN
+    BDB_BackZeit.bdb_Verwaltung.Adresse AS a ON f.AdresseID = a.AdresseID
+WHERE
+    NOT EXISTS
+        (SELECT 1
+        FROM DWH_BackZeit.dbo.D_Filiale AS df
+            WHERE df.FilialID = f.FilialID
+        );
+END
+GO
+-- Stored Procedure ausführen
+EXECUTE sp_FillDimFiliale;
+GO
+-- Ergebnis kontrollieren
+SELECT *
+FROM   DWH_BackZeit.dbo.D_Filiale;C20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">--- ETL für Dimension Datum
+USE DWH_BackZeit;
+-- Entfernen der Stored Procedure, falls sie existiert
+IF OBJECT_ID('sp_FillDimDatum', 'P') IS NOT NULL
+    BEGIN
+        DROP PROCEDURE sp_FillDimDatum;
+    END
+GO
+-- Erstellen der Stored Procedure
+CREATE PROCEDURE sp_FillDimDatum
+AS
+BEGIN
+    INSERT INTO DWH_BackZeit.dbo.D_Datum(DatumID, Tag, Quartal, Monat, Jahr, Wochentag, MonatLang, MonatKurz)
+    SELECT DISTINCT
+        CONVERT(INT, CONVERT(CHAR(8), Zeitpunkt, 112)) AS DatumID, -- 112 ist Format YYYYMMDD
+        CONVERT(CHAR(10), Zeitpunkt, 23) AS Tag, -- 23 ist Format YYYY-MM-DD
+        CONCAT(YEAR(Zeitpunkt), '-Q', DATEPART(QUARTER, Zeitpunkt)) AS Quartal,
+        CONVERT(CHAR(7), Zeitpunkt, 23) AS Monat,
+        YEAR(Zeitpunkt) AS Jahr,
+        --Wochentag bestimmen
+        --Variante1: Problem: hängt von den Server Einstellungen ab und kann daher falsche Werte liefern
+        --CASE DATEPART(WEEKDAY, Zeitpunkt)
+        --    WHEN 1 THEN 'Sonntag'
+        --    WHEN 2 THEN 'Montag'
+        --    WHEN 3 THEN 'Dienstag'
+        --    WHEN 4 THEN 'Mittwoch'
+        --    WHEN 5 THEN 'Donnerstag'
+        --    WHEN 6 THEN 'Freitag'
+        --    WHEN 7 THEN 'Samstag'
+        --END AS Wochentag,
+        --Variante2: Rechnet über einen bekannten Montag (1.1.1900) aus welcher Wochentag ist, dadurch ist das Ergebnis unabhängig von den Server Einstellungen
+        CASE
+            WHEN DATEDIFF(DAY, '19000101', Zeitpunkt) % 7 = 0 THEN 'Montag' -- Wenn die Differenz zwischen dem Zeitpunkt und 01.01.1900, restlos durch 7 teilbar ist, dann ist es ein Montag 
+            WHEN DATEDIFF(DAY, '19000101', Zeitpunkt) % 7 = 1 THEN 'Dienstag' -- Bei einem Rest von 1, muss es ein Dienstag sein usw.
+            WHEN DATEDIFF(DAY, '19000101', Zeitpunkt) % 7 = 2 THEN 'Mittwoch'
+            WHEN DATEDIFF(DAY, '19000101', Zeitpunkt) % 7 = 3 THEN 'Donnerstag'
+            WHEN DATEDIFF(DAY, '19000101', Zeitpunkt) % 7 = 4 THEN 'Freitag'
+            WHEN DATEDIFF(DAY, '19000101', Zeitpunkt) % 7 = 5 THEN 'Samstag'
+            WHEN DATEDIFF(DAY, '19000101', Zeitpunkt) % 7 = 6 THEN 'Sonntag'
+        END AS Wochentag,
+        CASE MONTH(Zeitpunkt)
+            WHEN 1 THEN 'Januar'
+            WHEN 2 THEN 'Februar'
+            WHEN 3 THEN 'März'
+            WHEN 4 THEN 'April'
+            WHEN 5 THEN 'Mai'
+            WHEN 6 THEN 'Juni'
+            WHEN 7 THEN 'Juli'
+            WHEN 8 THEN 'August'
+            WHEN 9 THEN 'September'
+            WHEN 10 THEN 'Oktober'
+            WHEN 11 THEN 'November'
+            WHEN 12 THEN 'Dezember'
+        END AS MonatLang,
+        CASE MONTH(Zeitpunkt)
+            WHEN 1 THEN 'Jan'
+            WHEN 2 THEN 'Feb'
+            WHEN 3 THEN 'Mär'
+            WHEN 4 THEN 'Apr'
+            WHEN 5 THEN 'Mai'
+            WHEN 6 THEN 'Jun'
+            WHEN 7 THEN 'Jul'
+            WHEN 8 THEN 'Aug'
+            WHEN 9 THEN 'Sep'
+            WHEN 10 THEN 'Okt'
+            WHEN 11 THEN 'Nov'
+            WHEN 12 THEN 'Dez'
+        END AS MonatKurz
+    FROM
+        BDB_BackZeit.bdb_Kassensystem.Verkauf v
+        -- Verhindert, dass bereits vorhandene Tage erneut eingefügt werden
+    WHERE NOT EXISTS
+    (
+        SELECT 1
+        FROM DWH_BackZeit.dbo.D_Datum d
+        WHERE d.DatumID =
+              CONVERT(
+                  INT,
+                  CONVERT(CHAR(8), v.Zeitpunkt, 112)
+              )
+    );
+END
+GO
+EXEC sp_FillDimDatum;
+SELECT * FROM DWH_BackZeit.dbo.D_Datum;
+---------
+</t>
+  </si>
+  <si>
+    <t>USE BDB_BackZeit;
+INSERT INTO DWH_BackZeit.dbo.D_Verkaufsvorgang(Zahlart, FilialID, Zeitpunkt, Umsatz) 
+SELECT
+    v.Zahlart,
+    wirdV.FilialID,
+    wirdV.Zeitpunkt,
+    SUM(wirdV.Menge * p.Bruttopreis) AS Umsatz
+FROM
+    BDB_BackZeit.bdb_Kassensystem.wirdVerkauft AS wirdV 
+JOIN
+    BDB_BackZeit.bdb_Kassensystem.Produkt AS p ON wirdV.ProduktID = p.ProduktID
+JOIN
+    BDB_BackZeit.bdb_Kassensystem.Verkauf AS v ON v.FilialID = wirdV.FilialID AND wirdV.Zeitpunkt = v.Zeitpunkt
+GROUP BY wirdV.FilialID, wirdV.Zeitpunkt, v.Zahlart;
+SELECT * FROM DWH_BackZeit.dbo.D_Verkaufsvorgang</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -513,8 +859,14 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -555,6 +907,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
         <bgColor rgb="FF33CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -683,7 +1041,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -748,29 +1106,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -782,6 +1120,23 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -797,6 +1152,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1075,30 +1442,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.25" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="29"/>
+      <c r="H1" s="40"/>
       <c r="I1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="J1" s="41" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1109,10 +1476,10 @@
       <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
       <c r="G2" s="5" t="s">
         <v>10</v>
       </c>
@@ -1120,86 +1487,86 @@
         <v>11</v>
       </c>
       <c r="I2" s="3"/>
-      <c r="J2" s="30"/>
+      <c r="J2" s="41"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="E3" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="F3" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="35" t="s">
+      <c r="G3" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="36" t="s">
+      <c r="H3" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="9" t="s">
+      <c r="J3" s="35"/>
+    </row>
+    <row r="4" spans="1:10" ht="15">
+      <c r="A4" s="37"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="28"/>
-    </row>
-    <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="31"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="28"/>
+      <c r="J4" s="35"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="9"/>
       <c r="B5" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="33"/>
+      <c r="D5" s="48"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="9" t="s">
         <v>22</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>23</v>
       </c>
       <c r="J5" s="9"/>
     </row>
     <row r="6" spans="1:10" ht="15">
       <c r="A6" s="9"/>
       <c r="B6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="33"/>
+      <c r="D6" s="48"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
@@ -1208,101 +1575,101 @@
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="33"/>
+      <c r="D7" s="48"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="9"/>
       <c r="H7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="9"/>
+      <c r="J7" s="36" t="s">
         <v>27</v>
-      </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="37" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15">
       <c r="A8" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>30</v>
-      </c>
       <c r="C8" s="11"/>
-      <c r="D8" s="33"/>
+      <c r="D8" s="48"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
       <c r="I8" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8" s="37"/>
+        <v>30</v>
+      </c>
+      <c r="J8" s="36"/>
     </row>
     <row r="9" spans="1:10" ht="15">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
-      <c r="D9" s="33"/>
+      <c r="D9" s="48"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
       <c r="I9" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="37"/>
+        <v>31</v>
+      </c>
+      <c r="J9" s="36"/>
     </row>
     <row r="10" spans="1:10" ht="15">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="33"/>
+      <c r="D10" s="48"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="J10" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="J10" s="36"/>
     </row>
     <row r="11" spans="1:10" ht="15">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
-      <c r="D11" s="33"/>
+      <c r="D11" s="48"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J11" s="37"/>
+        <v>33</v>
+      </c>
+      <c r="J11" s="36"/>
     </row>
     <row r="12" spans="1:10" ht="15">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="33"/>
+      <c r="D12" s="48"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
-      <c r="J12" s="37"/>
+      <c r="J12" s="36"/>
     </row>
     <row r="13" spans="1:10" ht="15">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="33"/>
+      <c r="D13" s="48"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J13" s="9"/>
     </row>
@@ -1310,7 +1677,7 @@
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="33"/>
+      <c r="D14" s="48"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="9"/>
@@ -1322,13 +1689,13 @@
       <c r="A15" s="9"/>
       <c r="B15" s="9"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="33"/>
+      <c r="D15" s="48"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J15" s="9"/>
     </row>
@@ -1336,7 +1703,7 @@
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="33"/>
+      <c r="D16" s="48"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
@@ -1345,94 +1712,94 @@
       <c r="J16" s="9"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="38"/>
-      <c r="B17" s="38"/>
+      <c r="A17" s="39"/>
+      <c r="B17" s="39"/>
       <c r="C17" s="12"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
       <c r="I17" s="9"/>
-      <c r="J17" s="28"/>
+      <c r="J17" s="35"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="38"/>
-      <c r="B18" s="38"/>
+      <c r="A18" s="39"/>
+      <c r="B18" s="39"/>
       <c r="C18" s="12"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
       <c r="I18" s="9"/>
-      <c r="J18" s="28"/>
+      <c r="J18" s="35"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="38"/>
-      <c r="B19" s="38"/>
+      <c r="A19" s="39"/>
+      <c r="B19" s="39"/>
       <c r="C19" s="12"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
       <c r="I19" s="9"/>
-      <c r="J19" s="28"/>
+      <c r="J19" s="35"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="38"/>
-      <c r="B20" s="38"/>
+      <c r="A20" s="39"/>
+      <c r="B20" s="39"/>
       <c r="C20" s="12"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
       <c r="I20" s="9"/>
-      <c r="J20" s="28"/>
+      <c r="J20" s="35"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="38"/>
-      <c r="B21" s="38"/>
+      <c r="A21" s="39"/>
+      <c r="B21" s="39"/>
       <c r="C21" s="12"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
       <c r="I21" s="9"/>
-      <c r="J21" s="28"/>
+      <c r="J21" s="35"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="38"/>
-      <c r="B22" s="38"/>
+      <c r="A22" s="39"/>
+      <c r="B22" s="39"/>
       <c r="C22" s="12"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
       <c r="I22" s="9"/>
-      <c r="J22" s="28"/>
+      <c r="J22" s="35"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="38"/>
-      <c r="B23" s="38"/>
+      <c r="A23" s="39"/>
+      <c r="B23" s="39"/>
       <c r="C23" s="12"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
       <c r="I23" s="9"/>
-      <c r="J23" s="28"/>
+      <c r="J23" s="35"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="33"/>
+      <c r="D24" s="48"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="9"/>
@@ -1444,7 +1811,7 @@
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="33"/>
+      <c r="D25" s="48"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="9"/>
@@ -1456,7 +1823,7 @@
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="33"/>
+      <c r="D26" s="48"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
@@ -1468,7 +1835,7 @@
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="33"/>
+      <c r="D27" s="48"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
@@ -1480,7 +1847,7 @@
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="33"/>
+      <c r="D28" s="48"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
@@ -1492,7 +1859,7 @@
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="33"/>
+      <c r="D29" s="48"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
@@ -1504,7 +1871,7 @@
       <c r="A30" s="9"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="33"/>
+      <c r="D30" s="48"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="9"/>
@@ -1516,7 +1883,7 @@
       <c r="A31" s="9"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="33"/>
+      <c r="D31" s="48"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="9"/>
@@ -1528,7 +1895,7 @@
       <c r="A32" s="9"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="33"/>
+      <c r="D32" s="48"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="9"/>
@@ -1540,7 +1907,7 @@
       <c r="A33" s="9"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
-      <c r="D33" s="33"/>
+      <c r="D33" s="48"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
@@ -1552,7 +1919,7 @@
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
-      <c r="D34" s="33"/>
+      <c r="D34" s="48"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="9"/>
@@ -1564,7 +1931,7 @@
       <c r="A35" s="9"/>
       <c r="B35" s="9"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="33"/>
+      <c r="D35" s="48"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="9"/>
@@ -1576,7 +1943,7 @@
       <c r="A36" s="9"/>
       <c r="B36" s="9"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="33"/>
+      <c r="D36" s="48"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="9"/>
@@ -1588,7 +1955,7 @@
       <c r="A37" s="9"/>
       <c r="B37" s="9"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="33"/>
+      <c r="D37" s="48"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="9"/>
@@ -1600,7 +1967,7 @@
       <c r="A38" s="9"/>
       <c r="B38" s="9"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="33"/>
+      <c r="D38" s="48"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="9"/>
@@ -1612,7 +1979,7 @@
       <c r="A39" s="9"/>
       <c r="B39" s="9"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="33"/>
+      <c r="D39" s="48"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="9"/>
@@ -1624,7 +1991,7 @@
       <c r="A40" s="9"/>
       <c r="B40" s="9"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="33"/>
+      <c r="D40" s="48"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="9"/>
@@ -1636,7 +2003,7 @@
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="33"/>
+      <c r="D41" s="48"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="9"/>
@@ -1648,7 +2015,7 @@
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="33"/>
+      <c r="D42" s="48"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="9"/>
@@ -1660,7 +2027,7 @@
       <c r="A43" s="9"/>
       <c r="B43" s="9"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="33"/>
+      <c r="D43" s="48"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="9"/>
@@ -1672,7 +2039,7 @@
       <c r="A44" s="9"/>
       <c r="B44" s="9"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="33"/>
+      <c r="D44" s="48"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="9"/>
@@ -1684,7 +2051,7 @@
       <c r="A45" s="9"/>
       <c r="B45" s="9"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="33"/>
+      <c r="D45" s="48"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="9"/>
@@ -1696,7 +2063,7 @@
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="33"/>
+      <c r="D46" s="48"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="9"/>
@@ -1708,7 +2075,7 @@
       <c r="A47" s="9"/>
       <c r="B47" s="9"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="33"/>
+      <c r="D47" s="48"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="9"/>
@@ -1720,7 +2087,7 @@
       <c r="A48" s="9"/>
       <c r="B48" s="9"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="33"/>
+      <c r="D48" s="48"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="9"/>
@@ -1732,7 +2099,7 @@
       <c r="A49" s="9"/>
       <c r="B49" s="9"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="33"/>
+      <c r="D49" s="48"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="9"/>
@@ -1744,7 +2111,7 @@
       <c r="A50" s="9"/>
       <c r="B50" s="9"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="33"/>
+      <c r="D50" s="48"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="9"/>
@@ -1756,7 +2123,7 @@
       <c r="A51" s="9"/>
       <c r="B51" s="9"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="33"/>
+      <c r="D51" s="48"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="9"/>
@@ -1768,7 +2135,7 @@
       <c r="A52" s="9"/>
       <c r="B52" s="9"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="33"/>
+      <c r="D52" s="48"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="9"/>
@@ -1780,7 +2147,7 @@
       <c r="A53" s="9"/>
       <c r="B53" s="9"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="33"/>
+      <c r="D53" s="48"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="9"/>
@@ -1792,7 +2159,7 @@
       <c r="A54" s="9"/>
       <c r="B54" s="9"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="33"/>
+      <c r="D54" s="48"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="9"/>
@@ -1804,7 +2171,7 @@
       <c r="A55" s="9"/>
       <c r="B55" s="9"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="33"/>
+      <c r="D55" s="48"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="9"/>
@@ -1816,7 +2183,7 @@
       <c r="A56" s="9"/>
       <c r="B56" s="9"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="33"/>
+      <c r="D56" s="48"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="9"/>
@@ -1828,7 +2195,7 @@
       <c r="A57" s="9"/>
       <c r="B57" s="9"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="33"/>
+      <c r="D57" s="48"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="9"/>
@@ -2750,13 +3117,8 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:J2"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="J3:J4"/>
@@ -2772,8 +3134,13 @@
     <mergeCell ref="G17:G23"/>
     <mergeCell ref="H17:H23"/>
     <mergeCell ref="J17:J23"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="F3:F4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2798,30 +3165,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.25" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="29"/>
+      <c r="H1" s="40"/>
       <c r="I1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="J1" s="41" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2832,10 +3199,10 @@
       <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
       <c r="G2" s="5" t="s">
         <v>10</v>
       </c>
@@ -2843,55 +3210,55 @@
         <v>11</v>
       </c>
       <c r="I2" s="3"/>
-      <c r="J2" s="30"/>
+      <c r="J2" s="41"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1">
       <c r="A3" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C3" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="47" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="17" t="s">
+      <c r="H3" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="I3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="9" t="s">
         <v>39</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15">
       <c r="A4" s="9"/>
       <c r="B4" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="33"/>
+      <c r="D4" s="48"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="19"/>
       <c r="H4" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15">
@@ -2902,7 +3269,7 @@
       <c r="C5" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="33"/>
+      <c r="D5" s="48"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="9"/>
@@ -2915,44 +3282,44 @@
     <row r="6" spans="1:10" ht="15">
       <c r="A6" s="9"/>
       <c r="B6" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="33"/>
+      <c r="D6" s="48"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J6" s="9"/>
     </row>
     <row r="7" spans="1:10" ht="67.5" customHeight="1">
       <c r="A7" s="9"/>
       <c r="C7" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="33"/>
+        <v>44</v>
+      </c>
+      <c r="D7" s="48"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="9"/>
       <c r="H7" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J7" s="9"/>
     </row>
     <row r="8" spans="1:10" ht="14.25" customHeight="1">
       <c r="A8" s="9"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="33"/>
+      <c r="D8" s="48"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="9"/>
@@ -2962,45 +3329,45 @@
     </row>
     <row r="9" spans="1:10" ht="15">
       <c r="A9" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="33"/>
+      <c r="D9" s="48"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
       <c r="I9" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J9" s="9"/>
     </row>
     <row r="10" spans="1:10" ht="15">
       <c r="A10" s="8"/>
       <c r="B10" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C10" s="9"/>
-      <c r="D10" s="33"/>
+      <c r="D10" s="48"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J10" s="9"/>
     </row>
     <row r="11" spans="1:10" ht="15">
       <c r="A11" s="8"/>
       <c r="B11" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="33"/>
+      <c r="D11" s="48"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="9"/>
@@ -3011,16 +3378,16 @@
     <row r="12" spans="1:10" ht="15">
       <c r="A12" s="8"/>
       <c r="B12" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="33"/>
+      <c r="D12" s="48"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J12" s="9"/>
     </row>
@@ -3028,7 +3395,7 @@
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="33"/>
+      <c r="D13" s="48"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="9"/>
@@ -3038,28 +3405,28 @@
     </row>
     <row r="14" spans="1:10" ht="15">
       <c r="A14" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C14" s="11"/>
-      <c r="D14" s="33"/>
+      <c r="D14" s="48"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
       <c r="I14" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J14" s="9"/>
     </row>
     <row r="15" spans="1:10" ht="15">
       <c r="B15" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C15" s="11"/>
-      <c r="D15" s="33"/>
+      <c r="D15" s="48"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
@@ -3069,95 +3436,95 @@
     </row>
     <row r="16" spans="1:10" ht="15">
       <c r="B16" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C16" s="12"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
       <c r="I16" s="9"/>
-      <c r="J16" s="28"/>
+      <c r="J16" s="35"/>
     </row>
     <row r="17" spans="1:10" ht="15">
       <c r="B17" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C17" s="12"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
       <c r="I17" s="9"/>
-      <c r="J17" s="28"/>
+      <c r="J17" s="35"/>
     </row>
     <row r="18" spans="1:10" ht="15">
       <c r="A18" s="21"/>
       <c r="B18" s="21"/>
       <c r="C18" s="12"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
       <c r="I18" s="9"/>
-      <c r="J18" s="28"/>
+      <c r="J18" s="35"/>
     </row>
     <row r="19" spans="1:10" ht="15">
       <c r="A19" s="21"/>
       <c r="B19" s="21"/>
       <c r="C19" s="12"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
       <c r="I19" s="9"/>
-      <c r="J19" s="28"/>
+      <c r="J19" s="35"/>
     </row>
     <row r="20" spans="1:10" ht="15">
       <c r="A20" s="21"/>
       <c r="B20" s="21"/>
       <c r="C20" s="12"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
       <c r="I20" s="9"/>
-      <c r="J20" s="28"/>
+      <c r="J20" s="35"/>
     </row>
     <row r="21" spans="1:10" ht="15">
       <c r="A21" s="21"/>
       <c r="B21" s="21"/>
       <c r="C21" s="12"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
       <c r="I21" s="9"/>
-      <c r="J21" s="28"/>
+      <c r="J21" s="35"/>
     </row>
     <row r="22" spans="1:10" ht="15">
       <c r="A22" s="21"/>
       <c r="B22" s="21"/>
       <c r="C22" s="12"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
       <c r="I22" s="9"/>
-      <c r="J22" s="28"/>
+      <c r="J22" s="35"/>
     </row>
     <row r="23" spans="1:10" ht="15">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
       <c r="C23" s="11"/>
-      <c r="D23" s="33"/>
+      <c r="D23" s="48"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="9"/>
@@ -3169,7 +3536,7 @@
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="33"/>
+      <c r="D24" s="48"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="9"/>
@@ -3181,7 +3548,7 @@
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="33"/>
+      <c r="D25" s="48"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
@@ -3193,7 +3560,7 @@
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="33"/>
+      <c r="D26" s="48"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
@@ -3205,7 +3572,7 @@
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="33"/>
+      <c r="D27" s="48"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
@@ -3217,7 +3584,7 @@
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="33"/>
+      <c r="D28" s="48"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
@@ -3229,7 +3596,7 @@
       <c r="A29" s="9"/>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="33"/>
+      <c r="D29" s="48"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
       <c r="G29" s="9"/>
@@ -3241,7 +3608,7 @@
       <c r="A30" s="9"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="33"/>
+      <c r="D30" s="48"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="9"/>
@@ -3253,7 +3620,7 @@
       <c r="A31" s="9"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="33"/>
+      <c r="D31" s="48"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="9"/>
@@ -3265,7 +3632,7 @@
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
-      <c r="D32" s="33"/>
+      <c r="D32" s="48"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
@@ -3277,7 +3644,7 @@
       <c r="A33" s="9"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
-      <c r="D33" s="33"/>
+      <c r="D33" s="48"/>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
       <c r="G33" s="9"/>
@@ -3289,7 +3656,7 @@
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="11"/>
-      <c r="D34" s="33"/>
+      <c r="D34" s="48"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="9"/>
@@ -3301,7 +3668,7 @@
       <c r="A35" s="9"/>
       <c r="B35" s="9"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="33"/>
+      <c r="D35" s="48"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="9"/>
@@ -3313,7 +3680,7 @@
       <c r="A36" s="9"/>
       <c r="B36" s="9"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="33"/>
+      <c r="D36" s="48"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="9"/>
@@ -3325,7 +3692,7 @@
       <c r="A37" s="9"/>
       <c r="B37" s="9"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="33"/>
+      <c r="D37" s="48"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="9"/>
@@ -3337,7 +3704,7 @@
       <c r="A38" s="9"/>
       <c r="B38" s="9"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="33"/>
+      <c r="D38" s="48"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="9"/>
@@ -3349,7 +3716,7 @@
       <c r="A39" s="9"/>
       <c r="B39" s="9"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="33"/>
+      <c r="D39" s="48"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="9"/>
@@ -3361,7 +3728,7 @@
       <c r="A40" s="9"/>
       <c r="B40" s="9"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="33"/>
+      <c r="D40" s="48"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="9"/>
@@ -3373,7 +3740,7 @@
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="33"/>
+      <c r="D41" s="48"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="9"/>
@@ -3385,7 +3752,7 @@
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="33"/>
+      <c r="D42" s="48"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="9"/>
@@ -3397,7 +3764,7 @@
       <c r="A43" s="9"/>
       <c r="B43" s="9"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="33"/>
+      <c r="D43" s="48"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="9"/>
@@ -3409,7 +3776,7 @@
       <c r="A44" s="9"/>
       <c r="B44" s="9"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="33"/>
+      <c r="D44" s="48"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="9"/>
@@ -3421,7 +3788,7 @@
       <c r="A45" s="9"/>
       <c r="B45" s="9"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="33"/>
+      <c r="D45" s="48"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="9"/>
@@ -3433,7 +3800,7 @@
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="33"/>
+      <c r="D46" s="48"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="9"/>
@@ -3445,7 +3812,7 @@
       <c r="A47" s="9"/>
       <c r="B47" s="9"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="33"/>
+      <c r="D47" s="48"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="9"/>
@@ -3457,7 +3824,7 @@
       <c r="A48" s="9"/>
       <c r="B48" s="9"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="33"/>
+      <c r="D48" s="48"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="9"/>
@@ -3469,7 +3836,7 @@
       <c r="A49" s="9"/>
       <c r="B49" s="9"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="33"/>
+      <c r="D49" s="48"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="9"/>
@@ -3481,7 +3848,7 @@
       <c r="A50" s="9"/>
       <c r="B50" s="9"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="33"/>
+      <c r="D50" s="48"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="9"/>
@@ -3493,7 +3860,7 @@
       <c r="A51" s="9"/>
       <c r="B51" s="9"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="33"/>
+      <c r="D51" s="48"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="9"/>
@@ -3505,7 +3872,7 @@
       <c r="A52" s="9"/>
       <c r="B52" s="9"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="33"/>
+      <c r="D52" s="48"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="9"/>
@@ -3517,7 +3884,7 @@
       <c r="A53" s="9"/>
       <c r="B53" s="9"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="33"/>
+      <c r="D53" s="48"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="9"/>
@@ -3529,7 +3896,7 @@
       <c r="A54" s="9"/>
       <c r="B54" s="9"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="33"/>
+      <c r="D54" s="48"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="9"/>
@@ -3541,7 +3908,7 @@
       <c r="A55" s="9"/>
       <c r="B55" s="9"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="33"/>
+      <c r="D55" s="48"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="9"/>
@@ -3553,7 +3920,7 @@
       <c r="A56" s="9"/>
       <c r="B56" s="9"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="33"/>
+      <c r="D56" s="48"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="9"/>
@@ -4475,11 +4842,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="D3:D56"/>
@@ -4488,6 +4850,11 @@
     <mergeCell ref="G16:G22"/>
     <mergeCell ref="H16:H22"/>
     <mergeCell ref="J16:J22"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4512,30 +4879,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.25" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="29"/>
+      <c r="H1" s="40"/>
       <c r="I1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="J1" s="41" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4546,10 +4913,10 @@
       <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
       <c r="G2" s="5" t="s">
         <v>10</v>
       </c>
@@ -4557,113 +4924,113 @@
         <v>11</v>
       </c>
       <c r="I2" s="3"/>
-      <c r="J2" s="30"/>
+      <c r="J2" s="41"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1">
       <c r="A3" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="F3" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="16" t="s">
-        <v>17</v>
-      </c>
       <c r="G3" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J3" s="9"/>
     </row>
     <row r="4" spans="1:10" ht="14.25" customHeight="1">
       <c r="A4" s="9"/>
       <c r="B4" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="33"/>
+      <c r="D4" s="48"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="9"/>
-      <c r="H4" s="44" t="s">
-        <v>59</v>
+      <c r="H4" s="43" t="s">
+        <v>58</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J4" s="9"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="9"/>
       <c r="B5" s="9"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="33"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="48"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="44"/>
+      <c r="H5" s="43"/>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
     </row>
     <row r="6" spans="1:10" ht="15">
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="33"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="48"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="44"/>
+      <c r="H6" s="43"/>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
     </row>
     <row r="7" spans="1:10" ht="15">
       <c r="A7" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="43"/>
-      <c r="D7" s="33"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="48"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="9"/>
-      <c r="H7" s="44"/>
+      <c r="H7" s="43"/>
       <c r="I7" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J7" s="9"/>
     </row>
     <row r="8" spans="1:10" ht="15">
       <c r="A8" s="9"/>
       <c r="B8" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="43"/>
-      <c r="D8" s="33"/>
+        <v>61</v>
+      </c>
+      <c r="C8" s="42"/>
+      <c r="D8" s="48"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="9"/>
-      <c r="H8" s="44"/>
+      <c r="H8" s="43"/>
       <c r="I8" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J8" s="9"/>
     </row>
@@ -4671,13 +5038,13 @@
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="11"/>
-      <c r="D9" s="33"/>
+      <c r="D9" s="48"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
       <c r="I9" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J9" s="9"/>
     </row>
@@ -4685,13 +5052,13 @@
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
-      <c r="D10" s="33"/>
+      <c r="D10" s="48"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J10" s="9"/>
     </row>
@@ -4699,7 +5066,7 @@
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="11"/>
-      <c r="D11" s="33"/>
+      <c r="D11" s="48"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="9"/>
@@ -4711,13 +5078,13 @@
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="33"/>
+      <c r="D12" s="48"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J12" s="9"/>
     </row>
@@ -4725,7 +5092,7 @@
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="33"/>
+      <c r="D13" s="48"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="9"/>
@@ -4737,13 +5104,13 @@
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="33"/>
+      <c r="D14" s="48"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
       <c r="I14" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J14" s="9"/>
     </row>
@@ -4751,7 +5118,7 @@
       <c r="A15" s="9"/>
       <c r="B15" s="9"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="33"/>
+      <c r="D15" s="48"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
@@ -4760,94 +5127,94 @@
       <c r="J15" s="9"/>
     </row>
     <row r="16" spans="1:10" ht="15">
-      <c r="A16" s="38"/>
-      <c r="B16" s="38"/>
+      <c r="A16" s="39"/>
+      <c r="B16" s="39"/>
       <c r="C16" s="12"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
       <c r="I16" s="9"/>
-      <c r="J16" s="28"/>
+      <c r="J16" s="35"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="38"/>
-      <c r="B17" s="38"/>
+      <c r="A17" s="39"/>
+      <c r="B17" s="39"/>
       <c r="C17" s="12"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
       <c r="I17" s="9"/>
-      <c r="J17" s="28"/>
+      <c r="J17" s="35"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="38"/>
-      <c r="B18" s="38"/>
+      <c r="A18" s="39"/>
+      <c r="B18" s="39"/>
       <c r="C18" s="12"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
       <c r="I18" s="9"/>
-      <c r="J18" s="28"/>
+      <c r="J18" s="35"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="38"/>
-      <c r="B19" s="38"/>
+      <c r="A19" s="39"/>
+      <c r="B19" s="39"/>
       <c r="C19" s="12"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
       <c r="I19" s="9"/>
-      <c r="J19" s="28"/>
+      <c r="J19" s="35"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="38"/>
-      <c r="B20" s="38"/>
+      <c r="A20" s="39"/>
+      <c r="B20" s="39"/>
       <c r="C20" s="12"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
       <c r="I20" s="9"/>
-      <c r="J20" s="28"/>
+      <c r="J20" s="35"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="38"/>
-      <c r="B21" s="38"/>
+      <c r="A21" s="39"/>
+      <c r="B21" s="39"/>
       <c r="C21" s="12"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
       <c r="I21" s="9"/>
-      <c r="J21" s="28"/>
+      <c r="J21" s="35"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="38"/>
-      <c r="B22" s="38"/>
+      <c r="A22" s="39"/>
+      <c r="B22" s="39"/>
       <c r="C22" s="12"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
       <c r="I22" s="9"/>
-      <c r="J22" s="28"/>
+      <c r="J22" s="35"/>
     </row>
     <row r="23" spans="1:10" ht="15">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
       <c r="C23" s="11"/>
-      <c r="D23" s="33"/>
+      <c r="D23" s="48"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="9"/>
@@ -4859,7 +5226,7 @@
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="33"/>
+      <c r="D24" s="48"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="9"/>
@@ -4871,7 +5238,7 @@
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="33"/>
+      <c r="D25" s="48"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
@@ -4883,7 +5250,7 @@
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="33"/>
+      <c r="D26" s="48"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
@@ -4895,7 +5262,7 @@
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="33"/>
+      <c r="D27" s="48"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
@@ -4907,7 +5274,7 @@
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="33"/>
+      <c r="D28" s="48"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
@@ -4919,7 +5286,7 @@
       <c r="A29" s="9"/>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="33"/>
+      <c r="D29" s="48"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
       <c r="G29" s="9"/>
@@ -4931,7 +5298,7 @@
       <c r="A30" s="9"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="33"/>
+      <c r="D30" s="48"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="9"/>
@@ -4943,7 +5310,7 @@
       <c r="A31" s="9"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="33"/>
+      <c r="D31" s="48"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="9"/>
@@ -4955,7 +5322,7 @@
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
-      <c r="D32" s="33"/>
+      <c r="D32" s="48"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
@@ -4967,7 +5334,7 @@
       <c r="A33" s="9"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
-      <c r="D33" s="33"/>
+      <c r="D33" s="48"/>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
       <c r="G33" s="9"/>
@@ -4979,7 +5346,7 @@
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="11"/>
-      <c r="D34" s="33"/>
+      <c r="D34" s="48"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="9"/>
@@ -4991,7 +5358,7 @@
       <c r="A35" s="9"/>
       <c r="B35" s="9"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="33"/>
+      <c r="D35" s="48"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="9"/>
@@ -5003,7 +5370,7 @@
       <c r="A36" s="9"/>
       <c r="B36" s="9"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="33"/>
+      <c r="D36" s="48"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="9"/>
@@ -5015,7 +5382,7 @@
       <c r="A37" s="9"/>
       <c r="B37" s="9"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="33"/>
+      <c r="D37" s="48"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="9"/>
@@ -5027,7 +5394,7 @@
       <c r="A38" s="9"/>
       <c r="B38" s="9"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="33"/>
+      <c r="D38" s="48"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="9"/>
@@ -5039,7 +5406,7 @@
       <c r="A39" s="9"/>
       <c r="B39" s="9"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="33"/>
+      <c r="D39" s="48"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="9"/>
@@ -5051,7 +5418,7 @@
       <c r="A40" s="9"/>
       <c r="B40" s="9"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="33"/>
+      <c r="D40" s="48"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="9"/>
@@ -5063,7 +5430,7 @@
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="33"/>
+      <c r="D41" s="48"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="9"/>
@@ -5075,7 +5442,7 @@
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="33"/>
+      <c r="D42" s="48"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="9"/>
@@ -5087,7 +5454,7 @@
       <c r="A43" s="9"/>
       <c r="B43" s="9"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="33"/>
+      <c r="D43" s="48"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="9"/>
@@ -5099,7 +5466,7 @@
       <c r="A44" s="9"/>
       <c r="B44" s="9"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="33"/>
+      <c r="D44" s="48"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="9"/>
@@ -5111,7 +5478,7 @@
       <c r="A45" s="9"/>
       <c r="B45" s="9"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="33"/>
+      <c r="D45" s="48"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="9"/>
@@ -5123,7 +5490,7 @@
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="33"/>
+      <c r="D46" s="48"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="9"/>
@@ -5135,7 +5502,7 @@
       <c r="A47" s="9"/>
       <c r="B47" s="9"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="33"/>
+      <c r="D47" s="48"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="9"/>
@@ -5147,7 +5514,7 @@
       <c r="A48" s="9"/>
       <c r="B48" s="9"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="33"/>
+      <c r="D48" s="48"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="9"/>
@@ -5159,7 +5526,7 @@
       <c r="A49" s="9"/>
       <c r="B49" s="9"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="33"/>
+      <c r="D49" s="48"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="9"/>
@@ -5171,7 +5538,7 @@
       <c r="A50" s="9"/>
       <c r="B50" s="9"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="33"/>
+      <c r="D50" s="48"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="9"/>
@@ -5183,7 +5550,7 @@
       <c r="A51" s="9"/>
       <c r="B51" s="9"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="33"/>
+      <c r="D51" s="48"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="9"/>
@@ -5195,7 +5562,7 @@
       <c r="A52" s="9"/>
       <c r="B52" s="9"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="33"/>
+      <c r="D52" s="48"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="9"/>
@@ -5207,7 +5574,7 @@
       <c r="A53" s="9"/>
       <c r="B53" s="9"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="33"/>
+      <c r="D53" s="48"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="9"/>
@@ -5219,7 +5586,7 @@
       <c r="A54" s="9"/>
       <c r="B54" s="9"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="33"/>
+      <c r="D54" s="48"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="9"/>
@@ -5231,7 +5598,7 @@
       <c r="A55" s="9"/>
       <c r="B55" s="9"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="33"/>
+      <c r="D55" s="48"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="9"/>
@@ -5243,7 +5610,7 @@
       <c r="A56" s="9"/>
       <c r="B56" s="9"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="33"/>
+      <c r="D56" s="48"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="9"/>
@@ -6165,11 +6532,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="A16:A22"/>
+    <mergeCell ref="B16:B22"/>
+    <mergeCell ref="E16:E22"/>
+    <mergeCell ref="F16:F22"/>
+    <mergeCell ref="G16:G22"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="D3:D56"/>
@@ -6177,11 +6544,11 @@
     <mergeCell ref="H4:H8"/>
     <mergeCell ref="H16:H22"/>
     <mergeCell ref="J16:J22"/>
-    <mergeCell ref="A16:A22"/>
-    <mergeCell ref="B16:B22"/>
-    <mergeCell ref="E16:E22"/>
-    <mergeCell ref="F16:F22"/>
-    <mergeCell ref="G16:G22"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6206,30 +6573,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.25" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="29"/>
+      <c r="H1" s="40"/>
       <c r="I1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="J1" s="41" t="s">
         <v>7</v>
       </c>
     </row>
@@ -6240,10 +6607,10 @@
       <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
       <c r="G2" s="5" t="s">
         <v>10</v>
       </c>
@@ -6251,59 +6618,59 @@
         <v>11</v>
       </c>
       <c r="I2" s="3"/>
-      <c r="J2" s="30"/>
+      <c r="J2" s="41"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A3" s="31"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="33" t="s">
+      <c r="A3" s="37"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="E3" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="F3" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="36" t="s">
+      <c r="G3" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="H3" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="H3" s="36" t="s">
-        <v>64</v>
-      </c>
       <c r="I3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="35"/>
+    </row>
+    <row r="4" spans="1:10" ht="15">
+      <c r="A4" s="37"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="28"/>
-    </row>
-    <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="31"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="28"/>
+      <c r="J4" s="35"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="9"/>
       <c r="B5" s="9"/>
       <c r="C5" s="11"/>
-      <c r="D5" s="33"/>
+      <c r="D5" s="48"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J5" s="9"/>
     </row>
@@ -6311,12 +6678,12 @@
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
       <c r="C6" s="11"/>
-      <c r="D6" s="33"/>
+      <c r="D6" s="48"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
@@ -6325,12 +6692,12 @@
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="33"/>
+      <c r="D7" s="48"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="9"/>
       <c r="H7" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
@@ -6339,15 +6706,15 @@
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="33"/>
+      <c r="D8" s="48"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J8" s="9"/>
     </row>
@@ -6355,15 +6722,15 @@
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
-      <c r="D9" s="33"/>
+      <c r="D9" s="48"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J9" s="9"/>
     </row>
@@ -6371,15 +6738,15 @@
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="33"/>
+      <c r="D10" s="48"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J10" s="9"/>
     </row>
@@ -6387,15 +6754,15 @@
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
-      <c r="D11" s="33"/>
+      <c r="D11" s="48"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J11" s="9"/>
     </row>
@@ -6403,7 +6770,7 @@
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="33"/>
+      <c r="D12" s="48"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="9"/>
@@ -6415,13 +6782,13 @@
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="33"/>
+      <c r="D13" s="48"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J13" s="9"/>
     </row>
@@ -6429,7 +6796,7 @@
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="33"/>
+      <c r="D14" s="48"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="9"/>
@@ -6441,13 +6808,13 @@
       <c r="A15" s="9"/>
       <c r="B15" s="9"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="33"/>
+      <c r="D15" s="48"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J15" s="9"/>
     </row>
@@ -6455,7 +6822,7 @@
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="33"/>
+      <c r="D16" s="48"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
@@ -6464,94 +6831,94 @@
       <c r="J16" s="9"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="38"/>
-      <c r="B17" s="38"/>
+      <c r="A17" s="39"/>
+      <c r="B17" s="39"/>
       <c r="C17" s="12"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
       <c r="I17" s="9"/>
-      <c r="J17" s="28"/>
+      <c r="J17" s="35"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="38"/>
-      <c r="B18" s="38"/>
+      <c r="A18" s="39"/>
+      <c r="B18" s="39"/>
       <c r="C18" s="12"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
       <c r="I18" s="9"/>
-      <c r="J18" s="28"/>
+      <c r="J18" s="35"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="38"/>
-      <c r="B19" s="38"/>
+      <c r="A19" s="39"/>
+      <c r="B19" s="39"/>
       <c r="C19" s="12"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
       <c r="I19" s="9"/>
-      <c r="J19" s="28"/>
+      <c r="J19" s="35"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="38"/>
-      <c r="B20" s="38"/>
+      <c r="A20" s="39"/>
+      <c r="B20" s="39"/>
       <c r="C20" s="12"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
       <c r="I20" s="9"/>
-      <c r="J20" s="28"/>
+      <c r="J20" s="35"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="38"/>
-      <c r="B21" s="38"/>
+      <c r="A21" s="39"/>
+      <c r="B21" s="39"/>
       <c r="C21" s="12"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
       <c r="I21" s="9"/>
-      <c r="J21" s="28"/>
+      <c r="J21" s="35"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="38"/>
-      <c r="B22" s="38"/>
+      <c r="A22" s="39"/>
+      <c r="B22" s="39"/>
       <c r="C22" s="12"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
       <c r="I22" s="9"/>
-      <c r="J22" s="28"/>
+      <c r="J22" s="35"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="38"/>
-      <c r="B23" s="38"/>
+      <c r="A23" s="39"/>
+      <c r="B23" s="39"/>
       <c r="C23" s="12"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
       <c r="I23" s="9"/>
-      <c r="J23" s="28"/>
+      <c r="J23" s="35"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="33"/>
+      <c r="D24" s="48"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="9"/>
@@ -6563,7 +6930,7 @@
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="33"/>
+      <c r="D25" s="48"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="9"/>
@@ -6575,7 +6942,7 @@
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="33"/>
+      <c r="D26" s="48"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
@@ -6587,7 +6954,7 @@
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="33"/>
+      <c r="D27" s="48"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
@@ -6599,7 +6966,7 @@
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="33"/>
+      <c r="D28" s="48"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
@@ -6611,7 +6978,7 @@
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="33"/>
+      <c r="D29" s="48"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
@@ -6623,7 +6990,7 @@
       <c r="A30" s="9"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="33"/>
+      <c r="D30" s="48"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="9"/>
@@ -6635,7 +7002,7 @@
       <c r="A31" s="9"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="33"/>
+      <c r="D31" s="48"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="9"/>
@@ -6647,7 +7014,7 @@
       <c r="A32" s="9"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="33"/>
+      <c r="D32" s="48"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="9"/>
@@ -6659,7 +7026,7 @@
       <c r="A33" s="9"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
-      <c r="D33" s="33"/>
+      <c r="D33" s="48"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
@@ -6671,7 +7038,7 @@
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
-      <c r="D34" s="33"/>
+      <c r="D34" s="48"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="9"/>
@@ -6683,7 +7050,7 @@
       <c r="A35" s="9"/>
       <c r="B35" s="9"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="33"/>
+      <c r="D35" s="48"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="9"/>
@@ -6695,7 +7062,7 @@
       <c r="A36" s="9"/>
       <c r="B36" s="9"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="33"/>
+      <c r="D36" s="48"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="9"/>
@@ -6707,7 +7074,7 @@
       <c r="A37" s="9"/>
       <c r="B37" s="9"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="33"/>
+      <c r="D37" s="48"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="9"/>
@@ -6719,7 +7086,7 @@
       <c r="A38" s="9"/>
       <c r="B38" s="9"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="33"/>
+      <c r="D38" s="48"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="9"/>
@@ -6731,7 +7098,7 @@
       <c r="A39" s="9"/>
       <c r="B39" s="9"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="33"/>
+      <c r="D39" s="48"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="9"/>
@@ -6743,7 +7110,7 @@
       <c r="A40" s="9"/>
       <c r="B40" s="9"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="33"/>
+      <c r="D40" s="48"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="9"/>
@@ -6755,7 +7122,7 @@
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="33"/>
+      <c r="D41" s="48"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="9"/>
@@ -6767,7 +7134,7 @@
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="33"/>
+      <c r="D42" s="48"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="9"/>
@@ -6779,7 +7146,7 @@
       <c r="A43" s="9"/>
       <c r="B43" s="9"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="33"/>
+      <c r="D43" s="48"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="9"/>
@@ -6791,7 +7158,7 @@
       <c r="A44" s="9"/>
       <c r="B44" s="9"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="33"/>
+      <c r="D44" s="48"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="9"/>
@@ -6803,7 +7170,7 @@
       <c r="A45" s="9"/>
       <c r="B45" s="9"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="33"/>
+      <c r="D45" s="48"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="9"/>
@@ -6815,7 +7182,7 @@
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="33"/>
+      <c r="D46" s="48"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="9"/>
@@ -6827,7 +7194,7 @@
       <c r="A47" s="9"/>
       <c r="B47" s="9"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="33"/>
+      <c r="D47" s="48"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="9"/>
@@ -6839,7 +7206,7 @@
       <c r="A48" s="9"/>
       <c r="B48" s="9"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="33"/>
+      <c r="D48" s="48"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="9"/>
@@ -6851,7 +7218,7 @@
       <c r="A49" s="9"/>
       <c r="B49" s="9"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="33"/>
+      <c r="D49" s="48"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="9"/>
@@ -6863,7 +7230,7 @@
       <c r="A50" s="9"/>
       <c r="B50" s="9"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="33"/>
+      <c r="D50" s="48"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="9"/>
@@ -6875,7 +7242,7 @@
       <c r="A51" s="9"/>
       <c r="B51" s="9"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="33"/>
+      <c r="D51" s="48"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="9"/>
@@ -6887,7 +7254,7 @@
       <c r="A52" s="9"/>
       <c r="B52" s="9"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="33"/>
+      <c r="D52" s="48"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="9"/>
@@ -6899,7 +7266,7 @@
       <c r="A53" s="9"/>
       <c r="B53" s="9"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="33"/>
+      <c r="D53" s="48"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="9"/>
@@ -6911,7 +7278,7 @@
       <c r="A54" s="9"/>
       <c r="B54" s="9"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="33"/>
+      <c r="D54" s="48"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="9"/>
@@ -6923,7 +7290,7 @@
       <c r="A55" s="9"/>
       <c r="B55" s="9"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="33"/>
+      <c r="D55" s="48"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="9"/>
@@ -6935,7 +7302,7 @@
       <c r="A56" s="9"/>
       <c r="B56" s="9"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="33"/>
+      <c r="D56" s="48"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="9"/>
@@ -6947,7 +7314,7 @@
       <c r="A57" s="9"/>
       <c r="B57" s="9"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="33"/>
+      <c r="D57" s="48"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="9"/>
@@ -7869,13 +8236,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
     <mergeCell ref="H17:H23"/>
     <mergeCell ref="J17:J23"/>
     <mergeCell ref="G1:H1"/>
@@ -7892,6 +8252,13 @@
     <mergeCell ref="A17:A23"/>
     <mergeCell ref="B17:B23"/>
     <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -7916,30 +8283,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.25" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="29"/>
+      <c r="H1" s="40"/>
       <c r="I1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="J1" s="41" t="s">
         <v>7</v>
       </c>
     </row>
@@ -7950,10 +8317,10 @@
       <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
       <c r="G2" s="5" t="s">
         <v>10</v>
       </c>
@@ -7961,59 +8328,59 @@
         <v>11</v>
       </c>
       <c r="I2" s="3"/>
-      <c r="J2" s="30"/>
+      <c r="J2" s="41"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A3" s="31"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="33" t="s">
+      <c r="A3" s="37"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="E3" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="F3" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="36" t="s">
+      <c r="G3" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="H3" s="36" t="s">
-        <v>73</v>
-      </c>
       <c r="I3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="35"/>
+    </row>
+    <row r="4" spans="1:10" ht="15">
+      <c r="A4" s="37"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="28"/>
-    </row>
-    <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="31"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="28"/>
+      <c r="J4" s="35"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="9"/>
       <c r="B5" s="9"/>
       <c r="C5" s="11"/>
-      <c r="D5" s="33"/>
+      <c r="D5" s="48"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J5" s="9"/>
     </row>
@@ -8021,12 +8388,12 @@
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
       <c r="C6" s="11"/>
-      <c r="D6" s="33"/>
+      <c r="D6" s="48"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
@@ -8035,7 +8402,7 @@
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="11"/>
-      <c r="D7" s="33"/>
+      <c r="D7" s="48"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="9"/>
@@ -8047,13 +8414,13 @@
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="33"/>
+      <c r="D8" s="48"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
       <c r="I8" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J8" s="9"/>
     </row>
@@ -8061,13 +8428,13 @@
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
-      <c r="D9" s="33"/>
+      <c r="D9" s="48"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
       <c r="I9" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J9" s="9"/>
     </row>
@@ -8075,13 +8442,13 @@
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="11"/>
-      <c r="D10" s="33"/>
+      <c r="D10" s="48"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J10" s="9"/>
     </row>
@@ -8089,13 +8456,13 @@
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
-      <c r="D11" s="33"/>
+      <c r="D11" s="48"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J11" s="9"/>
     </row>
@@ -8103,7 +8470,7 @@
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="33"/>
+      <c r="D12" s="48"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="9"/>
@@ -8115,13 +8482,13 @@
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="33"/>
+      <c r="D13" s="48"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J13" s="9"/>
     </row>
@@ -8129,7 +8496,7 @@
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="33"/>
+      <c r="D14" s="48"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="9"/>
@@ -8141,13 +8508,13 @@
       <c r="A15" s="9"/>
       <c r="B15" s="9"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="33"/>
+      <c r="D15" s="48"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J15" s="9"/>
     </row>
@@ -8155,7 +8522,7 @@
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="33"/>
+      <c r="D16" s="48"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
@@ -8164,94 +8531,94 @@
       <c r="J16" s="9"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="38"/>
-      <c r="B17" s="38"/>
+      <c r="A17" s="39"/>
+      <c r="B17" s="39"/>
       <c r="C17" s="12"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
       <c r="I17" s="9"/>
-      <c r="J17" s="28"/>
+      <c r="J17" s="35"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="38"/>
-      <c r="B18" s="38"/>
+      <c r="A18" s="39"/>
+      <c r="B18" s="39"/>
       <c r="C18" s="12"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
       <c r="I18" s="9"/>
-      <c r="J18" s="28"/>
+      <c r="J18" s="35"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="38"/>
-      <c r="B19" s="38"/>
+      <c r="A19" s="39"/>
+      <c r="B19" s="39"/>
       <c r="C19" s="12"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
       <c r="I19" s="9"/>
-      <c r="J19" s="28"/>
+      <c r="J19" s="35"/>
     </row>
     <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="38"/>
-      <c r="B20" s="38"/>
+      <c r="A20" s="39"/>
+      <c r="B20" s="39"/>
       <c r="C20" s="12"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
       <c r="I20" s="9"/>
-      <c r="J20" s="28"/>
+      <c r="J20" s="35"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="38"/>
-      <c r="B21" s="38"/>
+      <c r="A21" s="39"/>
+      <c r="B21" s="39"/>
       <c r="C21" s="12"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
       <c r="I21" s="9"/>
-      <c r="J21" s="28"/>
+      <c r="J21" s="35"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="38"/>
-      <c r="B22" s="38"/>
+      <c r="A22" s="39"/>
+      <c r="B22" s="39"/>
       <c r="C22" s="12"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
       <c r="I22" s="9"/>
-      <c r="J22" s="28"/>
+      <c r="J22" s="35"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="38"/>
-      <c r="B23" s="38"/>
+      <c r="A23" s="39"/>
+      <c r="B23" s="39"/>
       <c r="C23" s="12"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
       <c r="I23" s="9"/>
-      <c r="J23" s="28"/>
+      <c r="J23" s="35"/>
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="33"/>
+      <c r="D24" s="48"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="9"/>
@@ -8263,7 +8630,7 @@
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="33"/>
+      <c r="D25" s="48"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="9"/>
@@ -8275,7 +8642,7 @@
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="33"/>
+      <c r="D26" s="48"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
@@ -8287,7 +8654,7 @@
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="33"/>
+      <c r="D27" s="48"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
@@ -8299,7 +8666,7 @@
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="33"/>
+      <c r="D28" s="48"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
@@ -8311,7 +8678,7 @@
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="33"/>
+      <c r="D29" s="48"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
@@ -8323,7 +8690,7 @@
       <c r="A30" s="9"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="33"/>
+      <c r="D30" s="48"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="9"/>
@@ -8335,7 +8702,7 @@
       <c r="A31" s="9"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="33"/>
+      <c r="D31" s="48"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="9"/>
@@ -8347,7 +8714,7 @@
       <c r="A32" s="9"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="33"/>
+      <c r="D32" s="48"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="9"/>
@@ -8359,7 +8726,7 @@
       <c r="A33" s="9"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
-      <c r="D33" s="33"/>
+      <c r="D33" s="48"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
@@ -8371,7 +8738,7 @@
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
-      <c r="D34" s="33"/>
+      <c r="D34" s="48"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="9"/>
@@ -8383,7 +8750,7 @@
       <c r="A35" s="9"/>
       <c r="B35" s="9"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="33"/>
+      <c r="D35" s="48"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="9"/>
@@ -8395,7 +8762,7 @@
       <c r="A36" s="9"/>
       <c r="B36" s="9"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="33"/>
+      <c r="D36" s="48"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="9"/>
@@ -8407,7 +8774,7 @@
       <c r="A37" s="9"/>
       <c r="B37" s="9"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="33"/>
+      <c r="D37" s="48"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="9"/>
@@ -8419,7 +8786,7 @@
       <c r="A38" s="9"/>
       <c r="B38" s="9"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="33"/>
+      <c r="D38" s="48"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="9"/>
@@ -8431,7 +8798,7 @@
       <c r="A39" s="9"/>
       <c r="B39" s="9"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="33"/>
+      <c r="D39" s="48"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="9"/>
@@ -8443,7 +8810,7 @@
       <c r="A40" s="9"/>
       <c r="B40" s="9"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="33"/>
+      <c r="D40" s="48"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="9"/>
@@ -8455,7 +8822,7 @@
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="33"/>
+      <c r="D41" s="48"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="9"/>
@@ -8467,7 +8834,7 @@
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="33"/>
+      <c r="D42" s="48"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="9"/>
@@ -8479,7 +8846,7 @@
       <c r="A43" s="9"/>
       <c r="B43" s="9"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="33"/>
+      <c r="D43" s="48"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="9"/>
@@ -8491,7 +8858,7 @@
       <c r="A44" s="9"/>
       <c r="B44" s="9"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="33"/>
+      <c r="D44" s="48"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="9"/>
@@ -8503,7 +8870,7 @@
       <c r="A45" s="9"/>
       <c r="B45" s="9"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="33"/>
+      <c r="D45" s="48"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="9"/>
@@ -8515,7 +8882,7 @@
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="33"/>
+      <c r="D46" s="48"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="9"/>
@@ -8527,7 +8894,7 @@
       <c r="A47" s="9"/>
       <c r="B47" s="9"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="33"/>
+      <c r="D47" s="48"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="9"/>
@@ -8539,7 +8906,7 @@
       <c r="A48" s="9"/>
       <c r="B48" s="9"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="33"/>
+      <c r="D48" s="48"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="9"/>
@@ -8551,7 +8918,7 @@
       <c r="A49" s="9"/>
       <c r="B49" s="9"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="33"/>
+      <c r="D49" s="48"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="9"/>
@@ -8563,7 +8930,7 @@
       <c r="A50" s="9"/>
       <c r="B50" s="9"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="33"/>
+      <c r="D50" s="48"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="9"/>
@@ -8575,7 +8942,7 @@
       <c r="A51" s="9"/>
       <c r="B51" s="9"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="33"/>
+      <c r="D51" s="48"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="9"/>
@@ -8587,7 +8954,7 @@
       <c r="A52" s="9"/>
       <c r="B52" s="9"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="33"/>
+      <c r="D52" s="48"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="9"/>
@@ -8599,7 +8966,7 @@
       <c r="A53" s="9"/>
       <c r="B53" s="9"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="33"/>
+      <c r="D53" s="48"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="9"/>
@@ -8611,7 +8978,7 @@
       <c r="A54" s="9"/>
       <c r="B54" s="9"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="33"/>
+      <c r="D54" s="48"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="9"/>
@@ -8623,7 +8990,7 @@
       <c r="A55" s="9"/>
       <c r="B55" s="9"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="33"/>
+      <c r="D55" s="48"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="9"/>
@@ -8635,7 +9002,7 @@
       <c r="A56" s="9"/>
       <c r="B56" s="9"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="33"/>
+      <c r="D56" s="48"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="9"/>
@@ -8647,7 +9014,7 @@
       <c r="A57" s="9"/>
       <c r="B57" s="9"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="33"/>
+      <c r="D57" s="48"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="9"/>
@@ -9569,13 +9936,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
     <mergeCell ref="H17:H23"/>
     <mergeCell ref="J17:J23"/>
     <mergeCell ref="G1:H1"/>
@@ -9592,6 +9952,13 @@
     <mergeCell ref="A17:A23"/>
     <mergeCell ref="B17:B23"/>
     <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -9616,30 +9983,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.25" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="29"/>
+      <c r="H1" s="40"/>
       <c r="I1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="J1" s="41" t="s">
         <v>7</v>
       </c>
     </row>
@@ -9650,10 +10017,10 @@
       <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
       <c r="G2" s="5" t="s">
         <v>10</v>
       </c>
@@ -9661,232 +10028,232 @@
         <v>11</v>
       </c>
       <c r="I2" s="3"/>
-      <c r="J2" s="30"/>
+      <c r="J2" s="41"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C3" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="F3" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="35" t="s">
-        <v>17</v>
-      </c>
       <c r="G3" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J3" s="9"/>
     </row>
     <row r="4" spans="1:10" ht="15">
       <c r="B4" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="33"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="35"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="33"/>
       <c r="G4" s="9"/>
       <c r="H4" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J4" s="9"/>
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="B5" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="33"/>
+      <c r="D5" s="48"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
     </row>
     <row r="6" spans="1:10" ht="15">
       <c r="B6" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="33"/>
+      <c r="D6" s="48"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
     </row>
     <row r="7" spans="1:10" ht="60">
       <c r="C7" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" s="33"/>
+        <v>76</v>
+      </c>
+      <c r="D7" s="48"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="9"/>
       <c r="H7" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="24" t="s">
         <v>78</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" s="24" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30">
       <c r="C8" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" s="33"/>
+        <v>79</v>
+      </c>
+      <c r="D8" s="48"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="9" t="s">
         <v>81</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="30">
       <c r="C9" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D9" s="33"/>
+        <v>82</v>
+      </c>
+      <c r="D9" s="48"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="I9" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>85</v>
-      </c>
     </row>
     <row r="10" spans="1:10" ht="14.25" customHeight="1">
-      <c r="C10" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="D10" s="33"/>
+      <c r="C10" s="44" t="s">
+        <v>133</v>
+      </c>
+      <c r="D10" s="48"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="9"/>
-      <c r="H10" s="46" t="s">
-        <v>86</v>
+      <c r="H10" s="45" t="s">
+        <v>85</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J10" s="47"/>
+        <v>33</v>
+      </c>
+      <c r="J10" s="46"/>
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1">
-      <c r="C11" s="45"/>
-      <c r="D11" s="33"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="48"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="9"/>
-      <c r="H11" s="46"/>
+      <c r="H11" s="45"/>
       <c r="I11" s="9"/>
-      <c r="J11" s="47"/>
+      <c r="J11" s="46"/>
     </row>
     <row r="12" spans="1:10" ht="15">
-      <c r="C12" s="45"/>
-      <c r="D12" s="33"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="48"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="9"/>
-      <c r="H12" s="46"/>
+      <c r="H12" s="45"/>
       <c r="I12" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="J12" s="47"/>
+        <v>34</v>
+      </c>
+      <c r="J12" s="46"/>
     </row>
     <row r="13" spans="1:10" ht="45">
       <c r="C13" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" s="33"/>
+        <v>86</v>
+      </c>
+      <c r="D13" s="48"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
     </row>
     <row r="14" spans="1:10" ht="15">
       <c r="B14" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="33"/>
+      <c r="D14" s="48"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J14" s="9"/>
     </row>
     <row r="15" spans="1:10" ht="15">
       <c r="C15" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D15" s="33"/>
+        <v>88</v>
+      </c>
+      <c r="D15" s="48"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="9"/>
       <c r="H15" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
     </row>
     <row r="16" spans="1:10" ht="15">
-      <c r="D16" s="33"/>
+      <c r="D16" s="48"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
@@ -9895,9 +10262,9 @@
       <c r="J16" s="9"/>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="D17" s="33"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
@@ -9905,15 +10272,15 @@
     </row>
     <row r="18" spans="1:10" ht="15">
       <c r="A18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="C18" s="11"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="9"/>
@@ -9921,14 +10288,14 @@
     </row>
     <row r="19" spans="1:10" ht="15">
       <c r="B19" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="33"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
@@ -9936,12 +10303,12 @@
     </row>
     <row r="20" spans="1:10" ht="15">
       <c r="B20" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C20" s="11"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
@@ -9949,12 +10316,12 @@
     </row>
     <row r="21" spans="1:10" ht="15">
       <c r="B21" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C21" s="11"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
@@ -9962,12 +10329,12 @@
     </row>
     <row r="22" spans="1:10" ht="15">
       <c r="B22" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C22" s="11"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
@@ -9975,9 +10342,9 @@
     </row>
     <row r="23" spans="1:10" ht="15">
       <c r="C23" s="11"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
@@ -9985,13 +10352,13 @@
     </row>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C24" s="11"/>
-      <c r="D24" s="33"/>
+      <c r="D24" s="48"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="9"/>
@@ -10001,10 +10368,10 @@
     </row>
     <row r="25" spans="1:10" ht="15">
       <c r="B25" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C25" s="12"/>
-      <c r="D25" s="33"/>
+      <c r="D25" s="48"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="9"/>
@@ -10014,10 +10381,10 @@
     </row>
     <row r="26" spans="1:10" ht="15">
       <c r="B26" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C26" s="12"/>
-      <c r="D26" s="33"/>
+      <c r="D26" s="48"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
@@ -10027,10 +10394,10 @@
     </row>
     <row r="27" spans="1:10" ht="15">
       <c r="B27" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C27" s="12"/>
-      <c r="D27" s="33"/>
+      <c r="D27" s="48"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
@@ -10040,7 +10407,7 @@
     </row>
     <row r="28" spans="1:10" ht="15">
       <c r="C28" s="12"/>
-      <c r="D28" s="33"/>
+      <c r="D28" s="48"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
@@ -10050,13 +10417,13 @@
     </row>
     <row r="29" spans="1:10" ht="15">
       <c r="A29" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C29" s="12"/>
-      <c r="D29" s="33"/>
+      <c r="D29" s="48"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
@@ -10066,10 +10433,10 @@
     </row>
     <row r="30" spans="1:10" ht="15">
       <c r="B30" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C30" s="12"/>
-      <c r="D30" s="33"/>
+      <c r="D30" s="48"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="9"/>
@@ -10079,10 +10446,10 @@
     </row>
     <row r="31" spans="1:10" ht="15">
       <c r="B31" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C31" s="12"/>
-      <c r="D31" s="33"/>
+      <c r="D31" s="48"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="9"/>
@@ -10092,10 +10459,10 @@
     </row>
     <row r="32" spans="1:10" ht="15">
       <c r="B32" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C32" s="11"/>
-      <c r="D32" s="33"/>
+      <c r="D32" s="48"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="9"/>
@@ -10105,10 +10472,10 @@
     </row>
     <row r="33" spans="1:10" ht="15">
       <c r="B33" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C33" s="11"/>
-      <c r="D33" s="33"/>
+      <c r="D33" s="48"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
@@ -10118,10 +10485,10 @@
     </row>
     <row r="34" spans="1:10" ht="15">
       <c r="B34" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C34" s="11"/>
-      <c r="D34" s="33"/>
+      <c r="D34" s="48"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="9"/>
@@ -10131,10 +10498,10 @@
     </row>
     <row r="35" spans="1:10" ht="15">
       <c r="B35" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C35" s="11"/>
-      <c r="D35" s="33"/>
+      <c r="D35" s="48"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="9"/>
@@ -10144,10 +10511,10 @@
     </row>
     <row r="36" spans="1:10" ht="15">
       <c r="B36" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C36" s="11"/>
-      <c r="D36" s="33"/>
+      <c r="D36" s="48"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="9"/>
@@ -10159,7 +10526,7 @@
       <c r="A37" s="9"/>
       <c r="B37" s="9"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="33"/>
+      <c r="D37" s="48"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="9"/>
@@ -10169,13 +10536,13 @@
     </row>
     <row r="38" spans="1:10" ht="15">
       <c r="A38" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="C38" s="11"/>
-      <c r="D38" s="33"/>
+      <c r="D38" s="48"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="9"/>
@@ -10185,10 +10552,10 @@
     </row>
     <row r="39" spans="1:10" ht="15">
       <c r="B39" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C39" s="11"/>
-      <c r="D39" s="33"/>
+      <c r="D39" s="48"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="9"/>
@@ -10199,7 +10566,7 @@
     <row r="40" spans="1:10" ht="15">
       <c r="B40" s="9"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="33"/>
+      <c r="D40" s="48"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="9"/>
@@ -10210,7 +10577,7 @@
     <row r="41" spans="1:10" ht="15">
       <c r="B41" s="9"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="33"/>
+      <c r="D41" s="48"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="9"/>
@@ -10222,7 +10589,7 @@
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="33"/>
+      <c r="D42" s="48"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="9"/>
@@ -10234,7 +10601,7 @@
       <c r="A43" s="9"/>
       <c r="B43" s="9"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="33"/>
+      <c r="D43" s="48"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="9"/>
@@ -10246,7 +10613,7 @@
       <c r="A44" s="9"/>
       <c r="B44" s="9"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="33"/>
+      <c r="D44" s="48"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="9"/>
@@ -10258,7 +10625,7 @@
       <c r="A45" s="9"/>
       <c r="B45" s="9"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="33"/>
+      <c r="D45" s="48"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="9"/>
@@ -10270,7 +10637,7 @@
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="33"/>
+      <c r="D46" s="48"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="9"/>
@@ -10282,7 +10649,7 @@
       <c r="A47" s="9"/>
       <c r="B47" s="9"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="33"/>
+      <c r="D47" s="48"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="9"/>
@@ -10294,7 +10661,7 @@
       <c r="A48" s="9"/>
       <c r="B48" s="9"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="33"/>
+      <c r="D48" s="48"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="9"/>
@@ -10306,7 +10673,7 @@
       <c r="A49" s="9"/>
       <c r="B49" s="9"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="33"/>
+      <c r="D49" s="48"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="9"/>
@@ -10318,7 +10685,7 @@
       <c r="A50" s="9"/>
       <c r="B50" s="9"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="33"/>
+      <c r="D50" s="48"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="9"/>
@@ -10330,7 +10697,7 @@
       <c r="A51" s="9"/>
       <c r="B51" s="9"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="33"/>
+      <c r="D51" s="48"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="9"/>
@@ -10342,7 +10709,7 @@
       <c r="A52" s="9"/>
       <c r="B52" s="9"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="33"/>
+      <c r="D52" s="48"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="9"/>
@@ -10354,7 +10721,7 @@
       <c r="A53" s="9"/>
       <c r="B53" s="9"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="33"/>
+      <c r="D53" s="48"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="9"/>
@@ -10366,7 +10733,7 @@
       <c r="A54" s="9"/>
       <c r="B54" s="9"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="33"/>
+      <c r="D54" s="48"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="9"/>
@@ -10378,7 +10745,7 @@
       <c r="A55" s="9"/>
       <c r="B55" s="9"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="33"/>
+      <c r="D55" s="48"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="9"/>
@@ -10390,7 +10757,7 @@
       <c r="A56" s="9"/>
       <c r="B56" s="9"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="33"/>
+      <c r="D56" s="48"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="9"/>
@@ -10402,7 +10769,7 @@
       <c r="A57" s="9"/>
       <c r="B57" s="9"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="33"/>
+      <c r="D57" s="48"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="9"/>
@@ -11321,21 +11688,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="H10:H12"/>
+    <mergeCell ref="J10:J12"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="D3:D57"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="D3:D57"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="H10:H12"/>
-    <mergeCell ref="J10:J12"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -11358,71 +11725,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.25" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="E1" s="42" t="s">
+      <c r="D1" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30" t="s">
+      <c r="H1" s="40"/>
+      <c r="I1" s="41" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" ht="15" thickBot="1">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
       <c r="G2" s="5" t="s">
         <v>10</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="30"/>
+      <c r="I2" s="41"/>
     </row>
     <row r="3" spans="1:9" ht="14.25" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="E3" s="28"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="E3" s="34"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="I3" s="28"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1">
       <c r="A4" s="8"/>
@@ -11432,42 +11799,42 @@
       <c r="C4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="33"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="35"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="33"/>
       <c r="G4" s="9"/>
       <c r="H4" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="I4" s="28"/>
+        <v>112</v>
+      </c>
+      <c r="I4" s="35"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="10"/>
-      <c r="D5" s="33"/>
+      <c r="D5" s="49"/>
       <c r="E5" s="11"/>
       <c r="F5" s="16"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I5" s="9"/>
     </row>
     <row r="6" spans="1:9" ht="15">
       <c r="A6" s="8"/>
       <c r="B6" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" s="33"/>
+        <v>114</v>
+      </c>
+      <c r="D6" s="49"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I6" s="9"/>
     </row>
@@ -11475,62 +11842,62 @@
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="D7" s="33"/>
+        <v>116</v>
+      </c>
+      <c r="D7" s="49"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="9"/>
       <c r="H7" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I7" s="9"/>
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="C8" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D8" s="33"/>
+        <v>118</v>
+      </c>
+      <c r="D8" s="49"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I8" s="9"/>
     </row>
     <row r="9" spans="1:9" ht="52.5" customHeight="1">
       <c r="C9" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="D9" s="33"/>
+        <v>120</v>
+      </c>
+      <c r="D9" s="49"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I9" s="9"/>
     </row>
     <row r="10" spans="1:9" ht="42.75" customHeight="1">
       <c r="C10" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="D10" s="33"/>
+        <v>121</v>
+      </c>
+      <c r="D10" s="49"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I10" s="9"/>
     </row>
     <row r="11" spans="1:9" ht="15">
       <c r="A11" s="8"/>
       <c r="B11" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="33"/>
+        <v>40</v>
+      </c>
+      <c r="D11" s="49"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="9"/>
@@ -11538,7 +11905,7 @@
     </row>
     <row r="12" spans="1:9" ht="15">
       <c r="A12" s="8"/>
-      <c r="D12" s="33"/>
+      <c r="D12" s="49"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="9"/>
@@ -11547,12 +11914,12 @@
     </row>
     <row r="13" spans="1:9" ht="15">
       <c r="A13" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="33"/>
+      <c r="D13" s="49"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="9"/>
@@ -11562,9 +11929,9 @@
     <row r="14" spans="1:9" ht="15">
       <c r="A14" s="8"/>
       <c r="B14" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="33"/>
+        <v>42</v>
+      </c>
+      <c r="D14" s="49"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="9"/>
@@ -11574,10 +11941,10 @@
     <row r="15" spans="1:9" ht="15">
       <c r="A15" s="8"/>
       <c r="B15" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15" s="11"/>
-      <c r="D15" s="33"/>
+      <c r="D15" s="49"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="9"/>
@@ -11587,10 +11954,10 @@
     <row r="16" spans="1:9" ht="15">
       <c r="A16" s="8"/>
       <c r="B16" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C16" s="11"/>
-      <c r="D16" s="33"/>
+      <c r="D16" s="49"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
       <c r="G16" s="9"/>
@@ -11600,7 +11967,7 @@
     <row r="17" spans="1:9" ht="15">
       <c r="A17" s="9"/>
       <c r="C17" s="11"/>
-      <c r="D17" s="33"/>
+      <c r="D17" s="49"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
@@ -11610,74 +11977,74 @@
     <row r="18" spans="1:9" ht="15">
       <c r="A18" s="9"/>
       <c r="C18" s="11"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="28"/>
+      <c r="I18" s="35"/>
     </row>
     <row r="19" spans="1:9" ht="15">
       <c r="C19" s="9"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="28"/>
+      <c r="I19" s="35"/>
     </row>
     <row r="20" spans="1:9" ht="15">
       <c r="C20" s="11"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="28"/>
+      <c r="I20" s="35"/>
     </row>
     <row r="21" spans="1:9" ht="15">
       <c r="C21" s="9"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="28"/>
+      <c r="I21" s="35"/>
     </row>
     <row r="22" spans="1:9" ht="15">
       <c r="C22" s="11"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="28"/>
+      <c r="I22" s="35"/>
     </row>
     <row r="23" spans="1:9" ht="15">
       <c r="C23" s="11"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
-      <c r="I23" s="28"/>
+      <c r="I23" s="35"/>
     </row>
     <row r="24" spans="1:9" ht="15">
       <c r="A24" s="21"/>
       <c r="B24" s="21"/>
       <c r="C24" s="12"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
-      <c r="I24" s="28"/>
+      <c r="I24" s="35"/>
     </row>
     <row r="25" spans="1:9" ht="15">
       <c r="A25" s="9"/>
       <c r="B25" s="21"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="33"/>
+      <c r="D25" s="49"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="9"/>
@@ -11688,7 +12055,7 @@
       <c r="A26" s="9"/>
       <c r="B26" s="21"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="33"/>
+      <c r="D26" s="49"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="9"/>
@@ -11699,7 +12066,7 @@
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="33"/>
+      <c r="D27" s="49"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
@@ -11710,7 +12077,7 @@
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="33"/>
+      <c r="D28" s="49"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
@@ -11721,7 +12088,7 @@
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="33"/>
+      <c r="D29" s="49"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
@@ -11732,7 +12099,7 @@
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="33"/>
+      <c r="D30" s="49"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
@@ -11743,7 +12110,7 @@
       <c r="A31" s="9"/>
       <c r="B31" s="9"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="33"/>
+      <c r="D31" s="49"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="9"/>
@@ -11754,7 +12121,7 @@
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="33"/>
+      <c r="D32" s="49"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="9"/>
@@ -11765,7 +12132,7 @@
       <c r="A33" s="9"/>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
-      <c r="D33" s="33"/>
+      <c r="D33" s="49"/>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
       <c r="G33" s="9"/>
@@ -11776,7 +12143,7 @@
       <c r="A34" s="9"/>
       <c r="B34" s="11"/>
       <c r="C34" s="9"/>
-      <c r="D34" s="33"/>
+      <c r="D34" s="49"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
@@ -11787,7 +12154,7 @@
       <c r="A35" s="9"/>
       <c r="B35" s="11"/>
       <c r="C35" s="9"/>
-      <c r="D35" s="33"/>
+      <c r="D35" s="49"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="9"/>
@@ -11798,7 +12165,7 @@
       <c r="A36" s="9"/>
       <c r="B36" s="9"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="33"/>
+      <c r="D36" s="49"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="9"/>
@@ -11809,7 +12176,7 @@
       <c r="A37" s="9"/>
       <c r="B37" s="9"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="33"/>
+      <c r="D37" s="49"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="9"/>
@@ -11820,7 +12187,7 @@
       <c r="A38" s="9"/>
       <c r="B38" s="9"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="33"/>
+      <c r="D38" s="49"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="9"/>
@@ -11831,7 +12198,7 @@
       <c r="A39" s="9"/>
       <c r="B39" s="9"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="33"/>
+      <c r="D39" s="49"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="9"/>
@@ -11842,7 +12209,7 @@
       <c r="A40" s="9"/>
       <c r="B40" s="9"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="33"/>
+      <c r="D40" s="49"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="9"/>
@@ -11853,7 +12220,7 @@
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="33"/>
+      <c r="D41" s="49"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="9"/>
@@ -11864,7 +12231,7 @@
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="33"/>
+      <c r="D42" s="49"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="9"/>
@@ -11875,7 +12242,7 @@
       <c r="A43" s="9"/>
       <c r="B43" s="9"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="33"/>
+      <c r="D43" s="49"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="9"/>
@@ -11886,7 +12253,7 @@
       <c r="A44" s="9"/>
       <c r="B44" s="9"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="33"/>
+      <c r="D44" s="49"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="9"/>
@@ -11897,7 +12264,7 @@
       <c r="A45" s="9"/>
       <c r="B45" s="9"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="33"/>
+      <c r="D45" s="49"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="9"/>
@@ -11908,7 +12275,7 @@
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="33"/>
+      <c r="D46" s="49"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="9"/>
@@ -11919,7 +12286,7 @@
       <c r="A47" s="9"/>
       <c r="B47" s="9"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="33"/>
+      <c r="D47" s="49"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="9"/>
@@ -11930,7 +12297,7 @@
       <c r="A48" s="9"/>
       <c r="B48" s="9"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="33"/>
+      <c r="D48" s="49"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="9"/>
@@ -11941,7 +12308,7 @@
       <c r="A49" s="9"/>
       <c r="B49" s="9"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="33"/>
+      <c r="D49" s="49"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="9"/>
@@ -11952,7 +12319,7 @@
       <c r="A50" s="9"/>
       <c r="B50" s="9"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="33"/>
+      <c r="D50" s="49"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="9"/>
@@ -11963,7 +12330,7 @@
       <c r="A51" s="9"/>
       <c r="B51" s="9"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="33"/>
+      <c r="D51" s="49"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="9"/>
@@ -11974,7 +12341,7 @@
       <c r="A52" s="9"/>
       <c r="B52" s="9"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="33"/>
+      <c r="D52" s="49"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="9"/>
@@ -11985,7 +12352,7 @@
       <c r="A53" s="9"/>
       <c r="B53" s="9"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="33"/>
+      <c r="D53" s="49"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="9"/>
@@ -11996,7 +12363,7 @@
       <c r="A54" s="9"/>
       <c r="B54" s="9"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="33"/>
+      <c r="D54" s="49"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="9"/>
@@ -12007,7 +12374,7 @@
       <c r="A55" s="9"/>
       <c r="B55" s="9"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="33"/>
+      <c r="D55" s="49"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="9"/>
@@ -12018,7 +12385,7 @@
       <c r="A56" s="9"/>
       <c r="B56" s="9"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="33"/>
+      <c r="D56" s="49"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="9"/>
@@ -12029,7 +12396,7 @@
       <c r="A57" s="9"/>
       <c r="B57" s="9"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="33"/>
+      <c r="D57" s="49"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="9"/>
@@ -12040,7 +12407,7 @@
       <c r="A58" s="9"/>
       <c r="B58" s="9"/>
       <c r="C58" s="11"/>
-      <c r="D58" s="33"/>
+      <c r="D58" s="49"/>
       <c r="E58" s="11"/>
       <c r="F58" s="11"/>
       <c r="G58" s="9"/>
@@ -12890,11 +13257,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="D3:D58"/>
@@ -12904,6 +13266,11 @@
     <mergeCell ref="E18:E24"/>
     <mergeCell ref="F18:F24"/>
     <mergeCell ref="I18:I24"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -12926,27 +13293,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.25" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="E1" s="42" t="s">
+      <c r="D1" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30" t="s">
+      <c r="H1" s="40"/>
+      <c r="I1" s="41" t="s">
         <v>7</v>
       </c>
     </row>
@@ -12957,115 +13324,115 @@
       <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
       <c r="G2" s="5" t="s">
         <v>10</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="30"/>
+      <c r="I2" s="41"/>
     </row>
     <row r="3" spans="1:9" ht="14.25" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3" s="28"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="E3" s="34"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="I3" s="28"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="1:9" ht="14.25" customHeight="1">
       <c r="A4" s="8"/>
       <c r="B4" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="D4" s="33"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="35"/>
+        <v>124</v>
+      </c>
+      <c r="D4" s="48"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="33"/>
       <c r="G4" s="9"/>
       <c r="H4" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="I4" s="28"/>
+        <v>125</v>
+      </c>
+      <c r="I4" s="35"/>
     </row>
     <row r="5" spans="1:9" ht="15">
       <c r="C5" s="11"/>
-      <c r="D5" s="33"/>
+      <c r="D5" s="48"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I5" s="9"/>
     </row>
     <row r="6" spans="1:9" ht="15">
       <c r="C6" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D6" s="33"/>
+        <v>127</v>
+      </c>
+      <c r="D6" s="48"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I6" s="9"/>
     </row>
     <row r="7" spans="1:9" ht="30">
       <c r="C7" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="D7" s="33"/>
+        <v>129</v>
+      </c>
+      <c r="D7" s="48"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="9"/>
       <c r="H7" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I7" s="9"/>
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="C8" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D8" s="33"/>
+        <v>131</v>
+      </c>
+      <c r="D8" s="48"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I8" s="9"/>
     </row>
     <row r="9" spans="1:9" ht="15">
       <c r="A9" s="8"/>
       <c r="B9" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9" s="9"/>
-      <c r="D9" s="33"/>
+      <c r="D9" s="48"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="9"/>
@@ -13077,7 +13444,7 @@
         <v>13</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="33"/>
+      <c r="D10" s="48"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="9"/>
@@ -13087,7 +13454,7 @@
     <row r="11" spans="1:9" ht="15">
       <c r="A11" s="8"/>
       <c r="C11" s="9"/>
-      <c r="D11" s="33"/>
+      <c r="D11" s="48"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="9"/>
@@ -13096,13 +13463,13 @@
     </row>
     <row r="12" spans="1:9" ht="15">
       <c r="A12" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="11"/>
-      <c r="D12" s="33"/>
+      <c r="D12" s="48"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="9"/>
@@ -13112,10 +13479,10 @@
     <row r="13" spans="1:9" ht="15">
       <c r="A13" s="8"/>
       <c r="B13" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11"/>
-      <c r="D13" s="33"/>
+      <c r="D13" s="48"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="9"/>
@@ -13125,10 +13492,10 @@
     <row r="14" spans="1:9" ht="15">
       <c r="A14" s="8"/>
       <c r="B14" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C14" s="11"/>
-      <c r="D14" s="33"/>
+      <c r="D14" s="48"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="9"/>
@@ -13138,10 +13505,10 @@
     <row r="15" spans="1:9" ht="15">
       <c r="A15" s="8"/>
       <c r="B15" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C15" s="11"/>
-      <c r="D15" s="33"/>
+      <c r="D15" s="48"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="9"/>
@@ -13152,7 +13519,7 @@
       <c r="A16" s="27"/>
       <c r="B16" s="27"/>
       <c r="C16" s="11"/>
-      <c r="D16" s="33"/>
+      <c r="D16" s="48"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
@@ -13161,93 +13528,93 @@
     </row>
     <row r="17" spans="1:9" ht="15">
       <c r="A17" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>55</v>
-      </c>
       <c r="C17" s="12"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
     </row>
     <row r="18" spans="1:9" ht="15">
       <c r="A18" s="9"/>
       <c r="B18" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C18" s="12"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
     </row>
     <row r="19" spans="1:9" ht="15">
       <c r="A19" s="9"/>
       <c r="C19" s="12"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
     </row>
     <row r="20" spans="1:9" ht="15">
       <c r="A20" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>61</v>
-      </c>
       <c r="C20" s="12"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
     </row>
     <row r="21" spans="1:9" ht="15">
       <c r="A21" s="9"/>
       <c r="B21" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C21" s="12"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
     </row>
     <row r="22" spans="1:9" ht="15">
       <c r="C22" s="12"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
     </row>
     <row r="23" spans="1:9" ht="15">
       <c r="C23" s="12"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
     </row>
     <row r="24" spans="1:9" ht="15">
       <c r="A24" s="21"/>
       <c r="B24" s="21"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="33"/>
+      <c r="D24" s="48"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="9"/>
@@ -13258,7 +13625,7 @@
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="11"/>
-      <c r="D25" s="33"/>
+      <c r="D25" s="48"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="9"/>
@@ -13269,7 +13636,7 @@
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="33"/>
+      <c r="D26" s="48"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
@@ -13280,7 +13647,7 @@
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="33"/>
+      <c r="D27" s="48"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
@@ -13291,7 +13658,7 @@
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="33"/>
+      <c r="D28" s="48"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
@@ -13302,7 +13669,7 @@
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
       <c r="C29" s="11"/>
-      <c r="D29" s="33"/>
+      <c r="D29" s="48"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
@@ -13313,7 +13680,7 @@
       <c r="A30" s="9"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="33"/>
+      <c r="D30" s="48"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="9"/>
@@ -13324,7 +13691,7 @@
       <c r="A31" s="9"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
-      <c r="D31" s="33"/>
+      <c r="D31" s="48"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="9"/>
@@ -13335,7 +13702,7 @@
       <c r="A32" s="9"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
-      <c r="D32" s="33"/>
+      <c r="D32" s="48"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="9"/>
@@ -13346,7 +13713,7 @@
       <c r="A33" s="9"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
-      <c r="D33" s="33"/>
+      <c r="D33" s="48"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
@@ -13357,7 +13724,7 @@
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
-      <c r="D34" s="33"/>
+      <c r="D34" s="48"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="9"/>
@@ -13368,7 +13735,7 @@
       <c r="A35" s="9"/>
       <c r="B35" s="9"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="33"/>
+      <c r="D35" s="48"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="9"/>
@@ -13379,7 +13746,7 @@
       <c r="A36" s="9"/>
       <c r="B36" s="9"/>
       <c r="C36" s="11"/>
-      <c r="D36" s="33"/>
+      <c r="D36" s="48"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="9"/>
@@ -13390,7 +13757,7 @@
       <c r="A37" s="9"/>
       <c r="B37" s="9"/>
       <c r="C37" s="11"/>
-      <c r="D37" s="33"/>
+      <c r="D37" s="48"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="9"/>
@@ -13401,7 +13768,7 @@
       <c r="A38" s="9"/>
       <c r="B38" s="9"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="33"/>
+      <c r="D38" s="48"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="9"/>
@@ -13412,7 +13779,7 @@
       <c r="A39" s="9"/>
       <c r="B39" s="9"/>
       <c r="C39" s="11"/>
-      <c r="D39" s="33"/>
+      <c r="D39" s="48"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="9"/>
@@ -13423,7 +13790,7 @@
       <c r="A40" s="9"/>
       <c r="B40" s="9"/>
       <c r="C40" s="11"/>
-      <c r="D40" s="33"/>
+      <c r="D40" s="48"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="9"/>
@@ -13434,7 +13801,7 @@
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="11"/>
-      <c r="D41" s="33"/>
+      <c r="D41" s="48"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="9"/>
@@ -13445,7 +13812,7 @@
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
       <c r="C42" s="11"/>
-      <c r="D42" s="33"/>
+      <c r="D42" s="48"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="9"/>
@@ -13456,7 +13823,7 @@
       <c r="A43" s="9"/>
       <c r="B43" s="9"/>
       <c r="C43" s="11"/>
-      <c r="D43" s="33"/>
+      <c r="D43" s="48"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="9"/>
@@ -13467,7 +13834,7 @@
       <c r="A44" s="9"/>
       <c r="B44" s="9"/>
       <c r="C44" s="11"/>
-      <c r="D44" s="33"/>
+      <c r="D44" s="48"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="9"/>
@@ -13478,7 +13845,7 @@
       <c r="A45" s="9"/>
       <c r="B45" s="9"/>
       <c r="C45" s="11"/>
-      <c r="D45" s="33"/>
+      <c r="D45" s="48"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="9"/>
@@ -13489,7 +13856,7 @@
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="11"/>
-      <c r="D46" s="33"/>
+      <c r="D46" s="48"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="9"/>
@@ -13500,7 +13867,7 @@
       <c r="A47" s="9"/>
       <c r="B47" s="9"/>
       <c r="C47" s="11"/>
-      <c r="D47" s="33"/>
+      <c r="D47" s="48"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="9"/>
@@ -13511,7 +13878,7 @@
       <c r="A48" s="9"/>
       <c r="B48" s="9"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="33"/>
+      <c r="D48" s="48"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="9"/>
@@ -13522,7 +13889,7 @@
       <c r="A49" s="9"/>
       <c r="B49" s="9"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="33"/>
+      <c r="D49" s="48"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="9"/>
@@ -13533,7 +13900,7 @@
       <c r="A50" s="9"/>
       <c r="B50" s="9"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="33"/>
+      <c r="D50" s="48"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="9"/>
@@ -13544,7 +13911,7 @@
       <c r="A51" s="9"/>
       <c r="B51" s="9"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="33"/>
+      <c r="D51" s="48"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="9"/>
@@ -13555,7 +13922,7 @@
       <c r="A52" s="9"/>
       <c r="B52" s="9"/>
       <c r="C52" s="11"/>
-      <c r="D52" s="33"/>
+      <c r="D52" s="48"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="9"/>
@@ -13566,7 +13933,7 @@
       <c r="A53" s="9"/>
       <c r="B53" s="9"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="33"/>
+      <c r="D53" s="48"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="9"/>
@@ -13577,7 +13944,7 @@
       <c r="A54" s="9"/>
       <c r="B54" s="9"/>
       <c r="C54" s="11"/>
-      <c r="D54" s="33"/>
+      <c r="D54" s="48"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="9"/>
@@ -13588,7 +13955,7 @@
       <c r="A55" s="9"/>
       <c r="B55" s="9"/>
       <c r="C55" s="11"/>
-      <c r="D55" s="33"/>
+      <c r="D55" s="48"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="9"/>
@@ -13599,7 +13966,7 @@
       <c r="A56" s="9"/>
       <c r="B56" s="9"/>
       <c r="C56" s="11"/>
-      <c r="D56" s="33"/>
+      <c r="D56" s="48"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="9"/>
@@ -13610,7 +13977,7 @@
       <c r="A57" s="9"/>
       <c r="B57" s="9"/>
       <c r="C57" s="11"/>
-      <c r="D57" s="33"/>
+      <c r="D57" s="48"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="9"/>
@@ -14455,11 +14822,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="D3:D57"/>
@@ -14471,8 +14833,13 @@
     <mergeCell ref="G17:G23"/>
     <mergeCell ref="H17:H23"/>
     <mergeCell ref="I17:I23"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Mapping Template BrotZeit.xlsx
+++ b/Mapping Template BrotZeit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tabita\Desktop\Data Science\Data Engineer\Projekt\BackZeit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B74BCB9-D1E3-424A-BDAA-0304F909892E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2364DF94-00CB-40F5-998A-594ECCBAA52E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="D_Filiale" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="145">
   <si>
     <t>Source DB / csv / ….</t>
   </si>
@@ -685,95 +685,6 @@
 FROM   DWH_BackZeit.dbo.D_Filiale;C20</t>
   </si>
   <si>
-    <t xml:space="preserve">--- ETL für Dimension Datum
-USE DWH_BackZeit;
--- Entfernen der Stored Procedure, falls sie existiert
-IF OBJECT_ID('sp_FillDimDatum', 'P') IS NOT NULL
-    BEGIN
-        DROP PROCEDURE sp_FillDimDatum;
-    END
-GO
--- Erstellen der Stored Procedure
-CREATE PROCEDURE sp_FillDimDatum
-AS
-BEGIN
-    INSERT INTO DWH_BackZeit.dbo.D_Datum(DatumID, Tag, Quartal, Monat, Jahr, Wochentag, MonatLang, MonatKurz)
-    SELECT DISTINCT
-        CONVERT(INT, CONVERT(CHAR(8), Zeitpunkt, 112)) AS DatumID, -- 112 ist Format YYYYMMDD
-        CONVERT(CHAR(10), Zeitpunkt, 23) AS Tag, -- 23 ist Format YYYY-MM-DD
-        CONCAT(YEAR(Zeitpunkt), '-Q', DATEPART(QUARTER, Zeitpunkt)) AS Quartal,
-        CONVERT(CHAR(7), Zeitpunkt, 23) AS Monat,
-        YEAR(Zeitpunkt) AS Jahr,
-        --Wochentag bestimmen
-        --Variante1: Problem: hängt von den Server Einstellungen ab und kann daher falsche Werte liefern
-        --CASE DATEPART(WEEKDAY, Zeitpunkt)
-        --    WHEN 1 THEN 'Sonntag'
-        --    WHEN 2 THEN 'Montag'
-        --    WHEN 3 THEN 'Dienstag'
-        --    WHEN 4 THEN 'Mittwoch'
-        --    WHEN 5 THEN 'Donnerstag'
-        --    WHEN 6 THEN 'Freitag'
-        --    WHEN 7 THEN 'Samstag'
-        --END AS Wochentag,
-        --Variante2: Rechnet über einen bekannten Montag (1.1.1900) aus welcher Wochentag ist, dadurch ist das Ergebnis unabhängig von den Server Einstellungen
-        CASE
-            WHEN DATEDIFF(DAY, '19000101', Zeitpunkt) % 7 = 0 THEN 'Montag' -- Wenn die Differenz zwischen dem Zeitpunkt und 01.01.1900, restlos durch 7 teilbar ist, dann ist es ein Montag 
-            WHEN DATEDIFF(DAY, '19000101', Zeitpunkt) % 7 = 1 THEN 'Dienstag' -- Bei einem Rest von 1, muss es ein Dienstag sein usw.
-            WHEN DATEDIFF(DAY, '19000101', Zeitpunkt) % 7 = 2 THEN 'Mittwoch'
-            WHEN DATEDIFF(DAY, '19000101', Zeitpunkt) % 7 = 3 THEN 'Donnerstag'
-            WHEN DATEDIFF(DAY, '19000101', Zeitpunkt) % 7 = 4 THEN 'Freitag'
-            WHEN DATEDIFF(DAY, '19000101', Zeitpunkt) % 7 = 5 THEN 'Samstag'
-            WHEN DATEDIFF(DAY, '19000101', Zeitpunkt) % 7 = 6 THEN 'Sonntag'
-        END AS Wochentag,
-        CASE MONTH(Zeitpunkt)
-            WHEN 1 THEN 'Januar'
-            WHEN 2 THEN 'Februar'
-            WHEN 3 THEN 'März'
-            WHEN 4 THEN 'April'
-            WHEN 5 THEN 'Mai'
-            WHEN 6 THEN 'Juni'
-            WHEN 7 THEN 'Juli'
-            WHEN 8 THEN 'August'
-            WHEN 9 THEN 'September'
-            WHEN 10 THEN 'Oktober'
-            WHEN 11 THEN 'November'
-            WHEN 12 THEN 'Dezember'
-        END AS MonatLang,
-        CASE MONTH(Zeitpunkt)
-            WHEN 1 THEN 'Jan'
-            WHEN 2 THEN 'Feb'
-            WHEN 3 THEN 'Mär'
-            WHEN 4 THEN 'Apr'
-            WHEN 5 THEN 'Mai'
-            WHEN 6 THEN 'Jun'
-            WHEN 7 THEN 'Jul'
-            WHEN 8 THEN 'Aug'
-            WHEN 9 THEN 'Sep'
-            WHEN 10 THEN 'Okt'
-            WHEN 11 THEN 'Nov'
-            WHEN 12 THEN 'Dez'
-        END AS MonatKurz
-    FROM
-        BDB_BackZeit.bdb_Kassensystem.Verkauf v
-        -- Verhindert, dass bereits vorhandene Tage erneut eingefügt werden
-    WHERE NOT EXISTS
-    (
-        SELECT 1
-        FROM DWH_BackZeit.dbo.D_Datum d
-        WHERE d.DatumID =
-              CONVERT(
-                  INT,
-                  CONVERT(CHAR(8), v.Zeitpunkt, 112)
-              )
-    );
-END
-GO
-EXEC sp_FillDimDatum;
-SELECT * FROM DWH_BackZeit.dbo.D_Datum;
----------
-</t>
-  </si>
-  <si>
     <t>USE BDB_BackZeit;
 INSERT INTO DWH_BackZeit.dbo.D_Verkaufsvorgang(Zahlart, FilialID, Zeitpunkt, Umsatz) 
 SELECT
@@ -831,6 +742,90 @@
   </si>
   <si>
     <t>Wird nur einmal zu Beginn komplett angelegt</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> --- ETL für Dimension Datum
+USE DWH_BackZeit;
+-- Entfernen der Stored Procedure, falls sie existiert
+IF OBJECT_ID('sp_FillDimDatum', 'P') IS NOT NULL
+    BEGIN
+        DROP PROCEDURE sp_FillDimDatum;
+    END
+GO
+-- Erstellen der Stored Procedure
+CREATE PROCEDURE sp_FillDimDatum
+  @Jahr varChar(4)
+AS
+BEGIN
+    SET NOCOUNT ON;
+    DECLARE @StartDate DATE;
+    DECLARE @EndDate DATE;
+    DECLARE @WeekDay INT;
+    SET @StartDate = CONVERT(DATE, CONCAT(@jahr, '-01-01'));
+    SET @WeekDay = DATEDIFF(DAY, '19000101', @StartDate) % 7;
+    SET @EndDate = CONVERT(DATE, CONCAT(@jahr, '-12-31'));
+    WHILE @StartDate &lt;= @EndDate
+    BEGIN
+        INSERT INTO DWH_BackZeit.dbo.D_Datum (DatumID, Tag, Quartal, Monat, Jahr, Wochentag, MonatLang, MonatKurz)
+        VALUES (
+            CONVERT(INT, CONVERT(CHAR(8), @StartDate, 112)), -- 112 ist Format YYYYMMDD
+            @StartDate,
+            Concat(Year(@StartDate),'-Q', DATEPART(QUARTER, @Startdate)),
+            Concat(Year(@StartDate),'-', CASE WHEN MONTH(@startdate) &lt; 10 THEN '0' ELSE '' END, Month(@Startdate)),
+            CONVERT(VARCHAR(4), YEAR(@StartDate)),
+            CASE @WeekDay
+                WHEN 0 THEN 'Montag' -- Wenn die Differenz zwischen dem Zeitpunkt und 01.01.1900, restlos durch 7 teilbar ist, dann ist es ein Montag 
+                WHEN 1 THEN 'Dienstag' -- Bei einem Rest von 1, muss es ein Dienstag sein usw.
+                WHEN 2 THEN 'Mittwoch'
+                WHEN 3 THEN 'Donnerstag'
+                WHEN 4 THEN 'Freitag'
+                WHEN 5 THEN 'Samstag'
+                WHEN 6 THEN 'Sonntag'
+            END,
+            CASE MONTH(@StartDate)
+                WHEN 1 THEN 'Januar'
+                WHEN 2 THEN 'Februar'
+                WHEN 3 THEN 'März'
+                WHEN 4 THEN 'April'
+                WHEN 5 THEN 'Mai'
+                WHEN 6 THEN 'Juni'
+                WHEN 7 THEN 'Juli'
+                WHEN 8 THEN 'August'
+                WHEN 9 THEN 'September'
+                WHEN 10 THEN 'Oktober'
+                WHEN 11 THEN 'November'
+                WHEN 12 THEN 'Dezember'
+            END,
+            CASE MONTH(@StartDate)
+                WHEN 1 THEN 'Jan'
+                WHEN 2 THEN 'Feb'
+                WHEN 3 THEN 'Mär'
+                WHEN 4 THEN 'Apr'
+                WHEN 5 THEN 'Mai'
+                WHEN 6 THEN 'Jun'
+                WHEN 7 THEN 'Jul'
+                WHEN 8 THEN 'Aug'
+                WHEN 9 THEN 'Sep'
+                WHEN 10 THEN 'Okt'
+                WHEN 11 THEN 'Nov'
+                WHEN 12 THEN 'Dez'
+            END
+        );
+        -- Zum nächsten Tag inkrementieren
+        SET @StartDate = DATEADD(DAY, 1, @StartDate);
+        -- Wochentag neu berechnen
+        SET @WeekDay = DATEDIFF(DAY, '19000101', @StartDate) % 7;
+    END
+END;
+GO
+DELETE DWH_BackZeit.dbo.D_Datum;
+EXEC sp_FillDimDatum 2026;
+SELECT * FROM DWH_BackZeit.dbo.D_Datum;
+---------
+</t>
+  </si>
+  <si>
+    <t>Wird jährlich für jedes Jahr angelegt</t>
   </si>
 </sst>
 </file>
@@ -1142,23 +1137,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1173,16 +1153,31 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1478,30 +1473,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="32" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="24"/>
+      <c r="H1" s="30"/>
       <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="31" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1512,10 +1507,10 @@
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
       <c r="G2" s="4" t="s">
         <v>10</v>
       </c>
@@ -1523,51 +1518,51 @@
         <v>11</v>
       </c>
       <c r="I2" s="2"/>
-      <c r="J2" s="25"/>
+      <c r="J2" s="31"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="39" t="s">
+      <c r="D3" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="G3" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="H3" s="37" t="s">
         <v>13</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="30"/>
+      <c r="J3" s="25"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="37"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
       <c r="I4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="30"/>
+      <c r="J4" s="25"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="8"/>
@@ -1577,7 +1572,7 @@
       <c r="C5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="27"/>
+      <c r="D5" s="35"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="8"/>
@@ -1597,7 +1592,7 @@
       <c r="C6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="27"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="8"/>
@@ -1611,7 +1606,7 @@
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="9"/>
-      <c r="D7" s="27"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="8"/>
@@ -1619,7 +1614,7 @@
         <v>26</v>
       </c>
       <c r="I7" s="8"/>
-      <c r="J7" s="36" t="s">
+      <c r="J7" s="39" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1631,7 +1626,7 @@
         <v>29</v>
       </c>
       <c r="C8" s="9"/>
-      <c r="D8" s="27"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="G8" s="8"/>
@@ -1639,13 +1634,13 @@
       <c r="I8" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="36"/>
+      <c r="J8" s="39"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
-      <c r="D9" s="27"/>
+      <c r="D9" s="35"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="8"/>
@@ -1653,13 +1648,13 @@
       <c r="I9" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="36"/>
+      <c r="J9" s="39"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="9"/>
-      <c r="D10" s="27"/>
+      <c r="D10" s="35"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="G10" s="8"/>
@@ -1667,13 +1662,13 @@
       <c r="I10" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="36"/>
+      <c r="J10" s="39"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
-      <c r="D11" s="27"/>
+      <c r="D11" s="35"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="8"/>
@@ -1681,25 +1676,25 @@
       <c r="I11" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J11" s="36"/>
+      <c r="J11" s="39"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="9"/>
-      <c r="D12" s="27"/>
+      <c r="D12" s="35"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
-      <c r="J12" s="36"/>
+      <c r="J12" s="39"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="9"/>
-      <c r="D13" s="27"/>
+      <c r="D13" s="35"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="8"/>
@@ -1713,7 +1708,7 @@
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="9"/>
-      <c r="D14" s="27"/>
+      <c r="D14" s="35"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="8"/>
@@ -1725,7 +1720,7 @@
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="9"/>
-      <c r="D15" s="27"/>
+      <c r="D15" s="35"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="8"/>
@@ -1739,7 +1734,7 @@
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
-      <c r="D16" s="27"/>
+      <c r="D16" s="35"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
@@ -1748,94 +1743,94 @@
       <c r="J16" s="8"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17" s="40"/>
-      <c r="B17" s="40"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="38"/>
       <c r="C17" s="10"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
       <c r="I17" s="8"/>
-      <c r="J17" s="30"/>
+      <c r="J17" s="25"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A18" s="40"/>
-      <c r="B18" s="40"/>
+      <c r="A18" s="38"/>
+      <c r="B18" s="38"/>
       <c r="C18" s="10"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
       <c r="I18" s="8"/>
-      <c r="J18" s="30"/>
+      <c r="J18" s="25"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A19" s="40"/>
-      <c r="B19" s="40"/>
+      <c r="A19" s="38"/>
+      <c r="B19" s="38"/>
       <c r="C19" s="10"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
       <c r="I19" s="8"/>
-      <c r="J19" s="30"/>
+      <c r="J19" s="25"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A20" s="40"/>
-      <c r="B20" s="40"/>
+      <c r="A20" s="38"/>
+      <c r="B20" s="38"/>
       <c r="C20" s="10"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
       <c r="I20" s="8"/>
-      <c r="J20" s="30"/>
+      <c r="J20" s="25"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A21" s="40"/>
-      <c r="B21" s="40"/>
+      <c r="A21" s="38"/>
+      <c r="B21" s="38"/>
       <c r="C21" s="10"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
       <c r="I21" s="8"/>
-      <c r="J21" s="30"/>
+      <c r="J21" s="25"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A22" s="40"/>
-      <c r="B22" s="40"/>
+      <c r="A22" s="38"/>
+      <c r="B22" s="38"/>
       <c r="C22" s="10"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
       <c r="I22" s="8"/>
-      <c r="J22" s="30"/>
+      <c r="J22" s="25"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A23" s="40"/>
-      <c r="B23" s="40"/>
+      <c r="A23" s="38"/>
+      <c r="B23" s="38"/>
       <c r="C23" s="10"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
       <c r="I23" s="8"/>
-      <c r="J23" s="30"/>
+      <c r="J23" s="25"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="9"/>
-      <c r="D24" s="27"/>
+      <c r="D24" s="35"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" s="8"/>
@@ -1847,7 +1842,7 @@
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="9"/>
-      <c r="D25" s="27"/>
+      <c r="D25" s="35"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="G25" s="8"/>
@@ -1859,7 +1854,7 @@
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="9"/>
-      <c r="D26" s="27"/>
+      <c r="D26" s="35"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
@@ -1871,7 +1866,7 @@
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="9"/>
-      <c r="D27" s="27"/>
+      <c r="D27" s="35"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
@@ -1883,7 +1878,7 @@
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="9"/>
-      <c r="D28" s="27"/>
+      <c r="D28" s="35"/>
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
@@ -1895,7 +1890,7 @@
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="9"/>
-      <c r="D29" s="27"/>
+      <c r="D29" s="35"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
@@ -1907,7 +1902,7 @@
       <c r="A30" s="8"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
-      <c r="D30" s="27"/>
+      <c r="D30" s="35"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="8"/>
@@ -1919,7 +1914,7 @@
       <c r="A31" s="8"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
-      <c r="D31" s="27"/>
+      <c r="D31" s="35"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="G31" s="8"/>
@@ -1931,7 +1926,7 @@
       <c r="A32" s="8"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
-      <c r="D32" s="27"/>
+      <c r="D32" s="35"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
       <c r="G32" s="8"/>
@@ -1943,7 +1938,7 @@
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
-      <c r="D33" s="27"/>
+      <c r="D33" s="35"/>
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
@@ -1955,7 +1950,7 @@
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
-      <c r="D34" s="27"/>
+      <c r="D34" s="35"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
       <c r="G34" s="8"/>
@@ -1967,7 +1962,7 @@
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="9"/>
-      <c r="D35" s="27"/>
+      <c r="D35" s="35"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
       <c r="G35" s="8"/>
@@ -1979,7 +1974,7 @@
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="9"/>
-      <c r="D36" s="27"/>
+      <c r="D36" s="35"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
       <c r="G36" s="8"/>
@@ -1991,7 +1986,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="9"/>
-      <c r="D37" s="27"/>
+      <c r="D37" s="35"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
       <c r="G37" s="8"/>
@@ -2003,7 +1998,7 @@
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="9"/>
-      <c r="D38" s="27"/>
+      <c r="D38" s="35"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
       <c r="G38" s="8"/>
@@ -2015,7 +2010,7 @@
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="9"/>
-      <c r="D39" s="27"/>
+      <c r="D39" s="35"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
       <c r="G39" s="8"/>
@@ -2027,7 +2022,7 @@
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="9"/>
-      <c r="D40" s="27"/>
+      <c r="D40" s="35"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
       <c r="G40" s="8"/>
@@ -2039,7 +2034,7 @@
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="9"/>
-      <c r="D41" s="27"/>
+      <c r="D41" s="35"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
       <c r="G41" s="8"/>
@@ -2051,7 +2046,7 @@
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="9"/>
-      <c r="D42" s="27"/>
+      <c r="D42" s="35"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
       <c r="G42" s="8"/>
@@ -2063,7 +2058,7 @@
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="9"/>
-      <c r="D43" s="27"/>
+      <c r="D43" s="35"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
       <c r="G43" s="8"/>
@@ -2075,7 +2070,7 @@
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="9"/>
-      <c r="D44" s="27"/>
+      <c r="D44" s="35"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
       <c r="G44" s="8"/>
@@ -2087,7 +2082,7 @@
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="9"/>
-      <c r="D45" s="27"/>
+      <c r="D45" s="35"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
       <c r="G45" s="8"/>
@@ -2099,7 +2094,7 @@
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="9"/>
-      <c r="D46" s="27"/>
+      <c r="D46" s="35"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
       <c r="G46" s="8"/>
@@ -2111,7 +2106,7 @@
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="9"/>
-      <c r="D47" s="27"/>
+      <c r="D47" s="35"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
       <c r="G47" s="8"/>
@@ -2123,7 +2118,7 @@
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="9"/>
-      <c r="D48" s="27"/>
+      <c r="D48" s="35"/>
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
       <c r="G48" s="8"/>
@@ -2135,7 +2130,7 @@
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="9"/>
-      <c r="D49" s="27"/>
+      <c r="D49" s="35"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9"/>
       <c r="G49" s="8"/>
@@ -2147,7 +2142,7 @@
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="9"/>
-      <c r="D50" s="27"/>
+      <c r="D50" s="35"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
       <c r="G50" s="8"/>
@@ -2159,7 +2154,7 @@
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="9"/>
-      <c r="D51" s="27"/>
+      <c r="D51" s="35"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
       <c r="G51" s="8"/>
@@ -2171,7 +2166,7 @@
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="9"/>
-      <c r="D52" s="27"/>
+      <c r="D52" s="35"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
       <c r="G52" s="8"/>
@@ -2183,7 +2178,7 @@
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="9"/>
-      <c r="D53" s="27"/>
+      <c r="D53" s="35"/>
       <c r="E53" s="9"/>
       <c r="F53" s="9"/>
       <c r="G53" s="8"/>
@@ -2195,7 +2190,7 @@
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="9"/>
-      <c r="D54" s="27"/>
+      <c r="D54" s="35"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
       <c r="G54" s="8"/>
@@ -2207,7 +2202,7 @@
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="9"/>
-      <c r="D55" s="27"/>
+      <c r="D55" s="35"/>
       <c r="E55" s="9"/>
       <c r="F55" s="9"/>
       <c r="G55" s="8"/>
@@ -2219,7 +2214,7 @@
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="9"/>
-      <c r="D56" s="27"/>
+      <c r="D56" s="35"/>
       <c r="E56" s="9"/>
       <c r="F56" s="9"/>
       <c r="G56" s="8"/>
@@ -2231,7 +2226,7 @@
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="9"/>
-      <c r="D57" s="27"/>
+      <c r="D57" s="35"/>
       <c r="E57" s="9"/>
       <c r="F57" s="9"/>
       <c r="G57" s="8"/>
@@ -3153,11 +3148,11 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="J3:J4"/>
     <mergeCell ref="J7:J12"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -3172,11 +3167,11 @@
     <mergeCell ref="J17:J23"/>
     <mergeCell ref="F17:F23"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3201,30 +3196,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="32" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="24"/>
+      <c r="H1" s="30"/>
       <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="31" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3235,10 +3230,10 @@
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
       <c r="G2" s="4" t="s">
         <v>10</v>
       </c>
@@ -3246,7 +3241,7 @@
         <v>11</v>
       </c>
       <c r="I2" s="2"/>
-      <c r="J2" s="25"/>
+      <c r="J2" s="31"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="13" t="s">
@@ -3255,8 +3250,8 @@
       <c r="C3" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="26" t="s">
-        <v>141</v>
+      <c r="D3" s="40" t="s">
+        <v>140</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>15</v>
@@ -3285,7 +3280,7 @@
       <c r="C4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="27"/>
+      <c r="D4" s="35"/>
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
       <c r="G4" s="17"/>
@@ -3305,7 +3300,7 @@
       <c r="C5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="27"/>
+      <c r="D5" s="35"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="8"/>
@@ -3323,7 +3318,7 @@
       <c r="C6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="27"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="8"/>
@@ -3340,7 +3335,7 @@
       <c r="C7" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="27"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="8"/>
@@ -3355,7 +3350,7 @@
     <row r="8" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="8"/>
       <c r="C8" s="9"/>
-      <c r="D8" s="27"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="G8" s="8"/>
@@ -3371,7 +3366,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="9"/>
-      <c r="D9" s="27"/>
+      <c r="D9" s="35"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="8"/>
@@ -3387,7 +3382,7 @@
         <v>42</v>
       </c>
       <c r="C10" s="8"/>
-      <c r="D10" s="27"/>
+      <c r="D10" s="35"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="G10" s="8"/>
@@ -3403,7 +3398,7 @@
         <v>47</v>
       </c>
       <c r="C11" s="9"/>
-      <c r="D11" s="27"/>
+      <c r="D11" s="35"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="8"/>
@@ -3417,7 +3412,7 @@
         <v>48</v>
       </c>
       <c r="C12" s="9"/>
-      <c r="D12" s="27"/>
+      <c r="D12" s="35"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="8"/>
@@ -3431,7 +3426,7 @@
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="9"/>
-      <c r="D13" s="27"/>
+      <c r="D13" s="35"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="8"/>
@@ -3447,7 +3442,7 @@
         <v>47</v>
       </c>
       <c r="C14" s="9"/>
-      <c r="D14" s="27"/>
+      <c r="D14" s="35"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="8"/>
@@ -3462,7 +3457,7 @@
         <v>50</v>
       </c>
       <c r="C15" s="9"/>
-      <c r="D15" s="27"/>
+      <c r="D15" s="35"/>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
@@ -3475,92 +3470,92 @@
         <v>51</v>
       </c>
       <c r="C16" s="10"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
       <c r="I16" s="8"/>
-      <c r="J16" s="30"/>
+      <c r="J16" s="25"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>52</v>
       </c>
       <c r="C17" s="10"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
       <c r="I17" s="8"/>
-      <c r="J17" s="30"/>
+      <c r="J17" s="25"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="18"/>
       <c r="B18" s="18"/>
       <c r="C18" s="10"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
       <c r="I18" s="8"/>
-      <c r="J18" s="30"/>
+      <c r="J18" s="25"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="18"/>
       <c r="B19" s="18"/>
       <c r="C19" s="10"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
       <c r="I19" s="8"/>
-      <c r="J19" s="30"/>
+      <c r="J19" s="25"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="18"/>
       <c r="B20" s="18"/>
       <c r="C20" s="10"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
       <c r="I20" s="8"/>
-      <c r="J20" s="30"/>
+      <c r="J20" s="25"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="18"/>
       <c r="B21" s="18"/>
       <c r="C21" s="10"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
       <c r="I21" s="8"/>
-      <c r="J21" s="30"/>
+      <c r="J21" s="25"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="18"/>
       <c r="B22" s="18"/>
       <c r="C22" s="10"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
       <c r="I22" s="8"/>
-      <c r="J22" s="30"/>
+      <c r="J22" s="25"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="9"/>
-      <c r="D23" s="27"/>
+      <c r="D23" s="35"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
       <c r="G23" s="8"/>
@@ -3572,7 +3567,7 @@
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="9"/>
-      <c r="D24" s="27"/>
+      <c r="D24" s="35"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" s="8"/>
@@ -3584,7 +3579,7 @@
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="9"/>
-      <c r="D25" s="27"/>
+      <c r="D25" s="35"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
@@ -3596,7 +3591,7 @@
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="9"/>
-      <c r="D26" s="27"/>
+      <c r="D26" s="35"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
@@ -3608,7 +3603,7 @@
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="9"/>
-      <c r="D27" s="27"/>
+      <c r="D27" s="35"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
@@ -3620,7 +3615,7 @@
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="9"/>
-      <c r="D28" s="27"/>
+      <c r="D28" s="35"/>
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
@@ -3632,7 +3627,7 @@
       <c r="A29" s="8"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
-      <c r="D29" s="27"/>
+      <c r="D29" s="35"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="G29" s="8"/>
@@ -3644,7 +3639,7 @@
       <c r="A30" s="8"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
-      <c r="D30" s="27"/>
+      <c r="D30" s="35"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="8"/>
@@ -3656,7 +3651,7 @@
       <c r="A31" s="8"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
-      <c r="D31" s="27"/>
+      <c r="D31" s="35"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="G31" s="8"/>
@@ -3668,7 +3663,7 @@
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
-      <c r="D32" s="27"/>
+      <c r="D32" s="35"/>
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
@@ -3680,7 +3675,7 @@
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
-      <c r="D33" s="27"/>
+      <c r="D33" s="35"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
       <c r="G33" s="8"/>
@@ -3692,7 +3687,7 @@
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="9"/>
-      <c r="D34" s="27"/>
+      <c r="D34" s="35"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
       <c r="G34" s="8"/>
@@ -3704,7 +3699,7 @@
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="9"/>
-      <c r="D35" s="27"/>
+      <c r="D35" s="35"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
       <c r="G35" s="8"/>
@@ -3716,7 +3711,7 @@
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="9"/>
-      <c r="D36" s="27"/>
+      <c r="D36" s="35"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
       <c r="G36" s="8"/>
@@ -3728,7 +3723,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="9"/>
-      <c r="D37" s="27"/>
+      <c r="D37" s="35"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
       <c r="G37" s="8"/>
@@ -3740,7 +3735,7 @@
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="9"/>
-      <c r="D38" s="27"/>
+      <c r="D38" s="35"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
       <c r="G38" s="8"/>
@@ -3752,7 +3747,7 @@
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="9"/>
-      <c r="D39" s="27"/>
+      <c r="D39" s="35"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
       <c r="G39" s="8"/>
@@ -3764,7 +3759,7 @@
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="9"/>
-      <c r="D40" s="27"/>
+      <c r="D40" s="35"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
       <c r="G40" s="8"/>
@@ -3776,7 +3771,7 @@
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="9"/>
-      <c r="D41" s="27"/>
+      <c r="D41" s="35"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
       <c r="G41" s="8"/>
@@ -3788,7 +3783,7 @@
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="9"/>
-      <c r="D42" s="27"/>
+      <c r="D42" s="35"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
       <c r="G42" s="8"/>
@@ -3800,7 +3795,7 @@
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="9"/>
-      <c r="D43" s="27"/>
+      <c r="D43" s="35"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
       <c r="G43" s="8"/>
@@ -3812,7 +3807,7 @@
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="9"/>
-      <c r="D44" s="27"/>
+      <c r="D44" s="35"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
       <c r="G44" s="8"/>
@@ -3824,7 +3819,7 @@
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="9"/>
-      <c r="D45" s="27"/>
+      <c r="D45" s="35"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
       <c r="G45" s="8"/>
@@ -3836,7 +3831,7 @@
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="9"/>
-      <c r="D46" s="27"/>
+      <c r="D46" s="35"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
       <c r="G46" s="8"/>
@@ -3848,7 +3843,7 @@
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="9"/>
-      <c r="D47" s="27"/>
+      <c r="D47" s="35"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
       <c r="G47" s="8"/>
@@ -3860,7 +3855,7 @@
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="9"/>
-      <c r="D48" s="27"/>
+      <c r="D48" s="35"/>
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
       <c r="G48" s="8"/>
@@ -3872,7 +3867,7 @@
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="9"/>
-      <c r="D49" s="27"/>
+      <c r="D49" s="35"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9"/>
       <c r="G49" s="8"/>
@@ -3884,7 +3879,7 @@
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="9"/>
-      <c r="D50" s="27"/>
+      <c r="D50" s="35"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
       <c r="G50" s="8"/>
@@ -3896,7 +3891,7 @@
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="9"/>
-      <c r="D51" s="27"/>
+      <c r="D51" s="35"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
       <c r="G51" s="8"/>
@@ -3908,7 +3903,7 @@
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="9"/>
-      <c r="D52" s="27"/>
+      <c r="D52" s="35"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
       <c r="G52" s="8"/>
@@ -3920,7 +3915,7 @@
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="9"/>
-      <c r="D53" s="27"/>
+      <c r="D53" s="35"/>
       <c r="E53" s="9"/>
       <c r="F53" s="9"/>
       <c r="G53" s="8"/>
@@ -3932,7 +3927,7 @@
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="9"/>
-      <c r="D54" s="27"/>
+      <c r="D54" s="35"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
       <c r="G54" s="8"/>
@@ -3944,7 +3939,7 @@
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="9"/>
-      <c r="D55" s="27"/>
+      <c r="D55" s="35"/>
       <c r="E55" s="9"/>
       <c r="F55" s="9"/>
       <c r="G55" s="8"/>
@@ -3956,7 +3951,7 @@
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="9"/>
-      <c r="D56" s="27"/>
+      <c r="D56" s="35"/>
       <c r="E56" s="9"/>
       <c r="F56" s="9"/>
       <c r="G56" s="8"/>
@@ -4878,11 +4873,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="D3:D56"/>
@@ -4891,6 +4881,11 @@
     <mergeCell ref="G16:G22"/>
     <mergeCell ref="H16:H22"/>
     <mergeCell ref="J16:J22"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4915,30 +4910,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="32" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="24"/>
+      <c r="H1" s="30"/>
       <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="31" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4949,10 +4944,10 @@
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
       <c r="G2" s="4" t="s">
         <v>10</v>
       </c>
@@ -4960,7 +4955,7 @@
         <v>11</v>
       </c>
       <c r="I2" s="2"/>
-      <c r="J2" s="25"/>
+      <c r="J2" s="31"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
@@ -4972,7 +4967,7 @@
       <c r="C3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="39" t="s">
+      <c r="D3" s="34" t="s">
         <v>137</v>
       </c>
       <c r="E3" s="9" t="s">
@@ -5000,7 +4995,7 @@
       <c r="C4" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="27"/>
+      <c r="D4" s="35"/>
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
       <c r="G4" s="8"/>
@@ -5016,7 +5011,7 @@
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="41"/>
-      <c r="D5" s="27"/>
+      <c r="D5" s="35"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="8"/>
@@ -5028,7 +5023,7 @@
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="41"/>
-      <c r="D6" s="27"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="8"/>
@@ -5044,7 +5039,7 @@
         <v>60</v>
       </c>
       <c r="C7" s="41"/>
-      <c r="D7" s="27"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="8"/>
@@ -5060,7 +5055,7 @@
         <v>61</v>
       </c>
       <c r="C8" s="41"/>
-      <c r="D8" s="27"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="G8" s="8"/>
@@ -5074,7 +5069,7 @@
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="9"/>
-      <c r="D9" s="27"/>
+      <c r="D9" s="35"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="8"/>
@@ -5088,7 +5083,7 @@
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
-      <c r="D10" s="27"/>
+      <c r="D10" s="35"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="G10" s="8"/>
@@ -5102,7 +5097,7 @@
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="9"/>
-      <c r="D11" s="27"/>
+      <c r="D11" s="35"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="8"/>
@@ -5114,7 +5109,7 @@
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="9"/>
-      <c r="D12" s="27"/>
+      <c r="D12" s="35"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="8"/>
@@ -5128,7 +5123,7 @@
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="9"/>
-      <c r="D13" s="27"/>
+      <c r="D13" s="35"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="8"/>
@@ -5140,7 +5135,7 @@
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="9"/>
-      <c r="D14" s="27"/>
+      <c r="D14" s="35"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="8"/>
@@ -5154,7 +5149,7 @@
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="9"/>
-      <c r="D15" s="27"/>
+      <c r="D15" s="35"/>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
@@ -5163,94 +5158,94 @@
       <c r="J15" s="8"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" s="40"/>
-      <c r="B16" s="40"/>
+      <c r="A16" s="38"/>
+      <c r="B16" s="38"/>
       <c r="C16" s="10"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
       <c r="I16" s="8"/>
-      <c r="J16" s="30"/>
+      <c r="J16" s="25"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17" s="40"/>
-      <c r="B17" s="40"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="38"/>
       <c r="C17" s="10"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
       <c r="I17" s="8"/>
-      <c r="J17" s="30"/>
+      <c r="J17" s="25"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A18" s="40"/>
-      <c r="B18" s="40"/>
+      <c r="A18" s="38"/>
+      <c r="B18" s="38"/>
       <c r="C18" s="10"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
       <c r="I18" s="8"/>
-      <c r="J18" s="30"/>
+      <c r="J18" s="25"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A19" s="40"/>
-      <c r="B19" s="40"/>
+      <c r="A19" s="38"/>
+      <c r="B19" s="38"/>
       <c r="C19" s="10"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
       <c r="I19" s="8"/>
-      <c r="J19" s="30"/>
+      <c r="J19" s="25"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A20" s="40"/>
-      <c r="B20" s="40"/>
+      <c r="A20" s="38"/>
+      <c r="B20" s="38"/>
       <c r="C20" s="10"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
       <c r="I20" s="8"/>
-      <c r="J20" s="30"/>
+      <c r="J20" s="25"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A21" s="40"/>
-      <c r="B21" s="40"/>
+      <c r="A21" s="38"/>
+      <c r="B21" s="38"/>
       <c r="C21" s="10"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
       <c r="I21" s="8"/>
-      <c r="J21" s="30"/>
+      <c r="J21" s="25"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A22" s="40"/>
-      <c r="B22" s="40"/>
+      <c r="A22" s="38"/>
+      <c r="B22" s="38"/>
       <c r="C22" s="10"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
       <c r="I22" s="8"/>
-      <c r="J22" s="30"/>
+      <c r="J22" s="25"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="9"/>
-      <c r="D23" s="27"/>
+      <c r="D23" s="35"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
       <c r="G23" s="8"/>
@@ -5262,7 +5257,7 @@
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="9"/>
-      <c r="D24" s="27"/>
+      <c r="D24" s="35"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" s="8"/>
@@ -5274,7 +5269,7 @@
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="9"/>
-      <c r="D25" s="27"/>
+      <c r="D25" s="35"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
@@ -5286,7 +5281,7 @@
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="9"/>
-      <c r="D26" s="27"/>
+      <c r="D26" s="35"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
@@ -5298,7 +5293,7 @@
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="9"/>
-      <c r="D27" s="27"/>
+      <c r="D27" s="35"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
@@ -5310,7 +5305,7 @@
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="9"/>
-      <c r="D28" s="27"/>
+      <c r="D28" s="35"/>
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
@@ -5322,7 +5317,7 @@
       <c r="A29" s="8"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
-      <c r="D29" s="27"/>
+      <c r="D29" s="35"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="G29" s="8"/>
@@ -5334,7 +5329,7 @@
       <c r="A30" s="8"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
-      <c r="D30" s="27"/>
+      <c r="D30" s="35"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="8"/>
@@ -5346,7 +5341,7 @@
       <c r="A31" s="8"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
-      <c r="D31" s="27"/>
+      <c r="D31" s="35"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="G31" s="8"/>
@@ -5358,7 +5353,7 @@
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
-      <c r="D32" s="27"/>
+      <c r="D32" s="35"/>
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
@@ -5370,7 +5365,7 @@
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
-      <c r="D33" s="27"/>
+      <c r="D33" s="35"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
       <c r="G33" s="8"/>
@@ -5382,7 +5377,7 @@
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="9"/>
-      <c r="D34" s="27"/>
+      <c r="D34" s="35"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
       <c r="G34" s="8"/>
@@ -5394,7 +5389,7 @@
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="9"/>
-      <c r="D35" s="27"/>
+      <c r="D35" s="35"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
       <c r="G35" s="8"/>
@@ -5406,7 +5401,7 @@
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="9"/>
-      <c r="D36" s="27"/>
+      <c r="D36" s="35"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
       <c r="G36" s="8"/>
@@ -5418,7 +5413,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="9"/>
-      <c r="D37" s="27"/>
+      <c r="D37" s="35"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
       <c r="G37" s="8"/>
@@ -5430,7 +5425,7 @@
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="9"/>
-      <c r="D38" s="27"/>
+      <c r="D38" s="35"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
       <c r="G38" s="8"/>
@@ -5442,7 +5437,7 @@
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="9"/>
-      <c r="D39" s="27"/>
+      <c r="D39" s="35"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
       <c r="G39" s="8"/>
@@ -5454,7 +5449,7 @@
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="9"/>
-      <c r="D40" s="27"/>
+      <c r="D40" s="35"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
       <c r="G40" s="8"/>
@@ -5466,7 +5461,7 @@
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="9"/>
-      <c r="D41" s="27"/>
+      <c r="D41" s="35"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
       <c r="G41" s="8"/>
@@ -5478,7 +5473,7 @@
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="9"/>
-      <c r="D42" s="27"/>
+      <c r="D42" s="35"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
       <c r="G42" s="8"/>
@@ -5490,7 +5485,7 @@
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="9"/>
-      <c r="D43" s="27"/>
+      <c r="D43" s="35"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
       <c r="G43" s="8"/>
@@ -5502,7 +5497,7 @@
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="9"/>
-      <c r="D44" s="27"/>
+      <c r="D44" s="35"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
       <c r="G44" s="8"/>
@@ -5514,7 +5509,7 @@
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="9"/>
-      <c r="D45" s="27"/>
+      <c r="D45" s="35"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
       <c r="G45" s="8"/>
@@ -5526,7 +5521,7 @@
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="9"/>
-      <c r="D46" s="27"/>
+      <c r="D46" s="35"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
       <c r="G46" s="8"/>
@@ -5538,7 +5533,7 @@
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="9"/>
-      <c r="D47" s="27"/>
+      <c r="D47" s="35"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
       <c r="G47" s="8"/>
@@ -5550,7 +5545,7 @@
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="9"/>
-      <c r="D48" s="27"/>
+      <c r="D48" s="35"/>
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
       <c r="G48" s="8"/>
@@ -5562,7 +5557,7 @@
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="9"/>
-      <c r="D49" s="27"/>
+      <c r="D49" s="35"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9"/>
       <c r="G49" s="8"/>
@@ -5574,7 +5569,7 @@
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="9"/>
-      <c r="D50" s="27"/>
+      <c r="D50" s="35"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
       <c r="G50" s="8"/>
@@ -5586,7 +5581,7 @@
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="9"/>
-      <c r="D51" s="27"/>
+      <c r="D51" s="35"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
       <c r="G51" s="8"/>
@@ -5598,7 +5593,7 @@
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="9"/>
-      <c r="D52" s="27"/>
+      <c r="D52" s="35"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
       <c r="G52" s="8"/>
@@ -5610,7 +5605,7 @@
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="9"/>
-      <c r="D53" s="27"/>
+      <c r="D53" s="35"/>
       <c r="E53" s="9"/>
       <c r="F53" s="9"/>
       <c r="G53" s="8"/>
@@ -5622,7 +5617,7 @@
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="9"/>
-      <c r="D54" s="27"/>
+      <c r="D54" s="35"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
       <c r="G54" s="8"/>
@@ -5634,7 +5629,7 @@
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="9"/>
-      <c r="D55" s="27"/>
+      <c r="D55" s="35"/>
       <c r="E55" s="9"/>
       <c r="F55" s="9"/>
       <c r="G55" s="8"/>
@@ -5646,7 +5641,7 @@
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="9"/>
-      <c r="D56" s="27"/>
+      <c r="D56" s="35"/>
       <c r="E56" s="9"/>
       <c r="F56" s="9"/>
       <c r="G56" s="8"/>
@@ -6568,11 +6563,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="A16:A22"/>
+    <mergeCell ref="B16:B22"/>
+    <mergeCell ref="E16:E22"/>
+    <mergeCell ref="F16:F22"/>
+    <mergeCell ref="G16:G22"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="D3:D56"/>
@@ -6580,11 +6575,11 @@
     <mergeCell ref="H4:H8"/>
     <mergeCell ref="H16:H22"/>
     <mergeCell ref="J16:J22"/>
-    <mergeCell ref="A16:A22"/>
-    <mergeCell ref="B16:B22"/>
-    <mergeCell ref="E16:E22"/>
-    <mergeCell ref="F16:F22"/>
-    <mergeCell ref="G16:G22"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6609,30 +6604,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="32" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="24"/>
+      <c r="H1" s="30"/>
       <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="31" t="s">
         <v>7</v>
       </c>
     </row>
@@ -6643,10 +6638,10 @@
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
       <c r="G2" s="4" t="s">
         <v>10</v>
       </c>
@@ -6654,51 +6649,53 @@
         <v>11</v>
       </c>
       <c r="I2" s="2"/>
-      <c r="J2" s="25"/>
+      <c r="J2" s="31"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="37"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="39" t="s">
-        <v>140</v>
-      </c>
-      <c r="E3" s="28" t="s">
+      <c r="A3" s="32"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="E3" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="G3" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="H3" s="37" t="s">
         <v>63</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="30"/>
+      <c r="J3" s="25" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="37"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
       <c r="I4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="30"/>
+      <c r="J4" s="25"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="9"/>
-      <c r="D5" s="27"/>
+      <c r="D5" s="35"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="8"/>
@@ -6714,7 +6711,7 @@
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="9"/>
-      <c r="D6" s="27"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="8"/>
@@ -6728,7 +6725,7 @@
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="9"/>
-      <c r="D7" s="27"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="8"/>
@@ -6742,7 +6739,7 @@
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="9"/>
-      <c r="D8" s="27"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="G8" s="8"/>
@@ -6758,7 +6755,7 @@
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
-      <c r="D9" s="27"/>
+      <c r="D9" s="35"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="8"/>
@@ -6774,7 +6771,7 @@
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="9"/>
-      <c r="D10" s="27"/>
+      <c r="D10" s="35"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="G10" s="8"/>
@@ -6790,7 +6787,7 @@
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
-      <c r="D11" s="27"/>
+      <c r="D11" s="35"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="8"/>
@@ -6806,7 +6803,7 @@
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="9"/>
-      <c r="D12" s="27"/>
+      <c r="D12" s="35"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="8"/>
@@ -6818,7 +6815,7 @@
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="9"/>
-      <c r="D13" s="27"/>
+      <c r="D13" s="35"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="8"/>
@@ -6832,7 +6829,7 @@
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="9"/>
-      <c r="D14" s="27"/>
+      <c r="D14" s="35"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="8"/>
@@ -6844,7 +6841,7 @@
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="9"/>
-      <c r="D15" s="27"/>
+      <c r="D15" s="35"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="8"/>
@@ -6858,7 +6855,7 @@
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
-      <c r="D16" s="27"/>
+      <c r="D16" s="35"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
@@ -6867,94 +6864,94 @@
       <c r="J16" s="8"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17" s="40"/>
-      <c r="B17" s="40"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="38"/>
       <c r="C17" s="10"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
       <c r="I17" s="8"/>
-      <c r="J17" s="30"/>
+      <c r="J17" s="25"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A18" s="40"/>
-      <c r="B18" s="40"/>
+      <c r="A18" s="38"/>
+      <c r="B18" s="38"/>
       <c r="C18" s="10"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
       <c r="I18" s="8"/>
-      <c r="J18" s="30"/>
+      <c r="J18" s="25"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A19" s="40"/>
-      <c r="B19" s="40"/>
+      <c r="A19" s="38"/>
+      <c r="B19" s="38"/>
       <c r="C19" s="10"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
       <c r="I19" s="8"/>
-      <c r="J19" s="30"/>
+      <c r="J19" s="25"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A20" s="40"/>
-      <c r="B20" s="40"/>
+      <c r="A20" s="38"/>
+      <c r="B20" s="38"/>
       <c r="C20" s="10"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
       <c r="I20" s="8"/>
-      <c r="J20" s="30"/>
+      <c r="J20" s="25"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A21" s="40"/>
-      <c r="B21" s="40"/>
+      <c r="A21" s="38"/>
+      <c r="B21" s="38"/>
       <c r="C21" s="10"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
       <c r="I21" s="8"/>
-      <c r="J21" s="30"/>
+      <c r="J21" s="25"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A22" s="40"/>
-      <c r="B22" s="40"/>
+      <c r="A22" s="38"/>
+      <c r="B22" s="38"/>
       <c r="C22" s="10"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
       <c r="I22" s="8"/>
-      <c r="J22" s="30"/>
+      <c r="J22" s="25"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A23" s="40"/>
-      <c r="B23" s="40"/>
+      <c r="A23" s="38"/>
+      <c r="B23" s="38"/>
       <c r="C23" s="10"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
       <c r="I23" s="8"/>
-      <c r="J23" s="30"/>
+      <c r="J23" s="25"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="9"/>
-      <c r="D24" s="27"/>
+      <c r="D24" s="35"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" s="8"/>
@@ -6966,7 +6963,7 @@
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="9"/>
-      <c r="D25" s="27"/>
+      <c r="D25" s="35"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="G25" s="8"/>
@@ -6978,7 +6975,7 @@
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="9"/>
-      <c r="D26" s="27"/>
+      <c r="D26" s="35"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
@@ -6990,7 +6987,7 @@
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="9"/>
-      <c r="D27" s="27"/>
+      <c r="D27" s="35"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
@@ -7002,7 +6999,7 @@
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="9"/>
-      <c r="D28" s="27"/>
+      <c r="D28" s="35"/>
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
@@ -7014,7 +7011,7 @@
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="9"/>
-      <c r="D29" s="27"/>
+      <c r="D29" s="35"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
@@ -7026,7 +7023,7 @@
       <c r="A30" s="8"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
-      <c r="D30" s="27"/>
+      <c r="D30" s="35"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="8"/>
@@ -7038,7 +7035,7 @@
       <c r="A31" s="8"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
-      <c r="D31" s="27"/>
+      <c r="D31" s="35"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="G31" s="8"/>
@@ -7050,7 +7047,7 @@
       <c r="A32" s="8"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
-      <c r="D32" s="27"/>
+      <c r="D32" s="35"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
       <c r="G32" s="8"/>
@@ -7062,7 +7059,7 @@
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
-      <c r="D33" s="27"/>
+      <c r="D33" s="35"/>
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
@@ -7074,7 +7071,7 @@
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
-      <c r="D34" s="27"/>
+      <c r="D34" s="35"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
       <c r="G34" s="8"/>
@@ -7086,7 +7083,7 @@
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="9"/>
-      <c r="D35" s="27"/>
+      <c r="D35" s="35"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
       <c r="G35" s="8"/>
@@ -7098,7 +7095,7 @@
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="9"/>
-      <c r="D36" s="27"/>
+      <c r="D36" s="35"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
       <c r="G36" s="8"/>
@@ -7110,7 +7107,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="9"/>
-      <c r="D37" s="27"/>
+      <c r="D37" s="35"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
       <c r="G37" s="8"/>
@@ -7122,7 +7119,7 @@
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="9"/>
-      <c r="D38" s="27"/>
+      <c r="D38" s="35"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
       <c r="G38" s="8"/>
@@ -7134,7 +7131,7 @@
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="9"/>
-      <c r="D39" s="27"/>
+      <c r="D39" s="35"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
       <c r="G39" s="8"/>
@@ -7146,7 +7143,7 @@
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="9"/>
-      <c r="D40" s="27"/>
+      <c r="D40" s="35"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
       <c r="G40" s="8"/>
@@ -7158,7 +7155,7 @@
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="9"/>
-      <c r="D41" s="27"/>
+      <c r="D41" s="35"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
       <c r="G41" s="8"/>
@@ -7170,7 +7167,7 @@
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="9"/>
-      <c r="D42" s="27"/>
+      <c r="D42" s="35"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
       <c r="G42" s="8"/>
@@ -7182,7 +7179,7 @@
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="9"/>
-      <c r="D43" s="27"/>
+      <c r="D43" s="35"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
       <c r="G43" s="8"/>
@@ -7194,7 +7191,7 @@
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="9"/>
-      <c r="D44" s="27"/>
+      <c r="D44" s="35"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
       <c r="G44" s="8"/>
@@ -7206,7 +7203,7 @@
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="9"/>
-      <c r="D45" s="27"/>
+      <c r="D45" s="35"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
       <c r="G45" s="8"/>
@@ -7218,7 +7215,7 @@
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="9"/>
-      <c r="D46" s="27"/>
+      <c r="D46" s="35"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
       <c r="G46" s="8"/>
@@ -7230,7 +7227,7 @@
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="9"/>
-      <c r="D47" s="27"/>
+      <c r="D47" s="35"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
       <c r="G47" s="8"/>
@@ -7242,7 +7239,7 @@
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="9"/>
-      <c r="D48" s="27"/>
+      <c r="D48" s="35"/>
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
       <c r="G48" s="8"/>
@@ -7254,7 +7251,7 @@
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="9"/>
-      <c r="D49" s="27"/>
+      <c r="D49" s="35"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9"/>
       <c r="G49" s="8"/>
@@ -7266,7 +7263,7 @@
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="9"/>
-      <c r="D50" s="27"/>
+      <c r="D50" s="35"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
       <c r="G50" s="8"/>
@@ -7278,7 +7275,7 @@
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="9"/>
-      <c r="D51" s="27"/>
+      <c r="D51" s="35"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
       <c r="G51" s="8"/>
@@ -7290,7 +7287,7 @@
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="9"/>
-      <c r="D52" s="27"/>
+      <c r="D52" s="35"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
       <c r="G52" s="8"/>
@@ -7302,7 +7299,7 @@
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="9"/>
-      <c r="D53" s="27"/>
+      <c r="D53" s="35"/>
       <c r="E53" s="9"/>
       <c r="F53" s="9"/>
       <c r="G53" s="8"/>
@@ -7314,7 +7311,7 @@
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="9"/>
-      <c r="D54" s="27"/>
+      <c r="D54" s="35"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
       <c r="G54" s="8"/>
@@ -7326,7 +7323,7 @@
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="9"/>
-      <c r="D55" s="27"/>
+      <c r="D55" s="35"/>
       <c r="E55" s="9"/>
       <c r="F55" s="9"/>
       <c r="G55" s="8"/>
@@ -7338,7 +7335,7 @@
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="9"/>
-      <c r="D56" s="27"/>
+      <c r="D56" s="35"/>
       <c r="E56" s="9"/>
       <c r="F56" s="9"/>
       <c r="G56" s="8"/>
@@ -7350,7 +7347,7 @@
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="9"/>
-      <c r="D57" s="27"/>
+      <c r="D57" s="35"/>
       <c r="E57" s="9"/>
       <c r="F57" s="9"/>
       <c r="G57" s="8"/>
@@ -8272,13 +8269,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
     <mergeCell ref="H17:H23"/>
     <mergeCell ref="J17:J23"/>
     <mergeCell ref="G1:H1"/>
@@ -8295,6 +8285,13 @@
     <mergeCell ref="A17:A23"/>
     <mergeCell ref="B17:B23"/>
     <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -8319,30 +8316,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="32" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="24"/>
+      <c r="H1" s="30"/>
       <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="31" t="s">
         <v>7</v>
       </c>
     </row>
@@ -8353,10 +8350,10 @@
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
       <c r="G2" s="4" t="s">
         <v>10</v>
       </c>
@@ -8364,53 +8361,53 @@
         <v>11</v>
       </c>
       <c r="I2" s="2"/>
-      <c r="J2" s="25"/>
+      <c r="J2" s="31"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="37"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="39" t="s">
-        <v>142</v>
-      </c>
-      <c r="E3" s="28" t="s">
+      <c r="A3" s="32"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="G3" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="H3" s="37" t="s">
         <v>72</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="30" t="s">
-        <v>143</v>
+      <c r="J3" s="25" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="37"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
       <c r="I4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="30"/>
+      <c r="J4" s="25"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="9"/>
-      <c r="D5" s="27"/>
+      <c r="D5" s="35"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="8"/>
@@ -8426,7 +8423,7 @@
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="9"/>
-      <c r="D6" s="27"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="8"/>
@@ -8440,7 +8437,7 @@
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="9"/>
-      <c r="D7" s="27"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="8"/>
@@ -8452,7 +8449,7 @@
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="9"/>
-      <c r="D8" s="27"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="G8" s="8"/>
@@ -8466,7 +8463,7 @@
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
-      <c r="D9" s="27"/>
+      <c r="D9" s="35"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="8"/>
@@ -8480,7 +8477,7 @@
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="9"/>
-      <c r="D10" s="27"/>
+      <c r="D10" s="35"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="G10" s="8"/>
@@ -8494,7 +8491,7 @@
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
-      <c r="D11" s="27"/>
+      <c r="D11" s="35"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="8"/>
@@ -8508,7 +8505,7 @@
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="9"/>
-      <c r="D12" s="27"/>
+      <c r="D12" s="35"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="8"/>
@@ -8520,7 +8517,7 @@
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="9"/>
-      <c r="D13" s="27"/>
+      <c r="D13" s="35"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="8"/>
@@ -8534,7 +8531,7 @@
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="9"/>
-      <c r="D14" s="27"/>
+      <c r="D14" s="35"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="8"/>
@@ -8546,7 +8543,7 @@
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="9"/>
-      <c r="D15" s="27"/>
+      <c r="D15" s="35"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="8"/>
@@ -8560,7 +8557,7 @@
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
-      <c r="D16" s="27"/>
+      <c r="D16" s="35"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
@@ -8569,94 +8566,94 @@
       <c r="J16" s="8"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17" s="40"/>
-      <c r="B17" s="40"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="38"/>
       <c r="C17" s="10"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
       <c r="I17" s="8"/>
-      <c r="J17" s="30"/>
+      <c r="J17" s="25"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A18" s="40"/>
-      <c r="B18" s="40"/>
+      <c r="A18" s="38"/>
+      <c r="B18" s="38"/>
       <c r="C18" s="10"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
       <c r="I18" s="8"/>
-      <c r="J18" s="30"/>
+      <c r="J18" s="25"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A19" s="40"/>
-      <c r="B19" s="40"/>
+      <c r="A19" s="38"/>
+      <c r="B19" s="38"/>
       <c r="C19" s="10"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
       <c r="I19" s="8"/>
-      <c r="J19" s="30"/>
+      <c r="J19" s="25"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A20" s="40"/>
-      <c r="B20" s="40"/>
+      <c r="A20" s="38"/>
+      <c r="B20" s="38"/>
       <c r="C20" s="10"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
       <c r="I20" s="8"/>
-      <c r="J20" s="30"/>
+      <c r="J20" s="25"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A21" s="40"/>
-      <c r="B21" s="40"/>
+      <c r="A21" s="38"/>
+      <c r="B21" s="38"/>
       <c r="C21" s="10"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
       <c r="I21" s="8"/>
-      <c r="J21" s="30"/>
+      <c r="J21" s="25"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A22" s="40"/>
-      <c r="B22" s="40"/>
+      <c r="A22" s="38"/>
+      <c r="B22" s="38"/>
       <c r="C22" s="10"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
       <c r="I22" s="8"/>
-      <c r="J22" s="30"/>
+      <c r="J22" s="25"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A23" s="40"/>
-      <c r="B23" s="40"/>
+      <c r="A23" s="38"/>
+      <c r="B23" s="38"/>
       <c r="C23" s="10"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
       <c r="I23" s="8"/>
-      <c r="J23" s="30"/>
+      <c r="J23" s="25"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="9"/>
-      <c r="D24" s="27"/>
+      <c r="D24" s="35"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" s="8"/>
@@ -8668,7 +8665,7 @@
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="9"/>
-      <c r="D25" s="27"/>
+      <c r="D25" s="35"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="G25" s="8"/>
@@ -8680,7 +8677,7 @@
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="9"/>
-      <c r="D26" s="27"/>
+      <c r="D26" s="35"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
@@ -8692,7 +8689,7 @@
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="9"/>
-      <c r="D27" s="27"/>
+      <c r="D27" s="35"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
@@ -8704,7 +8701,7 @@
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="9"/>
-      <c r="D28" s="27"/>
+      <c r="D28" s="35"/>
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
@@ -8716,7 +8713,7 @@
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="9"/>
-      <c r="D29" s="27"/>
+      <c r="D29" s="35"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
@@ -8728,7 +8725,7 @@
       <c r="A30" s="8"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
-      <c r="D30" s="27"/>
+      <c r="D30" s="35"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="8"/>
@@ -8740,7 +8737,7 @@
       <c r="A31" s="8"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
-      <c r="D31" s="27"/>
+      <c r="D31" s="35"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="G31" s="8"/>
@@ -8752,7 +8749,7 @@
       <c r="A32" s="8"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
-      <c r="D32" s="27"/>
+      <c r="D32" s="35"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
       <c r="G32" s="8"/>
@@ -8764,7 +8761,7 @@
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
-      <c r="D33" s="27"/>
+      <c r="D33" s="35"/>
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
@@ -8776,7 +8773,7 @@
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
-      <c r="D34" s="27"/>
+      <c r="D34" s="35"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
       <c r="G34" s="8"/>
@@ -8788,7 +8785,7 @@
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="9"/>
-      <c r="D35" s="27"/>
+      <c r="D35" s="35"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
       <c r="G35" s="8"/>
@@ -8800,7 +8797,7 @@
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="9"/>
-      <c r="D36" s="27"/>
+      <c r="D36" s="35"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
       <c r="G36" s="8"/>
@@ -8812,7 +8809,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="9"/>
-      <c r="D37" s="27"/>
+      <c r="D37" s="35"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
       <c r="G37" s="8"/>
@@ -8824,7 +8821,7 @@
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="9"/>
-      <c r="D38" s="27"/>
+      <c r="D38" s="35"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
       <c r="G38" s="8"/>
@@ -8836,7 +8833,7 @@
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="9"/>
-      <c r="D39" s="27"/>
+      <c r="D39" s="35"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
       <c r="G39" s="8"/>
@@ -8848,7 +8845,7 @@
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="9"/>
-      <c r="D40" s="27"/>
+      <c r="D40" s="35"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
       <c r="G40" s="8"/>
@@ -8860,7 +8857,7 @@
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="9"/>
-      <c r="D41" s="27"/>
+      <c r="D41" s="35"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
       <c r="G41" s="8"/>
@@ -8872,7 +8869,7 @@
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="9"/>
-      <c r="D42" s="27"/>
+      <c r="D42" s="35"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
       <c r="G42" s="8"/>
@@ -8884,7 +8881,7 @@
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="9"/>
-      <c r="D43" s="27"/>
+      <c r="D43" s="35"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
       <c r="G43" s="8"/>
@@ -8896,7 +8893,7 @@
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="9"/>
-      <c r="D44" s="27"/>
+      <c r="D44" s="35"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
       <c r="G44" s="8"/>
@@ -8908,7 +8905,7 @@
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="9"/>
-      <c r="D45" s="27"/>
+      <c r="D45" s="35"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
       <c r="G45" s="8"/>
@@ -8920,7 +8917,7 @@
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="9"/>
-      <c r="D46" s="27"/>
+      <c r="D46" s="35"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
       <c r="G46" s="8"/>
@@ -8932,7 +8929,7 @@
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="9"/>
-      <c r="D47" s="27"/>
+      <c r="D47" s="35"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
       <c r="G47" s="8"/>
@@ -8944,7 +8941,7 @@
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="9"/>
-      <c r="D48" s="27"/>
+      <c r="D48" s="35"/>
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
       <c r="G48" s="8"/>
@@ -8956,7 +8953,7 @@
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="9"/>
-      <c r="D49" s="27"/>
+      <c r="D49" s="35"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9"/>
       <c r="G49" s="8"/>
@@ -8968,7 +8965,7 @@
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="9"/>
-      <c r="D50" s="27"/>
+      <c r="D50" s="35"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
       <c r="G50" s="8"/>
@@ -8980,7 +8977,7 @@
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="9"/>
-      <c r="D51" s="27"/>
+      <c r="D51" s="35"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
       <c r="G51" s="8"/>
@@ -8992,7 +8989,7 @@
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="9"/>
-      <c r="D52" s="27"/>
+      <c r="D52" s="35"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
       <c r="G52" s="8"/>
@@ -9004,7 +9001,7 @@
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="9"/>
-      <c r="D53" s="27"/>
+      <c r="D53" s="35"/>
       <c r="E53" s="9"/>
       <c r="F53" s="9"/>
       <c r="G53" s="8"/>
@@ -9016,7 +9013,7 @@
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="9"/>
-      <c r="D54" s="27"/>
+      <c r="D54" s="35"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
       <c r="G54" s="8"/>
@@ -9028,7 +9025,7 @@
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="9"/>
-      <c r="D55" s="27"/>
+      <c r="D55" s="35"/>
       <c r="E55" s="9"/>
       <c r="F55" s="9"/>
       <c r="G55" s="8"/>
@@ -9040,7 +9037,7 @@
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="9"/>
-      <c r="D56" s="27"/>
+      <c r="D56" s="35"/>
       <c r="E56" s="9"/>
       <c r="F56" s="9"/>
       <c r="G56" s="8"/>
@@ -9052,7 +9049,7 @@
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="9"/>
-      <c r="D57" s="27"/>
+      <c r="D57" s="35"/>
       <c r="E57" s="9"/>
       <c r="F57" s="9"/>
       <c r="G57" s="8"/>
@@ -9974,13 +9971,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="F17:F23"/>
-    <mergeCell ref="G17:G23"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
     <mergeCell ref="H17:H23"/>
     <mergeCell ref="J17:J23"/>
     <mergeCell ref="G1:H1"/>
@@ -9997,6 +9987,13 @@
     <mergeCell ref="A17:A23"/>
     <mergeCell ref="B17:B23"/>
     <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G17:G23"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -10021,30 +10018,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="32" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="24"/>
+      <c r="H1" s="30"/>
       <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="31" t="s">
         <v>7</v>
       </c>
     </row>
@@ -10055,10 +10052,10 @@
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
       <c r="G2" s="4" t="s">
         <v>10</v>
       </c>
@@ -10066,7 +10063,7 @@
         <v>11</v>
       </c>
       <c r="I2" s="2"/>
-      <c r="J2" s="25"/>
+      <c r="J2" s="31"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
@@ -10078,13 +10075,13 @@
       <c r="C3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="36" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="7" t="s">
@@ -10105,9 +10102,9 @@
       <c r="C4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="29"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="36"/>
       <c r="G4" s="8"/>
       <c r="H4" s="8" t="s">
         <v>50</v>
@@ -10124,7 +10121,7 @@
       <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="27"/>
+      <c r="D5" s="35"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="8"/>
@@ -10141,7 +10138,7 @@
       <c r="C6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="27"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="8"/>
@@ -10155,7 +10152,7 @@
       <c r="C7" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="27"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="8"/>
@@ -10173,7 +10170,7 @@
       <c r="C8" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="27"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="G8" s="8"/>
@@ -10191,7 +10188,7 @@
       <c r="C9" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="27"/>
+      <c r="D9" s="35"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="8"/>
@@ -10209,7 +10206,7 @@
       <c r="C10" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="D10" s="27"/>
+      <c r="D10" s="35"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="G10" s="8"/>
@@ -10223,7 +10220,7 @@
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C11" s="43"/>
-      <c r="D11" s="27"/>
+      <c r="D11" s="35"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="8"/>
@@ -10233,7 +10230,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C12" s="43"/>
-      <c r="D12" s="27"/>
+      <c r="D12" s="35"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="8"/>
@@ -10247,7 +10244,7 @@
       <c r="C13" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="27"/>
+      <c r="D13" s="35"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="8"/>
@@ -10264,7 +10261,7 @@
       <c r="C14" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="27"/>
+      <c r="D14" s="35"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="8"/>
@@ -10280,7 +10277,7 @@
       <c r="C15" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="27"/>
+      <c r="D15" s="35"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="8"/>
@@ -10291,7 +10288,7 @@
       <c r="J15" s="8"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="D16" s="27"/>
+      <c r="D16" s="35"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
@@ -10300,9 +10297,9 @@
       <c r="J16" s="8"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="D17" s="27"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
@@ -10316,9 +10313,9 @@
         <v>91</v>
       </c>
       <c r="C18" s="9"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
@@ -10331,9 +10328,9 @@
       <c r="C19" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="27"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -10344,9 +10341,9 @@
         <v>93</v>
       </c>
       <c r="C20" s="9"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
@@ -10357,9 +10354,9 @@
         <v>94</v>
       </c>
       <c r="C21" s="9"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
@@ -10370,9 +10367,9 @@
         <v>95</v>
       </c>
       <c r="C22" s="9"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
@@ -10380,9 +10377,9 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C23" s="9"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
@@ -10396,7 +10393,7 @@
         <v>91</v>
       </c>
       <c r="C24" s="9"/>
-      <c r="D24" s="27"/>
+      <c r="D24" s="35"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" s="8"/>
@@ -10409,7 +10406,7 @@
         <v>97</v>
       </c>
       <c r="C25" s="10"/>
-      <c r="D25" s="27"/>
+      <c r="D25" s="35"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="G25" s="8"/>
@@ -10422,7 +10419,7 @@
         <v>47</v>
       </c>
       <c r="C26" s="10"/>
-      <c r="D26" s="27"/>
+      <c r="D26" s="35"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
@@ -10435,7 +10432,7 @@
         <v>48</v>
       </c>
       <c r="C27" s="10"/>
-      <c r="D27" s="27"/>
+      <c r="D27" s="35"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
@@ -10445,7 +10442,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C28" s="10"/>
-      <c r="D28" s="27"/>
+      <c r="D28" s="35"/>
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
@@ -10461,7 +10458,7 @@
         <v>47</v>
       </c>
       <c r="C29" s="10"/>
-      <c r="D29" s="27"/>
+      <c r="D29" s="35"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
@@ -10474,7 +10471,7 @@
         <v>97</v>
       </c>
       <c r="C30" s="10"/>
-      <c r="D30" s="27"/>
+      <c r="D30" s="35"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="8"/>
@@ -10487,7 +10484,7 @@
         <v>99</v>
       </c>
       <c r="C31" s="10"/>
-      <c r="D31" s="27"/>
+      <c r="D31" s="35"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="G31" s="8"/>
@@ -10500,7 +10497,7 @@
         <v>100</v>
       </c>
       <c r="C32" s="9"/>
-      <c r="D32" s="27"/>
+      <c r="D32" s="35"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
       <c r="G32" s="8"/>
@@ -10513,7 +10510,7 @@
         <v>101</v>
       </c>
       <c r="C33" s="9"/>
-      <c r="D33" s="27"/>
+      <c r="D33" s="35"/>
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
@@ -10526,7 +10523,7 @@
         <v>102</v>
       </c>
       <c r="C34" s="9"/>
-      <c r="D34" s="27"/>
+      <c r="D34" s="35"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
       <c r="G34" s="8"/>
@@ -10539,7 +10536,7 @@
         <v>103</v>
       </c>
       <c r="C35" s="9"/>
-      <c r="D35" s="27"/>
+      <c r="D35" s="35"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
       <c r="G35" s="8"/>
@@ -10552,7 +10549,7 @@
         <v>104</v>
       </c>
       <c r="C36" s="9"/>
-      <c r="D36" s="27"/>
+      <c r="D36" s="35"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
       <c r="G36" s="8"/>
@@ -10564,7 +10561,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="9"/>
-      <c r="D37" s="27"/>
+      <c r="D37" s="35"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
       <c r="G37" s="8"/>
@@ -10580,7 +10577,7 @@
         <v>106</v>
       </c>
       <c r="C38" s="9"/>
-      <c r="D38" s="27"/>
+      <c r="D38" s="35"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
       <c r="G38" s="8"/>
@@ -10593,7 +10590,7 @@
         <v>107</v>
       </c>
       <c r="C39" s="9"/>
-      <c r="D39" s="27"/>
+      <c r="D39" s="35"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
       <c r="G39" s="8"/>
@@ -10604,7 +10601,7 @@
     <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B40" s="8"/>
       <c r="C40" s="9"/>
-      <c r="D40" s="27"/>
+      <c r="D40" s="35"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
       <c r="G40" s="8"/>
@@ -10615,7 +10612,7 @@
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B41" s="8"/>
       <c r="C41" s="9"/>
-      <c r="D41" s="27"/>
+      <c r="D41" s="35"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
       <c r="G41" s="8"/>
@@ -10627,7 +10624,7 @@
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="9"/>
-      <c r="D42" s="27"/>
+      <c r="D42" s="35"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
       <c r="G42" s="8"/>
@@ -10639,7 +10636,7 @@
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="9"/>
-      <c r="D43" s="27"/>
+      <c r="D43" s="35"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
       <c r="G43" s="8"/>
@@ -10651,7 +10648,7 @@
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="9"/>
-      <c r="D44" s="27"/>
+      <c r="D44" s="35"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
       <c r="G44" s="8"/>
@@ -10663,7 +10660,7 @@
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="9"/>
-      <c r="D45" s="27"/>
+      <c r="D45" s="35"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
       <c r="G45" s="8"/>
@@ -10675,7 +10672,7 @@
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="9"/>
-      <c r="D46" s="27"/>
+      <c r="D46" s="35"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
       <c r="G46" s="8"/>
@@ -10687,7 +10684,7 @@
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="9"/>
-      <c r="D47" s="27"/>
+      <c r="D47" s="35"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
       <c r="G47" s="8"/>
@@ -10699,7 +10696,7 @@
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="9"/>
-      <c r="D48" s="27"/>
+      <c r="D48" s="35"/>
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
       <c r="G48" s="8"/>
@@ -10711,7 +10708,7 @@
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="9"/>
-      <c r="D49" s="27"/>
+      <c r="D49" s="35"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9"/>
       <c r="G49" s="8"/>
@@ -10723,7 +10720,7 @@
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="9"/>
-      <c r="D50" s="27"/>
+      <c r="D50" s="35"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
       <c r="G50" s="8"/>
@@ -10735,7 +10732,7 @@
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="9"/>
-      <c r="D51" s="27"/>
+      <c r="D51" s="35"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
       <c r="G51" s="8"/>
@@ -10747,7 +10744,7 @@
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="9"/>
-      <c r="D52" s="27"/>
+      <c r="D52" s="35"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
       <c r="G52" s="8"/>
@@ -10759,7 +10756,7 @@
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="9"/>
-      <c r="D53" s="27"/>
+      <c r="D53" s="35"/>
       <c r="E53" s="9"/>
       <c r="F53" s="9"/>
       <c r="G53" s="8"/>
@@ -10771,7 +10768,7 @@
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="9"/>
-      <c r="D54" s="27"/>
+      <c r="D54" s="35"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
       <c r="G54" s="8"/>
@@ -10783,7 +10780,7 @@
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="9"/>
-      <c r="D55" s="27"/>
+      <c r="D55" s="35"/>
       <c r="E55" s="9"/>
       <c r="F55" s="9"/>
       <c r="G55" s="8"/>
@@ -10795,7 +10792,7 @@
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="9"/>
-      <c r="D56" s="27"/>
+      <c r="D56" s="35"/>
       <c r="E56" s="9"/>
       <c r="F56" s="9"/>
       <c r="G56" s="8"/>
@@ -10807,7 +10804,7 @@
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="9"/>
-      <c r="D57" s="27"/>
+      <c r="D57" s="35"/>
       <c r="E57" s="9"/>
       <c r="F57" s="9"/>
       <c r="G57" s="8"/>
@@ -11726,21 +11723,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="H10:H12"/>
+    <mergeCell ref="J10:J12"/>
+    <mergeCell ref="E17:E23"/>
+    <mergeCell ref="F17:F23"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="D3:D57"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="D3:D57"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="H10:H12"/>
-    <mergeCell ref="J10:J12"/>
-    <mergeCell ref="E17:E23"/>
-    <mergeCell ref="F17:F23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -11763,27 +11760,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="32" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="24"/>
-      <c r="I1" s="25" t="s">
+      <c r="H1" s="30"/>
+      <c r="I1" s="31" t="s">
         <v>7</v>
       </c>
     </row>
@@ -11794,17 +11791,17 @@
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
       <c r="G2" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="25"/>
+      <c r="I2" s="31"/>
     </row>
     <row r="3" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
@@ -11816,18 +11813,18 @@
       <c r="C3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="E3" s="28"/>
-      <c r="F3" s="29"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="36"/>
       <c r="G3" s="7" t="s">
         <v>110</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="30"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7"/>
@@ -11838,13 +11835,13 @@
         <v>14</v>
       </c>
       <c r="D4" s="46"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="29"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="36"/>
       <c r="G4" s="8"/>
       <c r="H4" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="I4" s="30"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7"/>
@@ -12016,67 +12013,67 @@
       <c r="A18" s="8"/>
       <c r="C18" s="9"/>
       <c r="D18" s="46"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
-      <c r="I18" s="30"/>
+      <c r="I18" s="25"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C19" s="8"/>
       <c r="D19" s="46"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
-      <c r="I19" s="30"/>
+      <c r="I19" s="25"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C20" s="9"/>
       <c r="D20" s="46"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
-      <c r="I20" s="30"/>
+      <c r="I20" s="25"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C21" s="8"/>
       <c r="D21" s="46"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
-      <c r="I21" s="30"/>
+      <c r="I21" s="25"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C22" s="9"/>
       <c r="D22" s="46"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
-      <c r="I22" s="30"/>
+      <c r="I22" s="25"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C23" s="9"/>
       <c r="D23" s="46"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
-      <c r="I23" s="30"/>
+      <c r="I23" s="25"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="18"/>
       <c r="B24" s="18"/>
       <c r="C24" s="10"/>
       <c r="D24" s="46"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
-      <c r="I24" s="30"/>
+      <c r="I24" s="25"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="8"/>
@@ -13295,11 +13292,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="D3:D58"/>
@@ -13309,6 +13301,11 @@
     <mergeCell ref="E18:E24"/>
     <mergeCell ref="F18:F24"/>
     <mergeCell ref="I18:I24"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -13331,27 +13328,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="32" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="24"/>
-      <c r="I1" s="25" t="s">
+      <c r="H1" s="30"/>
+      <c r="I1" s="31" t="s">
         <v>7</v>
       </c>
     </row>
@@ -13362,17 +13359,17 @@
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
       <c r="G2" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="25"/>
+      <c r="I2" s="31"/>
     </row>
     <row r="3" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
@@ -13384,18 +13381,18 @@
       <c r="C3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="E3" s="28"/>
-      <c r="F3" s="29"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="36"/>
       <c r="G3" s="7" t="s">
         <v>123</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="30"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7"/>
@@ -13405,18 +13402,18 @@
       <c r="C4" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="29"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="36"/>
       <c r="G4" s="8"/>
       <c r="H4" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="I4" s="30"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C5" s="9"/>
-      <c r="D5" s="27"/>
+      <c r="D5" s="35"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="8"/>
@@ -13429,7 +13426,7 @@
       <c r="C6" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="D6" s="27"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="8"/>
@@ -13442,7 +13439,7 @@
       <c r="C7" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="D7" s="27"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="8"/>
@@ -13455,7 +13452,7 @@
       <c r="C8" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="D8" s="27"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="G8" s="8"/>
@@ -13470,7 +13467,7 @@
         <v>40</v>
       </c>
       <c r="C9" s="8"/>
-      <c r="D9" s="27"/>
+      <c r="D9" s="35"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="8"/>
@@ -13482,7 +13479,7 @@
         <v>13</v>
       </c>
       <c r="C10" s="9"/>
-      <c r="D10" s="27"/>
+      <c r="D10" s="35"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="G10" s="8"/>
@@ -13492,7 +13489,7 @@
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="7"/>
       <c r="C11" s="8"/>
-      <c r="D11" s="27"/>
+      <c r="D11" s="35"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="8"/>
@@ -13507,7 +13504,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="9"/>
-      <c r="D12" s="27"/>
+      <c r="D12" s="35"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="8"/>
@@ -13520,7 +13517,7 @@
         <v>42</v>
       </c>
       <c r="C13" s="9"/>
-      <c r="D13" s="27"/>
+      <c r="D13" s="35"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="8"/>
@@ -13533,7 +13530,7 @@
         <v>47</v>
       </c>
       <c r="C14" s="9"/>
-      <c r="D14" s="27"/>
+      <c r="D14" s="35"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="8"/>
@@ -13546,7 +13543,7 @@
         <v>48</v>
       </c>
       <c r="C15" s="9"/>
-      <c r="D15" s="27"/>
+      <c r="D15" s="35"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="8"/>
@@ -13555,7 +13552,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C16" s="9"/>
-      <c r="D16" s="27"/>
+      <c r="D16" s="35"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
@@ -13570,12 +13567,12 @@
         <v>54</v>
       </c>
       <c r="C17" s="10"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="8"/>
@@ -13583,22 +13580,22 @@
         <v>56</v>
       </c>
       <c r="C18" s="10"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="8"/>
       <c r="C19" s="10"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
@@ -13608,12 +13605,12 @@
         <v>60</v>
       </c>
       <c r="C20" s="10"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="8"/>
@@ -13621,36 +13618,36 @@
         <v>61</v>
       </c>
       <c r="C21" s="10"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C22" s="10"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C23" s="10"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="18"/>
       <c r="B24" s="18"/>
       <c r="C24" s="9"/>
-      <c r="D24" s="27"/>
+      <c r="D24" s="35"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" s="8"/>
@@ -13661,7 +13658,7 @@
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="9"/>
-      <c r="D25" s="27"/>
+      <c r="D25" s="35"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="G25" s="8"/>
@@ -13672,7 +13669,7 @@
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="9"/>
-      <c r="D26" s="27"/>
+      <c r="D26" s="35"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
@@ -13683,7 +13680,7 @@
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="9"/>
-      <c r="D27" s="27"/>
+      <c r="D27" s="35"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
@@ -13694,7 +13691,7 @@
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="9"/>
-      <c r="D28" s="27"/>
+      <c r="D28" s="35"/>
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
@@ -13705,7 +13702,7 @@
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="9"/>
-      <c r="D29" s="27"/>
+      <c r="D29" s="35"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
@@ -13716,7 +13713,7 @@
       <c r="A30" s="8"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
-      <c r="D30" s="27"/>
+      <c r="D30" s="35"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="8"/>
@@ -13727,7 +13724,7 @@
       <c r="A31" s="8"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
-      <c r="D31" s="27"/>
+      <c r="D31" s="35"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="G31" s="8"/>
@@ -13738,7 +13735,7 @@
       <c r="A32" s="8"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
-      <c r="D32" s="27"/>
+      <c r="D32" s="35"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
       <c r="G32" s="8"/>
@@ -13749,7 +13746,7 @@
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
-      <c r="D33" s="27"/>
+      <c r="D33" s="35"/>
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
@@ -13760,7 +13757,7 @@
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
-      <c r="D34" s="27"/>
+      <c r="D34" s="35"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
       <c r="G34" s="8"/>
@@ -13771,7 +13768,7 @@
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="9"/>
-      <c r="D35" s="27"/>
+      <c r="D35" s="35"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
       <c r="G35" s="8"/>
@@ -13782,7 +13779,7 @@
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="9"/>
-      <c r="D36" s="27"/>
+      <c r="D36" s="35"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
       <c r="G36" s="8"/>
@@ -13793,7 +13790,7 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="9"/>
-      <c r="D37" s="27"/>
+      <c r="D37" s="35"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
       <c r="G37" s="8"/>
@@ -13804,7 +13801,7 @@
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="9"/>
-      <c r="D38" s="27"/>
+      <c r="D38" s="35"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
       <c r="G38" s="8"/>
@@ -13815,7 +13812,7 @@
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="9"/>
-      <c r="D39" s="27"/>
+      <c r="D39" s="35"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
       <c r="G39" s="8"/>
@@ -13826,7 +13823,7 @@
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="9"/>
-      <c r="D40" s="27"/>
+      <c r="D40" s="35"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
       <c r="G40" s="8"/>
@@ -13837,7 +13834,7 @@
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="9"/>
-      <c r="D41" s="27"/>
+      <c r="D41" s="35"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
       <c r="G41" s="8"/>
@@ -13848,7 +13845,7 @@
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="9"/>
-      <c r="D42" s="27"/>
+      <c r="D42" s="35"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
       <c r="G42" s="8"/>
@@ -13859,7 +13856,7 @@
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="9"/>
-      <c r="D43" s="27"/>
+      <c r="D43" s="35"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
       <c r="G43" s="8"/>
@@ -13870,7 +13867,7 @@
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="9"/>
-      <c r="D44" s="27"/>
+      <c r="D44" s="35"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
       <c r="G44" s="8"/>
@@ -13881,7 +13878,7 @@
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="9"/>
-      <c r="D45" s="27"/>
+      <c r="D45" s="35"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
       <c r="G45" s="8"/>
@@ -13892,7 +13889,7 @@
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="9"/>
-      <c r="D46" s="27"/>
+      <c r="D46" s="35"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
       <c r="G46" s="8"/>
@@ -13903,7 +13900,7 @@
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="9"/>
-      <c r="D47" s="27"/>
+      <c r="D47" s="35"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
       <c r="G47" s="8"/>
@@ -13914,7 +13911,7 @@
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="9"/>
-      <c r="D48" s="27"/>
+      <c r="D48" s="35"/>
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
       <c r="G48" s="8"/>
@@ -13925,7 +13922,7 @@
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="9"/>
-      <c r="D49" s="27"/>
+      <c r="D49" s="35"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9"/>
       <c r="G49" s="8"/>
@@ -13936,7 +13933,7 @@
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="9"/>
-      <c r="D50" s="27"/>
+      <c r="D50" s="35"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
       <c r="G50" s="8"/>
@@ -13947,7 +13944,7 @@
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="9"/>
-      <c r="D51" s="27"/>
+      <c r="D51" s="35"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
       <c r="G51" s="8"/>
@@ -13958,7 +13955,7 @@
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="9"/>
-      <c r="D52" s="27"/>
+      <c r="D52" s="35"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
       <c r="G52" s="8"/>
@@ -13969,7 +13966,7 @@
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="9"/>
-      <c r="D53" s="27"/>
+      <c r="D53" s="35"/>
       <c r="E53" s="9"/>
       <c r="F53" s="9"/>
       <c r="G53" s="8"/>
@@ -13980,7 +13977,7 @@
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="9"/>
-      <c r="D54" s="27"/>
+      <c r="D54" s="35"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
       <c r="G54" s="8"/>
@@ -13991,7 +13988,7 @@
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="9"/>
-      <c r="D55" s="27"/>
+      <c r="D55" s="35"/>
       <c r="E55" s="9"/>
       <c r="F55" s="9"/>
       <c r="G55" s="8"/>
@@ -14002,7 +13999,7 @@
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="9"/>
-      <c r="D56" s="27"/>
+      <c r="D56" s="35"/>
       <c r="E56" s="9"/>
       <c r="F56" s="9"/>
       <c r="G56" s="8"/>
@@ -14013,7 +14010,7 @@
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="9"/>
-      <c r="D57" s="27"/>
+      <c r="D57" s="35"/>
       <c r="E57" s="9"/>
       <c r="F57" s="9"/>
       <c r="G57" s="8"/>
@@ -14858,11 +14855,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="D3:D57"/>
@@ -14874,6 +14866,11 @@
     <mergeCell ref="G17:G23"/>
     <mergeCell ref="H17:H23"/>
     <mergeCell ref="I17:I23"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
